--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,9 @@
     <t>['14']</t>
   </si>
   <si>
+    <t>['57', '72', '81']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -740,6 +743,9 @@
   </si>
   <si>
     <t>['66', '79']</t>
+  </si>
+  <si>
+    <t>['27', '42']</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1357,7 +1363,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1438,7 +1444,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1563,7 +1569,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1847,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -2053,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2181,7 +2187,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2468,7 +2474,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2593,7 +2599,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3005,7 +3011,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3083,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
         <v>1.1</v>
@@ -3211,7 +3217,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3417,7 +3423,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3498,7 +3504,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3907,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ14">
         <v>0.8</v>
@@ -4035,7 +4041,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4241,7 +4247,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4322,7 +4328,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4447,7 +4453,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4859,7 +4865,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -4937,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ19">
         <v>1.6</v>
@@ -5065,7 +5071,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5146,7 +5152,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5271,7 +5277,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5477,7 +5483,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5889,7 +5895,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6095,7 +6101,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6173,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25">
         <v>0.8</v>
@@ -6713,7 +6719,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7000,7 +7006,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7125,7 +7131,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7412,7 +7418,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR31">
         <v>1.29</v>
@@ -7537,7 +7543,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7821,10 +7827,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
         <v>0.97</v>
@@ -7949,7 +7955,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8027,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ34">
         <v>0.9</v>
@@ -8155,7 +8161,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8773,7 +8779,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8979,7 +8985,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9803,7 +9809,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10009,7 +10015,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10090,7 +10096,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10627,7 +10633,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10705,10 +10711,10 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR47">
         <v>1.06</v>
@@ -10833,7 +10839,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11039,7 +11045,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11117,7 +11123,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ49">
         <v>2.3</v>
@@ -11323,10 +11329,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR50">
         <v>1.74</v>
@@ -11657,7 +11663,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12069,7 +12075,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12275,7 +12281,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12687,7 +12693,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12893,7 +12899,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -12974,7 +12980,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13099,7 +13105,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13177,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ59">
         <v>0.6</v>
@@ -13383,7 +13389,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ60">
         <v>1.6</v>
@@ -13592,7 +13598,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR61">
         <v>1.69</v>
@@ -13717,7 +13723,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13795,7 +13801,7 @@
         <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ62">
         <v>1.1</v>
@@ -13923,7 +13929,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14004,7 +14010,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14129,7 +14135,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14747,7 +14753,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15159,7 +15165,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15365,7 +15371,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15652,7 +15658,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR71">
         <v>1.51</v>
@@ -15983,7 +15989,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16061,7 +16067,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ73">
         <v>1.7</v>
@@ -16395,7 +16401,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16601,7 +16607,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16679,10 +16685,10 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ76">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -16885,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ77">
         <v>0.6</v>
@@ -17013,7 +17019,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17094,7 +17100,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR78">
         <v>1.72</v>
@@ -17219,7 +17225,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17425,7 +17431,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17506,7 +17512,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR80">
         <v>1.08</v>
@@ -17712,7 +17718,7 @@
         <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17837,7 +17843,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18043,7 +18049,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18455,7 +18461,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18867,7 +18873,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -18945,7 +18951,7 @@
         <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ87">
         <v>1.3</v>
@@ -19357,7 +19363,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
         <v>1.5</v>
@@ -19485,7 +19491,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19566,7 +19572,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ90">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19691,7 +19697,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19897,7 +19903,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -19975,7 +19981,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ92">
         <v>1.7</v>
@@ -20184,7 +20190,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ93">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -20309,7 +20315,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20515,7 +20521,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20593,7 +20599,7 @@
         <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ95">
         <v>2.3</v>
@@ -20721,7 +20727,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21133,7 +21139,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21339,7 +21345,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21832,7 +21838,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
         <v>1.32</v>
@@ -21957,7 +21963,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22369,7 +22375,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22447,7 +22453,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ104">
         <v>1.9</v>
@@ -22862,7 +22868,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -23271,7 +23277,7 @@
         <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108">
         <v>1.3</v>
@@ -23477,7 +23483,7 @@
         <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ109">
         <v>0.5</v>
@@ -23811,7 +23817,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24017,7 +24023,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24304,7 +24310,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -24713,7 +24719,7 @@
         <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ115">
         <v>0.9</v>
@@ -24841,7 +24847,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -24922,7 +24928,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25047,7 +25053,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25253,7 +25259,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25459,7 +25465,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25537,7 +25543,7 @@
         <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ119">
         <v>2.3</v>
@@ -25665,7 +25671,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25746,7 +25752,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ120">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR120">
         <v>1.23</v>
@@ -26077,7 +26083,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26155,7 +26161,7 @@
         <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
         <v>1.9</v>
@@ -26283,7 +26289,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26489,7 +26495,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26570,7 +26576,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ124">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -27394,7 +27400,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR128">
         <v>1.37</v>
@@ -27519,7 +27525,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27600,7 +27606,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ129">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR129">
         <v>1.26</v>
@@ -27725,7 +27731,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27803,7 +27809,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ130">
         <v>1.5</v>
@@ -28012,7 +28018,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR131">
         <v>1.17</v>
@@ -28421,7 +28427,7 @@
         <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ133">
         <v>1.6</v>
@@ -28627,7 +28633,7 @@
         <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ134">
         <v>0.6</v>
@@ -28755,7 +28761,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29167,7 +29173,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29579,7 +29585,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -30148,6 +30154,624 @@
       </c>
       <c r="BP141">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7537435</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45689.54166666666</v>
+      </c>
+      <c r="F142">
+        <v>21</v>
+      </c>
+      <c r="G142" t="s">
+        <v>73</v>
+      </c>
+      <c r="H142" t="s">
+        <v>77</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>2</v>
+      </c>
+      <c r="K142">
+        <v>2</v>
+      </c>
+      <c r="L142">
+        <v>3</v>
+      </c>
+      <c r="M142">
+        <v>2</v>
+      </c>
+      <c r="N142">
+        <v>5</v>
+      </c>
+      <c r="O142" t="s">
+        <v>172</v>
+      </c>
+      <c r="P142" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q142">
+        <v>1.8</v>
+      </c>
+      <c r="R142">
+        <v>2.5</v>
+      </c>
+      <c r="S142">
+        <v>8</v>
+      </c>
+      <c r="T142">
+        <v>1.33</v>
+      </c>
+      <c r="U142">
+        <v>3.25</v>
+      </c>
+      <c r="V142">
+        <v>2.5</v>
+      </c>
+      <c r="W142">
+        <v>1.5</v>
+      </c>
+      <c r="X142">
+        <v>6</v>
+      </c>
+      <c r="Y142">
+        <v>1.13</v>
+      </c>
+      <c r="Z142">
+        <v>1.29</v>
+      </c>
+      <c r="AA142">
+        <v>5.25</v>
+      </c>
+      <c r="AB142">
+        <v>8.5</v>
+      </c>
+      <c r="AC142">
+        <v>1.01</v>
+      </c>
+      <c r="AD142">
+        <v>13</v>
+      </c>
+      <c r="AE142">
+        <v>1.22</v>
+      </c>
+      <c r="AF142">
+        <v>4.1</v>
+      </c>
+      <c r="AG142">
+        <v>1.67</v>
+      </c>
+      <c r="AH142">
+        <v>2</v>
+      </c>
+      <c r="AI142">
+        <v>2</v>
+      </c>
+      <c r="AJ142">
+        <v>1.75</v>
+      </c>
+      <c r="AK142">
+        <v>1.07</v>
+      </c>
+      <c r="AL142">
+        <v>1.18</v>
+      </c>
+      <c r="AM142">
+        <v>3.2</v>
+      </c>
+      <c r="AN142">
+        <v>2.1</v>
+      </c>
+      <c r="AO142">
+        <v>1.5</v>
+      </c>
+      <c r="AP142">
+        <v>2.18</v>
+      </c>
+      <c r="AQ142">
+        <v>1.36</v>
+      </c>
+      <c r="AR142">
+        <v>1.82</v>
+      </c>
+      <c r="AS142">
+        <v>1.02</v>
+      </c>
+      <c r="AT142">
+        <v>2.84</v>
+      </c>
+      <c r="AU142">
+        <v>9</v>
+      </c>
+      <c r="AV142">
+        <v>5</v>
+      </c>
+      <c r="AW142">
+        <v>11</v>
+      </c>
+      <c r="AX142">
+        <v>3</v>
+      </c>
+      <c r="AY142">
+        <v>23</v>
+      </c>
+      <c r="AZ142">
+        <v>8</v>
+      </c>
+      <c r="BA142">
+        <v>13</v>
+      </c>
+      <c r="BB142">
+        <v>1</v>
+      </c>
+      <c r="BC142">
+        <v>14</v>
+      </c>
+      <c r="BD142">
+        <v>1.05</v>
+      </c>
+      <c r="BE142">
+        <v>11.5</v>
+      </c>
+      <c r="BF142">
+        <v>11</v>
+      </c>
+      <c r="BG142">
+        <v>1.33</v>
+      </c>
+      <c r="BH142">
+        <v>2.95</v>
+      </c>
+      <c r="BI142">
+        <v>1.6</v>
+      </c>
+      <c r="BJ142">
+        <v>2.1</v>
+      </c>
+      <c r="BK142">
+        <v>2.05</v>
+      </c>
+      <c r="BL142">
+        <v>1.63</v>
+      </c>
+      <c r="BM142">
+        <v>2.8</v>
+      </c>
+      <c r="BN142">
+        <v>1.36</v>
+      </c>
+      <c r="BO142">
+        <v>4</v>
+      </c>
+      <c r="BP142">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7537437</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45689.60416666666</v>
+      </c>
+      <c r="F143">
+        <v>21</v>
+      </c>
+      <c r="G143" t="s">
+        <v>78</v>
+      </c>
+      <c r="H143" t="s">
+        <v>70</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>169</v>
+      </c>
+      <c r="P143" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q143">
+        <v>3.25</v>
+      </c>
+      <c r="R143">
+        <v>2</v>
+      </c>
+      <c r="S143">
+        <v>3.6</v>
+      </c>
+      <c r="T143">
+        <v>1.5</v>
+      </c>
+      <c r="U143">
+        <v>2.5</v>
+      </c>
+      <c r="V143">
+        <v>3.4</v>
+      </c>
+      <c r="W143">
+        <v>1.3</v>
+      </c>
+      <c r="X143">
+        <v>10</v>
+      </c>
+      <c r="Y143">
+        <v>1.06</v>
+      </c>
+      <c r="Z143">
+        <v>2.4</v>
+      </c>
+      <c r="AA143">
+        <v>3.1</v>
+      </c>
+      <c r="AB143">
+        <v>2.9</v>
+      </c>
+      <c r="AC143">
+        <v>1.1</v>
+      </c>
+      <c r="AD143">
+        <v>7</v>
+      </c>
+      <c r="AE143">
+        <v>1.49</v>
+      </c>
+      <c r="AF143">
+        <v>2.48</v>
+      </c>
+      <c r="AG143">
+        <v>2.1</v>
+      </c>
+      <c r="AH143">
+        <v>1.6</v>
+      </c>
+      <c r="AI143">
+        <v>1.95</v>
+      </c>
+      <c r="AJ143">
+        <v>1.8</v>
+      </c>
+      <c r="AK143">
+        <v>1.4</v>
+      </c>
+      <c r="AL143">
+        <v>1.39</v>
+      </c>
+      <c r="AM143">
+        <v>1.53</v>
+      </c>
+      <c r="AN143">
+        <v>1.2</v>
+      </c>
+      <c r="AO143">
+        <v>1.5</v>
+      </c>
+      <c r="AP143">
+        <v>1.18</v>
+      </c>
+      <c r="AQ143">
+        <v>1.45</v>
+      </c>
+      <c r="AR143">
+        <v>1.33</v>
+      </c>
+      <c r="AS143">
+        <v>0.96</v>
+      </c>
+      <c r="AT143">
+        <v>2.29</v>
+      </c>
+      <c r="AU143">
+        <v>5</v>
+      </c>
+      <c r="AV143">
+        <v>6</v>
+      </c>
+      <c r="AW143">
+        <v>6</v>
+      </c>
+      <c r="AX143">
+        <v>10</v>
+      </c>
+      <c r="AY143">
+        <v>12</v>
+      </c>
+      <c r="AZ143">
+        <v>19</v>
+      </c>
+      <c r="BA143">
+        <v>4</v>
+      </c>
+      <c r="BB143">
+        <v>4</v>
+      </c>
+      <c r="BC143">
+        <v>8</v>
+      </c>
+      <c r="BD143">
+        <v>1.89</v>
+      </c>
+      <c r="BE143">
+        <v>6.4</v>
+      </c>
+      <c r="BF143">
+        <v>2.1</v>
+      </c>
+      <c r="BG143">
+        <v>1.44</v>
+      </c>
+      <c r="BH143">
+        <v>2.4</v>
+      </c>
+      <c r="BI143">
+        <v>1.76</v>
+      </c>
+      <c r="BJ143">
+        <v>1.84</v>
+      </c>
+      <c r="BK143">
+        <v>2.25</v>
+      </c>
+      <c r="BL143">
+        <v>1.5</v>
+      </c>
+      <c r="BM143">
+        <v>2.95</v>
+      </c>
+      <c r="BN143">
+        <v>1.3</v>
+      </c>
+      <c r="BO143">
+        <v>3.95</v>
+      </c>
+      <c r="BP143">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7537434</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45690.47916666666</v>
+      </c>
+      <c r="F144">
+        <v>21</v>
+      </c>
+      <c r="G144" t="s">
+        <v>72</v>
+      </c>
+      <c r="H144" t="s">
+        <v>80</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144" t="s">
+        <v>84</v>
+      </c>
+      <c r="P144" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q144">
+        <v>8</v>
+      </c>
+      <c r="R144">
+        <v>2.25</v>
+      </c>
+      <c r="S144">
+        <v>1.95</v>
+      </c>
+      <c r="T144">
+        <v>1.44</v>
+      </c>
+      <c r="U144">
+        <v>2.63</v>
+      </c>
+      <c r="V144">
+        <v>3</v>
+      </c>
+      <c r="W144">
+        <v>1.36</v>
+      </c>
+      <c r="X144">
+        <v>9</v>
+      </c>
+      <c r="Y144">
+        <v>1.07</v>
+      </c>
+      <c r="Z144">
+        <v>6.5</v>
+      </c>
+      <c r="AA144">
+        <v>4.2</v>
+      </c>
+      <c r="AB144">
+        <v>1.4</v>
+      </c>
+      <c r="AC144">
+        <v>1.07</v>
+      </c>
+      <c r="AD144">
+        <v>5.8</v>
+      </c>
+      <c r="AE144">
+        <v>1.35</v>
+      </c>
+      <c r="AF144">
+        <v>3.05</v>
+      </c>
+      <c r="AG144">
+        <v>1.95</v>
+      </c>
+      <c r="AH144">
+        <v>1.7</v>
+      </c>
+      <c r="AI144">
+        <v>2.25</v>
+      </c>
+      <c r="AJ144">
+        <v>1.57</v>
+      </c>
+      <c r="AK144">
+        <v>2.75</v>
+      </c>
+      <c r="AL144">
+        <v>1.24</v>
+      </c>
+      <c r="AM144">
+        <v>1.09</v>
+      </c>
+      <c r="AN144">
+        <v>1</v>
+      </c>
+      <c r="AO144">
+        <v>2</v>
+      </c>
+      <c r="AP144">
+        <v>0.91</v>
+      </c>
+      <c r="AQ144">
+        <v>2.09</v>
+      </c>
+      <c r="AR144">
+        <v>1.16</v>
+      </c>
+      <c r="AS144">
+        <v>1.84</v>
+      </c>
+      <c r="AT144">
+        <v>3</v>
+      </c>
+      <c r="AU144">
+        <v>4</v>
+      </c>
+      <c r="AV144">
+        <v>4</v>
+      </c>
+      <c r="AW144">
+        <v>3</v>
+      </c>
+      <c r="AX144">
+        <v>11</v>
+      </c>
+      <c r="AY144">
+        <v>8</v>
+      </c>
+      <c r="AZ144">
+        <v>17</v>
+      </c>
+      <c r="BA144">
+        <v>3</v>
+      </c>
+      <c r="BB144">
+        <v>6</v>
+      </c>
+      <c r="BC144">
+        <v>9</v>
+      </c>
+      <c r="BD144">
+        <v>3.55</v>
+      </c>
+      <c r="BE144">
+        <v>6.75</v>
+      </c>
+      <c r="BF144">
+        <v>1.36</v>
+      </c>
+      <c r="BG144">
+        <v>1.54</v>
+      </c>
+      <c r="BH144">
+        <v>2.17</v>
+      </c>
+      <c r="BI144">
+        <v>1.95</v>
+      </c>
+      <c r="BJ144">
+        <v>1.85</v>
+      </c>
+      <c r="BK144">
+        <v>2.45</v>
+      </c>
+      <c r="BL144">
+        <v>1.42</v>
+      </c>
+      <c r="BM144">
+        <v>3.25</v>
+      </c>
+      <c r="BN144">
+        <v>1.25</v>
+      </c>
+      <c r="BO144">
+        <v>4.4</v>
+      </c>
+      <c r="BP144">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="245">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -747,6 +747,9 @@
   <si>
     <t>['27', '42']</t>
   </si>
+  <si>
+    <t>['37', '47']</t>
+  </si>
 </sst>
 </file>
 
@@ -1107,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1647,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3">
         <v>0.9</v>
@@ -2268,7 +2271,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ6">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2677,10 +2680,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2886,7 +2889,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ9">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3092,7 +3095,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3298,7 +3301,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ11">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3501,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
         <v>1.45</v>
@@ -3707,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
         <v>1.3</v>
@@ -4737,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18">
         <v>0.9</v>
@@ -4946,7 +4949,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ19">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR19">
         <v>1.38</v>
@@ -5561,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ22">
         <v>1.9</v>
@@ -5973,10 +5976,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR24">
         <v>2.26</v>
@@ -6591,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27">
         <v>1.9</v>
@@ -6800,7 +6803,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ28">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
         <v>1</v>
@@ -7621,7 +7624,7 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32">
         <v>1.5</v>
@@ -8242,7 +8245,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ35">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -8445,10 +8448,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ36">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR36">
         <v>2.14</v>
@@ -8857,7 +8860,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
         <v>0.8</v>
@@ -9272,7 +9275,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ40">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR40">
         <v>2.09</v>
@@ -9475,10 +9478,10 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
         <v>1.71</v>
@@ -10299,10 +10302,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ45">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10508,7 +10511,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR46">
         <v>1.16</v>
@@ -10917,7 +10920,7 @@
         <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ48">
         <v>1.5</v>
@@ -12977,7 +12980,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ58">
         <v>1.45</v>
@@ -13186,7 +13189,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ59">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13392,7 +13395,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR60">
         <v>1.32</v>
@@ -13595,7 +13598,7 @@
         <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
         <v>2.09</v>
@@ -13804,7 +13807,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ62">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR62">
         <v>1.7</v>
@@ -14007,7 +14010,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ63">
         <v>1.36</v>
@@ -14213,10 +14216,10 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ64">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR64">
         <v>1.31</v>
@@ -14625,7 +14628,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ66">
         <v>1.3</v>
@@ -15246,7 +15249,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ69">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15655,7 +15658,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ71">
         <v>1.36</v>
@@ -15861,10 +15864,10 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ72">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
         <v>1.28</v>
@@ -16070,7 +16073,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR73">
         <v>1.13</v>
@@ -16894,7 +16897,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ77">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR77">
         <v>1.69</v>
@@ -17097,7 +17100,7 @@
         <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ78">
         <v>2.09</v>
@@ -17303,7 +17306,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ79">
         <v>0.9</v>
@@ -17921,7 +17924,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ82">
         <v>1.9</v>
@@ -18127,7 +18130,7 @@
         <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ83">
         <v>2.3</v>
@@ -18336,7 +18339,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ84">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR84">
         <v>2.03</v>
@@ -18748,7 +18751,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ86">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR86">
         <v>1.38</v>
@@ -19160,7 +19163,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ88">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR88">
         <v>1.86</v>
@@ -19775,7 +19778,7 @@
         <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
         <v>0.5</v>
@@ -19984,7 +19987,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ92">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR92">
         <v>1.7</v>
@@ -20396,7 +20399,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20808,7 +20811,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ96">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21011,7 +21014,7 @@
         <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
         <v>1.9</v>
@@ -21423,7 +21426,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ99">
         <v>0.8</v>
@@ -21632,7 +21635,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ100">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -22659,7 +22662,7 @@
         <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
         <v>2.3</v>
@@ -22865,7 +22868,7 @@
         <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ106">
         <v>2.09</v>
@@ -23074,7 +23077,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ107">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR107">
         <v>1.96</v>
@@ -23689,10 +23692,10 @@
         <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ110">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR110">
         <v>1.66</v>
@@ -24101,10 +24104,10 @@
         <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR112">
         <v>1.43</v>
@@ -24513,10 +24516,10 @@
         <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ114">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR114">
         <v>1.39</v>
@@ -25134,7 +25137,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ117">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25749,7 +25752,7 @@
         <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ120">
         <v>2.09</v>
@@ -25958,7 +25961,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ121">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR121">
         <v>1.96</v>
@@ -26370,7 +26373,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ123">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR123">
         <v>1.09</v>
@@ -26573,7 +26576,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ124">
         <v>1.45</v>
@@ -26985,7 +26988,7 @@
         <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ126">
         <v>1.3</v>
@@ -27397,7 +27400,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ128">
         <v>1.45</v>
@@ -28015,7 +28018,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ131">
         <v>1.36</v>
@@ -28430,7 +28433,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ133">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR133">
         <v>1.91</v>
@@ -28636,7 +28639,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ134">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
@@ -28842,7 +28845,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ135">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR135">
         <v>1.26</v>
@@ -29045,7 +29048,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP136">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ136">
         <v>0.5</v>
@@ -29666,7 +29669,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ139">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR139">
         <v>1.11</v>
@@ -29869,7 +29872,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ140">
         <v>0.8</v>
@@ -30772,6 +30775,830 @@
       </c>
       <c r="BP144">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7537433</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45690.5</v>
+      </c>
+      <c r="F145">
+        <v>21</v>
+      </c>
+      <c r="G145" t="s">
+        <v>83</v>
+      </c>
+      <c r="H145" t="s">
+        <v>82</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>84</v>
+      </c>
+      <c r="P145" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q145">
+        <v>4.5</v>
+      </c>
+      <c r="R145">
+        <v>2</v>
+      </c>
+      <c r="S145">
+        <v>2.75</v>
+      </c>
+      <c r="T145">
+        <v>1.5</v>
+      </c>
+      <c r="U145">
+        <v>2.5</v>
+      </c>
+      <c r="V145">
+        <v>3.4</v>
+      </c>
+      <c r="W145">
+        <v>1.3</v>
+      </c>
+      <c r="X145">
+        <v>10</v>
+      </c>
+      <c r="Y145">
+        <v>1.06</v>
+      </c>
+      <c r="Z145">
+        <v>3.8</v>
+      </c>
+      <c r="AA145">
+        <v>3.1</v>
+      </c>
+      <c r="AB145">
+        <v>2</v>
+      </c>
+      <c r="AC145">
+        <v>1.09</v>
+      </c>
+      <c r="AD145">
+        <v>4.8</v>
+      </c>
+      <c r="AE145">
+        <v>1.43</v>
+      </c>
+      <c r="AF145">
+        <v>2.7</v>
+      </c>
+      <c r="AG145">
+        <v>2.1</v>
+      </c>
+      <c r="AH145">
+        <v>1.6</v>
+      </c>
+      <c r="AI145">
+        <v>1.95</v>
+      </c>
+      <c r="AJ145">
+        <v>1.8</v>
+      </c>
+      <c r="AK145">
+        <v>1.75</v>
+      </c>
+      <c r="AL145">
+        <v>1.39</v>
+      </c>
+      <c r="AM145">
+        <v>1.25</v>
+      </c>
+      <c r="AN145">
+        <v>1</v>
+      </c>
+      <c r="AO145">
+        <v>1.1</v>
+      </c>
+      <c r="AP145">
+        <v>0.91</v>
+      </c>
+      <c r="AQ145">
+        <v>1.27</v>
+      </c>
+      <c r="AR145">
+        <v>1.37</v>
+      </c>
+      <c r="AS145">
+        <v>1.18</v>
+      </c>
+      <c r="AT145">
+        <v>2.55</v>
+      </c>
+      <c r="AU145">
+        <v>3</v>
+      </c>
+      <c r="AV145">
+        <v>2</v>
+      </c>
+      <c r="AW145">
+        <v>14</v>
+      </c>
+      <c r="AX145">
+        <v>11</v>
+      </c>
+      <c r="AY145">
+        <v>26</v>
+      </c>
+      <c r="AZ145">
+        <v>16</v>
+      </c>
+      <c r="BA145">
+        <v>10</v>
+      </c>
+      <c r="BB145">
+        <v>4</v>
+      </c>
+      <c r="BC145">
+        <v>14</v>
+      </c>
+      <c r="BD145">
+        <v>2.4</v>
+      </c>
+      <c r="BE145">
+        <v>6.4</v>
+      </c>
+      <c r="BF145">
+        <v>1.72</v>
+      </c>
+      <c r="BG145">
+        <v>1.43</v>
+      </c>
+      <c r="BH145">
+        <v>2.43</v>
+      </c>
+      <c r="BI145">
+        <v>1.85</v>
+      </c>
+      <c r="BJ145">
+        <v>1.95</v>
+      </c>
+      <c r="BK145">
+        <v>2.23</v>
+      </c>
+      <c r="BL145">
+        <v>1.52</v>
+      </c>
+      <c r="BM145">
+        <v>2.9</v>
+      </c>
+      <c r="BN145">
+        <v>1.3</v>
+      </c>
+      <c r="BO145">
+        <v>3.85</v>
+      </c>
+      <c r="BP145">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7537438</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45690.60416666666</v>
+      </c>
+      <c r="F146">
+        <v>21</v>
+      </c>
+      <c r="G146" t="s">
+        <v>71</v>
+      </c>
+      <c r="H146" t="s">
+        <v>75</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="M146">
+        <v>2</v>
+      </c>
+      <c r="N146">
+        <v>3</v>
+      </c>
+      <c r="O146" t="s">
+        <v>136</v>
+      </c>
+      <c r="P146" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q146">
+        <v>3.25</v>
+      </c>
+      <c r="R146">
+        <v>2.1</v>
+      </c>
+      <c r="S146">
+        <v>3.4</v>
+      </c>
+      <c r="T146">
+        <v>1.44</v>
+      </c>
+      <c r="U146">
+        <v>2.63</v>
+      </c>
+      <c r="V146">
+        <v>3.25</v>
+      </c>
+      <c r="W146">
+        <v>1.33</v>
+      </c>
+      <c r="X146">
+        <v>9</v>
+      </c>
+      <c r="Y146">
+        <v>1.07</v>
+      </c>
+      <c r="Z146">
+        <v>2.55</v>
+      </c>
+      <c r="AA146">
+        <v>3.2</v>
+      </c>
+      <c r="AB146">
+        <v>2.62</v>
+      </c>
+      <c r="AC146">
+        <v>1.07</v>
+      </c>
+      <c r="AD146">
+        <v>5.6</v>
+      </c>
+      <c r="AE146">
+        <v>1.35</v>
+      </c>
+      <c r="AF146">
+        <v>3.05</v>
+      </c>
+      <c r="AG146">
+        <v>1.95</v>
+      </c>
+      <c r="AH146">
+        <v>1.7</v>
+      </c>
+      <c r="AI146">
+        <v>1.8</v>
+      </c>
+      <c r="AJ146">
+        <v>1.95</v>
+      </c>
+      <c r="AK146">
+        <v>1.46</v>
+      </c>
+      <c r="AL146">
+        <v>1.37</v>
+      </c>
+      <c r="AM146">
+        <v>1.48</v>
+      </c>
+      <c r="AN146">
+        <v>1.4</v>
+      </c>
+      <c r="AO146">
+        <v>1.6</v>
+      </c>
+      <c r="AP146">
+        <v>1.27</v>
+      </c>
+      <c r="AQ146">
+        <v>1.73</v>
+      </c>
+      <c r="AR146">
+        <v>1.73</v>
+      </c>
+      <c r="AS146">
+        <v>1.72</v>
+      </c>
+      <c r="AT146">
+        <v>3.45</v>
+      </c>
+      <c r="AU146">
+        <v>6</v>
+      </c>
+      <c r="AV146">
+        <v>6</v>
+      </c>
+      <c r="AW146">
+        <v>6</v>
+      </c>
+      <c r="AX146">
+        <v>10</v>
+      </c>
+      <c r="AY146">
+        <v>13</v>
+      </c>
+      <c r="AZ146">
+        <v>20</v>
+      </c>
+      <c r="BA146">
+        <v>3</v>
+      </c>
+      <c r="BB146">
+        <v>3</v>
+      </c>
+      <c r="BC146">
+        <v>6</v>
+      </c>
+      <c r="BD146">
+        <v>2.05</v>
+      </c>
+      <c r="BE146">
+        <v>6.1</v>
+      </c>
+      <c r="BF146">
+        <v>1.98</v>
+      </c>
+      <c r="BG146">
+        <v>1.41</v>
+      </c>
+      <c r="BH146">
+        <v>2.5</v>
+      </c>
+      <c r="BI146">
+        <v>1.71</v>
+      </c>
+      <c r="BJ146">
+        <v>1.9</v>
+      </c>
+      <c r="BK146">
+        <v>2.15</v>
+      </c>
+      <c r="BL146">
+        <v>1.55</v>
+      </c>
+      <c r="BM146">
+        <v>2.8</v>
+      </c>
+      <c r="BN146">
+        <v>1.32</v>
+      </c>
+      <c r="BO146">
+        <v>3.8</v>
+      </c>
+      <c r="BP146">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7537436</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45690.64583333334</v>
+      </c>
+      <c r="F147">
+        <v>21</v>
+      </c>
+      <c r="G147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H147" t="s">
+        <v>74</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147" t="s">
+        <v>84</v>
+      </c>
+      <c r="P147" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q147">
+        <v>4</v>
+      </c>
+      <c r="R147">
+        <v>1.83</v>
+      </c>
+      <c r="S147">
+        <v>3.5</v>
+      </c>
+      <c r="T147">
+        <v>1.62</v>
+      </c>
+      <c r="U147">
+        <v>2.2</v>
+      </c>
+      <c r="V147">
+        <v>4</v>
+      </c>
+      <c r="W147">
+        <v>1.22</v>
+      </c>
+      <c r="X147">
+        <v>15</v>
+      </c>
+      <c r="Y147">
+        <v>1.03</v>
+      </c>
+      <c r="Z147">
+        <v>3</v>
+      </c>
+      <c r="AA147">
+        <v>2.8</v>
+      </c>
+      <c r="AB147">
+        <v>2.5</v>
+      </c>
+      <c r="AC147">
+        <v>1.14</v>
+      </c>
+      <c r="AD147">
+        <v>3.8</v>
+      </c>
+      <c r="AE147">
+        <v>1.5</v>
+      </c>
+      <c r="AF147">
+        <v>2.25</v>
+      </c>
+      <c r="AG147">
+        <v>2.22</v>
+      </c>
+      <c r="AH147">
+        <v>1.56</v>
+      </c>
+      <c r="AI147">
+        <v>2.2</v>
+      </c>
+      <c r="AJ147">
+        <v>1.62</v>
+      </c>
+      <c r="AK147">
+        <v>1.49</v>
+      </c>
+      <c r="AL147">
+        <v>1.44</v>
+      </c>
+      <c r="AM147">
+        <v>1.38</v>
+      </c>
+      <c r="AN147">
+        <v>1.3</v>
+      </c>
+      <c r="AO147">
+        <v>1.7</v>
+      </c>
+      <c r="AP147">
+        <v>1.18</v>
+      </c>
+      <c r="AQ147">
+        <v>1.82</v>
+      </c>
+      <c r="AR147">
+        <v>1.16</v>
+      </c>
+      <c r="AS147">
+        <v>1.04</v>
+      </c>
+      <c r="AT147">
+        <v>2.2</v>
+      </c>
+      <c r="AU147">
+        <v>0</v>
+      </c>
+      <c r="AV147">
+        <v>9</v>
+      </c>
+      <c r="AW147">
+        <v>6</v>
+      </c>
+      <c r="AX147">
+        <v>14</v>
+      </c>
+      <c r="AY147">
+        <v>6</v>
+      </c>
+      <c r="AZ147">
+        <v>27</v>
+      </c>
+      <c r="BA147">
+        <v>0</v>
+      </c>
+      <c r="BB147">
+        <v>5</v>
+      </c>
+      <c r="BC147">
+        <v>5</v>
+      </c>
+      <c r="BD147">
+        <v>2.2</v>
+      </c>
+      <c r="BE147">
+        <v>6.4</v>
+      </c>
+      <c r="BF147">
+        <v>1.81</v>
+      </c>
+      <c r="BG147">
+        <v>1.43</v>
+      </c>
+      <c r="BH147">
+        <v>2.43</v>
+      </c>
+      <c r="BI147">
+        <v>1.82</v>
+      </c>
+      <c r="BJ147">
+        <v>1.98</v>
+      </c>
+      <c r="BK147">
+        <v>2.2</v>
+      </c>
+      <c r="BL147">
+        <v>1.52</v>
+      </c>
+      <c r="BM147">
+        <v>2.85</v>
+      </c>
+      <c r="BN147">
+        <v>1.32</v>
+      </c>
+      <c r="BO147">
+        <v>3.85</v>
+      </c>
+      <c r="BP147">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7537432</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45691.54166666666</v>
+      </c>
+      <c r="F148">
+        <v>21</v>
+      </c>
+      <c r="G148" t="s">
+        <v>79</v>
+      </c>
+      <c r="H148" t="s">
+        <v>81</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148" t="s">
+        <v>124</v>
+      </c>
+      <c r="P148" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q148">
+        <v>2.4</v>
+      </c>
+      <c r="R148">
+        <v>2</v>
+      </c>
+      <c r="S148">
+        <v>6</v>
+      </c>
+      <c r="T148">
+        <v>1.57</v>
+      </c>
+      <c r="U148">
+        <v>2.25</v>
+      </c>
+      <c r="V148">
+        <v>3.75</v>
+      </c>
+      <c r="W148">
+        <v>1.25</v>
+      </c>
+      <c r="X148">
+        <v>11</v>
+      </c>
+      <c r="Y148">
+        <v>1.05</v>
+      </c>
+      <c r="Z148">
+        <v>1.67</v>
+      </c>
+      <c r="AA148">
+        <v>3.4</v>
+      </c>
+      <c r="AB148">
+        <v>5.25</v>
+      </c>
+      <c r="AC148">
+        <v>1.09</v>
+      </c>
+      <c r="AD148">
+        <v>4.7</v>
+      </c>
+      <c r="AE148">
+        <v>1.48</v>
+      </c>
+      <c r="AF148">
+        <v>2.55</v>
+      </c>
+      <c r="AG148">
+        <v>2.37</v>
+      </c>
+      <c r="AH148">
+        <v>1.48</v>
+      </c>
+      <c r="AI148">
+        <v>2.38</v>
+      </c>
+      <c r="AJ148">
+        <v>1.53</v>
+      </c>
+      <c r="AK148">
+        <v>1.15</v>
+      </c>
+      <c r="AL148">
+        <v>1.3</v>
+      </c>
+      <c r="AM148">
+        <v>2.28</v>
+      </c>
+      <c r="AN148">
+        <v>1.6</v>
+      </c>
+      <c r="AO148">
+        <v>0.6</v>
+      </c>
+      <c r="AP148">
+        <v>1.73</v>
+      </c>
+      <c r="AQ148">
+        <v>0.55</v>
+      </c>
+      <c r="AR148">
+        <v>1.44</v>
+      </c>
+      <c r="AS148">
+        <v>0.96</v>
+      </c>
+      <c r="AT148">
+        <v>2.4</v>
+      </c>
+      <c r="AU148">
+        <v>5</v>
+      </c>
+      <c r="AV148">
+        <v>0</v>
+      </c>
+      <c r="AW148">
+        <v>10</v>
+      </c>
+      <c r="AX148">
+        <v>13</v>
+      </c>
+      <c r="AY148">
+        <v>17</v>
+      </c>
+      <c r="AZ148">
+        <v>18</v>
+      </c>
+      <c r="BA148">
+        <v>3</v>
+      </c>
+      <c r="BB148">
+        <v>4</v>
+      </c>
+      <c r="BC148">
+        <v>7</v>
+      </c>
+      <c r="BD148">
+        <v>1.25</v>
+      </c>
+      <c r="BE148">
+        <v>7.3</v>
+      </c>
+      <c r="BF148">
+        <v>5.25</v>
+      </c>
+      <c r="BG148">
+        <v>1.39</v>
+      </c>
+      <c r="BH148">
+        <v>2.65</v>
+      </c>
+      <c r="BI148">
+        <v>1.72</v>
+      </c>
+      <c r="BJ148">
+        <v>1.93</v>
+      </c>
+      <c r="BK148">
+        <v>2.25</v>
+      </c>
+      <c r="BL148">
+        <v>1.53</v>
+      </c>
+      <c r="BM148">
+        <v>3.1</v>
+      </c>
+      <c r="BN148">
+        <v>1.29</v>
+      </c>
+      <c r="BO148">
+        <v>4.15</v>
+      </c>
+      <c r="BP148">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="246">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -750,6 +750,9 @@
   <si>
     <t>['37', '47']</t>
   </si>
+  <si>
+    <t>['2', '8', '30', '58', '67']</t>
+  </si>
 </sst>
 </file>
 
@@ -1110,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1444,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ2">
         <v>2.09</v>
@@ -2886,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ9">
         <v>1.82</v>
@@ -3713,7 +3716,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
@@ -5152,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ20">
         <v>1.36</v>
@@ -5361,7 +5364,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ21">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR21">
         <v>1.23</v>
@@ -6391,7 +6394,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ26">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR26">
         <v>1.48</v>
@@ -6800,7 +6803,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ28">
         <v>1.27</v>
@@ -7212,10 +7215,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ30">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR30">
         <v>0.96</v>
@@ -8654,7 +8657,7 @@
         <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ37">
         <v>0.5</v>
@@ -9066,10 +9069,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ39">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -11129,7 +11132,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ49">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11538,7 +11541,7 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ51">
         <v>0.9</v>
@@ -11747,7 +11750,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ52">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR52">
         <v>1.4</v>
@@ -12362,7 +12365,7 @@
         <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ55">
         <v>1.9</v>
@@ -12777,7 +12780,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ57">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR57">
         <v>1.84</v>
@@ -14631,7 +14634,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ66">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR66">
         <v>1.31</v>
@@ -15040,7 +15043,7 @@
         <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ68">
         <v>1.9</v>
@@ -15455,7 +15458,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ70">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR70">
         <v>1.11</v>
@@ -16482,7 +16485,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -18133,7 +18136,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ83">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR83">
         <v>1.54</v>
@@ -18748,7 +18751,7 @@
         <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ86">
         <v>0.55</v>
@@ -18957,7 +18960,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ87">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR87">
         <v>1.2</v>
@@ -19572,7 +19575,7 @@
         <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ90">
         <v>2.09</v>
@@ -20605,7 +20608,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ95">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR95">
         <v>1.27</v>
@@ -20808,7 +20811,7 @@
         <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ96">
         <v>1.73</v>
@@ -21223,7 +21226,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ98">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR98">
         <v>1.1</v>
@@ -22044,7 +22047,7 @@
         <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ102">
         <v>1.5</v>
@@ -22665,7 +22668,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ105">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR105">
         <v>1.29</v>
@@ -23283,7 +23286,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ108">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR108">
         <v>1.22</v>
@@ -24310,7 +24313,7 @@
         <v>1.71</v>
       </c>
       <c r="AP113">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ113">
         <v>1.45</v>
@@ -25134,7 +25137,7 @@
         <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ117">
         <v>1.73</v>
@@ -25549,7 +25552,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ119">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR119">
         <v>1.85</v>
@@ -26991,7 +26994,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ126">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27194,7 +27197,7 @@
         <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ127">
         <v>0.8</v>
@@ -28227,7 +28230,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR132">
         <v>1.43</v>
@@ -28842,7 +28845,7 @@
         <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ135">
         <v>1.82</v>
@@ -29254,7 +29257,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ137">
         <v>0.9</v>
@@ -29463,7 +29466,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ138">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR138">
         <v>2.02</v>
@@ -31599,6 +31602,418 @@
       </c>
       <c r="BP148">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7537442</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F149">
+        <v>22</v>
+      </c>
+      <c r="G149" t="s">
+        <v>70</v>
+      </c>
+      <c r="H149" t="s">
+        <v>76</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="O149" t="s">
+        <v>84</v>
+      </c>
+      <c r="P149" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q149">
+        <v>3.2</v>
+      </c>
+      <c r="R149">
+        <v>1.91</v>
+      </c>
+      <c r="S149">
+        <v>4</v>
+      </c>
+      <c r="T149">
+        <v>1.57</v>
+      </c>
+      <c r="U149">
+        <v>2.25</v>
+      </c>
+      <c r="V149">
+        <v>3.75</v>
+      </c>
+      <c r="W149">
+        <v>1.25</v>
+      </c>
+      <c r="X149">
+        <v>13</v>
+      </c>
+      <c r="Y149">
+        <v>1.04</v>
+      </c>
+      <c r="Z149">
+        <v>2.3</v>
+      </c>
+      <c r="AA149">
+        <v>2.9</v>
+      </c>
+      <c r="AB149">
+        <v>3.3</v>
+      </c>
+      <c r="AC149">
+        <v>1.06</v>
+      </c>
+      <c r="AD149">
+        <v>6.45</v>
+      </c>
+      <c r="AE149">
+        <v>1.48</v>
+      </c>
+      <c r="AF149">
+        <v>2.37</v>
+      </c>
+      <c r="AG149">
+        <v>2.65</v>
+      </c>
+      <c r="AH149">
+        <v>1.42</v>
+      </c>
+      <c r="AI149">
+        <v>2.05</v>
+      </c>
+      <c r="AJ149">
+        <v>1.7</v>
+      </c>
+      <c r="AK149">
+        <v>1.33</v>
+      </c>
+      <c r="AL149">
+        <v>1.43</v>
+      </c>
+      <c r="AM149">
+        <v>1.61</v>
+      </c>
+      <c r="AN149">
+        <v>0.5</v>
+      </c>
+      <c r="AO149">
+        <v>1.3</v>
+      </c>
+      <c r="AP149">
+        <v>0.45</v>
+      </c>
+      <c r="AQ149">
+        <v>1.45</v>
+      </c>
+      <c r="AR149">
+        <v>1.24</v>
+      </c>
+      <c r="AS149">
+        <v>0.96</v>
+      </c>
+      <c r="AT149">
+        <v>2.2</v>
+      </c>
+      <c r="AU149">
+        <v>3</v>
+      </c>
+      <c r="AV149">
+        <v>4</v>
+      </c>
+      <c r="AW149">
+        <v>13</v>
+      </c>
+      <c r="AX149">
+        <v>4</v>
+      </c>
+      <c r="AY149">
+        <v>20</v>
+      </c>
+      <c r="AZ149">
+        <v>8</v>
+      </c>
+      <c r="BA149">
+        <v>7</v>
+      </c>
+      <c r="BB149">
+        <v>1</v>
+      </c>
+      <c r="BC149">
+        <v>8</v>
+      </c>
+      <c r="BD149">
+        <v>1.74</v>
+      </c>
+      <c r="BE149">
+        <v>6.1</v>
+      </c>
+      <c r="BF149">
+        <v>2.38</v>
+      </c>
+      <c r="BG149">
+        <v>1.5</v>
+      </c>
+      <c r="BH149">
+        <v>2.25</v>
+      </c>
+      <c r="BI149">
+        <v>1.88</v>
+      </c>
+      <c r="BJ149">
+        <v>1.92</v>
+      </c>
+      <c r="BK149">
+        <v>2.35</v>
+      </c>
+      <c r="BL149">
+        <v>1.46</v>
+      </c>
+      <c r="BM149">
+        <v>3.1</v>
+      </c>
+      <c r="BN149">
+        <v>1.27</v>
+      </c>
+      <c r="BO149">
+        <v>4.3</v>
+      </c>
+      <c r="BP149">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7537444</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45696.625</v>
+      </c>
+      <c r="F150">
+        <v>22</v>
+      </c>
+      <c r="G150" t="s">
+        <v>77</v>
+      </c>
+      <c r="H150" t="s">
+        <v>71</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>3</v>
+      </c>
+      <c r="K150">
+        <v>3</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>5</v>
+      </c>
+      <c r="N150">
+        <v>5</v>
+      </c>
+      <c r="O150" t="s">
+        <v>84</v>
+      </c>
+      <c r="P150" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q150">
+        <v>5.5</v>
+      </c>
+      <c r="R150">
+        <v>2.25</v>
+      </c>
+      <c r="S150">
+        <v>2.25</v>
+      </c>
+      <c r="T150">
+        <v>1.36</v>
+      </c>
+      <c r="U150">
+        <v>3</v>
+      </c>
+      <c r="V150">
+        <v>2.75</v>
+      </c>
+      <c r="W150">
+        <v>1.4</v>
+      </c>
+      <c r="X150">
+        <v>8</v>
+      </c>
+      <c r="Y150">
+        <v>1.08</v>
+      </c>
+      <c r="Z150">
+        <v>6</v>
+      </c>
+      <c r="AA150">
+        <v>3.6</v>
+      </c>
+      <c r="AB150">
+        <v>1.65</v>
+      </c>
+      <c r="AC150">
+        <v>1.06</v>
+      </c>
+      <c r="AD150">
+        <v>11</v>
+      </c>
+      <c r="AE150">
+        <v>1.28</v>
+      </c>
+      <c r="AF150">
+        <v>3.6</v>
+      </c>
+      <c r="AG150">
+        <v>1.85</v>
+      </c>
+      <c r="AH150">
+        <v>1.95</v>
+      </c>
+      <c r="AI150">
+        <v>1.8</v>
+      </c>
+      <c r="AJ150">
+        <v>1.95</v>
+      </c>
+      <c r="AK150">
+        <v>2.22</v>
+      </c>
+      <c r="AL150">
+        <v>1.3</v>
+      </c>
+      <c r="AM150">
+        <v>1.17</v>
+      </c>
+      <c r="AN150">
+        <v>1.2</v>
+      </c>
+      <c r="AO150">
+        <v>2.3</v>
+      </c>
+      <c r="AP150">
+        <v>1.09</v>
+      </c>
+      <c r="AQ150">
+        <v>2.36</v>
+      </c>
+      <c r="AR150">
+        <v>1.42</v>
+      </c>
+      <c r="AS150">
+        <v>1.57</v>
+      </c>
+      <c r="AT150">
+        <v>2.99</v>
+      </c>
+      <c r="AU150">
+        <v>3</v>
+      </c>
+      <c r="AV150">
+        <v>12</v>
+      </c>
+      <c r="AW150">
+        <v>5</v>
+      </c>
+      <c r="AX150">
+        <v>8</v>
+      </c>
+      <c r="AY150">
+        <v>12</v>
+      </c>
+      <c r="AZ150">
+        <v>23</v>
+      </c>
+      <c r="BA150">
+        <v>4</v>
+      </c>
+      <c r="BB150">
+        <v>5</v>
+      </c>
+      <c r="BC150">
+        <v>9</v>
+      </c>
+      <c r="BD150">
+        <v>3.84</v>
+      </c>
+      <c r="BE150">
+        <v>9</v>
+      </c>
+      <c r="BF150">
+        <v>1.4</v>
+      </c>
+      <c r="BG150">
+        <v>1.44</v>
+      </c>
+      <c r="BH150">
+        <v>2.51</v>
+      </c>
+      <c r="BI150">
+        <v>1.81</v>
+      </c>
+      <c r="BJ150">
+        <v>1.89</v>
+      </c>
+      <c r="BK150">
+        <v>2.32</v>
+      </c>
+      <c r="BL150">
+        <v>1.51</v>
+      </c>
+      <c r="BM150">
+        <v>3.14</v>
+      </c>
+      <c r="BN150">
+        <v>1.27</v>
+      </c>
+      <c r="BO150">
+        <v>3.8</v>
+      </c>
+      <c r="BP150">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="249">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -533,6 +533,15 @@
   </si>
   <si>
     <t>['57', '72', '81']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['43', '50']</t>
+  </si>
+  <si>
+    <t>['8', '23', '73', '81', '84']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1113,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1369,7 +1378,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1575,7 +1584,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1656,7 +1665,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ3">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2068,7 +2077,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2193,7 +2202,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2477,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ7">
         <v>1.36</v>
@@ -2605,7 +2614,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3017,7 +3026,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3223,7 +3232,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3301,7 +3310,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ11">
         <v>0.55</v>
@@ -3429,7 +3438,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -4047,7 +4056,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4125,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4253,7 +4262,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4459,7 +4468,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4537,10 +4546,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4746,7 +4755,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ18">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -4871,7 +4880,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5077,7 +5086,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5283,7 +5292,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5489,7 +5498,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5570,7 +5579,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5901,7 +5910,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6107,7 +6116,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6391,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ26">
         <v>1.45</v>
@@ -6600,7 +6609,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ27">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR27">
         <v>1.95</v>
@@ -6725,7 +6734,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7009,7 +7018,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ29">
         <v>1.45</v>
@@ -7137,7 +7146,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7421,7 +7430,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ31">
         <v>2.09</v>
@@ -7549,7 +7558,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7630,7 +7639,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -7961,7 +7970,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8042,7 +8051,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ34">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR34">
         <v>1.44</v>
@@ -8167,7 +8176,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8785,7 +8794,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8991,7 +9000,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9275,7 +9284,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ40">
         <v>1.82</v>
@@ -9687,10 +9696,10 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ42">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR42">
         <v>1.99</v>
@@ -9815,7 +9824,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9896,7 +9905,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ43">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR43">
         <v>1.06</v>
@@ -10021,7 +10030,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10511,7 +10520,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ46">
         <v>0.55</v>
@@ -10639,7 +10648,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10845,7 +10854,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10926,7 +10935,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11051,7 +11060,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11544,7 +11553,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ51">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -11669,7 +11678,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11956,7 +11965,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ53">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12081,7 +12090,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12159,7 +12168,7 @@
         <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ54">
         <v>0.8</v>
@@ -12287,7 +12296,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12368,7 +12377,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ55">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR55">
         <v>1.16</v>
@@ -12571,7 +12580,7 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56">
         <v>0.5</v>
@@ -12699,7 +12708,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12777,7 +12786,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ57">
         <v>2.36</v>
@@ -12905,7 +12914,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13111,7 +13120,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13729,7 +13738,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13935,7 +13944,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14141,7 +14150,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14425,10 +14434,10 @@
         <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ65">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR65">
         <v>1.98</v>
@@ -14759,7 +14768,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14837,7 +14846,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ67">
         <v>0.8</v>
@@ -15046,7 +15055,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ68">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR68">
         <v>1.45</v>
@@ -15171,7 +15180,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15377,7 +15386,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15995,7 +16004,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16279,10 +16288,10 @@
         <v>1.8</v>
       </c>
       <c r="AP74">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR74">
         <v>1.64</v>
@@ -16407,7 +16416,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16613,7 +16622,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17025,7 +17034,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17231,7 +17240,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17312,7 +17321,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ79">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17437,7 +17446,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17721,7 +17730,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ81">
         <v>1.45</v>
@@ -17849,7 +17858,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -17930,7 +17939,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ82">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR82">
         <v>1.27</v>
@@ -18055,7 +18064,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18339,7 +18348,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ84">
         <v>1.73</v>
@@ -18467,7 +18476,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18879,7 +18888,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19163,7 +19172,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ88">
         <v>1.27</v>
@@ -19372,7 +19381,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR89">
         <v>1.12</v>
@@ -19497,7 +19506,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19703,7 +19712,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19909,7 +19918,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20193,7 +20202,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ93">
         <v>1.45</v>
@@ -20321,7 +20330,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20399,7 +20408,7 @@
         <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
         <v>1.82</v>
@@ -20527,7 +20536,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20733,7 +20742,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21020,7 +21029,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ97">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21145,7 +21154,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21351,7 +21360,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21969,7 +21978,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22050,7 +22059,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -22253,10 +22262,10 @@
         <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ103">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR103">
         <v>1.47</v>
@@ -22381,7 +22390,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22462,7 +22471,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ104">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR104">
         <v>1.19</v>
@@ -23077,7 +23086,7 @@
         <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ107">
         <v>0.55</v>
@@ -23823,7 +23832,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23901,7 +23910,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ111">
         <v>0.8</v>
@@ -24029,7 +24038,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24728,7 +24737,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ115">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -24853,7 +24862,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -24931,7 +24940,7 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ116">
         <v>1.36</v>
@@ -25059,7 +25068,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25265,7 +25274,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25346,7 +25355,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR118">
         <v>1.32</v>
@@ -25471,7 +25480,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25677,7 +25686,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25961,7 +25970,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ121">
         <v>1.27</v>
@@ -26089,7 +26098,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26170,7 +26179,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR122">
         <v>1.28</v>
@@ -26295,7 +26304,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26501,7 +26510,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26785,7 +26794,7 @@
         <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ125">
         <v>0.5</v>
@@ -27531,7 +27540,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27737,7 +27746,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27818,7 +27827,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ130">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR130">
         <v>1.17</v>
@@ -28227,7 +28236,7 @@
         <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ132">
         <v>2.36</v>
@@ -28767,7 +28776,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29179,7 +29188,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29260,7 +29269,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ137">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
         <v>1.31</v>
@@ -29463,7 +29472,7 @@
         <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ138">
         <v>1.45</v>
@@ -29591,7 +29600,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -30081,10 +30090,10 @@
         <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ141">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR141">
         <v>1.93</v>
@@ -30209,7 +30218,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30415,7 +30424,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -31033,7 +31042,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31857,7 +31866,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32014,6 +32023,624 @@
       </c>
       <c r="BP150">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7537443</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45697.5</v>
+      </c>
+      <c r="F151">
+        <v>22</v>
+      </c>
+      <c r="G151" t="s">
+        <v>80</v>
+      </c>
+      <c r="H151" t="s">
+        <v>79</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>2</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>2</v>
+      </c>
+      <c r="O151" t="s">
+        <v>173</v>
+      </c>
+      <c r="P151" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q151">
+        <v>1.8</v>
+      </c>
+      <c r="R151">
+        <v>2.4</v>
+      </c>
+      <c r="S151">
+        <v>9.5</v>
+      </c>
+      <c r="T151">
+        <v>1.36</v>
+      </c>
+      <c r="U151">
+        <v>3</v>
+      </c>
+      <c r="V151">
+        <v>2.63</v>
+      </c>
+      <c r="W151">
+        <v>1.44</v>
+      </c>
+      <c r="X151">
+        <v>7</v>
+      </c>
+      <c r="Y151">
+        <v>1.1</v>
+      </c>
+      <c r="Z151">
+        <v>1.25</v>
+      </c>
+      <c r="AA151">
+        <v>5.25</v>
+      </c>
+      <c r="AB151">
+        <v>9</v>
+      </c>
+      <c r="AC151">
+        <v>1.04</v>
+      </c>
+      <c r="AD151">
+        <v>12</v>
+      </c>
+      <c r="AE151">
+        <v>1.27</v>
+      </c>
+      <c r="AF151">
+        <v>3.7</v>
+      </c>
+      <c r="AG151">
+        <v>1.85</v>
+      </c>
+      <c r="AH151">
+        <v>1.75</v>
+      </c>
+      <c r="AI151">
+        <v>2.25</v>
+      </c>
+      <c r="AJ151">
+        <v>1.57</v>
+      </c>
+      <c r="AK151">
+        <v>1.06</v>
+      </c>
+      <c r="AL151">
+        <v>1.18</v>
+      </c>
+      <c r="AM151">
+        <v>3.55</v>
+      </c>
+      <c r="AN151">
+        <v>2.4</v>
+      </c>
+      <c r="AO151">
+        <v>1.5</v>
+      </c>
+      <c r="AP151">
+        <v>2.27</v>
+      </c>
+      <c r="AQ151">
+        <v>1.45</v>
+      </c>
+      <c r="AR151">
+        <v>1.88</v>
+      </c>
+      <c r="AS151">
+        <v>1.11</v>
+      </c>
+      <c r="AT151">
+        <v>2.99</v>
+      </c>
+      <c r="AU151">
+        <v>5</v>
+      </c>
+      <c r="AV151">
+        <v>3</v>
+      </c>
+      <c r="AW151">
+        <v>20</v>
+      </c>
+      <c r="AX151">
+        <v>2</v>
+      </c>
+      <c r="AY151">
+        <v>32</v>
+      </c>
+      <c r="AZ151">
+        <v>5</v>
+      </c>
+      <c r="BA151">
+        <v>12</v>
+      </c>
+      <c r="BB151">
+        <v>0</v>
+      </c>
+      <c r="BC151">
+        <v>12</v>
+      </c>
+      <c r="BD151">
+        <v>1.24</v>
+      </c>
+      <c r="BE151">
+        <v>8</v>
+      </c>
+      <c r="BF151">
+        <v>4.4</v>
+      </c>
+      <c r="BG151">
+        <v>1.38</v>
+      </c>
+      <c r="BH151">
+        <v>2.55</v>
+      </c>
+      <c r="BI151">
+        <v>1.8</v>
+      </c>
+      <c r="BJ151">
+        <v>2</v>
+      </c>
+      <c r="BK151">
+        <v>2.1</v>
+      </c>
+      <c r="BL151">
+        <v>1.58</v>
+      </c>
+      <c r="BM151">
+        <v>2.7</v>
+      </c>
+      <c r="BN151">
+        <v>1.35</v>
+      </c>
+      <c r="BO151">
+        <v>3.55</v>
+      </c>
+      <c r="BP151">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7537440</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F152">
+        <v>22</v>
+      </c>
+      <c r="G152" t="s">
+        <v>82</v>
+      </c>
+      <c r="H152" t="s">
+        <v>73</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="L152">
+        <v>2</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>174</v>
+      </c>
+      <c r="P152" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q152">
+        <v>4.75</v>
+      </c>
+      <c r="R152">
+        <v>2.05</v>
+      </c>
+      <c r="S152">
+        <v>2.63</v>
+      </c>
+      <c r="T152">
+        <v>1.5</v>
+      </c>
+      <c r="U152">
+        <v>2.5</v>
+      </c>
+      <c r="V152">
+        <v>3.4</v>
+      </c>
+      <c r="W152">
+        <v>1.3</v>
+      </c>
+      <c r="X152">
+        <v>10</v>
+      </c>
+      <c r="Y152">
+        <v>1.06</v>
+      </c>
+      <c r="Z152">
+        <v>4</v>
+      </c>
+      <c r="AA152">
+        <v>3.3</v>
+      </c>
+      <c r="AB152">
+        <v>1.87</v>
+      </c>
+      <c r="AC152">
+        <v>1.08</v>
+      </c>
+      <c r="AD152">
+        <v>8</v>
+      </c>
+      <c r="AE152">
+        <v>1.46</v>
+      </c>
+      <c r="AF152">
+        <v>2.4</v>
+      </c>
+      <c r="AG152">
+        <v>2.15</v>
+      </c>
+      <c r="AH152">
+        <v>1.57</v>
+      </c>
+      <c r="AI152">
+        <v>2</v>
+      </c>
+      <c r="AJ152">
+        <v>1.75</v>
+      </c>
+      <c r="AK152">
+        <v>1.85</v>
+      </c>
+      <c r="AL152">
+        <v>1.36</v>
+      </c>
+      <c r="AM152">
+        <v>1.26</v>
+      </c>
+      <c r="AN152">
+        <v>2</v>
+      </c>
+      <c r="AO152">
+        <v>1.9</v>
+      </c>
+      <c r="AP152">
+        <v>2.09</v>
+      </c>
+      <c r="AQ152">
+        <v>1.73</v>
+      </c>
+      <c r="AR152">
+        <v>1.42</v>
+      </c>
+      <c r="AS152">
+        <v>1.53</v>
+      </c>
+      <c r="AT152">
+        <v>2.95</v>
+      </c>
+      <c r="AU152">
+        <v>8</v>
+      </c>
+      <c r="AV152">
+        <v>3</v>
+      </c>
+      <c r="AW152">
+        <v>7</v>
+      </c>
+      <c r="AX152">
+        <v>5</v>
+      </c>
+      <c r="AY152">
+        <v>20</v>
+      </c>
+      <c r="AZ152">
+        <v>8</v>
+      </c>
+      <c r="BA152">
+        <v>5</v>
+      </c>
+      <c r="BB152">
+        <v>7</v>
+      </c>
+      <c r="BC152">
+        <v>12</v>
+      </c>
+      <c r="BD152">
+        <v>2.55</v>
+      </c>
+      <c r="BE152">
+        <v>6.25</v>
+      </c>
+      <c r="BF152">
+        <v>1.63</v>
+      </c>
+      <c r="BG152">
+        <v>1.46</v>
+      </c>
+      <c r="BH152">
+        <v>2.45</v>
+      </c>
+      <c r="BI152">
+        <v>1.85</v>
+      </c>
+      <c r="BJ152">
+        <v>1.85</v>
+      </c>
+      <c r="BK152">
+        <v>2.4</v>
+      </c>
+      <c r="BL152">
+        <v>1.48</v>
+      </c>
+      <c r="BM152">
+        <v>3.28</v>
+      </c>
+      <c r="BN152">
+        <v>1.25</v>
+      </c>
+      <c r="BO152">
+        <v>4.1</v>
+      </c>
+      <c r="BP152">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7537439</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45697.64583333334</v>
+      </c>
+      <c r="F153">
+        <v>22</v>
+      </c>
+      <c r="G153" t="s">
+        <v>75</v>
+      </c>
+      <c r="H153" t="s">
+        <v>78</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>2</v>
+      </c>
+      <c r="L153">
+        <v>5</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>5</v>
+      </c>
+      <c r="O153" t="s">
+        <v>175</v>
+      </c>
+      <c r="P153" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q153">
+        <v>1.5</v>
+      </c>
+      <c r="R153">
+        <v>3</v>
+      </c>
+      <c r="S153">
+        <v>15</v>
+      </c>
+      <c r="T153">
+        <v>1.25</v>
+      </c>
+      <c r="U153">
+        <v>3.75</v>
+      </c>
+      <c r="V153">
+        <v>2.2</v>
+      </c>
+      <c r="W153">
+        <v>1.62</v>
+      </c>
+      <c r="X153">
+        <v>5</v>
+      </c>
+      <c r="Y153">
+        <v>1.17</v>
+      </c>
+      <c r="Z153">
+        <v>1.12</v>
+      </c>
+      <c r="AA153">
+        <v>8</v>
+      </c>
+      <c r="AB153">
+        <v>15</v>
+      </c>
+      <c r="AC153">
+        <v>1.01</v>
+      </c>
+      <c r="AD153">
+        <v>17</v>
+      </c>
+      <c r="AE153">
+        <v>1.15</v>
+      </c>
+      <c r="AF153">
+        <v>5.4</v>
+      </c>
+      <c r="AG153">
+        <v>1.56</v>
+      </c>
+      <c r="AH153">
+        <v>2.22</v>
+      </c>
+      <c r="AI153">
+        <v>2.5</v>
+      </c>
+      <c r="AJ153">
+        <v>1.5</v>
+      </c>
+      <c r="AK153">
+        <v>1.03</v>
+      </c>
+      <c r="AL153">
+        <v>1.09</v>
+      </c>
+      <c r="AM153">
+        <v>5.6</v>
+      </c>
+      <c r="AN153">
+        <v>2.4</v>
+      </c>
+      <c r="AO153">
+        <v>0.9</v>
+      </c>
+      <c r="AP153">
+        <v>2.45</v>
+      </c>
+      <c r="AQ153">
+        <v>0.82</v>
+      </c>
+      <c r="AR153">
+        <v>2.03</v>
+      </c>
+      <c r="AS153">
+        <v>1.3</v>
+      </c>
+      <c r="AT153">
+        <v>3.33</v>
+      </c>
+      <c r="AU153">
+        <v>12</v>
+      </c>
+      <c r="AV153">
+        <v>5</v>
+      </c>
+      <c r="AW153">
+        <v>20</v>
+      </c>
+      <c r="AX153">
+        <v>6</v>
+      </c>
+      <c r="AY153">
+        <v>38</v>
+      </c>
+      <c r="AZ153">
+        <v>14</v>
+      </c>
+      <c r="BA153">
+        <v>10</v>
+      </c>
+      <c r="BB153">
+        <v>1</v>
+      </c>
+      <c r="BC153">
+        <v>11</v>
+      </c>
+      <c r="BD153">
+        <v>1.08</v>
+      </c>
+      <c r="BE153">
+        <v>11.5</v>
+      </c>
+      <c r="BF153">
+        <v>8</v>
+      </c>
+      <c r="BG153">
+        <v>1.4</v>
+      </c>
+      <c r="BH153">
+        <v>2.64</v>
+      </c>
+      <c r="BI153">
+        <v>1.74</v>
+      </c>
+      <c r="BJ153">
+        <v>1.98</v>
+      </c>
+      <c r="BK153">
+        <v>2.21</v>
+      </c>
+      <c r="BL153">
+        <v>1.56</v>
+      </c>
+      <c r="BM153">
+        <v>2.97</v>
+      </c>
+      <c r="BN153">
+        <v>1.3</v>
+      </c>
+      <c r="BO153">
+        <v>3.1</v>
+      </c>
+      <c r="BP153">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="251">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -762,6 +762,12 @@
   <si>
     <t>['2', '8', '30', '58', '67']</t>
   </si>
+  <si>
+    <t>['9', '45']</t>
+  </si>
+  <si>
+    <t>['4', '16']</t>
+  </si>
 </sst>
 </file>
 
@@ -1122,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1871,7 +1877,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2280,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ6">
         <v>1.27</v>
@@ -3931,7 +3937,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4137,7 +4143,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4340,7 +4346,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ16">
         <v>2.09</v>
@@ -5370,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ21">
         <v>2.36</v>
@@ -5782,10 +5788,10 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR23">
         <v>0.92</v>
@@ -6197,7 +6203,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ25">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>0.98</v>
@@ -8254,7 +8260,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ35">
         <v>0.55</v>
@@ -8669,7 +8675,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
         <v>1.17</v>
@@ -8875,7 +8881,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9902,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ43">
         <v>0.82</v>
@@ -10108,7 +10114,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ44">
         <v>1.45</v>
@@ -11756,7 +11762,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ52">
         <v>1.45</v>
@@ -11962,7 +11968,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ53">
         <v>1.45</v>
@@ -12171,7 +12177,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ54">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>2.03</v>
@@ -12583,7 +12589,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR56">
         <v>1.14</v>
@@ -14849,7 +14855,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ67">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -15258,7 +15264,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ69">
         <v>1.73</v>
@@ -15464,7 +15470,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ70">
         <v>2.36</v>
@@ -16497,7 +16503,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR75">
         <v>1.19</v>
@@ -17524,7 +17530,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ80">
         <v>1.36</v>
@@ -18554,10 +18560,10 @@
         <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ85">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR85">
         <v>1.32</v>
@@ -19793,7 +19799,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -21232,7 +21238,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ98">
         <v>1.45</v>
@@ -21441,7 +21447,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ99">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -21644,7 +21650,7 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ100">
         <v>1.73</v>
@@ -21850,7 +21856,7 @@
         <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ101">
         <v>1.36</v>
@@ -23501,7 +23507,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ109">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR109">
         <v>1.74</v>
@@ -23913,7 +23919,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ111">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR111">
         <v>1.89</v>
@@ -25352,7 +25358,7 @@
         <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ118">
         <v>1.45</v>
@@ -26382,7 +26388,7 @@
         <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ123">
         <v>1.82</v>
@@ -26797,7 +26803,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ125">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR125">
         <v>1.95</v>
@@ -27209,7 +27215,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ127">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27618,7 +27624,7 @@
         <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ129">
         <v>2.09</v>
@@ -29063,7 +29069,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR136">
         <v>1.4</v>
@@ -29678,7 +29684,7 @@
         <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ139">
         <v>1.27</v>
@@ -29887,7 +29893,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ140">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.7</v>
@@ -32641,6 +32647,418 @@
       </c>
       <c r="BP153">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7537441</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45698.54166666666</v>
+      </c>
+      <c r="F154">
+        <v>22</v>
+      </c>
+      <c r="G154" t="s">
+        <v>74</v>
+      </c>
+      <c r="H154" t="s">
+        <v>83</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>2</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>2</v>
+      </c>
+      <c r="N154">
+        <v>3</v>
+      </c>
+      <c r="O154" t="s">
+        <v>147</v>
+      </c>
+      <c r="P154" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q154">
+        <v>2.63</v>
+      </c>
+      <c r="R154">
+        <v>1.95</v>
+      </c>
+      <c r="S154">
+        <v>5.5</v>
+      </c>
+      <c r="T154">
+        <v>1.57</v>
+      </c>
+      <c r="U154">
+        <v>2.25</v>
+      </c>
+      <c r="V154">
+        <v>3.75</v>
+      </c>
+      <c r="W154">
+        <v>1.25</v>
+      </c>
+      <c r="X154">
+        <v>13</v>
+      </c>
+      <c r="Y154">
+        <v>1.04</v>
+      </c>
+      <c r="Z154">
+        <v>1.87</v>
+      </c>
+      <c r="AA154">
+        <v>3.1</v>
+      </c>
+      <c r="AB154">
+        <v>4.4</v>
+      </c>
+      <c r="AC154">
+        <v>1.11</v>
+      </c>
+      <c r="AD154">
+        <v>6.6</v>
+      </c>
+      <c r="AE154">
+        <v>1.55</v>
+      </c>
+      <c r="AF154">
+        <v>2.3</v>
+      </c>
+      <c r="AG154">
+        <v>2.3</v>
+      </c>
+      <c r="AH154">
+        <v>1.5</v>
+      </c>
+      <c r="AI154">
+        <v>2.25</v>
+      </c>
+      <c r="AJ154">
+        <v>1.57</v>
+      </c>
+      <c r="AK154">
+        <v>1.22</v>
+      </c>
+      <c r="AL154">
+        <v>1.38</v>
+      </c>
+      <c r="AM154">
+        <v>1.88</v>
+      </c>
+      <c r="AN154">
+        <v>0.8</v>
+      </c>
+      <c r="AO154">
+        <v>0.5</v>
+      </c>
+      <c r="AP154">
+        <v>0.73</v>
+      </c>
+      <c r="AQ154">
+        <v>0.73</v>
+      </c>
+      <c r="AR154">
+        <v>1.19</v>
+      </c>
+      <c r="AS154">
+        <v>0.9</v>
+      </c>
+      <c r="AT154">
+        <v>2.09</v>
+      </c>
+      <c r="AU154">
+        <v>6</v>
+      </c>
+      <c r="AV154">
+        <v>6</v>
+      </c>
+      <c r="AW154">
+        <v>10</v>
+      </c>
+      <c r="AX154">
+        <v>7</v>
+      </c>
+      <c r="AY154">
+        <v>20</v>
+      </c>
+      <c r="AZ154">
+        <v>15</v>
+      </c>
+      <c r="BA154">
+        <v>10</v>
+      </c>
+      <c r="BB154">
+        <v>6</v>
+      </c>
+      <c r="BC154">
+        <v>16</v>
+      </c>
+      <c r="BD154">
+        <v>1.57</v>
+      </c>
+      <c r="BE154">
+        <v>6.4</v>
+      </c>
+      <c r="BF154">
+        <v>2.65</v>
+      </c>
+      <c r="BG154">
+        <v>1.5</v>
+      </c>
+      <c r="BH154">
+        <v>2.23</v>
+      </c>
+      <c r="BI154">
+        <v>1.86</v>
+      </c>
+      <c r="BJ154">
+        <v>1.74</v>
+      </c>
+      <c r="BK154">
+        <v>2.4</v>
+      </c>
+      <c r="BL154">
+        <v>1.44</v>
+      </c>
+      <c r="BM154">
+        <v>3.2</v>
+      </c>
+      <c r="BN154">
+        <v>1.26</v>
+      </c>
+      <c r="BO154">
+        <v>4.25</v>
+      </c>
+      <c r="BP154">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7537445</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45698.54166666666</v>
+      </c>
+      <c r="F155">
+        <v>22</v>
+      </c>
+      <c r="G155" t="s">
+        <v>81</v>
+      </c>
+      <c r="H155" t="s">
+        <v>72</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>2</v>
+      </c>
+      <c r="O155" t="s">
+        <v>84</v>
+      </c>
+      <c r="P155" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q155">
+        <v>4</v>
+      </c>
+      <c r="R155">
+        <v>1.91</v>
+      </c>
+      <c r="S155">
+        <v>3.25</v>
+      </c>
+      <c r="T155">
+        <v>1.62</v>
+      </c>
+      <c r="U155">
+        <v>2.2</v>
+      </c>
+      <c r="V155">
+        <v>4</v>
+      </c>
+      <c r="W155">
+        <v>1.22</v>
+      </c>
+      <c r="X155">
+        <v>13</v>
+      </c>
+      <c r="Y155">
+        <v>1.04</v>
+      </c>
+      <c r="Z155">
+        <v>3.25</v>
+      </c>
+      <c r="AA155">
+        <v>2.88</v>
+      </c>
+      <c r="AB155">
+        <v>2.3</v>
+      </c>
+      <c r="AC155">
+        <v>1.12</v>
+      </c>
+      <c r="AD155">
+        <v>6.4</v>
+      </c>
+      <c r="AE155">
+        <v>1.5</v>
+      </c>
+      <c r="AF155">
+        <v>2.3</v>
+      </c>
+      <c r="AG155">
+        <v>2.33</v>
+      </c>
+      <c r="AH155">
+        <v>1.5</v>
+      </c>
+      <c r="AI155">
+        <v>2.2</v>
+      </c>
+      <c r="AJ155">
+        <v>1.62</v>
+      </c>
+      <c r="AK155">
+        <v>1.59</v>
+      </c>
+      <c r="AL155">
+        <v>1.41</v>
+      </c>
+      <c r="AM155">
+        <v>1.35</v>
+      </c>
+      <c r="AN155">
+        <v>0.3</v>
+      </c>
+      <c r="AO155">
+        <v>0.8</v>
+      </c>
+      <c r="AP155">
+        <v>0.27</v>
+      </c>
+      <c r="AQ155">
+        <v>1</v>
+      </c>
+      <c r="AR155">
+        <v>1.07</v>
+      </c>
+      <c r="AS155">
+        <v>1.06</v>
+      </c>
+      <c r="AT155">
+        <v>2.13</v>
+      </c>
+      <c r="AU155">
+        <v>3</v>
+      </c>
+      <c r="AV155">
+        <v>6</v>
+      </c>
+      <c r="AW155">
+        <v>15</v>
+      </c>
+      <c r="AX155">
+        <v>3</v>
+      </c>
+      <c r="AY155">
+        <v>24</v>
+      </c>
+      <c r="AZ155">
+        <v>10</v>
+      </c>
+      <c r="BA155">
+        <v>9</v>
+      </c>
+      <c r="BB155">
+        <v>5</v>
+      </c>
+      <c r="BC155">
+        <v>14</v>
+      </c>
+      <c r="BD155">
+        <v>2.46</v>
+      </c>
+      <c r="BE155">
+        <v>8.1</v>
+      </c>
+      <c r="BF155">
+        <v>1.8</v>
+      </c>
+      <c r="BG155">
+        <v>1.37</v>
+      </c>
+      <c r="BH155">
+        <v>2.75</v>
+      </c>
+      <c r="BI155">
+        <v>1.69</v>
+      </c>
+      <c r="BJ155">
+        <v>2.04</v>
+      </c>
+      <c r="BK155">
+        <v>2.14</v>
+      </c>
+      <c r="BL155">
+        <v>1.6</v>
+      </c>
+      <c r="BM155">
+        <v>2.83</v>
+      </c>
+      <c r="BN155">
+        <v>1.33</v>
+      </c>
+      <c r="BO155">
+        <v>4.3</v>
+      </c>
+      <c r="BP155">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ2">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1874,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ8">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2901,22 +2901,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3110,19 +3110,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3316,10 +3316,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ11">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3516,25 +3516,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ12">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3728,19 +3728,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AT13">
-        <v>1.83</v>
+        <v>3.09</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3931,22 +3931,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AT14">
-        <v>1.21</v>
+        <v>2.59</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4134,25 +4134,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ15">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>0.36</v>
+        <v>2.07</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4340,25 +4340,25 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ16">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS16">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AT16">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4546,25 +4546,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ17">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS17">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AT17">
-        <v>1.15</v>
+        <v>3.02</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4758,19 +4758,19 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AS18">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT18">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -4958,25 +4958,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ19">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR19">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT19">
-        <v>1.38</v>
+        <v>3.42</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5164,25 +5164,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ20">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR20">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AS20">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="AT20">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5373,22 +5373,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT21">
-        <v>1.23</v>
+        <v>3.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5576,25 +5576,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5782,25 +5782,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO23">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP23">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ23">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR23">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="AS23">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="AT23">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -5988,25 +5988,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP24">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ24">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR24">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="AS24">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT24">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6197,22 +6197,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR25">
-        <v>0.98</v>
+        <v>1.23</v>
       </c>
       <c r="AS25">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AT25">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6403,22 +6403,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ26">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR26">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AS26">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="AT26">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6609,22 +6609,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ27">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR27">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AS27">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AT27">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6812,25 +6812,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP28">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ28">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR28">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT28">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -7018,25 +7018,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ29">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR29">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AS29">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AT29">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7224,25 +7224,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP30">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ30">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR30">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AT30">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7430,25 +7430,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO31">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP31">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ31">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR31">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS31">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AT31">
-        <v>3.01</v>
+        <v>3.32</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7636,25 +7636,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ32">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR32">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AT32">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7845,22 +7845,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR33">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AS33">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="AT33">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8048,25 +8048,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP34">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ34">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS34">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8254,25 +8254,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP35">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ35">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS35">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="AT35">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8460,25 +8460,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP36">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ36">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR36">
-        <v>2.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS36">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AT36">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8666,25 +8666,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AO37">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP37">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ37">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR37">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="AT37">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8872,25 +8872,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR38">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AS38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT38">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9078,25 +9078,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ39">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR39">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="AS39">
-        <v>0.68</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9287,22 +9287,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ40">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AS40">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AT40">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9490,25 +9490,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AO41">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP41">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR41">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT41">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9696,25 +9696,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ42">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR42">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS42">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AT42">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9902,25 +9902,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ43">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR43">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="AS43">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AT43">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10111,22 +10111,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR44">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS44">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AT44">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10317,22 +10317,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ45">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR45">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AS45">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AT45">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10520,25 +10520,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO46">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP46">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ46">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR46">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS46">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="AT46">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10726,25 +10726,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR47">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AS47">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="AT47">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10932,25 +10932,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO48">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ48">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR48">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="AS48">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AT48">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11141,22 +11141,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP49">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ49">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS49">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AT49">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11344,25 +11344,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP50">
+        <v>1.95</v>
+      </c>
+      <c r="AQ50">
         <v>2.18</v>
       </c>
-      <c r="AQ50">
-        <v>2.09</v>
-      </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AS50">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AT50">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11550,25 +11550,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AO51">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ51">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR51">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AS51">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11756,25 +11756,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO52">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP52">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ52">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR52">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS52">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AT52">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11962,25 +11962,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AO53">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP53">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ53">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR53">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS53">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT53">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12168,25 +12168,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP54">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR54">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AS54">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT54">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12374,25 +12374,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO55">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ55">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR55">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="AS55">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AT55">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12580,25 +12580,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AP56">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ56">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR56">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AS56">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AT56">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12786,25 +12786,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AP57">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ57">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR57">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AS57">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AT57">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -12995,22 +12995,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="AP58">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ58">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR58">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AS58">
-        <v>0.8100000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="AT58">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13198,25 +13198,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP59">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ59">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR59">
+        <v>0.93</v>
+      </c>
+      <c r="AS59">
         <v>0.99</v>
       </c>
-      <c r="AS59">
-        <v>0.88</v>
-      </c>
       <c r="AT59">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13404,25 +13404,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="AO60">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AP60">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR60">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS60">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AT60">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13610,25 +13610,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO61">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AP61">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ61">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR61">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AS61">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AT61">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13816,25 +13816,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO62">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP62">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ62">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR62">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AS62">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT62">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14022,25 +14022,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO63">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP63">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AS63">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="AT63">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14228,25 +14228,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AO64">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP64">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ64">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR64">
-        <v>1.31</v>
+        <v>0.96</v>
       </c>
       <c r="AS64">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AT64">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14434,25 +14434,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO65">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AP65">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ65">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR65">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AS65">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT65">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14640,25 +14640,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO66">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP66">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ66">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR66">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AS66">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AT66">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14846,22 +14846,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO67">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR67">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS67">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15052,25 +15052,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="AO68">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP68">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ68">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR68">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS68">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT68">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15258,25 +15258,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR69">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS69">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AT69">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15464,25 +15464,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AO70">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP70">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ70">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR70">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AS70">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AT70">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15670,25 +15670,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AO71">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AP71">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ71">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR71">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS71">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT71">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15876,25 +15876,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO72">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AP72">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ72">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR72">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AS72">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AT72">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16085,22 +16085,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AP73">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ73">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR73">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS73">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT73">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16288,25 +16288,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO74">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP74">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ74">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR74">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AS74">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AT74">
-        <v>2.69</v>
+        <v>3.01</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16494,25 +16494,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
+        <v>1.23</v>
+      </c>
+      <c r="AQ75">
+        <v>0.82</v>
+      </c>
+      <c r="AR75">
         <v>1.09</v>
       </c>
-      <c r="AQ75">
-        <v>0.73</v>
-      </c>
-      <c r="AR75">
-        <v>1.19</v>
-      </c>
       <c r="AS75">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AT75">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16703,22 +16703,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR76">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AS76">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AT76">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16909,22 +16909,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP77">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ77">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR77">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AS77">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT77">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17112,25 +17112,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO78">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AP78">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ78">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR78">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AT78">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17318,25 +17318,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP79">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ79">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR79">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT79">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17524,25 +17524,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AO80">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AP80">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ80">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR80">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AS80">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT80">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17730,25 +17730,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AO81">
-        <v>1.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP81">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ81">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR81">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AS81">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT81">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17936,25 +17936,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AO82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AP82">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ82">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR82">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AS82">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18142,25 +18142,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO83">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AP83">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ83">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR83">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AS83">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AT83">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18348,25 +18348,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO84">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AP84">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ84">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR84">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS84">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AT84">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18554,25 +18554,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>0.67</v>
+        <v>1.27</v>
       </c>
       <c r="AO85">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AP85">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR85">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS85">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT85">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18760,25 +18760,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
       <c r="AO86">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ86">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR86">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AS86">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AT86">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -18966,25 +18966,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO87">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ87">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR87">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AS87">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="AT87">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19172,25 +19172,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO88">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ88">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR88">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AS88">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AT88">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19378,25 +19378,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO89">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP89">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ89">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR89">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS89">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT89">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19584,25 +19584,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO90">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ90">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR90">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS90">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AT90">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19790,25 +19790,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.17</v>
+        <v>1.92</v>
       </c>
       <c r="AO91">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ91">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR91">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AS91">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="AT91">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19999,22 +19999,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AP92">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ92">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR92">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS92">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT92">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20202,25 +20202,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AO93">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AP93">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR93">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AS93">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="AT93">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20408,25 +20408,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AO94">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ94">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR94">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AS94">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT94">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20614,25 +20614,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO95">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AP95">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR95">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS95">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AT95">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20820,25 +20820,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO96">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AP96">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ96">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR96">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AT96">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21026,25 +21026,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO97">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AP97">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ97">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR97">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS97">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT97">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21232,25 +21232,25 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO98">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP98">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ98">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR98">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AS98">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT98">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21438,25 +21438,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="AP99">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR99">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AT99">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21644,25 +21644,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="AO100">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AP100">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ100">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR100">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AS100">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AT100">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21850,25 +21850,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO101">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AP101">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR101">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AS101">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT101">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22056,25 +22056,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="AO102">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ102">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR102">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AS102">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT102">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22262,25 +22262,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="AO103">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP103">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ103">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR103">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS103">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT103">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22468,25 +22468,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO104">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP104">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ104">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR104">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AS104">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AT104">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22674,25 +22674,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AO105">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ105">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR105">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AS105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AT105">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22880,25 +22880,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AO106">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AP106">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ106">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR106">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AS106">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AT106">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23086,25 +23086,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AO107">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ107">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR107">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AS107">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT107">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23292,25 +23292,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO108">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR108">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AS108">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
       <c r="AT108">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23498,25 +23498,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AO109">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="AP109">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ109">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR109">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AS109">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT109">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23704,25 +23704,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO110">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AP110">
+        <v>1.82</v>
+      </c>
+      <c r="AQ110">
         <v>1.27</v>
       </c>
-      <c r="AQ110">
-        <v>1.82</v>
-      </c>
       <c r="AR110">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT110">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23910,25 +23910,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AO111">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP111">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR111">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AS111">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT111">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24116,25 +24116,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ112">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR112">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT112">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24322,25 +24322,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO113">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AP113">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ113">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR113">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AS113">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="AT113">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24528,25 +24528,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO114">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP114">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ114">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR114">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AS114">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="AT114">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24737,22 +24737,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AP115">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ115">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR115">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT115">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24940,25 +24940,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AO116">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP116">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ116">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR116">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS116">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT116">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25146,25 +25146,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO117">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AP117">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ117">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR117">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AS117">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AT117">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25352,25 +25352,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AO118">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AP118">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ118">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR118">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS118">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT118">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25558,25 +25558,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO119">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AP119">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ119">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR119">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25764,25 +25764,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AO120">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP120">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ120">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR120">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AS120">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AT120">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -25970,25 +25970,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AP121">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ121">
+        <v>1.68</v>
+      </c>
+      <c r="AR121">
+        <v>1.87</v>
+      </c>
+      <c r="AS121">
         <v>1.27</v>
       </c>
-      <c r="AR121">
-        <v>1.96</v>
-      </c>
-      <c r="AS121">
-        <v>1.1</v>
-      </c>
       <c r="AT121">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26179,22 +26179,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AP122">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR122">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AS122">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AT122">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26382,25 +26382,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AO123">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AP123">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ123">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR123">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AS123">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AT123">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26588,25 +26588,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AO124">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ124">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR124">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS124">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="AT124">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26794,25 +26794,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO125">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AP125">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ125">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR125">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AS125">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AT125">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27000,25 +27000,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AO126">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP126">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ126">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR126">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AS126">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="AT126">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27206,25 +27206,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AO127">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP127">
+        <v>1.23</v>
+      </c>
+      <c r="AQ127">
+        <v>0.95</v>
+      </c>
+      <c r="AR127">
         <v>1.09</v>
       </c>
-      <c r="AQ127">
-        <v>1</v>
-      </c>
-      <c r="AR127">
-        <v>1.2</v>
-      </c>
       <c r="AS127">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AT127">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27412,25 +27412,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AO128">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="AP128">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ128">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR128">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AS128">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT128">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27618,25 +27618,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO129">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AP129">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR129">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AS129">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AT129">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27824,25 +27824,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
+        <v>1</v>
+      </c>
+      <c r="AO130">
+        <v>1.39</v>
+      </c>
+      <c r="AP130">
+        <v>0.95</v>
+      </c>
+      <c r="AQ130">
+        <v>1.59</v>
+      </c>
+      <c r="AR130">
         <v>1.11</v>
       </c>
-      <c r="AO130">
-        <v>1.33</v>
-      </c>
-      <c r="AP130">
-        <v>0.91</v>
-      </c>
-      <c r="AQ130">
-        <v>1.45</v>
-      </c>
-      <c r="AR130">
-        <v>1.17</v>
-      </c>
       <c r="AS130">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AT130">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -28030,25 +28030,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AO131">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AP131">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ131">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR131">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AS131">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AT131">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28236,25 +28236,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AP132">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ132">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR132">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS132">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT132">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28445,22 +28445,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AP133">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ133">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR133">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AS133">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AT133">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28651,22 +28651,22 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ134">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AT134">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28854,25 +28854,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AO135">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AP135">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ135">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR135">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AS135">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AT135">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29060,25 +29060,25 @@
         <v>1.86</v>
       </c>
       <c r="AN136">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AO136">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AP136">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ136">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR136">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS136">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AT136">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29266,25 +29266,25 @@
         <v>1.77</v>
       </c>
       <c r="AN137">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP137">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ137">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR137">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS137">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AT137">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29472,25 +29472,25 @@
         <v>4.6</v>
       </c>
       <c r="AN138">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AO138">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AP138">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ138">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR138">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AS138">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AT138">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU138">
         <v>5</v>
@@ -29678,25 +29678,25 @@
         <v>1.21</v>
       </c>
       <c r="AN139">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AO139">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AP139">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ139">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR139">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AS139">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AT139">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU139">
         <v>2</v>
@@ -29884,22 +29884,22 @@
         <v>3.6</v>
       </c>
       <c r="AN140">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AO140">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AP140">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR140">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AS140">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AT140">
         <v>2.75</v>
@@ -30090,25 +30090,25 @@
         <v>1.93</v>
       </c>
       <c r="AN141">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AO141">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AP141">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ141">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR141">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AS141">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AT141">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30296,25 +30296,25 @@
         <v>3.2</v>
       </c>
       <c r="AN142">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AO142">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AP142">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AQ142">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AR142">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS142">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT142">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AU142">
         <v>9</v>
@@ -30502,25 +30502,25 @@
         <v>1.53</v>
       </c>
       <c r="AN143">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AO143">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ143">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AR143">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS143">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="AT143">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="AU143">
         <v>5</v>
@@ -30708,25 +30708,25 @@
         <v>1.09</v>
       </c>
       <c r="AN144">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AO144">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP144">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AQ144">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AR144">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AS144">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AT144">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30914,25 +30914,25 @@
         <v>1.25</v>
       </c>
       <c r="AN145">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO145">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AP145">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AQ145">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR145">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="AS145">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AT145">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31120,25 +31120,25 @@
         <v>1.48</v>
       </c>
       <c r="AN146">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AO146">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AQ146">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AR146">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AS146">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AT146">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31329,22 +31329,22 @@
         <v>1.3</v>
       </c>
       <c r="AO147">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AP147">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AQ147">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AR147">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AS147">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AT147">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU147">
         <v>0</v>
@@ -31532,25 +31532,25 @@
         <v>2.28</v>
       </c>
       <c r="AN148">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AO148">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="AP148">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AQ148">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AR148">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AS148">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AT148">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31738,25 +31738,25 @@
         <v>1.61</v>
       </c>
       <c r="AN149">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO149">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AP149">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="AQ149">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR149">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AS149">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="AT149">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -31944,25 +31944,25 @@
         <v>1.17</v>
       </c>
       <c r="AN150">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AO150">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AP150">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AQ150">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AR150">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AS150">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AT150">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AU150">
         <v>3</v>
@@ -32150,25 +32150,25 @@
         <v>3.55</v>
       </c>
       <c r="AN151">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AO151">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AP151">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AQ151">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AR151">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AS151">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AT151">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32356,25 +32356,25 @@
         <v>1.26</v>
       </c>
       <c r="AN152">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO152">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AP152">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AQ152">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AR152">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS152">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AT152">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="AU152">
         <v>8</v>
@@ -32562,25 +32562,25 @@
         <v>5.6</v>
       </c>
       <c r="AN153">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AO153">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AP153">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR153">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AS153">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT153">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="AU153">
         <v>12</v>
@@ -32768,25 +32768,25 @@
         <v>1.88</v>
       </c>
       <c r="AN154">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="AO154">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP154">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AQ154">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR154">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AS154">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="AT154">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="AU154">
         <v>6</v>
@@ -32974,25 +32974,25 @@
         <v>1.35</v>
       </c>
       <c r="AN155">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="AO155">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AP155">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AR155">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AS155">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AT155">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AU155">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ2">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1874,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ4">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ5">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
+        <v>0.73</v>
+      </c>
+      <c r="AQ6">
         <v>1.27</v>
-      </c>
-      <c r="AQ6">
-        <v>1.68</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ7">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2901,22 +2901,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ9">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR9">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3110,19 +3110,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR10">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3316,10 +3316,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ11">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3516,25 +3516,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3728,19 +3728,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.09</v>
+        <v>1.83</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3931,22 +3931,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ14">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.59</v>
+        <v>1.21</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4134,25 +4134,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR15">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>2.07</v>
+        <v>0.36</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4340,25 +4340,25 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ16">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR16">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AT16">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4546,25 +4546,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR17">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AT17">
-        <v>3.02</v>
+        <v>1.15</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4758,19 +4758,19 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR18">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AT18">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -4958,25 +4958,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ19">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR19">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS19">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>3.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5164,25 +5164,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ20">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR20">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AS20">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
       <c r="AT20">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5373,22 +5373,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ21">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR21">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS21">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>3.23</v>
+        <v>1.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5576,25 +5576,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5782,25 +5782,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ23">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR23">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AS23">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="AT23">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -5988,25 +5988,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR24">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="AS24">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT24">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6197,22 +6197,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR25">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="AS25">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AT25">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6403,22 +6403,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ26">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR26">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AS26">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="AT26">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6609,22 +6609,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27">
+        <v>1.73</v>
+      </c>
+      <c r="AR27">
         <v>1.95</v>
       </c>
-      <c r="AR27">
-        <v>1.67</v>
-      </c>
       <c r="AS27">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AT27">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6812,25 +6812,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ28">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AS28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT28">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -7018,25 +7018,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ29">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR29">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AS29">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="AT29">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7224,25 +7224,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ30">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR30">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="AS30">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7430,25 +7430,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ31">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR31">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS31">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AT31">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7636,25 +7636,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS32">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AT32">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7845,22 +7845,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ33">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="AS33">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="AT33">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8048,25 +8048,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO34">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR34">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS34">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AT34">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8254,25 +8254,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO35">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ35">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS35">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="AT35">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8460,25 +8460,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ36">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR36">
-        <v>1.16</v>
+        <v>2.14</v>
       </c>
       <c r="AS36">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AT36">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8666,25 +8666,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AO37">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ37">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AS37">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="AT37">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8872,25 +8872,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR38">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AS38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT38">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9078,25 +9078,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ39">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR39">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
       <c r="AT39">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9287,22 +9287,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ40">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR40">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AS40">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT40">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9490,25 +9490,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AO41">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS41">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT41">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9696,25 +9696,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ42">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR42">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AS42">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AT42">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9902,25 +9902,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO43">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR43">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="AS43">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10111,22 +10111,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ44">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR44">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS44">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AT44">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10317,22 +10317,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ45">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR45">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AS45">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AT45">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10520,25 +10520,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO46">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ46">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR46">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS46">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT46">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10726,25 +10726,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR47">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AS47">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="AT47">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10932,25 +10932,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO48">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ48">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR48">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="AS48">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AT48">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11141,22 +11141,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AP49">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ49">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR49">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AS49">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT49">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11344,25 +11344,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO50">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ50">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR50">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AT50">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11550,25 +11550,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AO51">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR51">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AS51">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT51">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11756,25 +11756,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ52">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR52">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS52">
-        <v>1.1</v>
+        <v>0.84</v>
       </c>
       <c r="AT52">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11962,25 +11962,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AO53">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ53">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR53">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AS53">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT53">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12168,25 +12168,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO54">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ54">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR54">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AS54">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT54">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12374,25 +12374,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ55">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR55">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="AS55">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AT55">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12580,25 +12580,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO56">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR56">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS56">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AT56">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12786,25 +12786,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO57">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ57">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR57">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS57">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AT57">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -12995,22 +12995,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ58">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR58">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AS58">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT58">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13198,25 +13198,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO59">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ59">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR59">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AS59">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="AT59">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13404,25 +13404,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="AO60">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ60">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR60">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS60">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AT60">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13610,25 +13610,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>1.25</v>
+        <v>0.33</v>
       </c>
       <c r="AO61">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR61">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AS61">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AT61">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13816,25 +13816,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ62">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR62">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AS62">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT62">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14022,25 +14022,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO63">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ63">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14228,25 +14228,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ64">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR64">
-        <v>0.96</v>
+        <v>1.31</v>
       </c>
       <c r="AS64">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AT64">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14434,25 +14434,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO65">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR65">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AS65">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AT65">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14640,25 +14640,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO66">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ66">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR66">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AS66">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AT66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14846,22 +14846,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ67">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR67">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS67">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15052,25 +15052,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="AO68">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ68">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR68">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS68">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AT68">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15258,25 +15258,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="AO69">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ69">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS69">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AT69">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15464,25 +15464,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="AO70">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ70">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR70">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AS70">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AT70">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15670,25 +15670,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ71">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR71">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AS71">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT71">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15876,25 +15876,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO72">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ72">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AS72">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AT72">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16085,22 +16085,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ73">
+        <v>1.82</v>
+      </c>
+      <c r="AR73">
+        <v>1.13</v>
+      </c>
+      <c r="AS73">
         <v>1.27</v>
       </c>
-      <c r="AR73">
-        <v>1.23</v>
-      </c>
-      <c r="AS73">
-        <v>1.3</v>
-      </c>
       <c r="AT73">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16288,25 +16288,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
+        <v>2.2</v>
+      </c>
+      <c r="AO74">
         <v>1.8</v>
       </c>
-      <c r="AO74">
-        <v>1.6</v>
-      </c>
       <c r="AP74">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ74">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR74">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AS74">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AT74">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16494,25 +16494,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ75">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR75">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AS75">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AT75">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16703,22 +16703,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ76">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR76">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AS76">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AT76">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16909,22 +16909,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ77">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR77">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AS77">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AT77">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17112,25 +17112,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO78">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ78">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AS78">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT78">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17318,25 +17318,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AO79">
+        <v>1</v>
+      </c>
+      <c r="AP79">
         <v>0.91</v>
       </c>
-      <c r="AP79">
+      <c r="AQ79">
         <v>0.82</v>
       </c>
-      <c r="AQ79">
-        <v>1</v>
-      </c>
       <c r="AR79">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS79">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17524,25 +17524,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="AO80">
+        <v>1.67</v>
+      </c>
+      <c r="AP80">
+        <v>0.27</v>
+      </c>
+      <c r="AQ80">
         <v>1.36</v>
       </c>
-      <c r="AP80">
-        <v>0.41</v>
-      </c>
-      <c r="AQ80">
-        <v>1.23</v>
-      </c>
       <c r="AR80">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AS80">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT80">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17730,25 +17730,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AO81">
-        <v>0.91</v>
+        <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ81">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR81">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS81">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT81">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17936,25 +17936,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AO82">
+        <v>1.6</v>
+      </c>
+      <c r="AP82">
+        <v>1.18</v>
+      </c>
+      <c r="AQ82">
         <v>1.73</v>
       </c>
-      <c r="AP82">
-        <v>1.32</v>
-      </c>
-      <c r="AQ82">
-        <v>1.95</v>
-      </c>
       <c r="AR82">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AT82">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18142,25 +18142,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO83">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ83">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR83">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AS83">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AT83">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18348,25 +18348,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AO84">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ84">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR84">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AS84">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AT84">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18554,25 +18554,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>1.27</v>
+        <v>0.67</v>
       </c>
       <c r="AO85">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ85">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR85">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS85">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT85">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18760,25 +18760,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>1.08</v>
+        <v>0.17</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ86">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR86">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AS86">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AT86">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -18966,25 +18966,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ87">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR87">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AS87">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="AT87">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19172,25 +19172,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO88">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ88">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR88">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AS88">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AT88">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19378,25 +19378,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AO89">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR89">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS89">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT89">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19584,25 +19584,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ90">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR90">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS90">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AT90">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19790,25 +19790,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO91">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR91">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AS91">
-        <v>1.22</v>
+        <v>0.95</v>
       </c>
       <c r="AT91">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19999,22 +19999,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ92">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR92">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS92">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AT92">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20202,25 +20202,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AO93">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ93">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AS93">
-        <v>1.19</v>
+        <v>0.96</v>
       </c>
       <c r="AT93">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20408,25 +20408,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AO94">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR94">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AS94">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT94">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20614,25 +20614,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO95">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ95">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR95">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS95">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AT95">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20820,25 +20820,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ96">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR96">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS96">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AT96">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21026,25 +21026,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO97">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR97">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AS97">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT97">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21232,25 +21232,25 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AO98">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ98">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR98">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT98">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21438,25 +21438,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AO99">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ99">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AS99">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AT99">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21644,25 +21644,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="AO100">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ100">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS100">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AT100">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21850,25 +21850,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO101">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ101">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AS101">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT101">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22056,25 +22056,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>1</v>
+        <v>0.29</v>
       </c>
       <c r="AO102">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ102">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR102">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AS102">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT102">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22262,25 +22262,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="AO103">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR103">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS103">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT103">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22468,25 +22468,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO104">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP104">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ104">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR104">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AS104">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT104">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22674,25 +22674,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AO105">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR105">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AS105">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AT105">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22880,25 +22880,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="AO106">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ106">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR106">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AS106">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AT106">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23086,25 +23086,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AO107">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ107">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR107">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AS107">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AT107">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23292,25 +23292,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO108">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR108">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AS108">
-        <v>1.07</v>
+        <v>0.89</v>
       </c>
       <c r="AT108">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23498,25 +23498,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AO109">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ109">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR109">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AS109">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT109">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23704,25 +23704,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO110">
+        <v>1.57</v>
+      </c>
+      <c r="AP110">
         <v>1.27</v>
       </c>
-      <c r="AP110">
+      <c r="AQ110">
         <v>1.82</v>
       </c>
-      <c r="AQ110">
-        <v>1.27</v>
-      </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AS110">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT110">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23910,25 +23910,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AO111">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ111">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR111">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AS111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24116,25 +24116,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO112">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AS112">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AT112">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24322,25 +24322,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
+        <v>0.71</v>
+      </c>
+      <c r="AO113">
+        <v>1.71</v>
+      </c>
+      <c r="AP113">
+        <v>1.09</v>
+      </c>
+      <c r="AQ113">
+        <v>1.45</v>
+      </c>
+      <c r="AR113">
         <v>1.13</v>
       </c>
-      <c r="AO113">
-        <v>1.13</v>
-      </c>
-      <c r="AP113">
-        <v>1.23</v>
-      </c>
-      <c r="AQ113">
-        <v>0.95</v>
-      </c>
-      <c r="AR113">
-        <v>1.07</v>
-      </c>
       <c r="AS113">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="AT113">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24528,25 +24528,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO114">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ114">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR114">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AS114">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="AT114">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24737,22 +24737,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR115">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS115">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24940,25 +24940,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="AO116">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ116">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR116">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS116">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AT116">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25146,25 +25146,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>1.06</v>
+        <v>0.63</v>
       </c>
       <c r="AO117">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ117">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR117">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AS117">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AT117">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25352,25 +25352,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AO118">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ118">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR118">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT118">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25558,25 +25558,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO119">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ119">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR119">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25764,25 +25764,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AO120">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ120">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AS120">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AT120">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -25970,25 +25970,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AO121">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ121">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR121">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AS121">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AT121">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26179,22 +26179,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR122">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AS122">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AT122">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26382,25 +26382,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="AO123">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ123">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR123">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AS123">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AT123">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26588,25 +26588,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AO124">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ124">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR124">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS124">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="AT124">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26794,25 +26794,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO125">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ125">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR125">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AS125">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AT125">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27000,25 +27000,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AO126">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ126">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR126">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS126">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT126">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27206,25 +27206,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ127">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR127">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AS127">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AT127">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27412,25 +27412,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AO128">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ128">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR128">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AS128">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT128">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27618,25 +27618,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO129">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ129">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR129">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AS129">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AT129">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27824,25 +27824,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO130">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ130">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR130">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AS130">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AT130">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -28030,25 +28030,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AO131">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ131">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR131">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AS131">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AT131">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28236,25 +28236,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="AO132">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ132">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR132">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS132">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AT132">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28445,22 +28445,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ133">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR133">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AS133">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT133">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28651,22 +28651,22 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ134">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT134">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28854,25 +28854,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO135">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="AQ135">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR135">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AS135">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AT135">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29060,25 +29060,25 @@
         <v>1.86</v>
       </c>
       <c r="AN136">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AO136">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP136">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ136">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR136">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS136">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="AT136">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29266,25 +29266,25 @@
         <v>1.77</v>
       </c>
       <c r="AN137">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AO137">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS137">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AT137">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29472,25 +29472,25 @@
         <v>4.6</v>
       </c>
       <c r="AN138">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AO138">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ138">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR138">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AS138">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="AT138">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU138">
         <v>5</v>
@@ -29678,25 +29678,25 @@
         <v>1.21</v>
       </c>
       <c r="AN139">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AO139">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ139">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR139">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AS139">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AT139">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU139">
         <v>2</v>
@@ -29884,22 +29884,22 @@
         <v>3.6</v>
       </c>
       <c r="AN140">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AO140">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ140">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR140">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AS140">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AT140">
         <v>2.75</v>
@@ -30090,25 +30090,25 @@
         <v>1.93</v>
       </c>
       <c r="AN141">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AO141">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ141">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR141">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AS141">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AT141">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30296,25 +30296,25 @@
         <v>3.2</v>
       </c>
       <c r="AN142">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AO142">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AP142">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AQ142">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR142">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS142">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT142">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AU142">
         <v>9</v>
@@ -30502,25 +30502,25 @@
         <v>1.53</v>
       </c>
       <c r="AN143">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AO143">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP143">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ143">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AR143">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS143">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="AT143">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AU143">
         <v>5</v>
@@ -30708,25 +30708,25 @@
         <v>1.09</v>
       </c>
       <c r="AN144">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AO144">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP144">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ144">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AR144">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AS144">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AT144">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30914,25 +30914,25 @@
         <v>1.25</v>
       </c>
       <c r="AN145">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO145">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="AP145">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ145">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AR145">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AS145">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AT145">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31120,25 +31120,25 @@
         <v>1.48</v>
       </c>
       <c r="AN146">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AO146">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP146">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AQ146">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AR146">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AS146">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AT146">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31329,22 +31329,22 @@
         <v>1.3</v>
       </c>
       <c r="AO147">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AP147">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AQ147">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AR147">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AS147">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AT147">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU147">
         <v>0</v>
@@ -31532,25 +31532,25 @@
         <v>2.28</v>
       </c>
       <c r="AN148">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AO148">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AP148">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AQ148">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AR148">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AS148">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AT148">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31738,25 +31738,25 @@
         <v>1.61</v>
       </c>
       <c r="AN149">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO149">
+        <v>1.3</v>
+      </c>
+      <c r="AP149">
+        <v>0.45</v>
+      </c>
+      <c r="AQ149">
+        <v>1.45</v>
+      </c>
+      <c r="AR149">
         <v>1.24</v>
       </c>
-      <c r="AP149">
-        <v>0.95</v>
-      </c>
-      <c r="AQ149">
-        <v>1.32</v>
-      </c>
-      <c r="AR149">
-        <v>1.14</v>
-      </c>
       <c r="AS149">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="AT149">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -31944,25 +31944,25 @@
         <v>1.17</v>
       </c>
       <c r="AN150">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AO150">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AP150">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AQ150">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR150">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AS150">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AT150">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AU150">
         <v>3</v>
@@ -32150,25 +32150,25 @@
         <v>3.55</v>
       </c>
       <c r="AN151">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AO151">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AQ151">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR151">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AS151">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AT151">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32356,25 +32356,25 @@
         <v>1.26</v>
       </c>
       <c r="AN152">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO152">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AP152">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AQ152">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AR152">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AS152">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AT152">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="AU152">
         <v>8</v>
@@ -32562,25 +32562,25 @@
         <v>5.6</v>
       </c>
       <c r="AN153">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AO153">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AP153">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR153">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AS153">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT153">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="AU153">
         <v>12</v>
@@ -32768,25 +32768,25 @@
         <v>1.88</v>
       </c>
       <c r="AN154">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="AO154">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>1.27</v>
+        <v>0.73</v>
       </c>
       <c r="AQ154">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR154">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AS154">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="AT154">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="AU154">
         <v>6</v>
@@ -32974,25 +32974,25 @@
         <v>1.35</v>
       </c>
       <c r="AN155">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="AO155">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="AQ155">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AR155">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AS155">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT155">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AU155">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="254">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -544,6 +544,12 @@
     <t>['8', '23', '73', '81', '84']</t>
   </si>
   <si>
+    <t>['59', '90+2']</t>
+  </si>
+  <si>
+    <t>['32', '90+4']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -767,6 +773,9 @@
   </si>
   <si>
     <t>['4', '16']</t>
+  </si>
+  <si>
+    <t>['10']</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1384,7 +1393,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1590,7 +1599,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2083,7 +2092,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2208,7 +2217,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2492,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7">
         <v>1.36</v>
@@ -2620,7 +2629,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2904,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3032,7 +3041,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3238,7 +3247,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3316,7 +3325,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
         <v>0.55</v>
@@ -3444,7 +3453,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -4062,7 +4071,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4268,7 +4277,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4474,7 +4483,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4555,7 +4564,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ17">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4886,7 +4895,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5092,7 +5101,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5298,7 +5307,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5504,7 +5513,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5916,7 +5925,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5997,7 +6006,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ24">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR24">
         <v>2.26</v>
@@ -6122,7 +6131,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6740,7 +6749,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6818,7 +6827,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
         <v>1.27</v>
@@ -7024,7 +7033,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ29">
         <v>1.45</v>
@@ -7152,7 +7161,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7564,7 +7573,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7645,7 +7654,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ32">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -7976,7 +7985,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8182,7 +8191,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8800,7 +8809,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9006,7 +9015,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9084,7 +9093,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ39">
         <v>1.45</v>
@@ -9293,7 +9302,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ40">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
         <v>2.09</v>
@@ -9702,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ42">
         <v>1.73</v>
@@ -9830,7 +9839,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10036,7 +10045,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10654,7 +10663,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10860,7 +10869,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10941,7 +10950,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ48">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11066,7 +11075,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11684,7 +11693,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11971,7 +11980,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ53">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12096,7 +12105,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12302,7 +12311,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12380,7 +12389,7 @@
         <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ55">
         <v>1.73</v>
@@ -12714,7 +12723,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12792,7 +12801,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57">
         <v>2.36</v>
@@ -12920,7 +12929,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13126,7 +13135,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13744,7 +13753,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13950,7 +13959,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14156,7 +14165,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14237,7 +14246,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ64">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR64">
         <v>1.31</v>
@@ -14774,7 +14783,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15186,7 +15195,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15392,7 +15401,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -16010,7 +16019,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16091,7 +16100,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR73">
         <v>1.13</v>
@@ -16294,10 +16303,10 @@
         <v>1.8</v>
       </c>
       <c r="AP74">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ74">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR74">
         <v>1.64</v>
@@ -16422,7 +16431,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16500,7 +16509,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75">
         <v>0.73</v>
@@ -16628,7 +16637,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17040,7 +17049,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17246,7 +17255,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17452,7 +17461,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17864,7 +17873,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18070,7 +18079,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18482,7 +18491,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18894,7 +18903,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19178,7 +19187,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ88">
         <v>1.27</v>
@@ -19387,7 +19396,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
         <v>1.12</v>
@@ -19512,7 +19521,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19590,7 +19599,7 @@
         <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ90">
         <v>2.09</v>
@@ -19718,7 +19727,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19924,7 +19933,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20005,7 +20014,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ92">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR92">
         <v>1.7</v>
@@ -20336,7 +20345,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20417,7 +20426,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20542,7 +20551,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20748,7 +20757,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20826,7 +20835,7 @@
         <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
         <v>1.73</v>
@@ -21160,7 +21169,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21366,7 +21375,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21984,7 +21993,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22065,7 +22074,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ102">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -22396,7 +22405,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -23713,7 +23722,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ110">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR110">
         <v>1.66</v>
@@ -23838,7 +23847,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23916,7 +23925,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ111">
         <v>1</v>
@@ -24044,7 +24053,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24328,7 +24337,7 @@
         <v>1.71</v>
       </c>
       <c r="AP113">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ113">
         <v>1.45</v>
@@ -24868,7 +24877,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25074,7 +25083,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25280,7 +25289,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25361,7 +25370,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ118">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR118">
         <v>1.32</v>
@@ -25486,7 +25495,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25692,7 +25701,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26104,7 +26113,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26310,7 +26319,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26391,7 +26400,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ123">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR123">
         <v>1.09</v>
@@ -26516,7 +26525,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26800,7 +26809,7 @@
         <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ125">
         <v>0.73</v>
@@ -27212,7 +27221,7 @@
         <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27546,7 +27555,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27752,7 +27761,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27833,7 +27842,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ130">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR130">
         <v>1.17</v>
@@ -28782,7 +28791,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -28863,7 +28872,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ135">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR135">
         <v>1.26</v>
@@ -29194,7 +29203,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29272,7 +29281,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137">
         <v>0.82</v>
@@ -29478,7 +29487,7 @@
         <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ138">
         <v>1.45</v>
@@ -29606,7 +29615,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -30224,7 +30233,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30430,7 +30439,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -31048,7 +31057,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31335,7 +31344,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ147">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31872,7 +31881,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -31950,7 +31959,7 @@
         <v>2.3</v>
       </c>
       <c r="AP150">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ150">
         <v>2.36</v>
@@ -32078,7 +32087,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32159,7 +32168,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ151">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.88</v>
@@ -32568,7 +32577,7 @@
         <v>0.9</v>
       </c>
       <c r="AP153">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ153">
         <v>0.82</v>
@@ -32696,7 +32705,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32902,7 +32911,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33059,6 +33068,418 @@
       </c>
       <c r="BP155">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7537448</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F156">
+        <v>23</v>
+      </c>
+      <c r="G156" t="s">
+        <v>77</v>
+      </c>
+      <c r="H156" t="s">
+        <v>79</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>2</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>3</v>
+      </c>
+      <c r="O156" t="s">
+        <v>176</v>
+      </c>
+      <c r="P156" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q156">
+        <v>3.2</v>
+      </c>
+      <c r="R156">
+        <v>2</v>
+      </c>
+      <c r="S156">
+        <v>3.75</v>
+      </c>
+      <c r="T156">
+        <v>1.5</v>
+      </c>
+      <c r="U156">
+        <v>2.5</v>
+      </c>
+      <c r="V156">
+        <v>3.4</v>
+      </c>
+      <c r="W156">
+        <v>1.3</v>
+      </c>
+      <c r="X156">
+        <v>10</v>
+      </c>
+      <c r="Y156">
+        <v>1.06</v>
+      </c>
+      <c r="Z156">
+        <v>2.4</v>
+      </c>
+      <c r="AA156">
+        <v>3.1</v>
+      </c>
+      <c r="AB156">
+        <v>2.8</v>
+      </c>
+      <c r="AC156">
+        <v>1.08</v>
+      </c>
+      <c r="AD156">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE156">
+        <v>1.4</v>
+      </c>
+      <c r="AF156">
+        <v>2.85</v>
+      </c>
+      <c r="AG156">
+        <v>2.25</v>
+      </c>
+      <c r="AH156">
+        <v>1.53</v>
+      </c>
+      <c r="AI156">
+        <v>1.95</v>
+      </c>
+      <c r="AJ156">
+        <v>1.8</v>
+      </c>
+      <c r="AK156">
+        <v>1.4</v>
+      </c>
+      <c r="AL156">
+        <v>1.38</v>
+      </c>
+      <c r="AM156">
+        <v>1.57</v>
+      </c>
+      <c r="AN156">
+        <v>1.09</v>
+      </c>
+      <c r="AO156">
+        <v>1.45</v>
+      </c>
+      <c r="AP156">
+        <v>1.25</v>
+      </c>
+      <c r="AQ156">
+        <v>1.33</v>
+      </c>
+      <c r="AR156">
+        <v>1.37</v>
+      </c>
+      <c r="AS156">
+        <v>1.07</v>
+      </c>
+      <c r="AT156">
+        <v>2.44</v>
+      </c>
+      <c r="AU156">
+        <v>6</v>
+      </c>
+      <c r="AV156">
+        <v>3</v>
+      </c>
+      <c r="AW156">
+        <v>13</v>
+      </c>
+      <c r="AX156">
+        <v>2</v>
+      </c>
+      <c r="AY156">
+        <v>22</v>
+      </c>
+      <c r="AZ156">
+        <v>5</v>
+      </c>
+      <c r="BA156">
+        <v>4</v>
+      </c>
+      <c r="BB156">
+        <v>4</v>
+      </c>
+      <c r="BC156">
+        <v>8</v>
+      </c>
+      <c r="BD156">
+        <v>2.05</v>
+      </c>
+      <c r="BE156">
+        <v>5.6</v>
+      </c>
+      <c r="BF156">
+        <v>2.15</v>
+      </c>
+      <c r="BG156">
+        <v>1.46</v>
+      </c>
+      <c r="BH156">
+        <v>2.52</v>
+      </c>
+      <c r="BI156">
+        <v>1.8</v>
+      </c>
+      <c r="BJ156">
+        <v>2</v>
+      </c>
+      <c r="BK156">
+        <v>2.31</v>
+      </c>
+      <c r="BL156">
+        <v>1.57</v>
+      </c>
+      <c r="BM156">
+        <v>2.98</v>
+      </c>
+      <c r="BN156">
+        <v>1.34</v>
+      </c>
+      <c r="BO156">
+        <v>4.15</v>
+      </c>
+      <c r="BP156">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7537446</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45703.625</v>
+      </c>
+      <c r="F157">
+        <v>23</v>
+      </c>
+      <c r="G157" t="s">
+        <v>75</v>
+      </c>
+      <c r="H157" t="s">
+        <v>74</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>2</v>
+      </c>
+      <c r="L157">
+        <v>2</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>177</v>
+      </c>
+      <c r="P157" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q157">
+        <v>1.73</v>
+      </c>
+      <c r="R157">
+        <v>2.4</v>
+      </c>
+      <c r="S157">
+        <v>11</v>
+      </c>
+      <c r="T157">
+        <v>1.36</v>
+      </c>
+      <c r="U157">
+        <v>3</v>
+      </c>
+      <c r="V157">
+        <v>2.75</v>
+      </c>
+      <c r="W157">
+        <v>1.4</v>
+      </c>
+      <c r="X157">
+        <v>8</v>
+      </c>
+      <c r="Y157">
+        <v>1.08</v>
+      </c>
+      <c r="Z157">
+        <v>1.22</v>
+      </c>
+      <c r="AA157">
+        <v>5.25</v>
+      </c>
+      <c r="AB157">
+        <v>11</v>
+      </c>
+      <c r="AC157">
+        <v>1.05</v>
+      </c>
+      <c r="AD157">
+        <v>12</v>
+      </c>
+      <c r="AE157">
+        <v>1.29</v>
+      </c>
+      <c r="AF157">
+        <v>3.55</v>
+      </c>
+      <c r="AG157">
+        <v>1.65</v>
+      </c>
+      <c r="AH157">
+        <v>2</v>
+      </c>
+      <c r="AI157">
+        <v>2.63</v>
+      </c>
+      <c r="AJ157">
+        <v>1.44</v>
+      </c>
+      <c r="AK157">
+        <v>1.06</v>
+      </c>
+      <c r="AL157">
+        <v>1.17</v>
+      </c>
+      <c r="AM157">
+        <v>3.7</v>
+      </c>
+      <c r="AN157">
+        <v>2.45</v>
+      </c>
+      <c r="AO157">
+        <v>1.82</v>
+      </c>
+      <c r="AP157">
+        <v>2.5</v>
+      </c>
+      <c r="AQ157">
+        <v>1.67</v>
+      </c>
+      <c r="AR157">
+        <v>2.15</v>
+      </c>
+      <c r="AS157">
+        <v>1.17</v>
+      </c>
+      <c r="AT157">
+        <v>3.32</v>
+      </c>
+      <c r="AU157">
+        <v>5</v>
+      </c>
+      <c r="AV157">
+        <v>7</v>
+      </c>
+      <c r="AW157">
+        <v>18</v>
+      </c>
+      <c r="AX157">
+        <v>4</v>
+      </c>
+      <c r="AY157">
+        <v>27</v>
+      </c>
+      <c r="AZ157">
+        <v>12</v>
+      </c>
+      <c r="BA157">
+        <v>6</v>
+      </c>
+      <c r="BB157">
+        <v>0</v>
+      </c>
+      <c r="BC157">
+        <v>6</v>
+      </c>
+      <c r="BD157">
+        <v>1.26</v>
+      </c>
+      <c r="BE157">
+        <v>7.5</v>
+      </c>
+      <c r="BF157">
+        <v>4.35</v>
+      </c>
+      <c r="BG157">
+        <v>1.5</v>
+      </c>
+      <c r="BH157">
+        <v>2.25</v>
+      </c>
+      <c r="BI157">
+        <v>1.8</v>
+      </c>
+      <c r="BJ157">
+        <v>2</v>
+      </c>
+      <c r="BK157">
+        <v>2.38</v>
+      </c>
+      <c r="BL157">
+        <v>1.45</v>
+      </c>
+      <c r="BM157">
+        <v>3.1</v>
+      </c>
+      <c r="BN157">
+        <v>1.27</v>
+      </c>
+      <c r="BO157">
+        <v>4.1</v>
+      </c>
+      <c r="BP157">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="261">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -550,6 +550,18 @@
     <t>['32', '90+4']</t>
   </si>
   <si>
+    <t>['21', '51', '54', '79']</t>
+  </si>
+  <si>
+    <t>['20', '55']</t>
+  </si>
+  <si>
+    <t>['25', '37', '51', '58', '72', '86', '90+2']</t>
+  </si>
+  <si>
+    <t>['85', '90+8']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -776,6 +788,15 @@
   </si>
   <si>
     <t>['10']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['20', '27', '53', '75']</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1393,7 +1414,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1474,7 +1495,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ2">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1599,7 +1620,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1677,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
         <v>0.82</v>
@@ -1883,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2089,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5">
         <v>1.33</v>
@@ -2217,7 +2238,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2298,7 +2319,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ6">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2629,7 +2650,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2707,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3041,7 +3062,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3119,10 +3140,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3247,7 +3268,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3328,7 +3349,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ11">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3453,7 +3474,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3534,7 +3555,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3737,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13">
         <v>1.45</v>
@@ -3943,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4071,7 +4092,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4152,7 +4173,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ15">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4277,7 +4298,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4358,7 +4379,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ16">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4483,7 +4504,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4767,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
         <v>0.82</v>
@@ -4895,7 +4916,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -4973,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
         <v>1.73</v>
@@ -5101,7 +5122,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5307,7 +5328,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5513,7 +5534,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5800,7 +5821,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ23">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR23">
         <v>0.92</v>
@@ -5925,7 +5946,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6131,7 +6152,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6209,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6621,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ27">
         <v>1.73</v>
@@ -6749,7 +6770,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6830,7 +6851,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
         <v>1</v>
@@ -7036,7 +7057,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ29">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7161,7 +7182,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7448,7 +7469,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ31">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR31">
         <v>1.29</v>
@@ -7573,7 +7594,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7651,7 +7672,7 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
         <v>1.33</v>
@@ -7857,7 +7878,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
         <v>1.36</v>
@@ -7985,7 +8006,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8063,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ34">
         <v>0.82</v>
@@ -8191,7 +8212,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8272,7 +8293,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ35">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -8684,7 +8705,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ37">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR37">
         <v>1.17</v>
@@ -8809,7 +8830,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9015,7 +9036,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9505,10 +9526,10 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR41">
         <v>1.71</v>
@@ -9839,7 +9860,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10045,7 +10066,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10126,7 +10147,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ44">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10329,7 +10350,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
         <v>1.73</v>
@@ -10538,7 +10559,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ46">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR46">
         <v>1.16</v>
@@ -10663,7 +10684,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10741,7 +10762,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ47">
         <v>1.36</v>
@@ -10869,7 +10890,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11075,7 +11096,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11153,7 +11174,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ49">
         <v>2.36</v>
@@ -11359,10 +11380,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ50">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR50">
         <v>1.74</v>
@@ -11693,7 +11714,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12105,7 +12126,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12311,7 +12332,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12598,7 +12619,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ56">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR56">
         <v>1.14</v>
@@ -12723,7 +12744,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12929,7 +12950,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13007,10 +13028,10 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13135,7 +13156,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13213,10 +13234,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13419,7 +13440,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ60">
         <v>1.73</v>
@@ -13628,7 +13649,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR61">
         <v>1.69</v>
@@ -13753,7 +13774,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13831,10 +13852,10 @@
         <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
         <v>1.7</v>
@@ -13959,7 +13980,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14037,7 +14058,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ63">
         <v>1.36</v>
@@ -14165,7 +14186,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14783,7 +14804,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15195,7 +15216,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15401,7 +15422,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15891,10 +15912,10 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
         <v>1.28</v>
@@ -16019,7 +16040,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16097,7 +16118,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73">
         <v>1.67</v>
@@ -16431,7 +16452,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16512,7 +16533,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ75">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR75">
         <v>1.19</v>
@@ -16637,7 +16658,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16715,10 +16736,10 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -16921,10 +16942,10 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ77">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR77">
         <v>1.69</v>
@@ -17049,7 +17070,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17127,10 +17148,10 @@
         <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ78">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR78">
         <v>1.72</v>
@@ -17255,7 +17276,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17461,7 +17482,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17748,7 +17769,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ81">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17873,7 +17894,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -17951,7 +17972,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ82">
         <v>1.73</v>
@@ -18079,7 +18100,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18491,7 +18512,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18778,7 +18799,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ86">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR86">
         <v>1.38</v>
@@ -18903,7 +18924,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -18981,7 +19002,7 @@
         <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ87">
         <v>1.45</v>
@@ -19190,7 +19211,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ88">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR88">
         <v>1.86</v>
@@ -19393,7 +19414,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ89">
         <v>1.33</v>
@@ -19521,7 +19542,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19602,7 +19623,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ90">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19727,7 +19748,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19805,10 +19826,10 @@
         <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19933,7 +19954,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20011,7 +20032,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ92">
         <v>1.67</v>
@@ -20220,7 +20241,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -20345,7 +20366,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20551,7 +20572,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20629,7 +20650,7 @@
         <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
         <v>2.36</v>
@@ -20757,7 +20778,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21169,7 +21190,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21375,7 +21396,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21993,7 +22014,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22405,7 +22426,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22483,7 +22504,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ104">
         <v>1.73</v>
@@ -22689,7 +22710,7 @@
         <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105">
         <v>2.36</v>
@@ -22898,7 +22919,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ106">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -23104,7 +23125,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ107">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.96</v>
@@ -23307,7 +23328,7 @@
         <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>1.45</v>
@@ -23513,10 +23534,10 @@
         <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ109">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR109">
         <v>1.74</v>
@@ -23719,7 +23740,7 @@
         <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
         <v>1.67</v>
@@ -23847,7 +23868,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24053,7 +24074,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24134,7 +24155,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ112">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR112">
         <v>1.43</v>
@@ -24340,7 +24361,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ113">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -24546,7 +24567,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ114">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR114">
         <v>1.39</v>
@@ -24749,7 +24770,7 @@
         <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ115">
         <v>0.82</v>
@@ -24877,7 +24898,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25083,7 +25104,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25289,7 +25310,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25495,7 +25516,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25573,7 +25594,7 @@
         <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ119">
         <v>2.36</v>
@@ -25701,7 +25722,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25779,10 +25800,10 @@
         <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR120">
         <v>1.23</v>
@@ -25988,7 +26009,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ121">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR121">
         <v>1.96</v>
@@ -26113,7 +26134,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26191,7 +26212,7 @@
         <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
         <v>1.73</v>
@@ -26319,7 +26340,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26525,7 +26546,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26603,10 +26624,10 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ124">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -26812,7 +26833,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ125">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR125">
         <v>1.95</v>
@@ -27430,7 +27451,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ128">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR128">
         <v>1.37</v>
@@ -27555,7 +27576,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27636,7 +27657,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ129">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR129">
         <v>1.26</v>
@@ -27761,7 +27782,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27839,7 +27860,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ130">
         <v>1.33</v>
@@ -28045,7 +28066,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ131">
         <v>1.36</v>
@@ -28457,7 +28478,7 @@
         <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ133">
         <v>1.73</v>
@@ -28663,10 +28684,10 @@
         <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ134">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
@@ -28791,7 +28812,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29078,7 +29099,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ136">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
         <v>1.4</v>
@@ -29203,7 +29224,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29615,7 +29636,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29696,7 +29717,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ139">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR139">
         <v>1.11</v>
@@ -29899,7 +29920,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30233,7 +30254,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30311,7 +30332,7 @@
         <v>1.5</v>
       </c>
       <c r="AP142">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ142">
         <v>1.36</v>
@@ -30439,7 +30460,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30517,10 +30538,10 @@
         <v>1.5</v>
       </c>
       <c r="AP143">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ143">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR143">
         <v>1.33</v>
@@ -30723,10 +30744,10 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ144">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR144">
         <v>1.16</v>
@@ -30932,7 +30953,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ145">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31057,7 +31078,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31135,7 +31156,7 @@
         <v>1.6</v>
       </c>
       <c r="AP146">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ146">
         <v>1.73</v>
@@ -31341,7 +31362,7 @@
         <v>1.7</v>
       </c>
       <c r="AP147">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
         <v>1.67</v>
@@ -31550,7 +31571,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ148">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR148">
         <v>1.44</v>
@@ -31881,7 +31902,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32087,7 +32108,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32705,7 +32726,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32786,7 +32807,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ154">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR154">
         <v>1.19</v>
@@ -32911,7 +32932,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33323,7 +33344,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33480,6 +33501,1036 @@
       </c>
       <c r="BP157">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7537447</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F158">
+        <v>23</v>
+      </c>
+      <c r="G158" t="s">
+        <v>72</v>
+      </c>
+      <c r="H158" t="s">
+        <v>82</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>2</v>
+      </c>
+      <c r="L158">
+        <v>4</v>
+      </c>
+      <c r="M158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>5</v>
+      </c>
+      <c r="O158" t="s">
+        <v>178</v>
+      </c>
+      <c r="P158" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q158">
+        <v>4.33</v>
+      </c>
+      <c r="R158">
+        <v>1.91</v>
+      </c>
+      <c r="S158">
+        <v>3.1</v>
+      </c>
+      <c r="T158">
+        <v>1.57</v>
+      </c>
+      <c r="U158">
+        <v>2.25</v>
+      </c>
+      <c r="V158">
+        <v>3.75</v>
+      </c>
+      <c r="W158">
+        <v>1.25</v>
+      </c>
+      <c r="X158">
+        <v>13</v>
+      </c>
+      <c r="Y158">
+        <v>1.04</v>
+      </c>
+      <c r="Z158">
+        <v>3.4</v>
+      </c>
+      <c r="AA158">
+        <v>2.9</v>
+      </c>
+      <c r="AB158">
+        <v>2.2</v>
+      </c>
+      <c r="AC158">
+        <v>1.11</v>
+      </c>
+      <c r="AD158">
+        <v>6.6</v>
+      </c>
+      <c r="AE158">
+        <v>1.5</v>
+      </c>
+      <c r="AF158">
+        <v>2.4</v>
+      </c>
+      <c r="AG158">
+        <v>2.25</v>
+      </c>
+      <c r="AH158">
+        <v>1.5</v>
+      </c>
+      <c r="AI158">
+        <v>2.2</v>
+      </c>
+      <c r="AJ158">
+        <v>1.62</v>
+      </c>
+      <c r="AK158">
+        <v>1.64</v>
+      </c>
+      <c r="AL158">
+        <v>1.4</v>
+      </c>
+      <c r="AM158">
+        <v>1.33</v>
+      </c>
+      <c r="AN158">
+        <v>0.91</v>
+      </c>
+      <c r="AO158">
+        <v>1.27</v>
+      </c>
+      <c r="AP158">
+        <v>1.08</v>
+      </c>
+      <c r="AQ158">
+        <v>1.17</v>
+      </c>
+      <c r="AR158">
+        <v>1.13</v>
+      </c>
+      <c r="AS158">
+        <v>1.18</v>
+      </c>
+      <c r="AT158">
+        <v>2.31</v>
+      </c>
+      <c r="AU158">
+        <v>6</v>
+      </c>
+      <c r="AV158">
+        <v>3</v>
+      </c>
+      <c r="AW158">
+        <v>7</v>
+      </c>
+      <c r="AX158">
+        <v>7</v>
+      </c>
+      <c r="AY158">
+        <v>17</v>
+      </c>
+      <c r="AZ158">
+        <v>12</v>
+      </c>
+      <c r="BA158">
+        <v>6</v>
+      </c>
+      <c r="BB158">
+        <v>3</v>
+      </c>
+      <c r="BC158">
+        <v>9</v>
+      </c>
+      <c r="BD158">
+        <v>2.23</v>
+      </c>
+      <c r="BE158">
+        <v>6.1</v>
+      </c>
+      <c r="BF158">
+        <v>1.82</v>
+      </c>
+      <c r="BG158">
+        <v>1.52</v>
+      </c>
+      <c r="BH158">
+        <v>2.2</v>
+      </c>
+      <c r="BI158">
+        <v>1.82</v>
+      </c>
+      <c r="BJ158">
+        <v>1.98</v>
+      </c>
+      <c r="BK158">
+        <v>2.45</v>
+      </c>
+      <c r="BL158">
+        <v>1.42</v>
+      </c>
+      <c r="BM158">
+        <v>3.3</v>
+      </c>
+      <c r="BN158">
+        <v>1.24</v>
+      </c>
+      <c r="BO158">
+        <v>4.4</v>
+      </c>
+      <c r="BP158">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7537450</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45704.5</v>
+      </c>
+      <c r="F159">
+        <v>23</v>
+      </c>
+      <c r="G159" t="s">
+        <v>73</v>
+      </c>
+      <c r="H159" t="s">
+        <v>70</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159">
+        <v>2</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>3</v>
+      </c>
+      <c r="O159" t="s">
+        <v>179</v>
+      </c>
+      <c r="P159" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q159">
+        <v>1.73</v>
+      </c>
+      <c r="R159">
+        <v>2.5</v>
+      </c>
+      <c r="S159">
+        <v>11</v>
+      </c>
+      <c r="T159">
+        <v>1.36</v>
+      </c>
+      <c r="U159">
+        <v>3</v>
+      </c>
+      <c r="V159">
+        <v>2.63</v>
+      </c>
+      <c r="W159">
+        <v>1.44</v>
+      </c>
+      <c r="X159">
+        <v>7</v>
+      </c>
+      <c r="Y159">
+        <v>1.1</v>
+      </c>
+      <c r="Z159">
+        <v>1.25</v>
+      </c>
+      <c r="AA159">
+        <v>5.5</v>
+      </c>
+      <c r="AB159">
+        <v>10</v>
+      </c>
+      <c r="AC159">
+        <v>1.05</v>
+      </c>
+      <c r="AD159">
+        <v>12</v>
+      </c>
+      <c r="AE159">
+        <v>1.28</v>
+      </c>
+      <c r="AF159">
+        <v>3.6</v>
+      </c>
+      <c r="AG159">
+        <v>1.67</v>
+      </c>
+      <c r="AH159">
+        <v>2</v>
+      </c>
+      <c r="AI159">
+        <v>2.63</v>
+      </c>
+      <c r="AJ159">
+        <v>1.44</v>
+      </c>
+      <c r="AK159">
+        <v>1.05</v>
+      </c>
+      <c r="AL159">
+        <v>1.16</v>
+      </c>
+      <c r="AM159">
+        <v>3.9</v>
+      </c>
+      <c r="AN159">
+        <v>2.18</v>
+      </c>
+      <c r="AO159">
+        <v>1.45</v>
+      </c>
+      <c r="AP159">
+        <v>2.25</v>
+      </c>
+      <c r="AQ159">
+        <v>1.33</v>
+      </c>
+      <c r="AR159">
+        <v>1.89</v>
+      </c>
+      <c r="AS159">
+        <v>1.04</v>
+      </c>
+      <c r="AT159">
+        <v>2.93</v>
+      </c>
+      <c r="AU159">
+        <v>8</v>
+      </c>
+      <c r="AV159">
+        <v>3</v>
+      </c>
+      <c r="AW159">
+        <v>13</v>
+      </c>
+      <c r="AX159">
+        <v>4</v>
+      </c>
+      <c r="AY159">
+        <v>25</v>
+      </c>
+      <c r="AZ159">
+        <v>8</v>
+      </c>
+      <c r="BA159">
+        <v>6</v>
+      </c>
+      <c r="BB159">
+        <v>3</v>
+      </c>
+      <c r="BC159">
+        <v>9</v>
+      </c>
+      <c r="BD159">
+        <v>1.23</v>
+      </c>
+      <c r="BE159">
+        <v>8</v>
+      </c>
+      <c r="BF159">
+        <v>4.6</v>
+      </c>
+      <c r="BG159">
+        <v>1.38</v>
+      </c>
+      <c r="BH159">
+        <v>2.6</v>
+      </c>
+      <c r="BI159">
+        <v>1.68</v>
+      </c>
+      <c r="BJ159">
+        <v>1.93</v>
+      </c>
+      <c r="BK159">
+        <v>2.1</v>
+      </c>
+      <c r="BL159">
+        <v>1.57</v>
+      </c>
+      <c r="BM159">
+        <v>2.7</v>
+      </c>
+      <c r="BN159">
+        <v>1.36</v>
+      </c>
+      <c r="BO159">
+        <v>3.45</v>
+      </c>
+      <c r="BP159">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7537452</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45704.5</v>
+      </c>
+      <c r="F160">
+        <v>23</v>
+      </c>
+      <c r="G160" t="s">
+        <v>78</v>
+      </c>
+      <c r="H160" t="s">
+        <v>80</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>2</v>
+      </c>
+      <c r="K160">
+        <v>2</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>4</v>
+      </c>
+      <c r="N160">
+        <v>4</v>
+      </c>
+      <c r="O160" t="s">
+        <v>84</v>
+      </c>
+      <c r="P160" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q160">
+        <v>13</v>
+      </c>
+      <c r="R160">
+        <v>2.6</v>
+      </c>
+      <c r="S160">
+        <v>1.62</v>
+      </c>
+      <c r="T160">
+        <v>1.33</v>
+      </c>
+      <c r="U160">
+        <v>3.25</v>
+      </c>
+      <c r="V160">
+        <v>2.5</v>
+      </c>
+      <c r="W160">
+        <v>1.5</v>
+      </c>
+      <c r="X160">
+        <v>6.5</v>
+      </c>
+      <c r="Y160">
+        <v>1.11</v>
+      </c>
+      <c r="Z160">
+        <v>14</v>
+      </c>
+      <c r="AA160">
+        <v>6</v>
+      </c>
+      <c r="AB160">
+        <v>1.18</v>
+      </c>
+      <c r="AC160">
+        <v>1.01</v>
+      </c>
+      <c r="AD160">
+        <v>13</v>
+      </c>
+      <c r="AE160">
+        <v>1.23</v>
+      </c>
+      <c r="AF160">
+        <v>4.2</v>
+      </c>
+      <c r="AG160">
+        <v>1.6</v>
+      </c>
+      <c r="AH160">
+        <v>2.1</v>
+      </c>
+      <c r="AI160">
+        <v>2.63</v>
+      </c>
+      <c r="AJ160">
+        <v>1.44</v>
+      </c>
+      <c r="AK160">
+        <v>4.6</v>
+      </c>
+      <c r="AL160">
+        <v>1.13</v>
+      </c>
+      <c r="AM160">
+        <v>1.04</v>
+      </c>
+      <c r="AN160">
+        <v>1.18</v>
+      </c>
+      <c r="AO160">
+        <v>2.09</v>
+      </c>
+      <c r="AP160">
+        <v>1.08</v>
+      </c>
+      <c r="AQ160">
+        <v>2.17</v>
+      </c>
+      <c r="AR160">
+        <v>1.33</v>
+      </c>
+      <c r="AS160">
+        <v>1.84</v>
+      </c>
+      <c r="AT160">
+        <v>3.17</v>
+      </c>
+      <c r="AU160">
+        <v>2</v>
+      </c>
+      <c r="AV160">
+        <v>10</v>
+      </c>
+      <c r="AW160">
+        <v>4</v>
+      </c>
+      <c r="AX160">
+        <v>8</v>
+      </c>
+      <c r="AY160">
+        <v>7</v>
+      </c>
+      <c r="AZ160">
+        <v>22</v>
+      </c>
+      <c r="BA160">
+        <v>0</v>
+      </c>
+      <c r="BB160">
+        <v>7</v>
+      </c>
+      <c r="BC160">
+        <v>7</v>
+      </c>
+      <c r="BD160">
+        <v>4.6</v>
+      </c>
+      <c r="BE160">
+        <v>7.5</v>
+      </c>
+      <c r="BF160">
+        <v>1.24</v>
+      </c>
+      <c r="BG160">
+        <v>1.54</v>
+      </c>
+      <c r="BH160">
+        <v>2.16</v>
+      </c>
+      <c r="BI160">
+        <v>1.95</v>
+      </c>
+      <c r="BJ160">
+        <v>1.85</v>
+      </c>
+      <c r="BK160">
+        <v>2.48</v>
+      </c>
+      <c r="BL160">
+        <v>1.41</v>
+      </c>
+      <c r="BM160">
+        <v>3.3</v>
+      </c>
+      <c r="BN160">
+        <v>1.24</v>
+      </c>
+      <c r="BO160">
+        <v>4.5</v>
+      </c>
+      <c r="BP160">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7537453</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45704.625</v>
+      </c>
+      <c r="F161">
+        <v>23</v>
+      </c>
+      <c r="G161" t="s">
+        <v>71</v>
+      </c>
+      <c r="H161" t="s">
+        <v>81</v>
+      </c>
+      <c r="I161">
+        <v>2</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>2</v>
+      </c>
+      <c r="L161">
+        <v>7</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>7</v>
+      </c>
+      <c r="O161" t="s">
+        <v>180</v>
+      </c>
+      <c r="P161" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q161">
+        <v>1.53</v>
+      </c>
+      <c r="R161">
+        <v>2.88</v>
+      </c>
+      <c r="S161">
+        <v>13</v>
+      </c>
+      <c r="T161">
+        <v>1.25</v>
+      </c>
+      <c r="U161">
+        <v>3.75</v>
+      </c>
+      <c r="V161">
+        <v>2.25</v>
+      </c>
+      <c r="W161">
+        <v>1.57</v>
+      </c>
+      <c r="X161">
+        <v>5.5</v>
+      </c>
+      <c r="Y161">
+        <v>1.14</v>
+      </c>
+      <c r="Z161">
+        <v>1.13</v>
+      </c>
+      <c r="AA161">
+        <v>7.5</v>
+      </c>
+      <c r="AB161">
+        <v>15</v>
+      </c>
+      <c r="AC161">
+        <v>1.01</v>
+      </c>
+      <c r="AD161">
+        <v>17</v>
+      </c>
+      <c r="AE161">
+        <v>1.18</v>
+      </c>
+      <c r="AF161">
+        <v>5</v>
+      </c>
+      <c r="AG161">
+        <v>1.52</v>
+      </c>
+      <c r="AH161">
+        <v>2.36</v>
+      </c>
+      <c r="AI161">
+        <v>2.5</v>
+      </c>
+      <c r="AJ161">
+        <v>1.5</v>
+      </c>
+      <c r="AK161">
+        <v>1.03</v>
+      </c>
+      <c r="AL161">
+        <v>1.1</v>
+      </c>
+      <c r="AM161">
+        <v>5.2</v>
+      </c>
+      <c r="AN161">
+        <v>1.27</v>
+      </c>
+      <c r="AO161">
+        <v>0.55</v>
+      </c>
+      <c r="AP161">
+        <v>1.42</v>
+      </c>
+      <c r="AQ161">
+        <v>0.5</v>
+      </c>
+      <c r="AR161">
+        <v>1.7</v>
+      </c>
+      <c r="AS161">
+        <v>0.98</v>
+      </c>
+      <c r="AT161">
+        <v>2.68</v>
+      </c>
+      <c r="AU161">
+        <v>12</v>
+      </c>
+      <c r="AV161">
+        <v>3</v>
+      </c>
+      <c r="AW161">
+        <v>6</v>
+      </c>
+      <c r="AX161">
+        <v>4</v>
+      </c>
+      <c r="AY161">
+        <v>20</v>
+      </c>
+      <c r="AZ161">
+        <v>8</v>
+      </c>
+      <c r="BA161">
+        <v>8</v>
+      </c>
+      <c r="BB161">
+        <v>3</v>
+      </c>
+      <c r="BC161">
+        <v>11</v>
+      </c>
+      <c r="BD161">
+        <v>1.05</v>
+      </c>
+      <c r="BE161">
+        <v>42</v>
+      </c>
+      <c r="BF161">
+        <v>55</v>
+      </c>
+      <c r="BG161">
+        <v>1.28</v>
+      </c>
+      <c r="BH161">
+        <v>3.08</v>
+      </c>
+      <c r="BI161">
+        <v>1.53</v>
+      </c>
+      <c r="BJ161">
+        <v>2.27</v>
+      </c>
+      <c r="BK161">
+        <v>1.94</v>
+      </c>
+      <c r="BL161">
+        <v>1.77</v>
+      </c>
+      <c r="BM161">
+        <v>2.51</v>
+      </c>
+      <c r="BN161">
+        <v>1.44</v>
+      </c>
+      <c r="BO161">
+        <v>3.34</v>
+      </c>
+      <c r="BP161">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7537451</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45704.64583333334</v>
+      </c>
+      <c r="F162">
+        <v>23</v>
+      </c>
+      <c r="G162" t="s">
+        <v>76</v>
+      </c>
+      <c r="H162" t="s">
+        <v>83</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>2</v>
+      </c>
+      <c r="O162" t="s">
+        <v>181</v>
+      </c>
+      <c r="P162" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q162">
+        <v>3.2</v>
+      </c>
+      <c r="R162">
+        <v>1.91</v>
+      </c>
+      <c r="S162">
+        <v>4.33</v>
+      </c>
+      <c r="T162">
+        <v>1.62</v>
+      </c>
+      <c r="U162">
+        <v>2.2</v>
+      </c>
+      <c r="V162">
+        <v>4</v>
+      </c>
+      <c r="W162">
+        <v>1.22</v>
+      </c>
+      <c r="X162">
+        <v>13</v>
+      </c>
+      <c r="Y162">
+        <v>1.04</v>
+      </c>
+      <c r="Z162">
+        <v>2.25</v>
+      </c>
+      <c r="AA162">
+        <v>3</v>
+      </c>
+      <c r="AB162">
+        <v>3.25</v>
+      </c>
+      <c r="AC162">
+        <v>1.12</v>
+      </c>
+      <c r="AD162">
+        <v>6.4</v>
+      </c>
+      <c r="AE162">
+        <v>1.55</v>
+      </c>
+      <c r="AF162">
+        <v>2.3</v>
+      </c>
+      <c r="AG162">
+        <v>2.37</v>
+      </c>
+      <c r="AH162">
+        <v>1.48</v>
+      </c>
+      <c r="AI162">
+        <v>2.2</v>
+      </c>
+      <c r="AJ162">
+        <v>1.62</v>
+      </c>
+      <c r="AK162">
+        <v>1.34</v>
+      </c>
+      <c r="AL162">
+        <v>1.41</v>
+      </c>
+      <c r="AM162">
+        <v>1.61</v>
+      </c>
+      <c r="AN162">
+        <v>1.18</v>
+      </c>
+      <c r="AO162">
+        <v>0.73</v>
+      </c>
+      <c r="AP162">
+        <v>1.33</v>
+      </c>
+      <c r="AQ162">
+        <v>0.67</v>
+      </c>
+      <c r="AR162">
+        <v>1.12</v>
+      </c>
+      <c r="AS162">
+        <v>0.95</v>
+      </c>
+      <c r="AT162">
+        <v>2.07</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>6</v>
+      </c>
+      <c r="AW162">
+        <v>9</v>
+      </c>
+      <c r="AX162">
+        <v>5</v>
+      </c>
+      <c r="AY162">
+        <v>14</v>
+      </c>
+      <c r="AZ162">
+        <v>12</v>
+      </c>
+      <c r="BA162">
+        <v>6</v>
+      </c>
+      <c r="BB162">
+        <v>3</v>
+      </c>
+      <c r="BC162">
+        <v>9</v>
+      </c>
+      <c r="BD162">
+        <v>1.79</v>
+      </c>
+      <c r="BE162">
+        <v>6.1</v>
+      </c>
+      <c r="BF162">
+        <v>2.3</v>
+      </c>
+      <c r="BG162">
+        <v>1.47</v>
+      </c>
+      <c r="BH162">
+        <v>2.42</v>
+      </c>
+      <c r="BI162">
+        <v>1.86</v>
+      </c>
+      <c r="BJ162">
+        <v>1.84</v>
+      </c>
+      <c r="BK162">
+        <v>2.42</v>
+      </c>
+      <c r="BL162">
+        <v>1.47</v>
+      </c>
+      <c r="BM162">
+        <v>3.34</v>
+      </c>
+      <c r="BN162">
+        <v>1.24</v>
+      </c>
+      <c r="BO162">
+        <v>3.9</v>
+      </c>
+      <c r="BP162">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ2">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1904,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2110,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2728,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2931,22 +2931,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3140,19 +3140,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3346,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3546,25 +3546,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3758,19 +3758,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ13">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AT13">
-        <v>1.83</v>
+        <v>3.09</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3961,22 +3961,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AT14">
-        <v>1.21</v>
+        <v>2.59</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4164,25 +4164,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>0.36</v>
+        <v>2.07</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4370,25 +4370,25 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ16">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS16">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AT16">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4576,25 +4576,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS17">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AT17">
-        <v>1.15</v>
+        <v>3.02</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4788,19 +4788,19 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AS18">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT18">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -4988,25 +4988,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ19">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR19">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT19">
-        <v>1.38</v>
+        <v>3.42</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5194,25 +5194,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR20">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AS20">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="AT20">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5403,22 +5403,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ21">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT21">
-        <v>1.23</v>
+        <v>3.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5606,25 +5606,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5812,25 +5812,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO23">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP23">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ23">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR23">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="AS23">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="AT23">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6018,25 +6018,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP24">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="AS24">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT24">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6227,22 +6227,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR25">
-        <v>0.98</v>
+        <v>1.23</v>
       </c>
       <c r="AS25">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AT25">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6433,22 +6433,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ26">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR26">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AS26">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="AT26">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6639,22 +6639,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ27">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR27">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AS27">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AT27">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6842,25 +6842,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR28">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT28">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -7048,25 +7048,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR29">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AS29">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AT29">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7254,25 +7254,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP30">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ30">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR30">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AT30">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7460,25 +7460,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO31">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP31">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ31">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR31">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS31">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AT31">
-        <v>3.01</v>
+        <v>3.32</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7666,25 +7666,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR32">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AT32">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7875,22 +7875,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR33">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AS33">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="AT33">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8078,25 +8078,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP34">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ34">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS34">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8284,25 +8284,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP35">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ35">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS35">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="AT35">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8490,25 +8490,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP36">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ36">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR36">
-        <v>2.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS36">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AT36">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8696,25 +8696,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AO37">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP37">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ37">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR37">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="AT37">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8902,25 +8902,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR38">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AS38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT38">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9108,25 +9108,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ39">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR39">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="AS39">
-        <v>0.68</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9317,22 +9317,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR40">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AS40">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AT40">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9520,25 +9520,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AO41">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP41">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ41">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR41">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT41">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9726,25 +9726,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ42">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR42">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS42">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AT42">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9932,25 +9932,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ43">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR43">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="AS43">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AT43">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10141,22 +10141,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR44">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS44">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AT44">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10347,22 +10347,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ45">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR45">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AS45">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AT45">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10550,25 +10550,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO46">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP46">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ46">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR46">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS46">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="AT46">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10756,25 +10756,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ47">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR47">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AS47">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="AT47">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10962,25 +10962,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO48">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR48">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="AS48">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AT48">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11171,22 +11171,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP49">
+        <v>1.04</v>
+      </c>
+      <c r="AQ49">
+        <v>1.87</v>
+      </c>
+      <c r="AR49">
         <v>1.08</v>
       </c>
-      <c r="AQ49">
-        <v>2.36</v>
-      </c>
-      <c r="AR49">
-        <v>1.09</v>
-      </c>
       <c r="AS49">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AT49">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11374,25 +11374,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP50">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AS50">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AT50">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11580,25 +11580,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AO51">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ51">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR51">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AS51">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11786,25 +11786,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO52">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP52">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ52">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR52">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS52">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AT52">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11992,25 +11992,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AO53">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP53">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR53">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS53">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT53">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12198,25 +12198,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP54">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR54">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AS54">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT54">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12404,25 +12404,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO55">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ55">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR55">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="AS55">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AT55">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12610,25 +12610,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AP56">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ56">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR56">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AS56">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AT56">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12816,25 +12816,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AP57">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ57">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR57">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AS57">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AT57">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -13025,22 +13025,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR58">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AS58">
-        <v>0.8100000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="AT58">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13228,25 +13228,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP59">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR59">
+        <v>0.93</v>
+      </c>
+      <c r="AS59">
         <v>0.99</v>
       </c>
-      <c r="AS59">
-        <v>0.88</v>
-      </c>
       <c r="AT59">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13434,25 +13434,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="AO60">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AP60">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR60">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS60">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AT60">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13640,25 +13640,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO61">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AP61">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ61">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR61">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AS61">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AT61">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13846,25 +13846,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO62">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR62">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AS62">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT62">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14052,25 +14052,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO63">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP63">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AS63">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="AT63">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14258,25 +14258,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AO64">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP64">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ64">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR64">
-        <v>1.31</v>
+        <v>0.96</v>
       </c>
       <c r="AS64">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AT64">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14464,25 +14464,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO65">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AP65">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ65">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR65">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AS65">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT65">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14670,25 +14670,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO66">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP66">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ66">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR66">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AS66">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AT66">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14876,22 +14876,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO67">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR67">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS67">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15082,25 +15082,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="AO68">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP68">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ68">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR68">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS68">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT68">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15288,25 +15288,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR69">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS69">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AT69">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15494,25 +15494,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AO70">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP70">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ70">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR70">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AS70">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AT70">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15700,25 +15700,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AO71">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AP71">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ71">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR71">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS71">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT71">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15906,25 +15906,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO72">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR72">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AS72">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AT72">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16115,22 +16115,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AP73">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ73">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR73">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS73">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT73">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16318,25 +16318,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO74">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP74">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR74">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AS74">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AT74">
-        <v>2.69</v>
+        <v>3.01</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16524,25 +16524,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR75">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AS75">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AT75">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16733,22 +16733,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR76">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AS76">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AT76">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16939,22 +16939,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP77">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR77">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AS77">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT77">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17142,25 +17142,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO78">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AP78">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ78">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR78">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AT78">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17348,25 +17348,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP79">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ79">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR79">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT79">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17554,25 +17554,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AO80">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AP80">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ80">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR80">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AS80">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT80">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17760,25 +17760,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AO81">
-        <v>1.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP81">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR81">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AS81">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT81">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17966,25 +17966,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AO82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AP82">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ82">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR82">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AS82">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18172,25 +18172,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO83">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AP83">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ83">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR83">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AS83">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AT83">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18378,25 +18378,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO84">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AP84">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ84">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR84">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS84">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AT84">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18584,25 +18584,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>0.67</v>
+        <v>1.27</v>
       </c>
       <c r="AO85">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AP85">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR85">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS85">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT85">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18790,25 +18790,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
       <c r="AO86">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR86">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AS86">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AT86">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -18996,25 +18996,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO87">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ87">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR87">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AS87">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="AT87">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19202,25 +19202,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO88">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR88">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AS88">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AT88">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19408,25 +19408,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO89">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP89">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR89">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS89">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT89">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19614,25 +19614,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO90">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR90">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS90">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AT90">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19820,25 +19820,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.17</v>
+        <v>1.92</v>
       </c>
       <c r="AO91">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR91">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AS91">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="AT91">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20029,22 +20029,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AP92">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR92">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS92">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT92">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20232,25 +20232,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AO93">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AP93">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR93">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AS93">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="AT93">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20438,25 +20438,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AO94">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ94">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR94">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AS94">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT94">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20644,25 +20644,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO95">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ95">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR95">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS95">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AT95">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20850,25 +20850,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO96">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ96">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR96">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AT96">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21056,25 +21056,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO97">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AP97">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ97">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR97">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS97">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT97">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21262,25 +21262,25 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO98">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP98">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ98">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR98">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AS98">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT98">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21468,25 +21468,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="AP99">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR99">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AT99">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21674,25 +21674,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="AO100">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AP100">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ100">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR100">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AS100">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AT100">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21880,25 +21880,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO101">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AP101">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR101">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AS101">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT101">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22086,25 +22086,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="AO102">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR102">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AS102">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT102">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22292,25 +22292,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="AO103">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP103">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ103">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR103">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS103">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT103">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22498,25 +22498,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO104">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP104">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ104">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR104">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AS104">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AT104">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22704,25 +22704,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AO105">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="AP105">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ105">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR105">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AS105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AT105">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22910,25 +22910,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AO106">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AP106">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ106">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR106">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AS106">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AT106">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23116,25 +23116,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AO107">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR107">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AS107">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT107">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23322,25 +23322,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO108">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ108">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR108">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AS108">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
       <c r="AT108">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23528,25 +23528,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AO109">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="AP109">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR109">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AS109">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT109">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23734,25 +23734,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO110">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ110">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR110">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT110">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23940,25 +23940,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AO111">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP111">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR111">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AS111">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT111">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24146,25 +24146,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR112">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT112">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24352,25 +24352,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO113">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AP113">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ113">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR113">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AS113">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="AT113">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24558,25 +24558,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO114">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP114">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ114">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR114">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AS114">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="AT114">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24767,22 +24767,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AP115">
+        <v>1.04</v>
+      </c>
+      <c r="AQ115">
+        <v>0.96</v>
+      </c>
+      <c r="AR115">
         <v>1.08</v>
       </c>
-      <c r="AQ115">
-        <v>0.82</v>
-      </c>
-      <c r="AR115">
-        <v>1.12</v>
-      </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT115">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24970,25 +24970,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AO116">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP116">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ116">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR116">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS116">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT116">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25176,25 +25176,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO117">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AP117">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ117">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR117">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AS117">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AT117">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25382,25 +25382,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AO118">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AP118">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ118">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR118">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS118">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT118">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25588,25 +25588,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO119">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AP119">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR119">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25794,25 +25794,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AO120">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ120">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR120">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AS120">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AT120">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26000,25 +26000,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AP121">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ121">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR121">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AS121">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AT121">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26209,22 +26209,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AP122">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ122">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR122">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AS122">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AT122">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26412,25 +26412,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AO123">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AP123">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ123">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR123">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AS123">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AT123">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26618,25 +26618,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AO124">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR124">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS124">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="AT124">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26824,25 +26824,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO125">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AP125">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ125">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR125">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AS125">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AT125">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27030,25 +27030,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AO126">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP126">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ126">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR126">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AS126">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="AT126">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27236,25 +27236,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AO127">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR127">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AS127">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AT127">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27442,25 +27442,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
+        <v>0.67</v>
+      </c>
+      <c r="AO128">
+        <v>1.11</v>
+      </c>
+      <c r="AP128">
         <v>0.78</v>
       </c>
-      <c r="AO128">
-        <v>1.67</v>
-      </c>
-      <c r="AP128">
+      <c r="AQ128">
         <v>0.91</v>
       </c>
-      <c r="AQ128">
-        <v>1.33</v>
-      </c>
       <c r="AR128">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AS128">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT128">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27648,25 +27648,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO129">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AP129">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ129">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR129">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AS129">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AT129">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27854,25 +27854,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
+        <v>1</v>
+      </c>
+      <c r="AO130">
+        <v>1.39</v>
+      </c>
+      <c r="AP130">
+        <v>1.04</v>
+      </c>
+      <c r="AQ130">
+        <v>1.52</v>
+      </c>
+      <c r="AR130">
         <v>1.11</v>
       </c>
-      <c r="AO130">
-        <v>1.33</v>
-      </c>
-      <c r="AP130">
-        <v>1.08</v>
-      </c>
-      <c r="AQ130">
-        <v>1.33</v>
-      </c>
-      <c r="AR130">
-        <v>1.17</v>
-      </c>
       <c r="AS130">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AT130">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -28060,25 +28060,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AO131">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AP131">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ131">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR131">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AS131">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AT131">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28266,25 +28266,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AP132">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ132">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR132">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS132">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT132">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28475,22 +28475,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AP133">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ133">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR133">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AS133">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AT133">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28681,22 +28681,22 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ134">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AT134">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28884,25 +28884,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AO135">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AP135">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ135">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR135">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AS135">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AT135">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29090,25 +29090,25 @@
         <v>1.86</v>
       </c>
       <c r="AN136">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AO136">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AP136">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR136">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS136">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AT136">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29296,25 +29296,25 @@
         <v>1.77</v>
       </c>
       <c r="AN137">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP137">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ137">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR137">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS137">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AT137">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29502,25 +29502,25 @@
         <v>4.6</v>
       </c>
       <c r="AN138">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AO138">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AP138">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ138">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR138">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AS138">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AT138">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU138">
         <v>5</v>
@@ -29708,25 +29708,25 @@
         <v>1.21</v>
       </c>
       <c r="AN139">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AO139">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AP139">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ139">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR139">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AS139">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AT139">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU139">
         <v>2</v>
@@ -29914,22 +29914,22 @@
         <v>3.6</v>
       </c>
       <c r="AN140">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AO140">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR140">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AS140">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AT140">
         <v>2.75</v>
@@ -30120,25 +30120,25 @@
         <v>1.93</v>
       </c>
       <c r="AN141">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AO141">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AP141">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ141">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR141">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AS141">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AT141">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30326,25 +30326,25 @@
         <v>3.2</v>
       </c>
       <c r="AN142">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AO142">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AP142">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR142">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS142">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT142">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AU142">
         <v>9</v>
@@ -30532,25 +30532,25 @@
         <v>1.53</v>
       </c>
       <c r="AN143">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AO143">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ143">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR143">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS143">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="AT143">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="AU143">
         <v>5</v>
@@ -30738,25 +30738,25 @@
         <v>1.09</v>
       </c>
       <c r="AN144">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AO144">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP144">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ144">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR144">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AS144">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AT144">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30944,25 +30944,25 @@
         <v>1.25</v>
       </c>
       <c r="AN145">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO145">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AP145">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AQ145">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR145">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="AS145">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AT145">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31150,25 +31150,25 @@
         <v>1.48</v>
       </c>
       <c r="AN146">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AO146">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ146">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AR146">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AS146">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AT146">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31359,22 +31359,22 @@
         <v>1.3</v>
       </c>
       <c r="AO147">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AQ147">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR147">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AS147">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AT147">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU147">
         <v>0</v>
@@ -31562,25 +31562,25 @@
         <v>2.28</v>
       </c>
       <c r="AN148">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AO148">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="AP148">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AQ148">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR148">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AS148">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AT148">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31768,25 +31768,25 @@
         <v>1.61</v>
       </c>
       <c r="AN149">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO149">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AP149">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AQ149">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AR149">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AS149">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="AT149">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -31974,25 +31974,25 @@
         <v>1.17</v>
       </c>
       <c r="AN150">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AO150">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AP150">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ150">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AR150">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AS150">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AT150">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AU150">
         <v>3</v>
@@ -32180,25 +32180,25 @@
         <v>3.55</v>
       </c>
       <c r="AN151">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AO151">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AP151">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR151">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AS151">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AT151">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32386,25 +32386,25 @@
         <v>1.26</v>
       </c>
       <c r="AN152">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO152">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AP152">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AQ152">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AR152">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS152">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AT152">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="AU152">
         <v>8</v>
@@ -32592,25 +32592,25 @@
         <v>5.6</v>
       </c>
       <c r="AN153">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AO153">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AP153">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AR153">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AS153">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT153">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="AU153">
         <v>12</v>
@@ -32798,25 +32798,25 @@
         <v>1.88</v>
       </c>
       <c r="AN154">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="AO154">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP154">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AQ154">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AR154">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AS154">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="AT154">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="AU154">
         <v>6</v>
@@ -33004,25 +33004,25 @@
         <v>1.35</v>
       </c>
       <c r="AN155">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="AO155">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AP155">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR155">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AS155">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AT155">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33210,25 +33210,25 @@
         <v>1.57</v>
       </c>
       <c r="AN156">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AO156">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AP156">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ156">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AR156">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AS156">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT156">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AU156">
         <v>6</v>
@@ -33416,25 +33416,25 @@
         <v>3.7</v>
       </c>
       <c r="AN157">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AO157">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AP157">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AQ157">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AR157">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AS157">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AT157">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="AU157">
         <v>5</v>
@@ -33622,25 +33622,25 @@
         <v>1.33</v>
       </c>
       <c r="AN158">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AO158">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AP158">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ158">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AR158">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AS158">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AT158">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AU158">
         <v>6</v>
@@ -33828,25 +33828,25 @@
         <v>3.9</v>
       </c>
       <c r="AN159">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AO159">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AP159">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="AR159">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AS159">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AT159">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="AU159">
         <v>8</v>
@@ -34034,25 +34034,25 @@
         <v>1.04</v>
       </c>
       <c r="AN160">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AO160">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AP160">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AQ160">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AR160">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AS160">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AT160">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AU160">
         <v>2</v>
@@ -34240,25 +34240,25 @@
         <v>5.2</v>
       </c>
       <c r="AN161">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AO161">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AP161">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AR161">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AS161">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="AT161">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="AU161">
         <v>12</v>
@@ -34446,25 +34446,25 @@
         <v>1.61</v>
       </c>
       <c r="AN162">
+        <v>1.32</v>
+      </c>
+      <c r="AO162">
+        <v>0.82</v>
+      </c>
+      <c r="AP162">
+        <v>1.39</v>
+      </c>
+      <c r="AQ162">
+        <v>0.78</v>
+      </c>
+      <c r="AR162">
+        <v>1.04</v>
+      </c>
+      <c r="AS162">
         <v>1.18</v>
       </c>
-      <c r="AO162">
-        <v>0.73</v>
-      </c>
-      <c r="AP162">
-        <v>1.33</v>
-      </c>
-      <c r="AQ162">
-        <v>0.67</v>
-      </c>
-      <c r="AR162">
-        <v>1.12</v>
-      </c>
-      <c r="AS162">
-        <v>0.95</v>
-      </c>
       <c r="AT162">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="AU162">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ2">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1904,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2110,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ6">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2728,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2931,22 +2931,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR9">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3140,19 +3140,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3346,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3546,25 +3546,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3758,19 +3758,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.09</v>
+        <v>1.83</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3961,22 +3961,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.59</v>
+        <v>1.21</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4164,25 +4164,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>2.07</v>
+        <v>0.36</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4370,25 +4370,25 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ16">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR16">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AT16">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4576,25 +4576,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AT17">
-        <v>3.02</v>
+        <v>1.15</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4788,19 +4788,19 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR18">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AT18">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -4988,25 +4988,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR19">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS19">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>3.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5194,25 +5194,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR20">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AS20">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
       <c r="AT20">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5403,22 +5403,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ21">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR21">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS21">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>3.23</v>
+        <v>1.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5606,25 +5606,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5812,25 +5812,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO23">
+        <v>0.5</v>
+      </c>
+      <c r="AP23">
+        <v>0.27</v>
+      </c>
+      <c r="AQ23">
         <v>0.67</v>
       </c>
-      <c r="AP23">
-        <v>0.39</v>
-      </c>
-      <c r="AQ23">
-        <v>0.78</v>
-      </c>
       <c r="AR23">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AS23">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="AT23">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6018,25 +6018,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR24">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="AS24">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT24">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6227,22 +6227,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR25">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="AS25">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AT25">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6433,22 +6433,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ26">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR26">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AS26">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="AT26">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6639,22 +6639,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR27">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AS27">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AT27">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6842,25 +6842,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AS28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT28">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -7048,25 +7048,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ29">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AS29">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="AT29">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7254,25 +7254,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ30">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR30">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="AS30">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7460,25 +7460,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ31">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR31">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS31">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AT31">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7666,25 +7666,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS32">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AT32">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7875,22 +7875,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="AS33">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="AT33">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8078,25 +8078,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO34">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ34">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR34">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS34">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AT34">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8284,25 +8284,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO35">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ35">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS35">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="AT35">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8490,25 +8490,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ36">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR36">
-        <v>1.16</v>
+        <v>2.14</v>
       </c>
       <c r="AS36">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AT36">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8696,25 +8696,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AO37">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ37">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AS37">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="AT37">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8902,25 +8902,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR38">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AS38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT38">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9108,25 +9108,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ39">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR39">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
       <c r="AT39">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9317,22 +9317,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ40">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AS40">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT40">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9520,25 +9520,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AO41">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ41">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS41">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT41">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9726,25 +9726,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ42">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR42">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AS42">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AT42">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9932,25 +9932,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO43">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ43">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR43">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="AS43">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10141,22 +10141,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ44">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS44">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AT44">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10347,22 +10347,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR45">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AS45">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AT45">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10550,25 +10550,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO46">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ46">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR46">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS46">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT46">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10756,25 +10756,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ47">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR47">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AS47">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="AT47">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10962,25 +10962,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO48">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ48">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="AS48">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AT48">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11171,22 +11171,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ49">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR49">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AS49">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT49">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11374,25 +11374,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO50">
+        <v>2</v>
+      </c>
+      <c r="AP50">
+        <v>2.25</v>
+      </c>
+      <c r="AQ50">
         <v>2.17</v>
       </c>
-      <c r="AP50">
-        <v>2</v>
-      </c>
-      <c r="AQ50">
-        <v>2.22</v>
-      </c>
       <c r="AR50">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AT50">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11580,25 +11580,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AO51">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ51">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR51">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AS51">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT51">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11786,25 +11786,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ52">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR52">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS52">
-        <v>1.1</v>
+        <v>0.84</v>
       </c>
       <c r="AT52">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11992,25 +11992,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AO53">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ53">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AS53">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT53">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12198,25 +12198,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO54">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ54">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR54">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AS54">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT54">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12404,25 +12404,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR55">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="AS55">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AT55">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12610,25 +12610,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO56">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR56">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS56">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AT56">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12816,25 +12816,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO57">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR57">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS57">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AT57">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -13025,22 +13025,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AS58">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT58">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13228,25 +13228,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO59">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AS59">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="AT59">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13434,25 +13434,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="AO60">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ60">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR60">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS60">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AT60">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13640,25 +13640,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>1.25</v>
+        <v>0.33</v>
       </c>
       <c r="AO61">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR61">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AS61">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AT61">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13846,25 +13846,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AS62">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT62">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14052,25 +14052,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO63">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ63">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14258,25 +14258,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ64">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR64">
-        <v>0.96</v>
+        <v>1.31</v>
       </c>
       <c r="AS64">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AT64">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14464,25 +14464,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO65">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ65">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR65">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AS65">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AT65">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14670,25 +14670,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO66">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ66">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR66">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AS66">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AT66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14876,22 +14876,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ67">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR67">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS67">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15082,25 +15082,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="AO68">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR68">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS68">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AT68">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15288,25 +15288,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="AO69">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ69">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS69">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AT69">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15494,25 +15494,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="AO70">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ70">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR70">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AS70">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AT70">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15700,25 +15700,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ71">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR71">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AS71">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT71">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15906,25 +15906,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO72">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AS72">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AT72">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16115,22 +16115,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR73">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT73">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16318,25 +16318,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
+        <v>2.2</v>
+      </c>
+      <c r="AO74">
         <v>1.8</v>
       </c>
-      <c r="AO74">
-        <v>1.6</v>
-      </c>
       <c r="AP74">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ74">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR74">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AS74">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AT74">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16524,25 +16524,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR75">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AS75">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AT75">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16733,22 +16733,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ76">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AS76">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AT76">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16939,22 +16939,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ77">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR77">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AS77">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AT77">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17142,25 +17142,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO78">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ78">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AS78">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT78">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17348,25 +17348,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AO79">
+        <v>1</v>
+      </c>
+      <c r="AP79">
         <v>0.91</v>
       </c>
-      <c r="AP79">
-        <v>0.78</v>
-      </c>
       <c r="AQ79">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR79">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS79">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17554,25 +17554,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="AO80">
+        <v>1.67</v>
+      </c>
+      <c r="AP80">
+        <v>0.27</v>
+      </c>
+      <c r="AQ80">
         <v>1.36</v>
       </c>
-      <c r="AP80">
-        <v>0.39</v>
-      </c>
-      <c r="AQ80">
-        <v>1.3</v>
-      </c>
       <c r="AR80">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AS80">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT80">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17760,25 +17760,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AO81">
-        <v>0.91</v>
+        <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ81">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR81">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS81">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT81">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17966,25 +17966,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AO82">
+        <v>1.6</v>
+      </c>
+      <c r="AP82">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82">
         <v>1.73</v>
       </c>
-      <c r="AP82">
-        <v>1.39</v>
-      </c>
-      <c r="AQ82">
-        <v>2</v>
-      </c>
       <c r="AR82">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AT82">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18172,25 +18172,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO83">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ83">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR83">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AS83">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AT83">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18378,25 +18378,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AO84">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ84">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR84">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AS84">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AT84">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18584,25 +18584,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>1.27</v>
+        <v>0.67</v>
       </c>
       <c r="AO85">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ85">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR85">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS85">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT85">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18790,25 +18790,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>1.08</v>
+        <v>0.17</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ86">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR86">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AS86">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AT86">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -18996,25 +18996,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ87">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR87">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AS87">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="AT87">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19202,25 +19202,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO88">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ88">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR88">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AS88">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AT88">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19408,25 +19408,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
+        <v>0.8</v>
+      </c>
+      <c r="AO89">
+        <v>1.5</v>
+      </c>
+      <c r="AP89">
         <v>1.08</v>
       </c>
-      <c r="AO89">
+      <c r="AQ89">
         <v>1.33</v>
       </c>
-      <c r="AP89">
-        <v>0.96</v>
-      </c>
-      <c r="AQ89">
-        <v>1.52</v>
-      </c>
       <c r="AR89">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS89">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT89">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19614,25 +19614,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ90">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR90">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS90">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AT90">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19820,25 +19820,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO91">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AS91">
-        <v>1.22</v>
+        <v>0.95</v>
       </c>
       <c r="AT91">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20029,22 +20029,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ92">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR92">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS92">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AT92">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20232,25 +20232,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AO93">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ93">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AS93">
-        <v>1.19</v>
+        <v>0.96</v>
       </c>
       <c r="AT93">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20438,25 +20438,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AO94">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR94">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AS94">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT94">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20644,25 +20644,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO95">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR95">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS95">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AT95">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20850,25 +20850,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR96">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS96">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AT96">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21056,25 +21056,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO97">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR97">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AS97">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT97">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21262,25 +21262,25 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AO98">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ98">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR98">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT98">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21468,25 +21468,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AO99">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ99">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AS99">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AT99">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21674,25 +21674,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="AO100">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ100">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS100">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AT100">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21880,25 +21880,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO101">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ101">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AS101">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT101">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22086,25 +22086,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>1</v>
+        <v>0.29</v>
       </c>
       <c r="AO102">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ102">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AS102">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT102">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22292,25 +22292,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="AO103">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ103">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR103">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS103">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT103">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22498,25 +22498,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO104">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP104">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ104">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR104">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AS104">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT104">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22704,25 +22704,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AO105">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR105">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AS105">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AT105">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22910,25 +22910,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="AO106">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ106">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR106">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AS106">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AT106">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23116,25 +23116,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AO107">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ107">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AS107">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AT107">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23322,25 +23322,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO108">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR108">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AS108">
-        <v>1.07</v>
+        <v>0.89</v>
       </c>
       <c r="AT108">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23528,25 +23528,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AO109">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ109">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR109">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AS109">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT109">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23734,25 +23734,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO110">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AS110">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT110">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23940,25 +23940,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AO111">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ111">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR111">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AS111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24146,25 +24146,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO112">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AS112">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AT112">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24352,25 +24352,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
+        <v>0.71</v>
+      </c>
+      <c r="AO113">
+        <v>1.71</v>
+      </c>
+      <c r="AP113">
+        <v>1.25</v>
+      </c>
+      <c r="AQ113">
+        <v>1.33</v>
+      </c>
+      <c r="AR113">
         <v>1.13</v>
       </c>
-      <c r="AO113">
-        <v>1.13</v>
-      </c>
-      <c r="AP113">
-        <v>1.3</v>
-      </c>
-      <c r="AQ113">
-        <v>0.91</v>
-      </c>
-      <c r="AR113">
-        <v>1.07</v>
-      </c>
       <c r="AS113">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="AT113">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24558,25 +24558,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO114">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ114">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR114">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AS114">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="AT114">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24767,22 +24767,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ115">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR115">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS115">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24970,25 +24970,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="AO116">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR116">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS116">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AT116">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25176,25 +25176,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>1.06</v>
+        <v>0.63</v>
       </c>
       <c r="AO117">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ117">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR117">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AS117">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AT117">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25382,25 +25382,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AO118">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ118">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR118">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT118">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25588,25 +25588,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO119">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ119">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR119">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25794,25 +25794,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AO120">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AS120">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AT120">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26000,25 +26000,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AO121">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ121">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR121">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AS121">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AT121">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26209,22 +26209,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR122">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AS122">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AT122">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26412,25 +26412,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="AO123">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ123">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR123">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AS123">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AT123">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26618,25 +26618,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AO124">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ124">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR124">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS124">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="AT124">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26824,25 +26824,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO125">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ125">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR125">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AS125">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AT125">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27030,25 +27030,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AO126">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ126">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR126">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS126">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT126">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27236,25 +27236,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ127">
+        <v>1</v>
+      </c>
+      <c r="AR127">
+        <v>1.2</v>
+      </c>
+      <c r="AS127">
         <v>1.04</v>
       </c>
-      <c r="AR127">
-        <v>1.09</v>
-      </c>
-      <c r="AS127">
-        <v>1.11</v>
-      </c>
       <c r="AT127">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27442,25 +27442,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AO128">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR128">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AS128">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT128">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27648,25 +27648,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO129">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ129">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR129">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AS129">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AT129">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27854,25 +27854,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO130">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ130">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR130">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AS130">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AT130">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -28060,25 +28060,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AO131">
+        <v>1.67</v>
+      </c>
+      <c r="AP131">
         <v>1.33</v>
       </c>
-      <c r="AP131">
-        <v>1.39</v>
-      </c>
       <c r="AQ131">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR131">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AS131">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AT131">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28266,25 +28266,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="AO132">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ132">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR132">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS132">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AT132">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28475,22 +28475,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ133">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR133">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AS133">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT133">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28681,22 +28681,22 @@
         <v>1</v>
       </c>
       <c r="AO134">
+        <v>0.67</v>
+      </c>
+      <c r="AP134">
+        <v>1.08</v>
+      </c>
+      <c r="AQ134">
         <v>0.5</v>
-      </c>
-      <c r="AP134">
-        <v>0.96</v>
-      </c>
-      <c r="AQ134">
-        <v>0.39</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT134">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28884,25 +28884,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO135">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AQ135">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR135">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AS135">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AT135">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29090,25 +29090,25 @@
         <v>1.86</v>
       </c>
       <c r="AN136">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AO136">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP136">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ136">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS136">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="AT136">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29296,25 +29296,25 @@
         <v>1.77</v>
       </c>
       <c r="AN137">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AO137">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS137">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AT137">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29502,25 +29502,25 @@
         <v>4.6</v>
       </c>
       <c r="AN138">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AO138">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ138">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR138">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AS138">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="AT138">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU138">
         <v>5</v>
@@ -29708,25 +29708,25 @@
         <v>1.21</v>
       </c>
       <c r="AN139">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AO139">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ139">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR139">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AS139">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AT139">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU139">
         <v>2</v>
@@ -29914,22 +29914,22 @@
         <v>3.6</v>
       </c>
       <c r="AN140">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AO140">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR140">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AS140">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AT140">
         <v>2.75</v>
@@ -30120,25 +30120,25 @@
         <v>1.93</v>
       </c>
       <c r="AN141">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AO141">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ141">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR141">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AS141">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AT141">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30326,25 +30326,25 @@
         <v>3.2</v>
       </c>
       <c r="AN142">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AO142">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ142">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR142">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS142">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT142">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AU142">
         <v>9</v>
@@ -30532,25 +30532,25 @@
         <v>1.53</v>
       </c>
       <c r="AN143">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AO143">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP143">
+        <v>1.08</v>
+      </c>
+      <c r="AQ143">
+        <v>1.33</v>
+      </c>
+      <c r="AR143">
+        <v>1.33</v>
+      </c>
+      <c r="AS143">
         <v>0.96</v>
       </c>
-      <c r="AQ143">
-        <v>0.91</v>
-      </c>
-      <c r="AR143">
-        <v>1.32</v>
-      </c>
-      <c r="AS143">
-        <v>1.1</v>
-      </c>
       <c r="AT143">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AU143">
         <v>5</v>
@@ -30738,25 +30738,25 @@
         <v>1.09</v>
       </c>
       <c r="AN144">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AO144">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP144">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ144">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR144">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AS144">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AT144">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30944,25 +30944,25 @@
         <v>1.25</v>
       </c>
       <c r="AN145">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO145">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="AP145">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AQ145">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR145">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AS145">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AT145">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31150,25 +31150,25 @@
         <v>1.48</v>
       </c>
       <c r="AN146">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AO146">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP146">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ146">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AR146">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AS146">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AT146">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31359,22 +31359,22 @@
         <v>1.3</v>
       </c>
       <c r="AO147">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AP147">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR147">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AS147">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AT147">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU147">
         <v>0</v>
@@ -31562,25 +31562,25 @@
         <v>2.28</v>
       </c>
       <c r="AN148">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AO148">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AP148">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AQ148">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR148">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AS148">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AT148">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31768,25 +31768,25 @@
         <v>1.61</v>
       </c>
       <c r="AN149">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO149">
+        <v>1.3</v>
+      </c>
+      <c r="AP149">
+        <v>0.45</v>
+      </c>
+      <c r="AQ149">
+        <v>1.45</v>
+      </c>
+      <c r="AR149">
         <v>1.24</v>
       </c>
-      <c r="AP149">
-        <v>0.91</v>
-      </c>
-      <c r="AQ149">
-        <v>1.39</v>
-      </c>
-      <c r="AR149">
-        <v>1.14</v>
-      </c>
       <c r="AS149">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="AT149">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -31974,25 +31974,25 @@
         <v>1.17</v>
       </c>
       <c r="AN150">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AO150">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AP150">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ150">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AR150">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AS150">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AT150">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AU150">
         <v>3</v>
@@ -32180,25 +32180,25 @@
         <v>3.55</v>
       </c>
       <c r="AN151">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AO151">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AQ151">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AS151">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AT151">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32386,25 +32386,25 @@
         <v>1.26</v>
       </c>
       <c r="AN152">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO152">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AP152">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AQ152">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AR152">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AS152">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AT152">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="AU152">
         <v>8</v>
@@ -32592,25 +32592,25 @@
         <v>5.6</v>
       </c>
       <c r="AN153">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AO153">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AP153">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ153">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AR153">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AS153">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT153">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="AU153">
         <v>12</v>
@@ -32798,25 +32798,25 @@
         <v>1.88</v>
       </c>
       <c r="AN154">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="AO154">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AQ154">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR154">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AS154">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="AT154">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="AU154">
         <v>6</v>
@@ -33004,25 +33004,25 @@
         <v>1.35</v>
       </c>
       <c r="AN155">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="AO155">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AQ155">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR155">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AS155">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT155">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33210,25 +33210,25 @@
         <v>1.57</v>
       </c>
       <c r="AN156">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AO156">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AP156">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ156">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR156">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AS156">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT156">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AU156">
         <v>6</v>
@@ -33416,25 +33416,25 @@
         <v>3.7</v>
       </c>
       <c r="AN157">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AO157">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AP157">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AQ157">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AR157">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AS157">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AT157">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="AU157">
         <v>5</v>
@@ -33622,25 +33622,25 @@
         <v>1.33</v>
       </c>
       <c r="AN158">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AO158">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AP158">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ158">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AR158">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AS158">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AT158">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AU158">
         <v>6</v>
@@ -33828,25 +33828,25 @@
         <v>3.9</v>
       </c>
       <c r="AN159">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AO159">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ159">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AR159">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AS159">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AT159">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="AU159">
         <v>8</v>
@@ -34034,25 +34034,25 @@
         <v>1.04</v>
       </c>
       <c r="AN160">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AO160">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AP160">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AQ160">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AR160">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AS160">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AT160">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AU160">
         <v>2</v>
@@ -34240,25 +34240,25 @@
         <v>5.2</v>
       </c>
       <c r="AN161">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AO161">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AP161">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AQ161">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="AR161">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AS161">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="AT161">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AU161">
         <v>12</v>
@@ -34446,25 +34446,25 @@
         <v>1.61</v>
       </c>
       <c r="AN162">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AO162">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AP162">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AR162">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AS162">
-        <v>1.18</v>
+        <v>0.95</v>
       </c>
       <c r="AT162">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AU162">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -562,6 +562,15 @@
     <t>['85', '90+8']</t>
   </si>
   <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -581,9 +590,6 @@
   </si>
   <si>
     <t>['12']</t>
-  </si>
-  <si>
-    <t>['60']</t>
   </si>
   <si>
     <t>['41', '79', '81']</t>
@@ -730,9 +736,6 @@
     <t>['56', '63', '69', '90+8']</t>
   </si>
   <si>
-    <t>['88']</t>
-  </si>
-  <si>
     <t>['57']</t>
   </si>
   <si>
@@ -797,6 +800,12 @@
   </si>
   <si>
     <t>['20', '27', '53', '75']</t>
+  </si>
+  <si>
+    <t>['28', '30', '43']</t>
+  </si>
+  <si>
+    <t>['81', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1414,7 +1423,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1492,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ2">
         <v>2.17</v>
@@ -1620,7 +1629,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1701,7 +1710,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2238,7 +2247,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2316,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ6">
         <v>1.17</v>
@@ -2525,7 +2534,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2650,7 +2659,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3062,7 +3071,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3268,7 +3277,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3474,7 +3483,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3967,7 +3976,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4092,7 +4101,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4298,7 +4307,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4504,7 +4513,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4791,7 +4800,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -4916,7 +4925,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5122,7 +5131,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5200,10 +5209,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ20">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5328,7 +5337,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5406,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ21">
         <v>2.36</v>
@@ -5534,7 +5543,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5612,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ22">
         <v>1.73</v>
@@ -5946,7 +5955,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6152,7 +6161,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6233,7 +6242,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR25">
         <v>0.98</v>
@@ -6770,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7182,7 +7191,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7260,7 +7269,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ30">
         <v>2.36</v>
@@ -7594,7 +7603,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7881,7 +7890,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
         <v>0.97</v>
@@ -8006,7 +8015,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8087,7 +8096,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ34">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR34">
         <v>1.44</v>
@@ -8212,7 +8221,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8290,7 +8299,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
@@ -8496,7 +8505,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ36">
         <v>1.73</v>
@@ -8702,7 +8711,7 @@
         <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ37">
         <v>0.67</v>
@@ -8830,7 +8839,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8911,7 +8920,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9036,7 +9045,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9860,7 +9869,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9941,7 +9950,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ43">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR43">
         <v>1.06</v>
@@ -10066,7 +10075,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10144,7 +10153,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ44">
         <v>1.33</v>
@@ -10684,7 +10693,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10765,7 +10774,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ47">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>1.06</v>
@@ -10890,7 +10899,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10968,7 +10977,7 @@
         <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -11096,7 +11105,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11586,10 +11595,10 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ51">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -11714,7 +11723,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11792,7 +11801,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ52">
         <v>1.45</v>
@@ -12126,7 +12135,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12207,7 +12216,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR54">
         <v>2.03</v>
@@ -12332,7 +12341,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12744,7 +12753,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12950,7 +12959,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13156,7 +13165,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13774,7 +13783,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13980,7 +13989,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14061,7 +14070,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14186,7 +14195,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14264,7 +14273,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ64">
         <v>1.67</v>
@@ -14473,7 +14482,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ65">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR65">
         <v>1.98</v>
@@ -14676,7 +14685,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ66">
         <v>1.45</v>
@@ -14804,7 +14813,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14885,7 +14894,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -15088,7 +15097,7 @@
         <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ68">
         <v>1.73</v>
@@ -15216,7 +15225,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15294,7 +15303,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ69">
         <v>1.73</v>
@@ -15422,7 +15431,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15709,7 +15718,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ71">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.51</v>
@@ -16040,7 +16049,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16452,7 +16461,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16658,7 +16667,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17070,7 +17079,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17276,7 +17285,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17354,10 +17363,10 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ79">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17482,7 +17491,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17563,7 +17572,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ80">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.08</v>
@@ -17894,7 +17903,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18100,7 +18109,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18512,7 +18521,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18590,10 +18599,10 @@
         <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR85">
         <v>1.32</v>
@@ -18796,7 +18805,7 @@
         <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ86">
         <v>0.5</v>
@@ -18924,7 +18933,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19542,7 +19551,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19748,7 +19757,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19954,7 +19963,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20366,7 +20375,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20572,7 +20581,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20778,7 +20787,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21190,7 +21199,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21396,7 +21405,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21474,10 +21483,10 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -21886,10 +21895,10 @@
         <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
         <v>1.32</v>
@@ -22014,7 +22023,7 @@
         <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -22092,7 +22101,7 @@
         <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ102">
         <v>1.33</v>
@@ -22301,7 +22310,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ103">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR103">
         <v>1.47</v>
@@ -22426,7 +22435,7 @@
         <v>84</v>
       </c>
       <c r="P104" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="Q104">
         <v>7.5</v>
@@ -22916,7 +22925,7 @@
         <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ106">
         <v>2.17</v>
@@ -23868,7 +23877,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23949,7 +23958,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR111">
         <v>1.89</v>
@@ -24074,7 +24083,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24564,7 +24573,7 @@
         <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ114">
         <v>0.5</v>
@@ -24773,7 +24782,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ115">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -24898,7 +24907,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -24979,7 +24988,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ116">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25104,7 +25113,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25182,7 +25191,7 @@
         <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ117">
         <v>1.73</v>
@@ -25310,7 +25319,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25388,7 +25397,7 @@
         <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ118">
         <v>1.33</v>
@@ -25516,7 +25525,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25722,7 +25731,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26134,7 +26143,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26340,7 +26349,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26546,7 +26555,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -27245,7 +27254,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27448,7 +27457,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ128">
         <v>1.33</v>
@@ -27576,7 +27585,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27654,7 +27663,7 @@
         <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ129">
         <v>2.17</v>
@@ -27782,7 +27791,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28069,7 +28078,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ131">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.17</v>
@@ -28812,7 +28821,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -28890,7 +28899,7 @@
         <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ135">
         <v>1.67</v>
@@ -29224,7 +29233,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29305,7 +29314,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR137">
         <v>1.31</v>
@@ -29636,7 +29645,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29923,7 +29932,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR140">
         <v>1.7</v>
@@ -30254,7 +30263,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30335,7 +30344,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ142">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
         <v>1.82</v>
@@ -30460,7 +30469,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30950,7 +30959,7 @@
         <v>1.1</v>
       </c>
       <c r="AP145">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ145">
         <v>1.17</v>
@@ -31078,7 +31087,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31774,7 +31783,7 @@
         <v>1.3</v>
       </c>
       <c r="AP149">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AQ149">
         <v>1.45</v>
@@ -31902,7 +31911,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32108,7 +32117,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32601,7 +32610,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR153">
         <v>2.03</v>
@@ -32726,7 +32735,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32804,7 +32813,7 @@
         <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ154">
         <v>0.67</v>
@@ -32932,7 +32941,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33013,7 +33022,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR155">
         <v>1.07</v>
@@ -33344,7 +33353,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33550,7 +33559,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33756,7 +33765,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33962,7 +33971,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34531,6 +34540,624 @@
       </c>
       <c r="BP162">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7537455</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F163">
+        <v>24</v>
+      </c>
+      <c r="G163" t="s">
+        <v>83</v>
+      </c>
+      <c r="H163" t="s">
+        <v>77</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>3</v>
+      </c>
+      <c r="K163">
+        <v>3</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>3</v>
+      </c>
+      <c r="N163">
+        <v>4</v>
+      </c>
+      <c r="O163" t="s">
+        <v>182</v>
+      </c>
+      <c r="P163" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q163">
+        <v>3.1</v>
+      </c>
+      <c r="R163">
+        <v>2.1</v>
+      </c>
+      <c r="S163">
+        <v>3.5</v>
+      </c>
+      <c r="T163">
+        <v>1.4</v>
+      </c>
+      <c r="U163">
+        <v>2.75</v>
+      </c>
+      <c r="V163">
+        <v>3</v>
+      </c>
+      <c r="W163">
+        <v>1.36</v>
+      </c>
+      <c r="X163">
+        <v>9</v>
+      </c>
+      <c r="Y163">
+        <v>1.07</v>
+      </c>
+      <c r="Z163">
+        <v>2.3</v>
+      </c>
+      <c r="AA163">
+        <v>3.2</v>
+      </c>
+      <c r="AB163">
+        <v>2.9</v>
+      </c>
+      <c r="AC163">
+        <v>1.06</v>
+      </c>
+      <c r="AD163">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE163">
+        <v>1.32</v>
+      </c>
+      <c r="AF163">
+        <v>3.3</v>
+      </c>
+      <c r="AG163">
+        <v>1.95</v>
+      </c>
+      <c r="AH163">
+        <v>1.7</v>
+      </c>
+      <c r="AI163">
+        <v>1.75</v>
+      </c>
+      <c r="AJ163">
+        <v>2</v>
+      </c>
+      <c r="AK163">
+        <v>1.42</v>
+      </c>
+      <c r="AL163">
+        <v>1.37</v>
+      </c>
+      <c r="AM163">
+        <v>1.56</v>
+      </c>
+      <c r="AN163">
+        <v>0.91</v>
+      </c>
+      <c r="AO163">
+        <v>1.36</v>
+      </c>
+      <c r="AP163">
+        <v>0.83</v>
+      </c>
+      <c r="AQ163">
+        <v>1.5</v>
+      </c>
+      <c r="AR163">
+        <v>1.4</v>
+      </c>
+      <c r="AS163">
+        <v>1.02</v>
+      </c>
+      <c r="AT163">
+        <v>2.42</v>
+      </c>
+      <c r="AU163">
+        <v>9</v>
+      </c>
+      <c r="AV163">
+        <v>8</v>
+      </c>
+      <c r="AW163">
+        <v>7</v>
+      </c>
+      <c r="AX163">
+        <v>2</v>
+      </c>
+      <c r="AY163">
+        <v>19</v>
+      </c>
+      <c r="AZ163">
+        <v>11</v>
+      </c>
+      <c r="BA163">
+        <v>10</v>
+      </c>
+      <c r="BB163">
+        <v>3</v>
+      </c>
+      <c r="BC163">
+        <v>13</v>
+      </c>
+      <c r="BD163">
+        <v>1.6</v>
+      </c>
+      <c r="BE163">
+        <v>6.9</v>
+      </c>
+      <c r="BF163">
+        <v>2.8</v>
+      </c>
+      <c r="BG163">
+        <v>1.36</v>
+      </c>
+      <c r="BH163">
+        <v>2.79</v>
+      </c>
+      <c r="BI163">
+        <v>1.67</v>
+      </c>
+      <c r="BJ163">
+        <v>2.07</v>
+      </c>
+      <c r="BK163">
+        <v>2</v>
+      </c>
+      <c r="BL163">
+        <v>1.8</v>
+      </c>
+      <c r="BM163">
+        <v>2.81</v>
+      </c>
+      <c r="BN163">
+        <v>1.33</v>
+      </c>
+      <c r="BO163">
+        <v>3.75</v>
+      </c>
+      <c r="BP163">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7537457</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45710.60416666666</v>
+      </c>
+      <c r="F164">
+        <v>24</v>
+      </c>
+      <c r="G164" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" t="s">
+        <v>78</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>183</v>
+      </c>
+      <c r="P164" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q164">
+        <v>2.6</v>
+      </c>
+      <c r="R164">
+        <v>2.05</v>
+      </c>
+      <c r="S164">
+        <v>5</v>
+      </c>
+      <c r="T164">
+        <v>1.5</v>
+      </c>
+      <c r="U164">
+        <v>2.5</v>
+      </c>
+      <c r="V164">
+        <v>3.4</v>
+      </c>
+      <c r="W164">
+        <v>1.3</v>
+      </c>
+      <c r="X164">
+        <v>10</v>
+      </c>
+      <c r="Y164">
+        <v>1.06</v>
+      </c>
+      <c r="Z164">
+        <v>1.8</v>
+      </c>
+      <c r="AA164">
+        <v>3.3</v>
+      </c>
+      <c r="AB164">
+        <v>4.33</v>
+      </c>
+      <c r="AC164">
+        <v>1.08</v>
+      </c>
+      <c r="AD164">
+        <v>8.4</v>
+      </c>
+      <c r="AE164">
+        <v>1.39</v>
+      </c>
+      <c r="AF164">
+        <v>2.9</v>
+      </c>
+      <c r="AG164">
+        <v>2.05</v>
+      </c>
+      <c r="AH164">
+        <v>1.61</v>
+      </c>
+      <c r="AI164">
+        <v>2</v>
+      </c>
+      <c r="AJ164">
+        <v>1.75</v>
+      </c>
+      <c r="AK164">
+        <v>1.24</v>
+      </c>
+      <c r="AL164">
+        <v>1.34</v>
+      </c>
+      <c r="AM164">
+        <v>1.91</v>
+      </c>
+      <c r="AN164">
+        <v>0.73</v>
+      </c>
+      <c r="AO164">
+        <v>0.82</v>
+      </c>
+      <c r="AP164">
+        <v>0.92</v>
+      </c>
+      <c r="AQ164">
+        <v>0.75</v>
+      </c>
+      <c r="AR164">
+        <v>1.26</v>
+      </c>
+      <c r="AS164">
+        <v>1.29</v>
+      </c>
+      <c r="AT164">
+        <v>2.55</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>4</v>
+      </c>
+      <c r="AW164">
+        <v>8</v>
+      </c>
+      <c r="AX164">
+        <v>6</v>
+      </c>
+      <c r="AY164">
+        <v>17</v>
+      </c>
+      <c r="AZ164">
+        <v>14</v>
+      </c>
+      <c r="BA164">
+        <v>6</v>
+      </c>
+      <c r="BB164">
+        <v>4</v>
+      </c>
+      <c r="BC164">
+        <v>10</v>
+      </c>
+      <c r="BD164">
+        <v>1.58</v>
+      </c>
+      <c r="BE164">
+        <v>6.4</v>
+      </c>
+      <c r="BF164">
+        <v>2.65</v>
+      </c>
+      <c r="BG164">
+        <v>1.43</v>
+      </c>
+      <c r="BH164">
+        <v>2.43</v>
+      </c>
+      <c r="BI164">
+        <v>1.8</v>
+      </c>
+      <c r="BJ164">
+        <v>2</v>
+      </c>
+      <c r="BK164">
+        <v>2.2</v>
+      </c>
+      <c r="BL164">
+        <v>1.52</v>
+      </c>
+      <c r="BM164">
+        <v>2.88</v>
+      </c>
+      <c r="BN164">
+        <v>1.3</v>
+      </c>
+      <c r="BO164">
+        <v>3.85</v>
+      </c>
+      <c r="BP164">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7537458</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45710.625</v>
+      </c>
+      <c r="F165">
+        <v>24</v>
+      </c>
+      <c r="G165" t="s">
+        <v>70</v>
+      </c>
+      <c r="H165" t="s">
+        <v>72</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>3</v>
+      </c>
+      <c r="O165" t="s">
+        <v>184</v>
+      </c>
+      <c r="P165" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q165">
+        <v>3.2</v>
+      </c>
+      <c r="R165">
+        <v>1.91</v>
+      </c>
+      <c r="S165">
+        <v>4</v>
+      </c>
+      <c r="T165">
+        <v>1.57</v>
+      </c>
+      <c r="U165">
+        <v>2.25</v>
+      </c>
+      <c r="V165">
+        <v>3.75</v>
+      </c>
+      <c r="W165">
+        <v>1.25</v>
+      </c>
+      <c r="X165">
+        <v>13</v>
+      </c>
+      <c r="Y165">
+        <v>1.04</v>
+      </c>
+      <c r="Z165">
+        <v>2.3</v>
+      </c>
+      <c r="AA165">
+        <v>2.9</v>
+      </c>
+      <c r="AB165">
+        <v>3.25</v>
+      </c>
+      <c r="AC165">
+        <v>1.11</v>
+      </c>
+      <c r="AD165">
+        <v>6.4</v>
+      </c>
+      <c r="AE165">
+        <v>1.52</v>
+      </c>
+      <c r="AF165">
+        <v>2.44</v>
+      </c>
+      <c r="AG165">
+        <v>2.37</v>
+      </c>
+      <c r="AH165">
+        <v>1.48</v>
+      </c>
+      <c r="AI165">
+        <v>2.1</v>
+      </c>
+      <c r="AJ165">
+        <v>1.67</v>
+      </c>
+      <c r="AK165">
+        <v>1.35</v>
+      </c>
+      <c r="AL165">
+        <v>1.42</v>
+      </c>
+      <c r="AM165">
+        <v>1.59</v>
+      </c>
+      <c r="AN165">
+        <v>0.45</v>
+      </c>
+      <c r="AO165">
+        <v>1</v>
+      </c>
+      <c r="AP165">
+        <v>0.42</v>
+      </c>
+      <c r="AQ165">
+        <v>1.17</v>
+      </c>
+      <c r="AR165">
+        <v>1.27</v>
+      </c>
+      <c r="AS165">
+        <v>1.08</v>
+      </c>
+      <c r="AT165">
+        <v>2.35</v>
+      </c>
+      <c r="AU165">
+        <v>2</v>
+      </c>
+      <c r="AV165">
+        <v>4</v>
+      </c>
+      <c r="AW165">
+        <v>7</v>
+      </c>
+      <c r="AX165">
+        <v>6</v>
+      </c>
+      <c r="AY165">
+        <v>12</v>
+      </c>
+      <c r="AZ165">
+        <v>13</v>
+      </c>
+      <c r="BA165">
+        <v>4</v>
+      </c>
+      <c r="BB165">
+        <v>2</v>
+      </c>
+      <c r="BC165">
+        <v>6</v>
+      </c>
+      <c r="BD165">
+        <v>1.79</v>
+      </c>
+      <c r="BE165">
+        <v>6.25</v>
+      </c>
+      <c r="BF165">
+        <v>2.23</v>
+      </c>
+      <c r="BG165">
+        <v>1.42</v>
+      </c>
+      <c r="BH165">
+        <v>2.45</v>
+      </c>
+      <c r="BI165">
+        <v>1.71</v>
+      </c>
+      <c r="BJ165">
+        <v>1.89</v>
+      </c>
+      <c r="BK165">
+        <v>2.15</v>
+      </c>
+      <c r="BL165">
+        <v>1.55</v>
+      </c>
+      <c r="BM165">
+        <v>2.8</v>
+      </c>
+      <c r="BN165">
+        <v>1.33</v>
+      </c>
+      <c r="BO165">
+        <v>3.75</v>
+      </c>
+      <c r="BP165">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,15 @@
     <t>['20']</t>
   </si>
   <si>
+    <t>['13', '30']</t>
+  </si>
+  <si>
+    <t>['4', '78', '90+2']</t>
+  </si>
+  <si>
+    <t>['6', '31']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -806,6 +815,15 @@
   </si>
   <si>
     <t>['81', '90+5']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['64', '76', '80']</t>
+  </si>
+  <si>
+    <t>['24']</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1423,7 +1441,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1629,7 +1647,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2247,7 +2265,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2659,7 +2677,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3071,7 +3089,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3277,7 +3295,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3483,7 +3501,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3561,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3770,7 +3788,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ13">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
@@ -4179,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4307,7 +4325,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4385,7 +4403,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16">
         <v>2.17</v>
@@ -4513,7 +4531,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4591,7 +4609,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -4925,7 +4943,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5006,7 +5024,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ19">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR19">
         <v>1.38</v>
@@ -5131,7 +5149,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5337,7 +5355,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5418,7 +5436,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ21">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR21">
         <v>1.23</v>
@@ -5543,7 +5561,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5624,7 +5642,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5827,7 +5845,7 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ23">
         <v>0.67</v>
@@ -5955,7 +5973,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6033,7 +6051,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ24">
         <v>1.67</v>
@@ -6161,7 +6179,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6445,10 +6463,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.48</v>
@@ -6654,7 +6672,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ27">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR27">
         <v>1.95</v>
@@ -6779,7 +6797,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7191,7 +7209,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7272,7 +7290,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ30">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR30">
         <v>0.96</v>
@@ -7475,7 +7493,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ31">
         <v>2.17</v>
@@ -7603,7 +7621,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -8015,7 +8033,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8221,7 +8239,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8508,7 +8526,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ36">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR36">
         <v>2.14</v>
@@ -8839,7 +8857,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8917,7 +8935,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ38">
         <v>1.17</v>
@@ -9045,7 +9063,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9126,7 +9144,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ39">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -9329,7 +9347,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
         <v>1.67</v>
@@ -9744,7 +9762,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ42">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR42">
         <v>1.99</v>
@@ -9869,7 +9887,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9947,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43">
         <v>0.75</v>
@@ -10075,7 +10093,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10362,7 +10380,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10565,7 +10583,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
@@ -10693,7 +10711,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10899,7 +10917,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11105,7 +11123,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11186,7 +11204,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ49">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11723,7 +11741,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11804,7 +11822,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ52">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
         <v>1.4</v>
@@ -12007,7 +12025,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12135,7 +12153,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12213,7 +12231,7 @@
         <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ54">
         <v>1.17</v>
@@ -12341,7 +12359,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12422,7 +12440,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ55">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR55">
         <v>1.16</v>
@@ -12625,7 +12643,7 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ56">
         <v>0.67</v>
@@ -12753,7 +12771,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12834,7 +12852,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ57">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR57">
         <v>1.84</v>
@@ -12959,7 +12977,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13165,7 +13183,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13452,7 +13470,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR60">
         <v>1.32</v>
@@ -13655,7 +13673,7 @@
         <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ61">
         <v>2.17</v>
@@ -13783,7 +13801,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13989,7 +14007,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14195,7 +14213,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14479,7 +14497,7 @@
         <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ65">
         <v>0.75</v>
@@ -14688,7 +14706,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ66">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.31</v>
@@ -14813,7 +14831,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14891,7 +14909,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ67">
         <v>1.17</v>
@@ -15100,7 +15118,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ68">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR68">
         <v>1.45</v>
@@ -15225,7 +15243,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15306,7 +15324,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15431,7 +15449,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15509,10 +15527,10 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR70">
         <v>1.11</v>
@@ -15715,7 +15733,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ71">
         <v>1.5</v>
@@ -16049,7 +16067,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16461,7 +16479,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16667,7 +16685,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17079,7 +17097,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17285,7 +17303,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17491,7 +17509,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17569,7 +17587,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -17775,7 +17793,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ81">
         <v>1.33</v>
@@ -17903,7 +17921,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -17984,7 +18002,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR82">
         <v>1.27</v>
@@ -18109,7 +18127,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18187,10 +18205,10 @@
         <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR83">
         <v>1.54</v>
@@ -18393,10 +18411,10 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ84">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR84">
         <v>2.03</v>
@@ -18521,7 +18539,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18933,7 +18951,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19014,7 +19032,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ87">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR87">
         <v>1.2</v>
@@ -19551,7 +19569,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19757,7 +19775,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19963,7 +19981,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20247,7 +20265,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20375,7 +20393,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20453,7 +20471,7 @@
         <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ94">
         <v>1.67</v>
@@ -20581,7 +20599,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20662,7 +20680,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR95">
         <v>1.27</v>
@@ -20787,7 +20805,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20868,7 +20886,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21071,10 +21089,10 @@
         <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ97">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21199,7 +21217,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21277,10 +21295,10 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ98">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR98">
         <v>1.1</v>
@@ -21405,7 +21423,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21689,10 +21707,10 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ100">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -22307,7 +22325,7 @@
         <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ103">
         <v>0.75</v>
@@ -22516,7 +22534,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ104">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR104">
         <v>1.19</v>
@@ -22722,7 +22740,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR105">
         <v>1.29</v>
@@ -23131,7 +23149,7 @@
         <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -23340,7 +23358,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR108">
         <v>1.22</v>
@@ -23877,7 +23895,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24083,7 +24101,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24161,7 +24179,7 @@
         <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ112">
         <v>1.17</v>
@@ -24907,7 +24925,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -24985,7 +25003,7 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ116">
         <v>1.5</v>
@@ -25113,7 +25131,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25194,7 +25212,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ117">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25319,7 +25337,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25525,7 +25543,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25606,7 +25624,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ119">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR119">
         <v>1.85</v>
@@ -25731,7 +25749,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26015,7 +26033,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ121">
         <v>1.17</v>
@@ -26143,7 +26161,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26224,7 +26242,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR122">
         <v>1.28</v>
@@ -26349,7 +26367,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26427,7 +26445,7 @@
         <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ123">
         <v>1.67</v>
@@ -26555,7 +26573,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -27045,10 +27063,10 @@
         <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ126">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27585,7 +27603,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27791,7 +27809,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28281,10 +28299,10 @@
         <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ132">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR132">
         <v>1.43</v>
@@ -28490,7 +28508,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ133">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR133">
         <v>1.91</v>
@@ -28821,7 +28839,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29105,7 +29123,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP136">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ136">
         <v>0.67</v>
@@ -29233,7 +29251,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29520,7 +29538,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ138">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR138">
         <v>2.02</v>
@@ -29645,7 +29663,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29723,7 +29741,7 @@
         <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ139">
         <v>1.17</v>
@@ -30135,10 +30153,10 @@
         <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ141">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR141">
         <v>1.93</v>
@@ -30263,7 +30281,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30469,7 +30487,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -31087,7 +31105,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31168,7 +31186,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ146">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR146">
         <v>1.73</v>
@@ -31577,7 +31595,7 @@
         <v>0.6</v>
       </c>
       <c r="AP148">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ148">
         <v>0.5</v>
@@ -31786,7 +31804,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ149">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR149">
         <v>1.24</v>
@@ -31911,7 +31929,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -31992,7 +32010,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ150">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32117,7 +32135,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32195,7 +32213,7 @@
         <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -32401,10 +32419,10 @@
         <v>1.9</v>
       </c>
       <c r="AP152">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ152">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR152">
         <v>1.42</v>
@@ -32735,7 +32753,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32941,7 +32959,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33019,7 +33037,7 @@
         <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ155">
         <v>1.17</v>
@@ -33353,7 +33371,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33559,7 +33577,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33765,7 +33783,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33971,7 +33989,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34589,7 +34607,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35001,7 +35019,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35158,6 +35176,830 @@
       </c>
       <c r="BP165">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7537456</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45711.47916666666</v>
+      </c>
+      <c r="F166">
+        <v>24</v>
+      </c>
+      <c r="G166" t="s">
+        <v>82</v>
+      </c>
+      <c r="H166" t="s">
+        <v>76</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>3</v>
+      </c>
+      <c r="O166" t="s">
+        <v>185</v>
+      </c>
+      <c r="P166" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q166">
+        <v>2.2</v>
+      </c>
+      <c r="R166">
+        <v>2.1</v>
+      </c>
+      <c r="S166">
+        <v>6.5</v>
+      </c>
+      <c r="T166">
+        <v>1.5</v>
+      </c>
+      <c r="U166">
+        <v>2.5</v>
+      </c>
+      <c r="V166">
+        <v>3.4</v>
+      </c>
+      <c r="W166">
+        <v>1.3</v>
+      </c>
+      <c r="X166">
+        <v>10</v>
+      </c>
+      <c r="Y166">
+        <v>1.06</v>
+      </c>
+      <c r="Z166">
+        <v>1.5</v>
+      </c>
+      <c r="AA166">
+        <v>3.8</v>
+      </c>
+      <c r="AB166">
+        <v>6.5</v>
+      </c>
+      <c r="AC166">
+        <v>1.08</v>
+      </c>
+      <c r="AD166">
+        <v>8.4</v>
+      </c>
+      <c r="AE166">
+        <v>1.4</v>
+      </c>
+      <c r="AF166">
+        <v>2.85</v>
+      </c>
+      <c r="AG166">
+        <v>2.05</v>
+      </c>
+      <c r="AH166">
+        <v>1.61</v>
+      </c>
+      <c r="AI166">
+        <v>2.25</v>
+      </c>
+      <c r="AJ166">
+        <v>1.57</v>
+      </c>
+      <c r="AK166">
+        <v>1.14</v>
+      </c>
+      <c r="AL166">
+        <v>1.28</v>
+      </c>
+      <c r="AM166">
+        <v>2.42</v>
+      </c>
+      <c r="AN166">
+        <v>2.09</v>
+      </c>
+      <c r="AO166">
+        <v>1.45</v>
+      </c>
+      <c r="AP166">
+        <v>2.17</v>
+      </c>
+      <c r="AQ166">
+        <v>1.33</v>
+      </c>
+      <c r="AR166">
+        <v>1.46</v>
+      </c>
+      <c r="AS166">
+        <v>0.96</v>
+      </c>
+      <c r="AT166">
+        <v>2.42</v>
+      </c>
+      <c r="AU166">
+        <v>11</v>
+      </c>
+      <c r="AV166">
+        <v>2</v>
+      </c>
+      <c r="AW166">
+        <v>13</v>
+      </c>
+      <c r="AX166">
+        <v>6</v>
+      </c>
+      <c r="AY166">
+        <v>30</v>
+      </c>
+      <c r="AZ166">
+        <v>11</v>
+      </c>
+      <c r="BA166">
+        <v>4</v>
+      </c>
+      <c r="BB166">
+        <v>6</v>
+      </c>
+      <c r="BC166">
+        <v>10</v>
+      </c>
+      <c r="BD166">
+        <v>1.43</v>
+      </c>
+      <c r="BE166">
+        <v>6.75</v>
+      </c>
+      <c r="BF166">
+        <v>3.2</v>
+      </c>
+      <c r="BG166">
+        <v>1.46</v>
+      </c>
+      <c r="BH166">
+        <v>2.33</v>
+      </c>
+      <c r="BI166">
+        <v>1.85</v>
+      </c>
+      <c r="BJ166">
+        <v>1.95</v>
+      </c>
+      <c r="BK166">
+        <v>2.28</v>
+      </c>
+      <c r="BL166">
+        <v>1.49</v>
+      </c>
+      <c r="BM166">
+        <v>3</v>
+      </c>
+      <c r="BN166">
+        <v>1.29</v>
+      </c>
+      <c r="BO166">
+        <v>4</v>
+      </c>
+      <c r="BP166">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7537460</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45711.5</v>
+      </c>
+      <c r="F167">
+        <v>24</v>
+      </c>
+      <c r="G167" t="s">
+        <v>81</v>
+      </c>
+      <c r="H167" t="s">
+        <v>73</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>3</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>4</v>
+      </c>
+      <c r="O167" t="s">
+        <v>186</v>
+      </c>
+      <c r="P167" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q167">
+        <v>9</v>
+      </c>
+      <c r="R167">
+        <v>2.38</v>
+      </c>
+      <c r="S167">
+        <v>1.83</v>
+      </c>
+      <c r="T167">
+        <v>1.4</v>
+      </c>
+      <c r="U167">
+        <v>2.75</v>
+      </c>
+      <c r="V167">
+        <v>2.75</v>
+      </c>
+      <c r="W167">
+        <v>1.4</v>
+      </c>
+      <c r="X167">
+        <v>8</v>
+      </c>
+      <c r="Y167">
+        <v>1.08</v>
+      </c>
+      <c r="Z167">
+        <v>8.5</v>
+      </c>
+      <c r="AA167">
+        <v>4.75</v>
+      </c>
+      <c r="AB167">
+        <v>1.3</v>
+      </c>
+      <c r="AC167">
+        <v>1.05</v>
+      </c>
+      <c r="AD167">
+        <v>11</v>
+      </c>
+      <c r="AE167">
+        <v>1.3</v>
+      </c>
+      <c r="AF167">
+        <v>3.45</v>
+      </c>
+      <c r="AG167">
+        <v>1.75</v>
+      </c>
+      <c r="AH167">
+        <v>1.85</v>
+      </c>
+      <c r="AI167">
+        <v>2.25</v>
+      </c>
+      <c r="AJ167">
+        <v>1.57</v>
+      </c>
+      <c r="AK167">
+        <v>3.3</v>
+      </c>
+      <c r="AL167">
+        <v>1.19</v>
+      </c>
+      <c r="AM167">
+        <v>1.07</v>
+      </c>
+      <c r="AN167">
+        <v>0.27</v>
+      </c>
+      <c r="AO167">
+        <v>1.73</v>
+      </c>
+      <c r="AP167">
+        <v>0.5</v>
+      </c>
+      <c r="AQ167">
+        <v>1.58</v>
+      </c>
+      <c r="AR167">
+        <v>1.13</v>
+      </c>
+      <c r="AS167">
+        <v>1.5</v>
+      </c>
+      <c r="AT167">
+        <v>2.63</v>
+      </c>
+      <c r="AU167">
+        <v>4</v>
+      </c>
+      <c r="AV167">
+        <v>10</v>
+      </c>
+      <c r="AW167">
+        <v>4</v>
+      </c>
+      <c r="AX167">
+        <v>11</v>
+      </c>
+      <c r="AY167">
+        <v>9</v>
+      </c>
+      <c r="AZ167">
+        <v>28</v>
+      </c>
+      <c r="BA167">
+        <v>5</v>
+      </c>
+      <c r="BB167">
+        <v>6</v>
+      </c>
+      <c r="BC167">
+        <v>11</v>
+      </c>
+      <c r="BD167">
+        <v>7.9</v>
+      </c>
+      <c r="BE167">
+        <v>9.1</v>
+      </c>
+      <c r="BF167">
+        <v>1.12</v>
+      </c>
+      <c r="BG167">
+        <v>1.38</v>
+      </c>
+      <c r="BH167">
+        <v>2.71</v>
+      </c>
+      <c r="BI167">
+        <v>1.7</v>
+      </c>
+      <c r="BJ167">
+        <v>2.03</v>
+      </c>
+      <c r="BK167">
+        <v>2.15</v>
+      </c>
+      <c r="BL167">
+        <v>1.59</v>
+      </c>
+      <c r="BM167">
+        <v>2.88</v>
+      </c>
+      <c r="BN167">
+        <v>1.32</v>
+      </c>
+      <c r="BO167">
+        <v>4.35</v>
+      </c>
+      <c r="BP167">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7537454</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45711.60416666666</v>
+      </c>
+      <c r="F168">
+        <v>24</v>
+      </c>
+      <c r="G168" t="s">
+        <v>79</v>
+      </c>
+      <c r="H168" t="s">
+        <v>75</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>3</v>
+      </c>
+      <c r="N168">
+        <v>3</v>
+      </c>
+      <c r="O168" t="s">
+        <v>84</v>
+      </c>
+      <c r="P168" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q168">
+        <v>7</v>
+      </c>
+      <c r="R168">
+        <v>2.2</v>
+      </c>
+      <c r="S168">
+        <v>2.1</v>
+      </c>
+      <c r="T168">
+        <v>1.44</v>
+      </c>
+      <c r="U168">
+        <v>2.63</v>
+      </c>
+      <c r="V168">
+        <v>3.25</v>
+      </c>
+      <c r="W168">
+        <v>1.33</v>
+      </c>
+      <c r="X168">
+        <v>9</v>
+      </c>
+      <c r="Y168">
+        <v>1.07</v>
+      </c>
+      <c r="Z168">
+        <v>6.5</v>
+      </c>
+      <c r="AA168">
+        <v>3.8</v>
+      </c>
+      <c r="AB168">
+        <v>1.47</v>
+      </c>
+      <c r="AC168">
+        <v>1.07</v>
+      </c>
+      <c r="AD168">
+        <v>9</v>
+      </c>
+      <c r="AE168">
+        <v>1.38</v>
+      </c>
+      <c r="AF168">
+        <v>2.95</v>
+      </c>
+      <c r="AG168">
+        <v>2</v>
+      </c>
+      <c r="AH168">
+        <v>1.67</v>
+      </c>
+      <c r="AI168">
+        <v>2.2</v>
+      </c>
+      <c r="AJ168">
+        <v>1.62</v>
+      </c>
+      <c r="AK168">
+        <v>2.5</v>
+      </c>
+      <c r="AL168">
+        <v>1.26</v>
+      </c>
+      <c r="AM168">
+        <v>1.13</v>
+      </c>
+      <c r="AN168">
+        <v>1.73</v>
+      </c>
+      <c r="AO168">
+        <v>1.73</v>
+      </c>
+      <c r="AP168">
+        <v>1.58</v>
+      </c>
+      <c r="AQ168">
+        <v>1.83</v>
+      </c>
+      <c r="AR168">
+        <v>1.45</v>
+      </c>
+      <c r="AS168">
+        <v>1.73</v>
+      </c>
+      <c r="AT168">
+        <v>3.18</v>
+      </c>
+      <c r="AU168">
+        <v>0</v>
+      </c>
+      <c r="AV168">
+        <v>6</v>
+      </c>
+      <c r="AW168">
+        <v>3</v>
+      </c>
+      <c r="AX168">
+        <v>9</v>
+      </c>
+      <c r="AY168">
+        <v>3</v>
+      </c>
+      <c r="AZ168">
+        <v>19</v>
+      </c>
+      <c r="BA168">
+        <v>0</v>
+      </c>
+      <c r="BB168">
+        <v>2</v>
+      </c>
+      <c r="BC168">
+        <v>2</v>
+      </c>
+      <c r="BD168">
+        <v>3.4</v>
+      </c>
+      <c r="BE168">
+        <v>7</v>
+      </c>
+      <c r="BF168">
+        <v>1.38</v>
+      </c>
+      <c r="BG168">
+        <v>1.28</v>
+      </c>
+      <c r="BH168">
+        <v>3.08</v>
+      </c>
+      <c r="BI168">
+        <v>1.53</v>
+      </c>
+      <c r="BJ168">
+        <v>2.27</v>
+      </c>
+      <c r="BK168">
+        <v>1.94</v>
+      </c>
+      <c r="BL168">
+        <v>1.77</v>
+      </c>
+      <c r="BM168">
+        <v>2.51</v>
+      </c>
+      <c r="BN168">
+        <v>1.44</v>
+      </c>
+      <c r="BO168">
+        <v>3.34</v>
+      </c>
+      <c r="BP168">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7537459</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45711.64583333334</v>
+      </c>
+      <c r="F169">
+        <v>24</v>
+      </c>
+      <c r="G169" t="s">
+        <v>80</v>
+      </c>
+      <c r="H169" t="s">
+        <v>71</v>
+      </c>
+      <c r="I169">
+        <v>2</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>3</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
+      </c>
+      <c r="M169">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>3</v>
+      </c>
+      <c r="O169" t="s">
+        <v>187</v>
+      </c>
+      <c r="P169" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q169">
+        <v>2.3</v>
+      </c>
+      <c r="R169">
+        <v>2.2</v>
+      </c>
+      <c r="S169">
+        <v>5.5</v>
+      </c>
+      <c r="T169">
+        <v>1.44</v>
+      </c>
+      <c r="U169">
+        <v>2.63</v>
+      </c>
+      <c r="V169">
+        <v>3</v>
+      </c>
+      <c r="W169">
+        <v>1.36</v>
+      </c>
+      <c r="X169">
+        <v>9</v>
+      </c>
+      <c r="Y169">
+        <v>1.07</v>
+      </c>
+      <c r="Z169">
+        <v>1.6</v>
+      </c>
+      <c r="AA169">
+        <v>3.7</v>
+      </c>
+      <c r="AB169">
+        <v>5.25</v>
+      </c>
+      <c r="AC169">
+        <v>1.06</v>
+      </c>
+      <c r="AD169">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE169">
+        <v>1.33</v>
+      </c>
+      <c r="AF169">
+        <v>3.25</v>
+      </c>
+      <c r="AG169">
+        <v>1.85</v>
+      </c>
+      <c r="AH169">
+        <v>1.75</v>
+      </c>
+      <c r="AI169">
+        <v>1.95</v>
+      </c>
+      <c r="AJ169">
+        <v>1.8</v>
+      </c>
+      <c r="AK169">
+        <v>1.18</v>
+      </c>
+      <c r="AL169">
+        <v>1.3</v>
+      </c>
+      <c r="AM169">
+        <v>2.19</v>
+      </c>
+      <c r="AN169">
+        <v>2.27</v>
+      </c>
+      <c r="AO169">
+        <v>2.36</v>
+      </c>
+      <c r="AP169">
+        <v>2.33</v>
+      </c>
+      <c r="AQ169">
+        <v>2.17</v>
+      </c>
+      <c r="AR169">
+        <v>1.94</v>
+      </c>
+      <c r="AS169">
+        <v>1.66</v>
+      </c>
+      <c r="AT169">
+        <v>3.6</v>
+      </c>
+      <c r="AU169">
+        <v>8</v>
+      </c>
+      <c r="AV169">
+        <v>8</v>
+      </c>
+      <c r="AW169">
+        <v>11</v>
+      </c>
+      <c r="AX169">
+        <v>2</v>
+      </c>
+      <c r="AY169">
+        <v>23</v>
+      </c>
+      <c r="AZ169">
+        <v>10</v>
+      </c>
+      <c r="BA169">
+        <v>2</v>
+      </c>
+      <c r="BB169">
+        <v>3</v>
+      </c>
+      <c r="BC169">
+        <v>5</v>
+      </c>
+      <c r="BD169">
+        <v>1.56</v>
+      </c>
+      <c r="BE169">
+        <v>6.4</v>
+      </c>
+      <c r="BF169">
+        <v>2.7</v>
+      </c>
+      <c r="BG169">
+        <v>1.45</v>
+      </c>
+      <c r="BH169">
+        <v>2.48</v>
+      </c>
+      <c r="BI169">
+        <v>1.83</v>
+      </c>
+      <c r="BJ169">
+        <v>1.87</v>
+      </c>
+      <c r="BK169">
+        <v>2.38</v>
+      </c>
+      <c r="BL169">
+        <v>1.49</v>
+      </c>
+      <c r="BM169">
+        <v>3.2</v>
+      </c>
+      <c r="BN169">
+        <v>1.26</v>
+      </c>
+      <c r="BO169">
+        <v>4.1</v>
+      </c>
+      <c r="BP169">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1519,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ2">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ3">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2137,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2343,10 +2343,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2549,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2958,22 +2958,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3167,19 +3167,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3373,7 +3373,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3573,25 +3573,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3794,10 +3794,10 @@
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AT13">
-        <v>1.83</v>
+        <v>3.09</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3988,22 +3988,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AT14">
-        <v>1.21</v>
+        <v>2.59</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4191,25 +4191,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>0.36</v>
+        <v>2.07</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4397,7 +4397,7 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO16">
         <v>3</v>
@@ -4406,16 +4406,16 @@
         <v>0.5</v>
       </c>
       <c r="AQ16">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS16">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AT16">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4603,25 +4603,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS17">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AT17">
-        <v>1.15</v>
+        <v>3.02</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4818,16 +4818,16 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AS18">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT18">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -5015,25 +5015,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ19">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR19">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT19">
-        <v>1.38</v>
+        <v>3.42</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5221,25 +5221,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR20">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AS20">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="AT20">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5430,22 +5430,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT21">
-        <v>1.23</v>
+        <v>3.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5633,25 +5633,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP22">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ22">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5839,25 +5839,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO23">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP23">
         <v>0.5</v>
       </c>
       <c r="AQ23">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="AS23">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="AT23">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6045,25 +6045,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP24">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR24">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="AS24">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT24">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6254,22 +6254,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ25">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR25">
-        <v>0.98</v>
+        <v>1.23</v>
       </c>
       <c r="AS25">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AT25">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6460,22 +6460,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AS26">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="AT26">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6666,22 +6666,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ27">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR27">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AS27">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AT27">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6869,25 +6869,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT28">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -7075,25 +7075,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR29">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AS29">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AT29">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7281,25 +7281,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP30">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ30">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR30">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AT30">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7487,25 +7487,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO31">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP31">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR31">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS31">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AT31">
-        <v>3.01</v>
+        <v>3.32</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7693,25 +7693,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP32">
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR32">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AT32">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7902,22 +7902,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR33">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AS33">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="AT33">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8105,25 +8105,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP34">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS34">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8311,25 +8311,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP35">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
       </c>
       <c r="AR35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS35">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="AT35">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8517,25 +8517,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP36">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ36">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR36">
-        <v>2.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS36">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AT36">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8723,25 +8723,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AO37">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP37">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ37">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR37">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="AT37">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8929,25 +8929,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP38">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR38">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AS38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT38">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9135,25 +9135,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
         <v>1.33</v>
       </c>
       <c r="AR39">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="AS39">
-        <v>0.68</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9344,22 +9344,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR40">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AS40">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AT40">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9547,25 +9547,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AO41">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP41">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ41">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR41">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT41">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9753,25 +9753,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ42">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR42">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS42">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AT42">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9959,25 +9959,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
         <v>0.5</v>
       </c>
       <c r="AQ43">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="AS43">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AT43">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10168,22 +10168,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR44">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS44">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AT44">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10374,22 +10374,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AP45">
         <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR45">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AS45">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AT45">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10577,25 +10577,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO46">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP46">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
       </c>
       <c r="AR46">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS46">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="AT46">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10783,25 +10783,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR47">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AS47">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="AT47">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10989,25 +10989,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO48">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR48">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="AS48">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AT48">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11198,22 +11198,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP49">
+        <v>1.13</v>
+      </c>
+      <c r="AQ49">
+        <v>1.79</v>
+      </c>
+      <c r="AR49">
         <v>1.08</v>
       </c>
-      <c r="AQ49">
-        <v>2.17</v>
-      </c>
-      <c r="AR49">
-        <v>1.09</v>
-      </c>
       <c r="AS49">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AT49">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11401,25 +11401,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP50">
+        <v>1.92</v>
+      </c>
+      <c r="AQ50">
         <v>2.25</v>
       </c>
-      <c r="AQ50">
-        <v>2.17</v>
-      </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AS50">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AT50">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11607,25 +11607,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AO51">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ51">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AS51">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11813,25 +11813,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO52">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP52">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
       </c>
       <c r="AR52">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS52">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AT52">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12019,25 +12019,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AO53">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP53">
         <v>0.5</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR53">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS53">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT53">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12225,25 +12225,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP54">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ54">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR54">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AS54">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT54">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12431,25 +12431,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO55">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ55">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR55">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="AS55">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AT55">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12637,25 +12637,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO56">
+        <v>0.71</v>
+      </c>
+      <c r="AP56">
+        <v>1.67</v>
+      </c>
+      <c r="AQ56">
         <v>0.75</v>
       </c>
-      <c r="AP56">
-        <v>2.17</v>
-      </c>
-      <c r="AQ56">
-        <v>0.67</v>
-      </c>
       <c r="AR56">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AS56">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AT56">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12843,25 +12843,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AP57">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ57">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR57">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AS57">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AT57">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -13052,22 +13052,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="AP58">
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR58">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AS58">
-        <v>0.8100000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="AT58">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13255,25 +13255,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP59">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ59">
         <v>0.5</v>
       </c>
       <c r="AR59">
+        <v>0.93</v>
+      </c>
+      <c r="AS59">
         <v>0.99</v>
       </c>
-      <c r="AS59">
-        <v>0.88</v>
-      </c>
       <c r="AT59">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13461,25 +13461,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="AO60">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AP60">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ60">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR60">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS60">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AT60">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13667,25 +13667,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO61">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AP61">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ61">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR61">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AS61">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AT61">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13873,25 +13873,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO62">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR62">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AS62">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT62">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14079,25 +14079,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO63">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP63">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AS63">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="AT63">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14285,25 +14285,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AO64">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP64">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ64">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR64">
-        <v>1.31</v>
+        <v>0.96</v>
       </c>
       <c r="AS64">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AT64">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14491,25 +14491,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO65">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AP65">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ65">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR65">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AS65">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT65">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14697,25 +14697,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO66">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP66">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ66">
         <v>1.33</v>
       </c>
       <c r="AR66">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AS66">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AT66">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14903,22 +14903,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO67">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ67">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR67">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS67">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15109,25 +15109,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="AO68">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP68">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ68">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR68">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS68">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT68">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15315,25 +15315,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ69">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR69">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS69">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AT69">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15521,25 +15521,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AO70">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP70">
         <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR70">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AS70">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AT70">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15727,25 +15727,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AO71">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AP71">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR71">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS71">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT71">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15933,25 +15933,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO72">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AP72">
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR72">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AS72">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AT72">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16142,22 +16142,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AP73">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ73">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR73">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS73">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT73">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16345,25 +16345,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO74">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP74">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR74">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AS74">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AT74">
-        <v>2.69</v>
+        <v>3.01</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16551,25 +16551,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR75">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AS75">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AT75">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16760,22 +16760,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR76">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AS76">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AT76">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16966,22 +16966,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP77">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ77">
         <v>0.5</v>
       </c>
       <c r="AR77">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AS77">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT77">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17169,25 +17169,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO78">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AP78">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ78">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR78">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AT78">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17375,25 +17375,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP79">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ79">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR79">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT79">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17581,25 +17581,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AO80">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AP80">
         <v>0.5</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR80">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AS80">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT80">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17787,25 +17787,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AO81">
-        <v>1.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP81">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR81">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AS81">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT81">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17993,25 +17993,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AO82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AP82">
         <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR82">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AS82">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18199,25 +18199,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO83">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AP83">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR83">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AS83">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AT83">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18405,25 +18405,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO84">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AP84">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ84">
+        <v>2.17</v>
+      </c>
+      <c r="AR84">
+        <v>1.9</v>
+      </c>
+      <c r="AS84">
         <v>1.83</v>
       </c>
-      <c r="AR84">
-        <v>2.03</v>
-      </c>
-      <c r="AS84">
-        <v>1.78</v>
-      </c>
       <c r="AT84">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18611,25 +18611,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>0.67</v>
+        <v>1.27</v>
       </c>
       <c r="AO85">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AP85">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ85">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR85">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS85">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT85">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18817,25 +18817,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
       <c r="AO86">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ86">
         <v>0.5</v>
       </c>
       <c r="AR86">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AS86">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AT86">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19023,25 +19023,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO87">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ87">
         <v>1.33</v>
       </c>
       <c r="AR87">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AS87">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="AT87">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19229,25 +19229,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO88">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AS88">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AT88">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19435,25 +19435,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO89">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP89">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR89">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS89">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT89">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19641,25 +19641,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO90">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ90">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR90">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS90">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AT90">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19847,25 +19847,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.17</v>
+        <v>1.92</v>
       </c>
       <c r="AO91">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR91">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AS91">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="AT91">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20056,22 +20056,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AP92">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR92">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS92">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT92">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20259,25 +20259,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AO93">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AP93">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR93">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AS93">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="AT93">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20465,25 +20465,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AO94">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AP94">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR94">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AS94">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT94">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20671,25 +20671,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO95">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ95">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR95">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS95">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AT95">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20877,25 +20877,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO96">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ96">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR96">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AT96">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21083,25 +21083,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AO97">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AP97">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ97">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR97">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS97">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT97">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21289,10 +21289,10 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO98">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP98">
         <v>0.5</v>
@@ -21301,13 +21301,13 @@
         <v>1.33</v>
       </c>
       <c r="AR98">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AS98">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT98">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21495,25 +21495,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="AP99">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR99">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AT99">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21701,25 +21701,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="AO100">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AP100">
         <v>0.5</v>
       </c>
       <c r="AQ100">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR100">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AS100">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AT100">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21907,25 +21907,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO101">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AP101">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR101">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AS101">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT101">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22113,25 +22113,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="AO102">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR102">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AS102">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT102">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22319,25 +22319,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="AO103">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AP103">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS103">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT103">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22525,25 +22525,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO104">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP104">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ104">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR104">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AS104">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AT104">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22731,25 +22731,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AO105">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="AP105">
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR105">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AS105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AT105">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22937,25 +22937,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AO106">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AP106">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ106">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR106">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AS106">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AT106">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23143,25 +23143,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AO107">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
       </c>
       <c r="AR107">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AS107">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT107">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23349,25 +23349,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO108">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ108">
         <v>1.33</v>
       </c>
       <c r="AR108">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AS108">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
       <c r="AT108">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23555,25 +23555,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AO109">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="AP109">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ109">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR109">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AS109">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="AT109">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23761,25 +23761,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO110">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ110">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR110">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT110">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23967,25 +23967,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AO111">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP111">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ111">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR111">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AS111">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT111">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24173,25 +24173,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR112">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT112">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24379,25 +24379,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO113">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AP113">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR113">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AS113">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="AT113">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24585,25 +24585,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO114">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP114">
         <v>0.75</v>
-      </c>
-      <c r="AP114">
-        <v>0.83</v>
       </c>
       <c r="AQ114">
         <v>0.5</v>
       </c>
       <c r="AR114">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AS114">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="AT114">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24794,22 +24794,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
+        <v>1.06</v>
+      </c>
+      <c r="AP115">
         <v>1.13</v>
       </c>
-      <c r="AP115">
+      <c r="AQ115">
+        <v>0.92</v>
+      </c>
+      <c r="AR115">
         <v>1.08</v>
       </c>
-      <c r="AQ115">
-        <v>0.75</v>
-      </c>
-      <c r="AR115">
-        <v>1.12</v>
-      </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT115">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24997,25 +24997,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AO116">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP116">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR116">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS116">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT116">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25203,25 +25203,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO117">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AP117">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ117">
+        <v>2.17</v>
+      </c>
+      <c r="AR117">
+        <v>1.1</v>
+      </c>
+      <c r="AS117">
         <v>1.83</v>
       </c>
-      <c r="AR117">
-        <v>1.31</v>
-      </c>
-      <c r="AS117">
-        <v>1.71</v>
-      </c>
       <c r="AT117">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25409,25 +25409,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AO118">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AP118">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ118">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR118">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS118">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT118">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25615,25 +25615,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO119">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AP119">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ119">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR119">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25821,25 +25821,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AO120">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AP120">
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR120">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AS120">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AT120">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26027,25 +26027,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AP121">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ121">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR121">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AS121">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AT121">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26236,22 +26236,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AP122">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ122">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR122">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AS122">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AT122">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26439,25 +26439,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AO123">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AP123">
         <v>0.5</v>
       </c>
       <c r="AQ123">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR123">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AS123">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AT123">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26645,25 +26645,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AO124">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR124">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS124">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="AT124">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26851,25 +26851,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO125">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AP125">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ125">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR125">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AS125">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AT125">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27057,25 +27057,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AO126">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP126">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ126">
         <v>1.33</v>
       </c>
       <c r="AR126">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AS126">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="AT126">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27263,25 +27263,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AO127">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ127">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR127">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AS127">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AT127">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27469,25 +27469,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AO128">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="AP128">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ128">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR128">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AS128">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT128">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27675,25 +27675,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO129">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AP129">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ129">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR129">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AS129">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AT129">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27881,25 +27881,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
+        <v>1</v>
+      </c>
+      <c r="AO130">
+        <v>1.39</v>
+      </c>
+      <c r="AP130">
+        <v>1.13</v>
+      </c>
+      <c r="AQ130">
+        <v>1.46</v>
+      </c>
+      <c r="AR130">
         <v>1.11</v>
       </c>
-      <c r="AO130">
-        <v>1.33</v>
-      </c>
-      <c r="AP130">
-        <v>1.08</v>
-      </c>
-      <c r="AQ130">
-        <v>1.33</v>
-      </c>
-      <c r="AR130">
-        <v>1.17</v>
-      </c>
       <c r="AS130">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AT130">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -28087,25 +28087,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AO131">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AP131">
         <v>1.33</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AS131">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AT131">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28293,25 +28293,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AP132">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ132">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR132">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS132">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT132">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28502,22 +28502,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AP133">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ133">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR133">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AS133">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AT133">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28708,10 +28708,10 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ134">
         <v>0.5</v>
@@ -28720,10 +28720,10 @@
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AT134">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28911,25 +28911,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AO135">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AP135">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ135">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR135">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AS135">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AT135">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29117,25 +29117,25 @@
         <v>1.86</v>
       </c>
       <c r="AN136">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AO136">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AP136">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR136">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS136">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AT136">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29323,25 +29323,25 @@
         <v>1.77</v>
       </c>
       <c r="AN137">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP137">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR137">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS137">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AT137">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29529,25 +29529,25 @@
         <v>4.6</v>
       </c>
       <c r="AN138">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AO138">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AP138">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ138">
         <v>1.33</v>
       </c>
       <c r="AR138">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AS138">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AT138">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU138">
         <v>5</v>
@@ -29735,25 +29735,25 @@
         <v>1.21</v>
       </c>
       <c r="AN139">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AO139">
-        <v>0.89</v>
+        <v>1.47</v>
       </c>
       <c r="AP139">
         <v>0.5</v>
       </c>
       <c r="AQ139">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR139">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AS139">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AT139">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU139">
         <v>2</v>
@@ -29941,22 +29941,22 @@
         <v>3.6</v>
       </c>
       <c r="AN140">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AO140">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ140">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR140">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AS140">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AT140">
         <v>2.75</v>
@@ -30147,25 +30147,25 @@
         <v>1.93</v>
       </c>
       <c r="AN141">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AO141">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AP141">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ141">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR141">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AS141">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AT141">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30353,25 +30353,25 @@
         <v>3.2</v>
       </c>
       <c r="AN142">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AO142">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AP142">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR142">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS142">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT142">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AU142">
         <v>9</v>
@@ -30559,25 +30559,25 @@
         <v>1.53</v>
       </c>
       <c r="AN143">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AO143">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ143">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR143">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS143">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="AT143">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="AU143">
         <v>5</v>
@@ -30765,25 +30765,25 @@
         <v>1.09</v>
       </c>
       <c r="AN144">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AO144">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP144">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ144">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR144">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AS144">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AT144">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30971,25 +30971,25 @@
         <v>1.25</v>
       </c>
       <c r="AN145">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO145">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AP145">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ145">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR145">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="AS145">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AT145">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31177,25 +31177,25 @@
         <v>1.48</v>
       </c>
       <c r="AN146">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AO146">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ146">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR146">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AS146">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AT146">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31386,22 +31386,22 @@
         <v>1.3</v>
       </c>
       <c r="AO147">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AP147">
         <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR147">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AS147">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AT147">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU147">
         <v>0</v>
@@ -31589,25 +31589,25 @@
         <v>2.28</v>
       </c>
       <c r="AN148">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AO148">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="AP148">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ148">
         <v>0.5</v>
       </c>
       <c r="AR148">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AS148">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AT148">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31795,25 +31795,25 @@
         <v>1.61</v>
       </c>
       <c r="AN149">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO149">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AP149">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ149">
         <v>1.33</v>
       </c>
       <c r="AR149">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AS149">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="AT149">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -32001,25 +32001,25 @@
         <v>1.17</v>
       </c>
       <c r="AN150">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AO150">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AP150">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ150">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR150">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AS150">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AT150">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AU150">
         <v>3</v>
@@ -32207,25 +32207,25 @@
         <v>3.55</v>
       </c>
       <c r="AN151">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AO151">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AP151">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR151">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AS151">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AT151">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32413,25 +32413,25 @@
         <v>1.26</v>
       </c>
       <c r="AN152">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO152">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AP152">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ152">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR152">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS152">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AT152">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="AU152">
         <v>8</v>
@@ -32619,25 +32619,25 @@
         <v>5.6</v>
       </c>
       <c r="AN153">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AO153">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AP153">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ153">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR153">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AS153">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT153">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="AU153">
         <v>12</v>
@@ -32825,25 +32825,25 @@
         <v>1.88</v>
       </c>
       <c r="AN154">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="AO154">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP154">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AQ154">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR154">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AS154">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="AT154">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="AU154">
         <v>6</v>
@@ -33031,25 +33031,25 @@
         <v>1.35</v>
       </c>
       <c r="AN155">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="AO155">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AP155">
         <v>0.5</v>
       </c>
       <c r="AQ155">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR155">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AS155">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AT155">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33237,25 +33237,25 @@
         <v>1.57</v>
       </c>
       <c r="AN156">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AO156">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AP156">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ156">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR156">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AS156">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT156">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AU156">
         <v>6</v>
@@ -33443,25 +33443,25 @@
         <v>3.7</v>
       </c>
       <c r="AN157">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AO157">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AP157">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AQ157">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AR157">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AS157">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AT157">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="AU157">
         <v>5</v>
@@ -33649,25 +33649,25 @@
         <v>1.33</v>
       </c>
       <c r="AN158">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AO158">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AP158">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AQ158">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AR158">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AS158">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AT158">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AU158">
         <v>6</v>
@@ -33855,25 +33855,25 @@
         <v>3.9</v>
       </c>
       <c r="AN159">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AO159">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="AP159">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AR159">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AS159">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AT159">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="AU159">
         <v>8</v>
@@ -34061,25 +34061,25 @@
         <v>1.04</v>
       </c>
       <c r="AN160">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AO160">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AP160">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ160">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AR160">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AS160">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AT160">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AU160">
         <v>2</v>
@@ -34267,25 +34267,25 @@
         <v>5.2</v>
       </c>
       <c r="AN161">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AO161">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="AP161">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
       </c>
       <c r="AR161">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AS161">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="AT161">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="AU161">
         <v>12</v>
@@ -34473,25 +34473,25 @@
         <v>1.61</v>
       </c>
       <c r="AN162">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AO162">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AP162">
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR162">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AS162">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="AT162">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="AU162">
         <v>4</v>
@@ -34679,22 +34679,22 @@
         <v>1.56</v>
       </c>
       <c r="AN163">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AO163">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AP163">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AQ163">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR163">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AS163">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AT163">
         <v>2.42</v>
@@ -34885,25 +34885,25 @@
         <v>1.91</v>
       </c>
       <c r="AN164">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="AO164">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AP164">
+        <v>1.29</v>
+      </c>
+      <c r="AQ164">
         <v>0.92</v>
       </c>
-      <c r="AQ164">
-        <v>0.75</v>
-      </c>
       <c r="AR164">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AS164">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AT164">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AU164">
         <v>6</v>
@@ -35091,25 +35091,25 @@
         <v>1.59</v>
       </c>
       <c r="AN165">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="AO165">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AP165">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AQ165">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR165">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS165">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AT165">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AU165">
         <v>2</v>
@@ -35297,25 +35297,25 @@
         <v>2.42</v>
       </c>
       <c r="AN166">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AO166">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AP166">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ166">
         <v>1.33</v>
       </c>
       <c r="AR166">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AS166">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="AT166">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AU166">
         <v>11</v>
@@ -35503,25 +35503,25 @@
         <v>1.07</v>
       </c>
       <c r="AN167">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AO167">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AP167">
         <v>0.5</v>
       </c>
       <c r="AQ167">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR167">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AS167">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AT167">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35709,25 +35709,25 @@
         <v>1.13</v>
       </c>
       <c r="AN168">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AO168">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AP168">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ168">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AR168">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AS168">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AT168">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AU168">
         <v>0</v>
@@ -35915,25 +35915,25 @@
         <v>2.19</v>
       </c>
       <c r="AN169">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AO169">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="AP169">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ169">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AR169">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AS169">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AT169">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AU169">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1519,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ2">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2137,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2343,10 +2343,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ6">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2549,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2958,22 +2958,22 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR9">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>3</v>
@@ -3167,19 +3167,19 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3373,7 +3373,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3573,25 +3573,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3794,10 +3794,10 @@
         <v>1.83</v>
       </c>
       <c r="AS13">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.09</v>
+        <v>1.83</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3988,22 +3988,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.59</v>
+        <v>1.21</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4191,25 +4191,25 @@
         <v>6.5</v>
       </c>
       <c r="AN15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS15">
         <v>0.36</v>
       </c>
       <c r="AT15">
-        <v>2.07</v>
+        <v>0.36</v>
       </c>
       <c r="AU15">
         <v>6</v>
@@ -4397,7 +4397,7 @@
         <v>1.05</v>
       </c>
       <c r="AN16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>3</v>
@@ -4406,16 +4406,16 @@
         <v>0.5</v>
       </c>
       <c r="AQ16">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR16">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AT16">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4603,25 +4603,25 @@
         <v>2.2</v>
       </c>
       <c r="AN17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AT17">
-        <v>3.02</v>
+        <v>1.15</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4818,16 +4818,16 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AT18">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AU18">
         <v>8</v>
@@ -5015,25 +5015,25 @@
         <v>1.03</v>
       </c>
       <c r="AN19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR19">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS19">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>3.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU19">
         <v>2</v>
@@ -5221,25 +5221,25 @@
         <v>1.61</v>
       </c>
       <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0.42</v>
+      </c>
+      <c r="AQ20">
         <v>1.5</v>
       </c>
-      <c r="AO20">
-        <v>0.5</v>
-      </c>
-      <c r="AP20">
-        <v>0.88</v>
-      </c>
-      <c r="AQ20">
-        <v>1.38</v>
-      </c>
       <c r="AR20">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AS20">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
       <c r="AT20">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5430,22 +5430,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ21">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR21">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS21">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>3.23</v>
+        <v>1.23</v>
       </c>
       <c r="AU21">
         <v>4</v>
@@ -5633,25 +5633,25 @@
         <v>1.05</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ22">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR22">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5839,25 +5839,25 @@
         <v>1.63</v>
       </c>
       <c r="AN23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP23">
         <v>0.5</v>
       </c>
       <c r="AQ23">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR23">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AS23">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="AT23">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6045,25 +6045,25 @@
         <v>1.85</v>
       </c>
       <c r="AN24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ24">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR24">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="AS24">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT24">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6254,22 +6254,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR25">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="AS25">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AT25">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6460,22 +6460,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AS26">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="AT26">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6666,22 +6666,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ27">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR27">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AS27">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AT27">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="AU27">
         <v>4</v>
@@ -6869,25 +6869,25 @@
         <v>1.38</v>
       </c>
       <c r="AN28">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AS28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT28">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -7075,25 +7075,25 @@
         <v>7.5</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ29">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AS29">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="AT29">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7281,25 +7281,25 @@
         <v>1.06</v>
       </c>
       <c r="AN30">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ30">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR30">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="AS30">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7487,25 +7487,25 @@
         <v>1.14</v>
       </c>
       <c r="AN31">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ31">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR31">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS31">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AT31">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="AU31">
         <v>5</v>
@@ -7693,25 +7693,25 @@
         <v>1.65</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP32">
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS32">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AT32">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7902,22 +7902,22 @@
         <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="AS33">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="AT33">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8105,25 +8105,25 @@
         <v>4.75</v>
       </c>
       <c r="AN34">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO34">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ34">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR34">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS34">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AT34">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AU34">
         <v>12</v>
@@ -8311,25 +8311,25 @@
         <v>2.05</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO35">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
       </c>
       <c r="AR35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS35">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="AT35">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8517,25 +8517,25 @@
         <v>1.06</v>
       </c>
       <c r="AN36">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ36">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR36">
-        <v>1.16</v>
+        <v>2.14</v>
       </c>
       <c r="AS36">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AT36">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8723,25 +8723,25 @@
         <v>1.64</v>
       </c>
       <c r="AN37">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AO37">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ37">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AS37">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="AT37">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AU37">
         <v>8</v>
@@ -8929,25 +8929,25 @@
         <v>1.96</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR38">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AS38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT38">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="AU38">
         <v>3</v>
@@ -9135,25 +9135,25 @@
         <v>1.87</v>
       </c>
       <c r="AN39">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ39">
         <v>1.33</v>
       </c>
       <c r="AR39">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
       <c r="AT39">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9344,22 +9344,22 @@
         <v>2</v>
       </c>
       <c r="AO40">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AS40">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT40">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9547,25 +9547,25 @@
         <v>2.6</v>
       </c>
       <c r="AN41">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AO41">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ41">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS41">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT41">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9753,25 +9753,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ42">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR42">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AS42">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AT42">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9959,25 +9959,25 @@
         <v>1.55</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO43">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP43">
         <v>0.5</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR43">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="AS43">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10168,22 +10168,22 @@
         <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS44">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AT44">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10374,22 +10374,22 @@
         <v>1.33</v>
       </c>
       <c r="AO45">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP45">
         <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR45">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AS45">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AT45">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="AU45">
         <v>6</v>
@@ -10577,25 +10577,25 @@
         <v>2.55</v>
       </c>
       <c r="AN46">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO46">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
       </c>
       <c r="AR46">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AS46">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT46">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10783,25 +10783,25 @@
         <v>1.47</v>
       </c>
       <c r="AN47">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO47">
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ47">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AS47">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="AT47">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10989,25 +10989,25 @@
         <v>1.39</v>
       </c>
       <c r="AN48">
+        <v>1</v>
+      </c>
+      <c r="AO48">
+        <v>1.67</v>
+      </c>
+      <c r="AP48">
         <v>0.83</v>
       </c>
-      <c r="AO48">
-        <v>1</v>
-      </c>
-      <c r="AP48">
-        <v>0.75</v>
-      </c>
       <c r="AQ48">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="AS48">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AT48">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AU48">
         <v>2</v>
@@ -11198,22 +11198,22 @@
         <v>0.67</v>
       </c>
       <c r="AO49">
+        <v>3</v>
+      </c>
+      <c r="AP49">
+        <v>1.08</v>
+      </c>
+      <c r="AQ49">
         <v>2.17</v>
       </c>
-      <c r="AP49">
-        <v>1.13</v>
-      </c>
-      <c r="AQ49">
-        <v>1.79</v>
-      </c>
       <c r="AR49">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AS49">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT49">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU49">
         <v>0</v>
@@ -11401,25 +11401,25 @@
         <v>1.49</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO50">
+        <v>2</v>
+      </c>
+      <c r="AP50">
+        <v>2.25</v>
+      </c>
+      <c r="AQ50">
         <v>2.17</v>
       </c>
-      <c r="AP50">
-        <v>1.92</v>
-      </c>
-      <c r="AQ50">
-        <v>2.25</v>
-      </c>
       <c r="AR50">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AT50">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11607,25 +11607,25 @@
         <v>1.6</v>
       </c>
       <c r="AN51">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AO51">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ51">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR51">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AS51">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT51">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11813,25 +11813,25 @@
         <v>1.18</v>
       </c>
       <c r="AN52">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
       </c>
       <c r="AR52">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS52">
-        <v>1.1</v>
+        <v>0.84</v>
       </c>
       <c r="AT52">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12019,25 +12019,25 @@
         <v>1.3</v>
       </c>
       <c r="AN53">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AO53">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AP53">
         <v>0.5</v>
       </c>
       <c r="AQ53">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AS53">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT53">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12225,25 +12225,25 @@
         <v>3.1</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO54">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ54">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR54">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AS54">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT54">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="AU54">
         <v>8</v>
@@ -12431,25 +12431,25 @@
         <v>1.16</v>
       </c>
       <c r="AN55">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ55">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR55">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="AS55">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AT55">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12637,25 +12637,25 @@
         <v>2.14</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO56">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ56">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR56">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS56">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="AT56">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AU56">
         <v>11</v>
@@ -12843,25 +12843,25 @@
         <v>1.73</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO57">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AP57">
+        <v>2.5</v>
+      </c>
+      <c r="AQ57">
         <v>2.17</v>
       </c>
-      <c r="AQ57">
-        <v>1.79</v>
-      </c>
       <c r="AR57">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS57">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AT57">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AU57">
         <v>0</v>
@@ -13052,22 +13052,22 @@
         <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="AP58">
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AS58">
-        <v>1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT58">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13255,25 +13255,25 @@
         <v>1.69</v>
       </c>
       <c r="AN59">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO59">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
         <v>0.5</v>
       </c>
       <c r="AR59">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AS59">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="AT59">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13461,25 +13461,25 @@
         <v>1.08</v>
       </c>
       <c r="AN60">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="AO60">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ60">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR60">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS60">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AT60">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13667,25 +13667,25 @@
         <v>1.08</v>
       </c>
       <c r="AN61">
-        <v>1.25</v>
+        <v>0.33</v>
       </c>
       <c r="AO61">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ61">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR61">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AS61">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AT61">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="AU61">
         <v>4</v>
@@ -13873,25 +13873,25 @@
         <v>1.96</v>
       </c>
       <c r="AN62">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AS62">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT62">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14079,25 +14079,25 @@
         <v>3.05</v>
       </c>
       <c r="AN63">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO63">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ63">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14285,25 +14285,25 @@
         <v>1.41</v>
       </c>
       <c r="AN64">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ64">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR64">
-        <v>0.96</v>
+        <v>1.31</v>
       </c>
       <c r="AS64">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AT64">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14491,25 +14491,25 @@
         <v>3.8</v>
       </c>
       <c r="AN65">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO65">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ65">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR65">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AS65">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AT65">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="AU65">
         <v>9</v>
@@ -14697,25 +14697,25 @@
         <v>1.48</v>
       </c>
       <c r="AN66">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO66">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ66">
         <v>1.33</v>
       </c>
       <c r="AR66">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AS66">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AT66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14903,22 +14903,22 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ67">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR67">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS67">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AT67">
         <v>2.33</v>
@@ -15109,25 +15109,25 @@
         <v>1.12</v>
       </c>
       <c r="AN68">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="AO68">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ68">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR68">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS68">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AT68">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15315,25 +15315,25 @@
         <v>1.14</v>
       </c>
       <c r="AN69">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="AO69">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ69">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR69">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS69">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AT69">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15521,25 +15521,25 @@
         <v>1.08</v>
       </c>
       <c r="AN70">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="AO70">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AP70">
         <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR70">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AS70">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AT70">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15727,25 +15727,25 @@
         <v>1.63</v>
       </c>
       <c r="AN71">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ71">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AS71">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT71">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AU71">
         <v>8</v>
@@ -15933,25 +15933,25 @@
         <v>1.21</v>
       </c>
       <c r="AN72">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO72">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AP72">
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AS72">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AT72">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AU72">
         <v>5</v>
@@ -16142,22 +16142,22 @@
         <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR73">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT73">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16345,25 +16345,25 @@
         <v>3.15</v>
       </c>
       <c r="AN74">
+        <v>2.2</v>
+      </c>
+      <c r="AO74">
         <v>1.8</v>
       </c>
-      <c r="AO74">
-        <v>1.6</v>
-      </c>
       <c r="AP74">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ74">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR74">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AS74">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AT74">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="AU74">
         <v>14</v>
@@ -16551,25 +16551,25 @@
         <v>1.8</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO75">
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75">
+        <v>0.67</v>
+      </c>
+      <c r="AR75">
+        <v>1.19</v>
+      </c>
+      <c r="AS75">
         <v>0.75</v>
       </c>
-      <c r="AR75">
-        <v>1.09</v>
-      </c>
-      <c r="AS75">
-        <v>1.06</v>
-      </c>
       <c r="AT75">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16760,22 +16760,22 @@
         <v>0.6</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ76">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AS76">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AT76">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AU76">
         <v>7</v>
@@ -16966,22 +16966,22 @@
         <v>1.6</v>
       </c>
       <c r="AO77">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ77">
         <v>0.5</v>
       </c>
       <c r="AR77">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AS77">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AT77">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17169,25 +17169,25 @@
         <v>1.44</v>
       </c>
       <c r="AN78">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO78">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ78">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AS78">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT78">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="AU78">
         <v>4</v>
@@ -17375,25 +17375,25 @@
         <v>1.58</v>
       </c>
       <c r="AN79">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AO79">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AP79">
+        <v>0.83</v>
+      </c>
+      <c r="AQ79">
         <v>0.75</v>
       </c>
-      <c r="AQ79">
-        <v>0.92</v>
-      </c>
       <c r="AR79">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AS79">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AU79">
         <v>8</v>
@@ -17581,25 +17581,25 @@
         <v>1.41</v>
       </c>
       <c r="AN80">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="AO80">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AP80">
         <v>0.5</v>
       </c>
       <c r="AQ80">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AS80">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AT80">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AU80">
         <v>4</v>
@@ -17787,25 +17787,25 @@
         <v>2.41</v>
       </c>
       <c r="AN81">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AO81">
-        <v>0.91</v>
+        <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ81">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR81">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS81">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT81">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -17993,25 +17993,25 @@
         <v>1.14</v>
       </c>
       <c r="AN82">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AO82">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AP82">
         <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR82">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AT82">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18199,25 +18199,25 @@
         <v>1.13</v>
       </c>
       <c r="AN83">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO83">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR83">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AS83">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AT83">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU83">
         <v>3</v>
@@ -18405,25 +18405,25 @@
         <v>1.6</v>
       </c>
       <c r="AN84">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AO84">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ84">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR84">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AS84">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AT84">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18611,25 +18611,25 @@
         <v>1.93</v>
       </c>
       <c r="AN85">
-        <v>1.27</v>
+        <v>0.67</v>
       </c>
       <c r="AO85">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ85">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR85">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS85">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT85">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18817,25 +18817,25 @@
         <v>1.71</v>
       </c>
       <c r="AN86">
-        <v>1.08</v>
+        <v>0.17</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ86">
         <v>0.5</v>
       </c>
       <c r="AR86">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AS86">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AT86">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19023,25 +19023,25 @@
         <v>1.49</v>
       </c>
       <c r="AN87">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ87">
         <v>1.33</v>
       </c>
       <c r="AR87">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AS87">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="AT87">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19229,25 +19229,25 @@
         <v>2.38</v>
       </c>
       <c r="AN88">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO88">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR88">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AS88">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AT88">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AU88">
         <v>10</v>
@@ -19435,25 +19435,25 @@
         <v>1.39</v>
       </c>
       <c r="AN89">
+        <v>0.8</v>
+      </c>
+      <c r="AO89">
+        <v>1.5</v>
+      </c>
+      <c r="AP89">
         <v>1.08</v>
       </c>
-      <c r="AO89">
+      <c r="AQ89">
         <v>1.33</v>
       </c>
-      <c r="AP89">
-        <v>0.92</v>
-      </c>
-      <c r="AQ89">
-        <v>1.46</v>
-      </c>
       <c r="AR89">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS89">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT89">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19641,25 +19641,25 @@
         <v>1.08</v>
       </c>
       <c r="AN90">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ90">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR90">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS90">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AT90">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -19847,25 +19847,25 @@
         <v>3.2</v>
       </c>
       <c r="AN91">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO91">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AS91">
-        <v>1.22</v>
+        <v>0.95</v>
       </c>
       <c r="AT91">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20056,22 +20056,22 @@
         <v>1.83</v>
       </c>
       <c r="AO92">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ92">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR92">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS92">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AT92">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20259,25 +20259,25 @@
         <v>5.6</v>
       </c>
       <c r="AN93">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AO93">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ93">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AS93">
-        <v>1.19</v>
+        <v>0.96</v>
       </c>
       <c r="AT93">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20465,25 +20465,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AO94">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP94">
+        <v>2.17</v>
+      </c>
+      <c r="AQ94">
         <v>1.67</v>
       </c>
-      <c r="AQ94">
-        <v>1.29</v>
-      </c>
       <c r="AR94">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AS94">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT94">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20671,25 +20671,25 @@
         <v>1.1</v>
       </c>
       <c r="AN95">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO95">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR95">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS95">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AT95">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20877,25 +20877,25 @@
         <v>1.13</v>
       </c>
       <c r="AN96">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR96">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AS96">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AT96">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21083,25 +21083,25 @@
         <v>1.18</v>
       </c>
       <c r="AN97">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AO97">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ97">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR97">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AS97">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT97">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21289,10 +21289,10 @@
         <v>1.46</v>
       </c>
       <c r="AN98">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AO98">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP98">
         <v>0.5</v>
@@ -21301,13 +21301,13 @@
         <v>1.33</v>
       </c>
       <c r="AR98">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT98">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21495,25 +21495,25 @@
         <v>1.58</v>
       </c>
       <c r="AN99">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AO99">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ99">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AS99">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AT99">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21701,25 +21701,25 @@
         <v>1.07</v>
       </c>
       <c r="AN100">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="AO100">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AP100">
         <v>0.5</v>
       </c>
       <c r="AQ100">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR100">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS100">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AT100">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21907,25 +21907,25 @@
         <v>1.86</v>
       </c>
       <c r="AN101">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO101">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AS101">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT101">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AU101">
         <v>4</v>
@@ -22113,25 +22113,25 @@
         <v>1.54</v>
       </c>
       <c r="AN102">
-        <v>1</v>
+        <v>0.29</v>
       </c>
       <c r="AO102">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ102">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AS102">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT102">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22319,25 +22319,25 @@
         <v>2.45</v>
       </c>
       <c r="AN103">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="AO103">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ103">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR103">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS103">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT103">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22525,25 +22525,25 @@
         <v>1.12</v>
       </c>
       <c r="AN104">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO104">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP104">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ104">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR104">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AS104">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT104">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22731,25 +22731,25 @@
         <v>1.15</v>
       </c>
       <c r="AN105">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AO105">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="AP105">
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR105">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AS105">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AT105">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22937,25 +22937,25 @@
         <v>1.09</v>
       </c>
       <c r="AN106">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="AO106">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ106">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR106">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AS106">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AT106">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="AU106">
         <v>2</v>
@@ -23143,25 +23143,25 @@
         <v>5.4</v>
       </c>
       <c r="AN107">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AO107">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
       </c>
       <c r="AR107">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AS107">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AT107">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23349,25 +23349,25 @@
         <v>1.6</v>
       </c>
       <c r="AN108">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO108">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>1.33</v>
       </c>
       <c r="AR108">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AS108">
-        <v>1.07</v>
+        <v>0.89</v>
       </c>
       <c r="AT108">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23555,25 +23555,25 @@
         <v>4.1</v>
       </c>
       <c r="AN109">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AO109">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ109">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR109">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AS109">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT109">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23761,25 +23761,25 @@
         <v>2.85</v>
       </c>
       <c r="AN110">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO110">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AS110">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT110">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23967,25 +23967,25 @@
         <v>5</v>
       </c>
       <c r="AN111">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AO111">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ111">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR111">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AS111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24173,25 +24173,25 @@
         <v>1.41</v>
       </c>
       <c r="AN112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO112">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ112">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AS112">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AT112">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24379,25 +24379,25 @@
         <v>1.75</v>
       </c>
       <c r="AN113">
+        <v>0.71</v>
+      </c>
+      <c r="AO113">
+        <v>1.71</v>
+      </c>
+      <c r="AP113">
+        <v>1.25</v>
+      </c>
+      <c r="AQ113">
+        <v>1.33</v>
+      </c>
+      <c r="AR113">
         <v>1.13</v>
       </c>
-      <c r="AO113">
-        <v>1.13</v>
-      </c>
-      <c r="AP113">
-        <v>1.38</v>
-      </c>
-      <c r="AQ113">
-        <v>0.88</v>
-      </c>
-      <c r="AR113">
-        <v>1.07</v>
-      </c>
       <c r="AS113">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="AT113">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24585,25 +24585,25 @@
         <v>1.59</v>
       </c>
       <c r="AN114">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AO114">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ114">
         <v>0.5</v>
       </c>
       <c r="AR114">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AS114">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="AT114">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24794,22 +24794,22 @@
         <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ115">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS115">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24997,25 +24997,25 @@
         <v>2.2</v>
       </c>
       <c r="AN116">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="AO116">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ116">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR116">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS116">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AT116">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU116">
         <v>3</v>
@@ -25203,25 +25203,25 @@
         <v>1.07</v>
       </c>
       <c r="AN117">
-        <v>1.06</v>
+        <v>0.63</v>
       </c>
       <c r="AO117">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ117">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR117">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AS117">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AT117">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="AU117">
         <v>5</v>
@@ -25409,25 +25409,25 @@
         <v>1.75</v>
       </c>
       <c r="AN118">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AO118">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ118">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR118">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT118">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU118">
         <v>2</v>
@@ -25615,25 +25615,25 @@
         <v>1.55</v>
       </c>
       <c r="AN119">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO119">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ119">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR119">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AS119">
         <v>1.65</v>
       </c>
       <c r="AT119">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AU119">
         <v>11</v>
@@ -25821,25 +25821,25 @@
         <v>1.09</v>
       </c>
       <c r="AN120">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AO120">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AP120">
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AS120">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AT120">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26027,25 +26027,25 @@
         <v>3.15</v>
       </c>
       <c r="AN121">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AO121">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ121">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR121">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AS121">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AT121">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26236,22 +26236,22 @@
         <v>1</v>
       </c>
       <c r="AO122">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR122">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AS122">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AT122">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26439,25 +26439,25 @@
         <v>1.32</v>
       </c>
       <c r="AN123">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="AO123">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AP123">
         <v>0.5</v>
       </c>
       <c r="AQ123">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR123">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AS123">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AT123">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AU123">
         <v>3</v>
@@ -26645,25 +26645,25 @@
         <v>4.2</v>
       </c>
       <c r="AN124">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AO124">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ124">
+        <v>1.33</v>
+      </c>
+      <c r="AR124">
+        <v>1.66</v>
+      </c>
+      <c r="AS124">
         <v>0.88</v>
       </c>
-      <c r="AR124">
-        <v>1.59</v>
-      </c>
-      <c r="AS124">
-        <v>1.08</v>
-      </c>
       <c r="AT124">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AU124">
         <v>6</v>
@@ -26851,25 +26851,25 @@
         <v>5.2</v>
       </c>
       <c r="AN125">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO125">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ125">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR125">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AS125">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AT125">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27057,25 +27057,25 @@
         <v>1.74</v>
       </c>
       <c r="AN126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AO126">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ126">
         <v>1.33</v>
       </c>
       <c r="AR126">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS126">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT126">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AU126">
         <v>5</v>
@@ -27263,25 +27263,25 @@
         <v>1.75</v>
       </c>
       <c r="AN127">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ127">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR127">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AS127">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AT127">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27469,25 +27469,25 @@
         <v>1.6</v>
       </c>
       <c r="AN128">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AO128">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ128">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR128">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AS128">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT128">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AU128">
         <v>5</v>
@@ -27675,25 +27675,25 @@
         <v>1.12</v>
       </c>
       <c r="AN129">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO129">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ129">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR129">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AS129">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AT129">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AU129">
         <v>2</v>
@@ -27881,25 +27881,25 @@
         <v>1.54</v>
       </c>
       <c r="AN130">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO130">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ130">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR130">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AS130">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AT130">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AU130">
         <v>5</v>
@@ -28087,25 +28087,25 @@
         <v>1.54</v>
       </c>
       <c r="AN131">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AO131">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP131">
         <v>1.33</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AS131">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AT131">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28293,25 +28293,25 @@
         <v>1.29</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="AO132">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ132">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR132">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS132">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AT132">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="AU132">
         <v>4</v>
@@ -28502,22 +28502,22 @@
         <v>2</v>
       </c>
       <c r="AO133">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ133">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR133">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AS133">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT133">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28708,10 +28708,10 @@
         <v>1</v>
       </c>
       <c r="AO134">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ134">
         <v>0.5</v>
@@ -28720,10 +28720,10 @@
         <v>1.25</v>
       </c>
       <c r="AS134">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT134">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AU134">
         <v>7</v>
@@ -28911,25 +28911,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO135">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ135">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR135">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AS135">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AT135">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29117,25 +29117,25 @@
         <v>1.86</v>
       </c>
       <c r="AN136">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AO136">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP136">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ136">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS136">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="AT136">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29323,25 +29323,25 @@
         <v>1.77</v>
       </c>
       <c r="AN137">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AO137">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR137">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS137">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AT137">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU137">
         <v>9</v>
@@ -29529,25 +29529,25 @@
         <v>4.6</v>
       </c>
       <c r="AN138">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AO138">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ138">
         <v>1.33</v>
       </c>
       <c r="AR138">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AS138">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="AT138">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU138">
         <v>5</v>
@@ -29735,25 +29735,25 @@
         <v>1.21</v>
       </c>
       <c r="AN139">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="AO139">
-        <v>1.47</v>
+        <v>0.89</v>
       </c>
       <c r="AP139">
         <v>0.5</v>
       </c>
       <c r="AQ139">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR139">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AS139">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AT139">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AU139">
         <v>2</v>
@@ -29941,22 +29941,22 @@
         <v>3.6</v>
       </c>
       <c r="AN140">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AO140">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR140">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AS140">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AT140">
         <v>2.75</v>
@@ -30147,25 +30147,25 @@
         <v>1.93</v>
       </c>
       <c r="AN141">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AO141">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ141">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR141">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AS141">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AT141">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30353,25 +30353,25 @@
         <v>3.2</v>
       </c>
       <c r="AN142">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AO142">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AP142">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ142">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS142">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AT142">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AU142">
         <v>9</v>
@@ -30559,25 +30559,25 @@
         <v>1.53</v>
       </c>
       <c r="AN143">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AO143">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP143">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ143">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR143">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS143">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="AT143">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AU143">
         <v>5</v>
@@ -30765,25 +30765,25 @@
         <v>1.09</v>
       </c>
       <c r="AN144">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AO144">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP144">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AQ144">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR144">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AS144">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AT144">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU144">
         <v>4</v>
@@ -30971,25 +30971,25 @@
         <v>1.25</v>
       </c>
       <c r="AN145">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO145">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="AP145">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ145">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR145">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AS145">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AT145">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31177,25 +31177,25 @@
         <v>1.48</v>
       </c>
       <c r="AN146">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AO146">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP146">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ146">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR146">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AS146">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AT146">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31386,22 +31386,22 @@
         <v>1.3</v>
       </c>
       <c r="AO147">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AP147">
         <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR147">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AS147">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AT147">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU147">
         <v>0</v>
@@ -31589,25 +31589,25 @@
         <v>2.28</v>
       </c>
       <c r="AN148">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AO148">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AP148">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ148">
         <v>0.5</v>
       </c>
       <c r="AR148">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AS148">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AT148">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31795,25 +31795,25 @@
         <v>1.61</v>
       </c>
       <c r="AN149">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO149">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AP149">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ149">
         <v>1.33</v>
       </c>
       <c r="AR149">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AS149">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="AT149">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -32001,25 +32001,25 @@
         <v>1.17</v>
       </c>
       <c r="AN150">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AO150">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AP150">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ150">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR150">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AS150">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AT150">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AU150">
         <v>3</v>
@@ -32207,25 +32207,25 @@
         <v>3.55</v>
       </c>
       <c r="AN151">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AO151">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ151">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AS151">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AT151">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32413,25 +32413,25 @@
         <v>1.26</v>
       </c>
       <c r="AN152">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO152">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AP152">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ152">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR152">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AS152">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AT152">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="AU152">
         <v>8</v>
@@ -32619,25 +32619,25 @@
         <v>5.6</v>
       </c>
       <c r="AN153">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AO153">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AP153">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ153">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR153">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AS153">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT153">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="AU153">
         <v>12</v>
@@ -32825,25 +32825,25 @@
         <v>1.88</v>
       </c>
       <c r="AN154">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="AO154">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AQ154">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR154">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AS154">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="AT154">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="AU154">
         <v>6</v>
@@ -33031,25 +33031,25 @@
         <v>1.35</v>
       </c>
       <c r="AN155">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="AO155">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AP155">
         <v>0.5</v>
       </c>
       <c r="AQ155">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR155">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AS155">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT155">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33237,25 +33237,25 @@
         <v>1.57</v>
       </c>
       <c r="AN156">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AO156">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AP156">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AQ156">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AR156">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AS156">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT156">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AU156">
         <v>6</v>
@@ -33443,25 +33443,25 @@
         <v>3.7</v>
       </c>
       <c r="AN157">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AO157">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="AP157">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AQ157">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AR157">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AS157">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AT157">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="AU157">
         <v>5</v>
@@ -33649,25 +33649,25 @@
         <v>1.33</v>
       </c>
       <c r="AN158">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AO158">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AP158">
+        <v>1.08</v>
+      </c>
+      <c r="AQ158">
+        <v>1.17</v>
+      </c>
+      <c r="AR158">
         <v>1.13</v>
       </c>
-      <c r="AQ158">
-        <v>1.67</v>
-      </c>
-      <c r="AR158">
-        <v>1.1</v>
-      </c>
       <c r="AS158">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AT158">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AU158">
         <v>6</v>
@@ -33855,25 +33855,25 @@
         <v>3.9</v>
       </c>
       <c r="AN159">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AO159">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="AP159">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AQ159">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR159">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AS159">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AT159">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="AU159">
         <v>8</v>
@@ -34061,25 +34061,25 @@
         <v>1.04</v>
       </c>
       <c r="AN160">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AO160">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AP160">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ160">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AR160">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AS160">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AT160">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AU160">
         <v>2</v>
@@ -34267,25 +34267,25 @@
         <v>5.2</v>
       </c>
       <c r="AN161">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="AO161">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="AP161">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
       </c>
       <c r="AR161">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AS161">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="AT161">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AU161">
         <v>12</v>
@@ -34473,25 +34473,25 @@
         <v>1.61</v>
       </c>
       <c r="AN162">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AO162">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AP162">
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR162">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AS162">
-        <v>1.18</v>
+        <v>0.95</v>
       </c>
       <c r="AT162">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AU162">
         <v>4</v>
@@ -34679,22 +34679,22 @@
         <v>1.56</v>
       </c>
       <c r="AN163">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AO163">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AP163">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AQ163">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR163">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AS163">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="AT163">
         <v>2.42</v>
@@ -34885,25 +34885,25 @@
         <v>1.91</v>
       </c>
       <c r="AN164">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="AO164">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AP164">
+        <v>0.92</v>
+      </c>
+      <c r="AQ164">
+        <v>0.75</v>
+      </c>
+      <c r="AR164">
+        <v>1.26</v>
+      </c>
+      <c r="AS164">
         <v>1.29</v>
       </c>
-      <c r="AQ164">
-        <v>0.92</v>
-      </c>
-      <c r="AR164">
-        <v>1.22</v>
-      </c>
-      <c r="AS164">
-        <v>1.28</v>
-      </c>
       <c r="AT164">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AU164">
         <v>6</v>
@@ -35091,25 +35091,25 @@
         <v>1.59</v>
       </c>
       <c r="AN165">
-        <v>0.91</v>
+        <v>0.45</v>
       </c>
       <c r="AO165">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AP165">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AQ165">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR165">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AS165">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AT165">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AU165">
         <v>2</v>
@@ -35297,25 +35297,25 @@
         <v>2.42</v>
       </c>
       <c r="AN166">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AO166">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AP166">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AQ166">
         <v>1.33</v>
       </c>
       <c r="AR166">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AS166">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="AT166">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AU166">
         <v>11</v>
@@ -35503,25 +35503,25 @@
         <v>1.07</v>
       </c>
       <c r="AN167">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="AO167">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AP167">
         <v>0.5</v>
       </c>
       <c r="AQ167">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR167">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AS167">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AT167">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35709,25 +35709,25 @@
         <v>1.13</v>
       </c>
       <c r="AN168">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AO168">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AP168">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AQ168">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AR168">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AS168">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AT168">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AU168">
         <v>0</v>
@@ -35915,25 +35915,25 @@
         <v>2.19</v>
       </c>
       <c r="AN169">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AO169">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="AP169">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ169">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AR169">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AS169">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AT169">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="AU169">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="273">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -578,6 +578,15 @@
   </si>
   <si>
     <t>['6', '31']</t>
+  </si>
+  <si>
+    <t>['21', '90']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['34', '79']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1185,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1441,7 +1450,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1519,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ2">
         <v>2.17</v>
@@ -1647,7 +1656,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1934,7 +1943,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2137,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ5">
         <v>1.33</v>
@@ -2265,7 +2274,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2346,7 +2355,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2677,7 +2686,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3089,7 +3098,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3167,10 +3176,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3295,7 +3304,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3501,7 +3510,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3788,7 +3797,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
@@ -3991,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ14">
         <v>1.17</v>
@@ -4200,7 +4209,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4325,7 +4334,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4531,7 +4540,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4943,7 +4952,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5149,7 +5158,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5227,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ20">
         <v>1.5</v>
@@ -5355,7 +5364,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5561,7 +5570,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5848,7 +5857,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ23">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR23">
         <v>0.92</v>
@@ -5973,7 +5982,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6179,7 +6188,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6257,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ25">
         <v>1.17</v>
@@ -6466,7 +6475,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR26">
         <v>1.48</v>
@@ -6797,7 +6806,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6878,7 +6887,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR28">
         <v>1</v>
@@ -7209,7 +7218,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7287,7 +7296,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ30">
         <v>2.17</v>
@@ -7621,7 +7630,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -8033,7 +8042,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8111,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ34">
         <v>0.75</v>
@@ -8239,7 +8248,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8729,10 +8738,10 @@
         <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ37">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR37">
         <v>1.17</v>
@@ -8857,7 +8866,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9063,7 +9072,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9144,7 +9153,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -9556,7 +9565,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ41">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.71</v>
@@ -9887,7 +9896,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10093,7 +10102,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10711,7 +10720,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10789,7 +10798,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ47">
         <v>1.5</v>
@@ -10917,7 +10926,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11123,7 +11132,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11407,7 +11416,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ50">
         <v>2.17</v>
@@ -11613,7 +11622,7 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ51">
         <v>0.75</v>
@@ -11741,7 +11750,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11822,7 +11831,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR52">
         <v>1.4</v>
@@ -12153,7 +12162,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12359,7 +12368,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12646,7 +12655,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ56">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR56">
         <v>1.14</v>
@@ -12771,7 +12780,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12977,7 +12986,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13183,7 +13192,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13467,7 +13476,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ60">
         <v>1.83</v>
@@ -13801,7 +13810,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13879,10 +13888,10 @@
         <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR62">
         <v>1.7</v>
@@ -14007,7 +14016,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14213,7 +14222,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14706,7 +14715,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR66">
         <v>1.31</v>
@@ -14831,7 +14840,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15115,7 +15124,7 @@
         <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ68">
         <v>1.58</v>
@@ -15243,7 +15252,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15449,7 +15458,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15942,7 +15951,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR72">
         <v>1.28</v>
@@ -16067,7 +16076,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16145,7 +16154,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ73">
         <v>1.67</v>
@@ -16479,7 +16488,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16560,7 +16569,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR75">
         <v>1.19</v>
@@ -16685,7 +16694,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16969,7 +16978,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ77">
         <v>0.5</v>
@@ -17097,7 +17106,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17303,7 +17312,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17509,7 +17518,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17921,7 +17930,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18127,7 +18136,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18539,7 +18548,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18823,7 +18832,7 @@
         <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ86">
         <v>0.5</v>
@@ -18951,7 +18960,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19032,7 +19041,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ87">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR87">
         <v>1.2</v>
@@ -19238,7 +19247,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR88">
         <v>1.86</v>
@@ -19441,7 +19450,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ89">
         <v>1.33</v>
@@ -19569,7 +19578,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19775,7 +19784,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19856,7 +19865,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19981,7 +19990,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20059,7 +20068,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ92">
         <v>1.67</v>
@@ -20393,7 +20402,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20599,7 +20608,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20677,7 +20686,7 @@
         <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ95">
         <v>2.17</v>
@@ -20805,7 +20814,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21217,7 +21226,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21298,7 +21307,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR98">
         <v>1.1</v>
@@ -21423,7 +21432,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22119,7 +22128,7 @@
         <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ102">
         <v>1.33</v>
@@ -23355,10 +23364,10 @@
         <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR108">
         <v>1.22</v>
@@ -23561,10 +23570,10 @@
         <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ109">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR109">
         <v>1.74</v>
@@ -23895,7 +23904,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24101,7 +24110,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24182,7 +24191,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>1.43</v>
@@ -24925,7 +24934,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25131,7 +25140,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25209,7 +25218,7 @@
         <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ117">
         <v>1.83</v>
@@ -25337,7 +25346,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25543,7 +25552,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25621,7 +25630,7 @@
         <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ119">
         <v>2.17</v>
@@ -25749,7 +25758,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26036,7 +26045,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ121">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR121">
         <v>1.96</v>
@@ -26161,7 +26170,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26239,7 +26248,7 @@
         <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ122">
         <v>1.58</v>
@@ -26367,7 +26376,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26573,7 +26582,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26860,7 +26869,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ125">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR125">
         <v>1.95</v>
@@ -27066,7 +27075,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ126">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27603,7 +27612,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27809,7 +27818,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28505,7 +28514,7 @@
         <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ133">
         <v>1.83</v>
@@ -28711,7 +28720,7 @@
         <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ134">
         <v>0.5</v>
@@ -28839,7 +28848,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -28917,7 +28926,7 @@
         <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ135">
         <v>1.67</v>
@@ -29126,7 +29135,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR136">
         <v>1.4</v>
@@ -29251,7 +29260,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29538,7 +29547,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ138">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR138">
         <v>2.02</v>
@@ -29663,7 +29672,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29744,7 +29753,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ139">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR139">
         <v>1.11</v>
@@ -30281,7 +30290,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30359,7 +30368,7 @@
         <v>1.5</v>
       </c>
       <c r="AP142">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ142">
         <v>1.5</v>
@@ -30487,7 +30496,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30565,7 +30574,7 @@
         <v>1.5</v>
       </c>
       <c r="AP143">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ143">
         <v>1.33</v>
@@ -30980,7 +30989,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ145">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31105,7 +31114,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31801,10 +31810,10 @@
         <v>1.3</v>
       </c>
       <c r="AP149">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ149">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR149">
         <v>1.24</v>
@@ -31929,7 +31938,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32135,7 +32144,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32753,7 +32762,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32834,7 +32843,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ154">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR154">
         <v>1.19</v>
@@ -32959,7 +32968,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33371,7 +33380,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33577,7 +33586,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33658,7 +33667,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ158">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR158">
         <v>1.13</v>
@@ -33783,7 +33792,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33861,7 +33870,7 @@
         <v>1.45</v>
       </c>
       <c r="AP159">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ159">
         <v>1.33</v>
@@ -33989,7 +33998,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34067,7 +34076,7 @@
         <v>2.09</v>
       </c>
       <c r="AP160">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ160">
         <v>2.17</v>
@@ -34482,7 +34491,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -34607,7 +34616,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35019,7 +35028,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35097,7 +35106,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ165">
         <v>1.17</v>
@@ -35225,7 +35234,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35306,7 +35315,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ166">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR166">
         <v>1.46</v>
@@ -35431,7 +35440,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35637,7 +35646,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35843,7 +35852,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36000,6 +36009,624 @@
       </c>
       <c r="BP169">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7537466</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F170">
+        <v>25</v>
+      </c>
+      <c r="G170" t="s">
+        <v>78</v>
+      </c>
+      <c r="H170" t="s">
+        <v>83</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>2</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>3</v>
+      </c>
+      <c r="O170" t="s">
+        <v>188</v>
+      </c>
+      <c r="P170" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q170">
+        <v>3.25</v>
+      </c>
+      <c r="R170">
+        <v>2.05</v>
+      </c>
+      <c r="S170">
+        <v>3.5</v>
+      </c>
+      <c r="T170">
+        <v>1.44</v>
+      </c>
+      <c r="U170">
+        <v>2.63</v>
+      </c>
+      <c r="V170">
+        <v>3.25</v>
+      </c>
+      <c r="W170">
+        <v>1.33</v>
+      </c>
+      <c r="X170">
+        <v>9</v>
+      </c>
+      <c r="Y170">
+        <v>1.07</v>
+      </c>
+      <c r="Z170">
+        <v>2.5</v>
+      </c>
+      <c r="AA170">
+        <v>3</v>
+      </c>
+      <c r="AB170">
+        <v>2.8</v>
+      </c>
+      <c r="AC170">
+        <v>1.08</v>
+      </c>
+      <c r="AD170">
+        <v>8.6</v>
+      </c>
+      <c r="AE170">
+        <v>1.38</v>
+      </c>
+      <c r="AF170">
+        <v>2.95</v>
+      </c>
+      <c r="AG170">
+        <v>2.15</v>
+      </c>
+      <c r="AH170">
+        <v>1.57</v>
+      </c>
+      <c r="AI170">
+        <v>1.8</v>
+      </c>
+      <c r="AJ170">
+        <v>1.95</v>
+      </c>
+      <c r="AK170">
+        <v>1.44</v>
+      </c>
+      <c r="AL170">
+        <v>1.38</v>
+      </c>
+      <c r="AM170">
+        <v>1.52</v>
+      </c>
+      <c r="AN170">
+        <v>1.08</v>
+      </c>
+      <c r="AO170">
+        <v>0.67</v>
+      </c>
+      <c r="AP170">
+        <v>1.23</v>
+      </c>
+      <c r="AQ170">
+        <v>0.62</v>
+      </c>
+      <c r="AR170">
+        <v>1.27</v>
+      </c>
+      <c r="AS170">
+        <v>1</v>
+      </c>
+      <c r="AT170">
+        <v>2.27</v>
+      </c>
+      <c r="AU170">
+        <v>7</v>
+      </c>
+      <c r="AV170">
+        <v>5</v>
+      </c>
+      <c r="AW170">
+        <v>10</v>
+      </c>
+      <c r="AX170">
+        <v>6</v>
+      </c>
+      <c r="AY170">
+        <v>19</v>
+      </c>
+      <c r="AZ170">
+        <v>11</v>
+      </c>
+      <c r="BA170">
+        <v>7</v>
+      </c>
+      <c r="BB170">
+        <v>3</v>
+      </c>
+      <c r="BC170">
+        <v>10</v>
+      </c>
+      <c r="BD170">
+        <v>1.95</v>
+      </c>
+      <c r="BE170">
+        <v>6.1</v>
+      </c>
+      <c r="BF170">
+        <v>2.07</v>
+      </c>
+      <c r="BG170">
+        <v>1.53</v>
+      </c>
+      <c r="BH170">
+        <v>2.2</v>
+      </c>
+      <c r="BI170">
+        <v>1.89</v>
+      </c>
+      <c r="BJ170">
+        <v>1.72</v>
+      </c>
+      <c r="BK170">
+        <v>2.43</v>
+      </c>
+      <c r="BL170">
+        <v>1.43</v>
+      </c>
+      <c r="BM170">
+        <v>3.25</v>
+      </c>
+      <c r="BN170">
+        <v>1.25</v>
+      </c>
+      <c r="BO170">
+        <v>4.4</v>
+      </c>
+      <c r="BP170">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7537462</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F171">
+        <v>25</v>
+      </c>
+      <c r="G171" t="s">
+        <v>70</v>
+      </c>
+      <c r="H171" t="s">
+        <v>82</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>2</v>
+      </c>
+      <c r="O171" t="s">
+        <v>189</v>
+      </c>
+      <c r="P171" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q171">
+        <v>4</v>
+      </c>
+      <c r="R171">
+        <v>1.95</v>
+      </c>
+      <c r="S171">
+        <v>3</v>
+      </c>
+      <c r="T171">
+        <v>1.53</v>
+      </c>
+      <c r="U171">
+        <v>2.38</v>
+      </c>
+      <c r="V171">
+        <v>3.5</v>
+      </c>
+      <c r="W171">
+        <v>1.29</v>
+      </c>
+      <c r="X171">
+        <v>11</v>
+      </c>
+      <c r="Y171">
+        <v>1.05</v>
+      </c>
+      <c r="Z171">
+        <v>3.3</v>
+      </c>
+      <c r="AA171">
+        <v>3</v>
+      </c>
+      <c r="AB171">
+        <v>2.2</v>
+      </c>
+      <c r="AC171">
+        <v>1.1</v>
+      </c>
+      <c r="AD171">
+        <v>7.2</v>
+      </c>
+      <c r="AE171">
+        <v>1.46</v>
+      </c>
+      <c r="AF171">
+        <v>2.6</v>
+      </c>
+      <c r="AG171">
+        <v>2.2</v>
+      </c>
+      <c r="AH171">
+        <v>1.55</v>
+      </c>
+      <c r="AI171">
+        <v>2</v>
+      </c>
+      <c r="AJ171">
+        <v>1.75</v>
+      </c>
+      <c r="AK171">
+        <v>1.66</v>
+      </c>
+      <c r="AL171">
+        <v>1.39</v>
+      </c>
+      <c r="AM171">
+        <v>1.33</v>
+      </c>
+      <c r="AN171">
+        <v>0.42</v>
+      </c>
+      <c r="AO171">
+        <v>1.17</v>
+      </c>
+      <c r="AP171">
+        <v>0.46</v>
+      </c>
+      <c r="AQ171">
+        <v>1.15</v>
+      </c>
+      <c r="AR171">
+        <v>1.25</v>
+      </c>
+      <c r="AS171">
+        <v>1.18</v>
+      </c>
+      <c r="AT171">
+        <v>2.43</v>
+      </c>
+      <c r="AU171">
+        <v>5</v>
+      </c>
+      <c r="AV171">
+        <v>8</v>
+      </c>
+      <c r="AW171">
+        <v>3</v>
+      </c>
+      <c r="AX171">
+        <v>3</v>
+      </c>
+      <c r="AY171">
+        <v>9</v>
+      </c>
+      <c r="AZ171">
+        <v>13</v>
+      </c>
+      <c r="BA171">
+        <v>8</v>
+      </c>
+      <c r="BB171">
+        <v>4</v>
+      </c>
+      <c r="BC171">
+        <v>12</v>
+      </c>
+      <c r="BD171">
+        <v>2.25</v>
+      </c>
+      <c r="BE171">
+        <v>6.25</v>
+      </c>
+      <c r="BF171">
+        <v>1.79</v>
+      </c>
+      <c r="BG171">
+        <v>1.49</v>
+      </c>
+      <c r="BH171">
+        <v>2.28</v>
+      </c>
+      <c r="BI171">
+        <v>1.84</v>
+      </c>
+      <c r="BJ171">
+        <v>1.77</v>
+      </c>
+      <c r="BK171">
+        <v>2.35</v>
+      </c>
+      <c r="BL171">
+        <v>1.46</v>
+      </c>
+      <c r="BM171">
+        <v>3.1</v>
+      </c>
+      <c r="BN171">
+        <v>1.26</v>
+      </c>
+      <c r="BO171">
+        <v>4.25</v>
+      </c>
+      <c r="BP171">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7537465</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45717.625</v>
+      </c>
+      <c r="F172">
+        <v>25</v>
+      </c>
+      <c r="G172" t="s">
+        <v>73</v>
+      </c>
+      <c r="H172" t="s">
+        <v>76</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172" t="s">
+        <v>190</v>
+      </c>
+      <c r="P172" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q172">
+        <v>1.73</v>
+      </c>
+      <c r="R172">
+        <v>2.38</v>
+      </c>
+      <c r="S172">
+        <v>12</v>
+      </c>
+      <c r="T172">
+        <v>1.4</v>
+      </c>
+      <c r="U172">
+        <v>2.75</v>
+      </c>
+      <c r="V172">
+        <v>3</v>
+      </c>
+      <c r="W172">
+        <v>1.36</v>
+      </c>
+      <c r="X172">
+        <v>8</v>
+      </c>
+      <c r="Y172">
+        <v>1.08</v>
+      </c>
+      <c r="Z172">
+        <v>1.3</v>
+      </c>
+      <c r="AA172">
+        <v>4.75</v>
+      </c>
+      <c r="AB172">
+        <v>9.5</v>
+      </c>
+      <c r="AC172">
+        <v>1.05</v>
+      </c>
+      <c r="AD172">
+        <v>11</v>
+      </c>
+      <c r="AE172">
+        <v>1.32</v>
+      </c>
+      <c r="AF172">
+        <v>3.3</v>
+      </c>
+      <c r="AG172">
+        <v>1.85</v>
+      </c>
+      <c r="AH172">
+        <v>1.8</v>
+      </c>
+      <c r="AI172">
+        <v>2.75</v>
+      </c>
+      <c r="AJ172">
+        <v>1.4</v>
+      </c>
+      <c r="AK172">
+        <v>1.05</v>
+      </c>
+      <c r="AL172">
+        <v>1.17</v>
+      </c>
+      <c r="AM172">
+        <v>3.75</v>
+      </c>
+      <c r="AN172">
+        <v>2.25</v>
+      </c>
+      <c r="AO172">
+        <v>1.33</v>
+      </c>
+      <c r="AP172">
+        <v>2.31</v>
+      </c>
+      <c r="AQ172">
+        <v>1.23</v>
+      </c>
+      <c r="AR172">
+        <v>1.91</v>
+      </c>
+      <c r="AS172">
+        <v>0.95</v>
+      </c>
+      <c r="AT172">
+        <v>2.86</v>
+      </c>
+      <c r="AU172">
+        <v>11</v>
+      </c>
+      <c r="AV172">
+        <v>3</v>
+      </c>
+      <c r="AW172">
+        <v>10</v>
+      </c>
+      <c r="AX172">
+        <v>8</v>
+      </c>
+      <c r="AY172">
+        <v>27</v>
+      </c>
+      <c r="AZ172">
+        <v>13</v>
+      </c>
+      <c r="BA172">
+        <v>5</v>
+      </c>
+      <c r="BB172">
+        <v>4</v>
+      </c>
+      <c r="BC172">
+        <v>9</v>
+      </c>
+      <c r="BD172">
+        <v>1.21</v>
+      </c>
+      <c r="BE172">
+        <v>8</v>
+      </c>
+      <c r="BF172">
+        <v>4.8</v>
+      </c>
+      <c r="BG172">
+        <v>1.45</v>
+      </c>
+      <c r="BH172">
+        <v>2.38</v>
+      </c>
+      <c r="BI172">
+        <v>1.75</v>
+      </c>
+      <c r="BJ172">
+        <v>1.86</v>
+      </c>
+      <c r="BK172">
+        <v>2.2</v>
+      </c>
+      <c r="BL172">
+        <v>1.52</v>
+      </c>
+      <c r="BM172">
+        <v>2.85</v>
+      </c>
+      <c r="BN172">
+        <v>1.32</v>
+      </c>
+      <c r="BO172">
+        <v>3.75</v>
+      </c>
+      <c r="BP172">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -589,6 +589,9 @@
     <t>['34', '79']</t>
   </si>
   <si>
+    <t>['25', '46', '84']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -833,6 +836,9 @@
   </si>
   <si>
     <t>['24']</t>
+  </si>
+  <si>
+    <t>['13', '83']</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1450,7 +1456,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1656,7 +1662,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1940,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>0.62</v>
@@ -2274,7 +2280,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2686,7 +2692,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2767,7 +2773,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2970,10 +2976,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3098,7 +3104,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3304,7 +3310,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3385,7 +3391,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -3510,7 +3516,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -4334,7 +4340,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4540,7 +4546,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4952,7 +4958,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5030,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>1.83</v>
@@ -5158,7 +5164,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5364,7 +5370,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5570,7 +5576,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5982,7 +5988,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6063,7 +6069,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR24">
         <v>2.26</v>
@@ -6188,7 +6194,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6806,7 +6812,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6884,7 +6890,7 @@
         <v>2</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28">
         <v>1.15</v>
@@ -7218,7 +7224,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7630,7 +7636,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7914,7 +7920,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>1.5</v>
@@ -8042,7 +8048,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8248,7 +8254,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8329,7 +8335,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ35">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -8866,7 +8872,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9072,7 +9078,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9150,7 +9156,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
         <v>1.23</v>
@@ -9359,7 +9365,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR40">
         <v>2.09</v>
@@ -9896,7 +9902,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10102,7 +10108,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10595,7 +10601,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ46">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR46">
         <v>1.16</v>
@@ -10720,7 +10726,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10926,7 +10932,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11132,7 +11138,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11210,7 +11216,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
         <v>2.17</v>
@@ -11750,7 +11756,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12162,7 +12168,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12368,7 +12374,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12446,7 +12452,7 @@
         <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ55">
         <v>1.58</v>
@@ -12780,7 +12786,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12986,7 +12992,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13192,7 +13198,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13270,10 +13276,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13810,7 +13816,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14016,7 +14022,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14222,7 +14228,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14303,7 +14309,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ64">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR64">
         <v>1.31</v>
@@ -14840,7 +14846,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15252,7 +15258,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15458,7 +15464,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -16076,7 +16082,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16157,7 +16163,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ73">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR73">
         <v>1.13</v>
@@ -16488,7 +16494,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16566,7 +16572,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ75">
         <v>0.62</v>
@@ -16694,7 +16700,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16772,7 +16778,7 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.33</v>
@@ -16981,7 +16987,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ77">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR77">
         <v>1.69</v>
@@ -17106,7 +17112,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17312,7 +17318,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17518,7 +17524,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17930,7 +17936,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18136,7 +18142,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18548,7 +18554,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18835,7 +18841,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR86">
         <v>1.38</v>
@@ -18960,7 +18966,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19038,7 +19044,7 @@
         <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
         <v>1.23</v>
@@ -19578,7 +19584,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19656,7 +19662,7 @@
         <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ90">
         <v>2.17</v>
@@ -19784,7 +19790,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19990,7 +19996,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20071,7 +20077,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR92">
         <v>1.7</v>
@@ -20402,7 +20408,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20483,7 +20489,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ94">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20608,7 +20614,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20814,7 +20820,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20892,7 +20898,7 @@
         <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ96">
         <v>1.83</v>
@@ -21226,7 +21232,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21432,7 +21438,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22540,7 +22546,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
         <v>1.58</v>
@@ -23161,7 +23167,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR107">
         <v>1.96</v>
@@ -23779,7 +23785,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR110">
         <v>1.66</v>
@@ -23904,7 +23910,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24110,7 +24116,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24394,7 +24400,7 @@
         <v>1.71</v>
       </c>
       <c r="AP113">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ113">
         <v>1.33</v>
@@ -24603,7 +24609,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ114">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR114">
         <v>1.39</v>
@@ -24806,7 +24812,7 @@
         <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>0.75</v>
@@ -24934,7 +24940,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25140,7 +25146,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25346,7 +25352,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25552,7 +25558,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25758,7 +25764,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26170,7 +26176,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26376,7 +26382,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26457,7 +26463,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ123">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR123">
         <v>1.09</v>
@@ -26582,7 +26588,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -27278,7 +27284,7 @@
         <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ127">
         <v>1.17</v>
@@ -27612,7 +27618,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27818,7 +27824,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27896,7 +27902,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
         <v>1.33</v>
@@ -28723,7 +28729,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ134">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
@@ -28848,7 +28854,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -28929,7 +28935,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ135">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR135">
         <v>1.26</v>
@@ -29260,7 +29266,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29338,7 +29344,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ137">
         <v>0.75</v>
@@ -29672,7 +29678,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -30290,7 +30296,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30496,7 +30502,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30780,7 +30786,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
         <v>2.17</v>
@@ -31114,7 +31120,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31401,7 +31407,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31607,7 +31613,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ148">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR148">
         <v>1.44</v>
@@ -31938,7 +31944,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32016,7 +32022,7 @@
         <v>2.3</v>
       </c>
       <c r="AP150">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ150">
         <v>2.17</v>
@@ -32144,7 +32150,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32762,7 +32768,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32968,7 +32974,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33252,7 +33258,7 @@
         <v>1.45</v>
       </c>
       <c r="AP156">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ156">
         <v>1.33</v>
@@ -33380,7 +33386,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33461,7 +33467,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ157">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR157">
         <v>2.15</v>
@@ -33586,7 +33592,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33664,7 +33670,7 @@
         <v>1.27</v>
       </c>
       <c r="AP158">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ158">
         <v>1.15</v>
@@ -33792,7 +33798,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33998,7 +34004,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34285,7 +34291,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -34616,7 +34622,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35028,7 +35034,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35234,7 +35240,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35440,7 +35446,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35646,7 +35652,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35852,7 +35858,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36058,7 +36064,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q170">
         <v>3.25</v>
@@ -36264,7 +36270,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q171">
         <v>4</v>
@@ -36627,6 +36633,418 @@
       </c>
       <c r="BP172">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7537463</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45718.47916666666</v>
+      </c>
+      <c r="F173">
+        <v>25</v>
+      </c>
+      <c r="G173" t="s">
+        <v>72</v>
+      </c>
+      <c r="H173" t="s">
+        <v>74</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>2</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>3</v>
+      </c>
+      <c r="O173" t="s">
+        <v>122</v>
+      </c>
+      <c r="P173" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q173">
+        <v>3.6</v>
+      </c>
+      <c r="R173">
+        <v>1.91</v>
+      </c>
+      <c r="S173">
+        <v>3.75</v>
+      </c>
+      <c r="T173">
+        <v>1.57</v>
+      </c>
+      <c r="U173">
+        <v>2.25</v>
+      </c>
+      <c r="V173">
+        <v>4</v>
+      </c>
+      <c r="W173">
+        <v>1.22</v>
+      </c>
+      <c r="X173">
+        <v>13</v>
+      </c>
+      <c r="Y173">
+        <v>1.04</v>
+      </c>
+      <c r="Z173">
+        <v>2.62</v>
+      </c>
+      <c r="AA173">
+        <v>2.8</v>
+      </c>
+      <c r="AB173">
+        <v>2.9</v>
+      </c>
+      <c r="AC173">
+        <v>1.12</v>
+      </c>
+      <c r="AD173">
+        <v>6.4</v>
+      </c>
+      <c r="AE173">
+        <v>1.5</v>
+      </c>
+      <c r="AF173">
+        <v>2.3</v>
+      </c>
+      <c r="AG173">
+        <v>2.38</v>
+      </c>
+      <c r="AH173">
+        <v>1.47</v>
+      </c>
+      <c r="AI173">
+        <v>2.1</v>
+      </c>
+      <c r="AJ173">
+        <v>1.67</v>
+      </c>
+      <c r="AK173">
+        <v>1.43</v>
+      </c>
+      <c r="AL173">
+        <v>1.43</v>
+      </c>
+      <c r="AM173">
+        <v>1.48</v>
+      </c>
+      <c r="AN173">
+        <v>1.08</v>
+      </c>
+      <c r="AO173">
+        <v>1.67</v>
+      </c>
+      <c r="AP173">
+        <v>1</v>
+      </c>
+      <c r="AQ173">
+        <v>1.77</v>
+      </c>
+      <c r="AR173">
+        <v>1.15</v>
+      </c>
+      <c r="AS173">
+        <v>1.19</v>
+      </c>
+      <c r="AT173">
+        <v>2.34</v>
+      </c>
+      <c r="AU173">
+        <v>7</v>
+      </c>
+      <c r="AV173">
+        <v>4</v>
+      </c>
+      <c r="AW173">
+        <v>10</v>
+      </c>
+      <c r="AX173">
+        <v>6</v>
+      </c>
+      <c r="AY173">
+        <v>22</v>
+      </c>
+      <c r="AZ173">
+        <v>12</v>
+      </c>
+      <c r="BA173">
+        <v>7</v>
+      </c>
+      <c r="BB173">
+        <v>2</v>
+      </c>
+      <c r="BC173">
+        <v>9</v>
+      </c>
+      <c r="BD173">
+        <v>1.88</v>
+      </c>
+      <c r="BE173">
+        <v>6.4</v>
+      </c>
+      <c r="BF173">
+        <v>2.15</v>
+      </c>
+      <c r="BG173">
+        <v>1.44</v>
+      </c>
+      <c r="BH173">
+        <v>2.4</v>
+      </c>
+      <c r="BI173">
+        <v>1.76</v>
+      </c>
+      <c r="BJ173">
+        <v>1.85</v>
+      </c>
+      <c r="BK173">
+        <v>2.23</v>
+      </c>
+      <c r="BL173">
+        <v>1.5</v>
+      </c>
+      <c r="BM173">
+        <v>2.95</v>
+      </c>
+      <c r="BN173">
+        <v>1.3</v>
+      </c>
+      <c r="BO173">
+        <v>3.95</v>
+      </c>
+      <c r="BP173">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7537464</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45718.5</v>
+      </c>
+      <c r="F174">
+        <v>25</v>
+      </c>
+      <c r="G174" t="s">
+        <v>77</v>
+      </c>
+      <c r="H174" t="s">
+        <v>81</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>3</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>3</v>
+      </c>
+      <c r="O174" t="s">
+        <v>191</v>
+      </c>
+      <c r="P174" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q174">
+        <v>2.1</v>
+      </c>
+      <c r="R174">
+        <v>2.2</v>
+      </c>
+      <c r="S174">
+        <v>6.5</v>
+      </c>
+      <c r="T174">
+        <v>1.44</v>
+      </c>
+      <c r="U174">
+        <v>2.63</v>
+      </c>
+      <c r="V174">
+        <v>3.25</v>
+      </c>
+      <c r="W174">
+        <v>1.33</v>
+      </c>
+      <c r="X174">
+        <v>9</v>
+      </c>
+      <c r="Y174">
+        <v>1.07</v>
+      </c>
+      <c r="Z174">
+        <v>1.5</v>
+      </c>
+      <c r="AA174">
+        <v>3.8</v>
+      </c>
+      <c r="AB174">
+        <v>6</v>
+      </c>
+      <c r="AC174">
+        <v>1.07</v>
+      </c>
+      <c r="AD174">
+        <v>9.4</v>
+      </c>
+      <c r="AE174">
+        <v>1.35</v>
+      </c>
+      <c r="AF174">
+        <v>3.1</v>
+      </c>
+      <c r="AG174">
+        <v>1.95</v>
+      </c>
+      <c r="AH174">
+        <v>1.7</v>
+      </c>
+      <c r="AI174">
+        <v>2.1</v>
+      </c>
+      <c r="AJ174">
+        <v>1.67</v>
+      </c>
+      <c r="AK174">
+        <v>1.14</v>
+      </c>
+      <c r="AL174">
+        <v>1.27</v>
+      </c>
+      <c r="AM174">
+        <v>2.43</v>
+      </c>
+      <c r="AN174">
+        <v>1.25</v>
+      </c>
+      <c r="AO174">
+        <v>0.5</v>
+      </c>
+      <c r="AP174">
+        <v>1.38</v>
+      </c>
+      <c r="AQ174">
+        <v>0.46</v>
+      </c>
+      <c r="AR174">
+        <v>1.42</v>
+      </c>
+      <c r="AS174">
+        <v>0.96</v>
+      </c>
+      <c r="AT174">
+        <v>2.38</v>
+      </c>
+      <c r="AU174">
+        <v>8</v>
+      </c>
+      <c r="AV174">
+        <v>6</v>
+      </c>
+      <c r="AW174">
+        <v>9</v>
+      </c>
+      <c r="AX174">
+        <v>7</v>
+      </c>
+      <c r="AY174">
+        <v>21</v>
+      </c>
+      <c r="AZ174">
+        <v>15</v>
+      </c>
+      <c r="BA174">
+        <v>5</v>
+      </c>
+      <c r="BB174">
+        <v>3</v>
+      </c>
+      <c r="BC174">
+        <v>8</v>
+      </c>
+      <c r="BD174">
+        <v>1.44</v>
+      </c>
+      <c r="BE174">
+        <v>9</v>
+      </c>
+      <c r="BF174">
+        <v>3.1</v>
+      </c>
+      <c r="BG174">
+        <v>1.39</v>
+      </c>
+      <c r="BH174">
+        <v>2.67</v>
+      </c>
+      <c r="BI174">
+        <v>1.72</v>
+      </c>
+      <c r="BJ174">
+        <v>2</v>
+      </c>
+      <c r="BK174">
+        <v>2.19</v>
+      </c>
+      <c r="BL174">
+        <v>1.57</v>
+      </c>
+      <c r="BM174">
+        <v>2.92</v>
+      </c>
+      <c r="BN174">
+        <v>1.31</v>
+      </c>
+      <c r="BO174">
+        <v>3.92</v>
+      </c>
+      <c r="BP174">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="276">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t>['25', '46', '84']</t>
+  </si>
+  <si>
+    <t>['24', '51']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -1200,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1456,7 +1459,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1537,7 +1540,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ2">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1662,7 +1665,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1740,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ3">
         <v>0.75</v>
@@ -2155,7 +2158,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2280,7 +2283,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2564,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2692,7 +2695,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3104,7 +3107,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3310,7 +3313,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3388,7 +3391,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ11">
         <v>0.46</v>
@@ -3516,7 +3519,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3800,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ13">
         <v>1.23</v>
@@ -4340,7 +4343,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4421,7 +4424,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ16">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4546,7 +4549,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4627,7 +4630,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4958,7 +4961,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5164,7 +5167,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5370,7 +5373,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5576,7 +5579,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5988,7 +5991,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6194,7 +6197,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6684,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ27">
         <v>1.58</v>
@@ -6812,7 +6815,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7096,7 +7099,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -7224,7 +7227,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7511,7 +7514,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ31">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR31">
         <v>1.29</v>
@@ -7636,7 +7639,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7717,7 +7720,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -8048,7 +8051,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8254,7 +8257,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8872,7 +8875,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9078,7 +9081,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9568,7 +9571,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ41">
         <v>1.15</v>
@@ -9774,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ42">
         <v>1.58</v>
@@ -9902,7 +9905,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10108,7 +10111,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10726,7 +10729,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10932,7 +10935,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11013,7 +11016,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11138,7 +11141,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11425,7 +11428,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ50">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR50">
         <v>1.74</v>
@@ -11756,7 +11759,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12043,7 +12046,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12168,7 +12171,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12374,7 +12377,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12786,7 +12789,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12864,7 +12867,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ57">
         <v>2.17</v>
@@ -12992,7 +12995,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13198,7 +13201,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13691,7 +13694,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ61">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR61">
         <v>1.69</v>
@@ -13816,7 +13819,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14022,7 +14025,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14100,7 +14103,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -14228,7 +14231,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14846,7 +14849,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15258,7 +15261,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15464,7 +15467,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -16082,7 +16085,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16366,10 +16369,10 @@
         <v>1.8</v>
       </c>
       <c r="AP74">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR74">
         <v>1.64</v>
@@ -16494,7 +16497,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16700,7 +16703,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17112,7 +17115,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17190,10 +17193,10 @@
         <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ78">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR78">
         <v>1.72</v>
@@ -17318,7 +17321,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17524,7 +17527,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17936,7 +17939,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18142,7 +18145,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18554,7 +18557,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18966,7 +18969,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19250,7 +19253,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ88">
         <v>1.15</v>
@@ -19459,7 +19462,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR89">
         <v>1.12</v>
@@ -19584,7 +19587,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19665,7 +19668,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ90">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19790,7 +19793,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19868,7 +19871,7 @@
         <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ91">
         <v>0.62</v>
@@ -19996,7 +19999,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20408,7 +20411,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20614,7 +20617,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20820,7 +20823,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21232,7 +21235,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21438,7 +21441,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22137,7 +22140,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -22961,7 +22964,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ106">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -23782,7 +23785,7 @@
         <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ110">
         <v>1.77</v>
@@ -23910,7 +23913,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23988,7 +23991,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ111">
         <v>1.17</v>
@@ -24116,7 +24119,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24940,7 +24943,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25146,7 +25149,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25352,7 +25355,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25433,7 +25436,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ118">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR118">
         <v>1.32</v>
@@ -25558,7 +25561,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25764,7 +25767,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25845,7 +25848,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR120">
         <v>1.23</v>
@@ -26176,7 +26179,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26382,7 +26385,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26588,7 +26591,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26666,7 +26669,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ124">
         <v>1.33</v>
@@ -26872,7 +26875,7 @@
         <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ125">
         <v>0.62</v>
@@ -27618,7 +27621,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27699,7 +27702,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ129">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR129">
         <v>1.26</v>
@@ -27824,7 +27827,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27905,7 +27908,7 @@
         <v>1</v>
       </c>
       <c r="AQ130">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR130">
         <v>1.17</v>
@@ -28854,7 +28857,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29266,7 +29269,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29550,7 +29553,7 @@
         <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ138">
         <v>1.23</v>
@@ -29678,7 +29681,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29962,7 +29965,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ140">
         <v>1.17</v>
@@ -30296,7 +30299,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30502,7 +30505,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30789,7 +30792,7 @@
         <v>1</v>
       </c>
       <c r="AQ144">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR144">
         <v>1.16</v>
@@ -31120,7 +31123,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31198,7 +31201,7 @@
         <v>1.6</v>
       </c>
       <c r="AP146">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ146">
         <v>1.83</v>
@@ -31944,7 +31947,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32150,7 +32153,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32231,7 +32234,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR151">
         <v>1.88</v>
@@ -32640,7 +32643,7 @@
         <v>0.9</v>
       </c>
       <c r="AP153">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ153">
         <v>0.75</v>
@@ -32768,7 +32771,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32974,7 +32977,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33261,7 +33264,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ156">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR156">
         <v>1.37</v>
@@ -33386,7 +33389,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33464,7 +33467,7 @@
         <v>1.82</v>
       </c>
       <c r="AP157">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ157">
         <v>1.77</v>
@@ -33592,7 +33595,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33798,7 +33801,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -34004,7 +34007,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34085,7 +34088,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ160">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR160">
         <v>1.33</v>
@@ -34288,7 +34291,7 @@
         <v>0.55</v>
       </c>
       <c r="AP161">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ161">
         <v>0.46</v>
@@ -34622,7 +34625,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35034,7 +35037,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35240,7 +35243,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35446,7 +35449,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35652,7 +35655,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35858,7 +35861,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36064,7 +36067,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q170">
         <v>3.25</v>
@@ -36270,7 +36273,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q171">
         <v>4</v>
@@ -36682,7 +36685,7 @@
         <v>122</v>
       </c>
       <c r="P173" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q173">
         <v>3.6</v>
@@ -37045,6 +37048,418 @@
       </c>
       <c r="BP174">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7537467</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F175">
+        <v>25</v>
+      </c>
+      <c r="G175" t="s">
+        <v>71</v>
+      </c>
+      <c r="H175" t="s">
+        <v>79</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>192</v>
+      </c>
+      <c r="P175" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q175">
+        <v>1.8</v>
+      </c>
+      <c r="R175">
+        <v>2.5</v>
+      </c>
+      <c r="S175">
+        <v>9</v>
+      </c>
+      <c r="T175">
+        <v>1.33</v>
+      </c>
+      <c r="U175">
+        <v>3.25</v>
+      </c>
+      <c r="V175">
+        <v>2.63</v>
+      </c>
+      <c r="W175">
+        <v>1.44</v>
+      </c>
+      <c r="X175">
+        <v>7</v>
+      </c>
+      <c r="Y175">
+        <v>1.1</v>
+      </c>
+      <c r="Z175">
+        <v>1.25</v>
+      </c>
+      <c r="AA175">
+        <v>5</v>
+      </c>
+      <c r="AB175">
+        <v>10</v>
+      </c>
+      <c r="AC175">
+        <v>1.04</v>
+      </c>
+      <c r="AD175">
+        <v>12</v>
+      </c>
+      <c r="AE175">
+        <v>1.27</v>
+      </c>
+      <c r="AF175">
+        <v>3.7</v>
+      </c>
+      <c r="AG175">
+        <v>1.75</v>
+      </c>
+      <c r="AH175">
+        <v>1.91</v>
+      </c>
+      <c r="AI175">
+        <v>2.2</v>
+      </c>
+      <c r="AJ175">
+        <v>1.62</v>
+      </c>
+      <c r="AK175">
+        <v>1.07</v>
+      </c>
+      <c r="AL175">
+        <v>1.18</v>
+      </c>
+      <c r="AM175">
+        <v>3.5</v>
+      </c>
+      <c r="AN175">
+        <v>1.42</v>
+      </c>
+      <c r="AO175">
+        <v>1.33</v>
+      </c>
+      <c r="AP175">
+        <v>1.54</v>
+      </c>
+      <c r="AQ175">
+        <v>1.23</v>
+      </c>
+      <c r="AR175">
+        <v>1.77</v>
+      </c>
+      <c r="AS175">
+        <v>1.04</v>
+      </c>
+      <c r="AT175">
+        <v>2.81</v>
+      </c>
+      <c r="AU175">
+        <v>6</v>
+      </c>
+      <c r="AV175">
+        <v>4</v>
+      </c>
+      <c r="AW175">
+        <v>10</v>
+      </c>
+      <c r="AX175">
+        <v>2</v>
+      </c>
+      <c r="AY175">
+        <v>16</v>
+      </c>
+      <c r="AZ175">
+        <v>7</v>
+      </c>
+      <c r="BA175">
+        <v>5</v>
+      </c>
+      <c r="BB175">
+        <v>6</v>
+      </c>
+      <c r="BC175">
+        <v>11</v>
+      </c>
+      <c r="BD175">
+        <v>1.24</v>
+      </c>
+      <c r="BE175">
+        <v>8</v>
+      </c>
+      <c r="BF175">
+        <v>4.6</v>
+      </c>
+      <c r="BG175">
+        <v>1.37</v>
+      </c>
+      <c r="BH175">
+        <v>2.63</v>
+      </c>
+      <c r="BI175">
+        <v>1.64</v>
+      </c>
+      <c r="BJ175">
+        <v>2</v>
+      </c>
+      <c r="BK175">
+        <v>2.04</v>
+      </c>
+      <c r="BL175">
+        <v>1.61</v>
+      </c>
+      <c r="BM175">
+        <v>2.6</v>
+      </c>
+      <c r="BN175">
+        <v>1.37</v>
+      </c>
+      <c r="BO175">
+        <v>3.45</v>
+      </c>
+      <c r="BP175">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7537461</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45718.64583333334</v>
+      </c>
+      <c r="F176">
+        <v>25</v>
+      </c>
+      <c r="G176" t="s">
+        <v>75</v>
+      </c>
+      <c r="H176" t="s">
+        <v>80</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>84</v>
+      </c>
+      <c r="P176" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q176">
+        <v>3.25</v>
+      </c>
+      <c r="R176">
+        <v>2</v>
+      </c>
+      <c r="S176">
+        <v>3.6</v>
+      </c>
+      <c r="T176">
+        <v>1.5</v>
+      </c>
+      <c r="U176">
+        <v>2.5</v>
+      </c>
+      <c r="V176">
+        <v>3.4</v>
+      </c>
+      <c r="W176">
+        <v>1.3</v>
+      </c>
+      <c r="X176">
+        <v>10</v>
+      </c>
+      <c r="Y176">
+        <v>1.06</v>
+      </c>
+      <c r="Z176">
+        <v>2.55</v>
+      </c>
+      <c r="AA176">
+        <v>3.1</v>
+      </c>
+      <c r="AB176">
+        <v>2.62</v>
+      </c>
+      <c r="AC176">
+        <v>1.09</v>
+      </c>
+      <c r="AD176">
+        <v>7.8</v>
+      </c>
+      <c r="AE176">
+        <v>1.42</v>
+      </c>
+      <c r="AF176">
+        <v>2.75</v>
+      </c>
+      <c r="AG176">
+        <v>2.15</v>
+      </c>
+      <c r="AH176">
+        <v>1.57</v>
+      </c>
+      <c r="AI176">
+        <v>1.95</v>
+      </c>
+      <c r="AJ176">
+        <v>1.8</v>
+      </c>
+      <c r="AK176">
+        <v>1.44</v>
+      </c>
+      <c r="AL176">
+        <v>1.39</v>
+      </c>
+      <c r="AM176">
+        <v>1.52</v>
+      </c>
+      <c r="AN176">
+        <v>2.5</v>
+      </c>
+      <c r="AO176">
+        <v>2.17</v>
+      </c>
+      <c r="AP176">
+        <v>2.31</v>
+      </c>
+      <c r="AQ176">
+        <v>2.23</v>
+      </c>
+      <c r="AR176">
+        <v>2.18</v>
+      </c>
+      <c r="AS176">
+        <v>1.88</v>
+      </c>
+      <c r="AT176">
+        <v>4.06</v>
+      </c>
+      <c r="AU176">
+        <v>0</v>
+      </c>
+      <c r="AV176">
+        <v>4</v>
+      </c>
+      <c r="AW176">
+        <v>6</v>
+      </c>
+      <c r="AX176">
+        <v>3</v>
+      </c>
+      <c r="AY176">
+        <v>8</v>
+      </c>
+      <c r="AZ176">
+        <v>7</v>
+      </c>
+      <c r="BA176">
+        <v>1</v>
+      </c>
+      <c r="BB176">
+        <v>1</v>
+      </c>
+      <c r="BC176">
+        <v>2</v>
+      </c>
+      <c r="BD176">
+        <v>1.64</v>
+      </c>
+      <c r="BE176">
+        <v>6.5</v>
+      </c>
+      <c r="BF176">
+        <v>2.55</v>
+      </c>
+      <c r="BG176">
+        <v>1.49</v>
+      </c>
+      <c r="BH176">
+        <v>2.28</v>
+      </c>
+      <c r="BI176">
+        <v>1.86</v>
+      </c>
+      <c r="BJ176">
+        <v>1.75</v>
+      </c>
+      <c r="BK176">
+        <v>2.38</v>
+      </c>
+      <c r="BL176">
+        <v>1.45</v>
+      </c>
+      <c r="BM176">
+        <v>3.15</v>
+      </c>
+      <c r="BN176">
+        <v>1.26</v>
+      </c>
+      <c r="BO176">
+        <v>4.25</v>
+      </c>
+      <c r="BP176">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -37002,13 +37002,13 @@
         <v>15</v>
       </c>
       <c r="BA174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB174">
         <v>3</v>
       </c>
       <c r="BC174">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD174">
         <v>1.44</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,21 @@
     <t>['24', '51']</t>
   </si>
   <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['14', '90']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['5']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -733,9 +748,6 @@
     <t>['68', '85']</t>
   </si>
   <si>
-    <t>['5']</t>
-  </si>
-  <si>
     <t>['84']</t>
   </si>
   <si>
@@ -842,6 +854,9 @@
   </si>
   <si>
     <t>['13', '83']</t>
+  </si>
+  <si>
+    <t>['60', '84']</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP176"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1459,7 +1474,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1665,7 +1680,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1746,7 +1761,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ3">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2283,7 +2298,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2570,7 +2585,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2695,7 +2710,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2773,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ8">
         <v>0.46</v>
@@ -3107,7 +3122,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3313,7 +3328,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3519,7 +3534,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3597,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4012,7 +4027,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4215,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ15">
         <v>0.62</v>
@@ -4343,7 +4358,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4421,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
         <v>2.23</v>
@@ -4549,7 +4564,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4627,7 +4642,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ17">
         <v>1.23</v>
@@ -4833,10 +4848,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -4961,7 +4976,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5042,7 +5057,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR19">
         <v>1.38</v>
@@ -5167,7 +5182,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5248,7 +5263,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5373,7 +5388,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5454,7 +5469,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ21">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>1.23</v>
@@ -5579,7 +5594,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5657,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5863,7 +5878,7 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ23">
         <v>0.62</v>
@@ -5991,7 +6006,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6069,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ24">
         <v>1.77</v>
@@ -6197,7 +6212,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6278,7 +6293,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ25">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR25">
         <v>0.98</v>
@@ -6481,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ26">
         <v>1.23</v>
@@ -6690,7 +6705,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ27">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR27">
         <v>1.95</v>
@@ -6815,7 +6830,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7102,7 +7117,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7227,7 +7242,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7308,7 +7323,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ30">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR30">
         <v>0.96</v>
@@ -7511,7 +7526,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ31">
         <v>2.23</v>
@@ -7639,7 +7654,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7717,7 +7732,7 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ32">
         <v>1.23</v>
@@ -7926,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR33">
         <v>0.97</v>
@@ -8051,7 +8066,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8132,7 +8147,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR34">
         <v>1.44</v>
@@ -8257,7 +8272,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8541,10 +8556,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR36">
         <v>2.14</v>
@@ -8875,7 +8890,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8953,10 +8968,10 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9081,7 +9096,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9365,7 +9380,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ40">
         <v>1.77</v>
@@ -9780,7 +9795,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ42">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR42">
         <v>1.99</v>
@@ -9905,7 +9920,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9983,10 +9998,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ43">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
         <v>1.06</v>
@@ -10111,7 +10126,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10192,7 +10207,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10395,10 +10410,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ45">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10601,7 +10616,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
         <v>0.46</v>
@@ -10729,7 +10744,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10810,7 +10825,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR47">
         <v>1.06</v>
@@ -10935,7 +10950,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11013,7 +11028,7 @@
         <v>1.67</v>
       </c>
       <c r="AP48">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>1.23</v>
@@ -11141,7 +11156,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11222,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="AQ49">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11634,7 +11649,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ51">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -11759,7 +11774,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12043,7 +12058,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ53">
         <v>1.23</v>
@@ -12171,7 +12186,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12249,10 +12264,10 @@
         <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ54">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR54">
         <v>2.03</v>
@@ -12377,7 +12392,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12458,7 +12473,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ55">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR55">
         <v>1.16</v>
@@ -12661,7 +12676,7 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ56">
         <v>0.62</v>
@@ -12789,7 +12804,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12870,7 +12885,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ57">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.84</v>
@@ -12995,7 +13010,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13073,10 +13088,10 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13201,7 +13216,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13488,7 +13503,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ60">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR60">
         <v>1.32</v>
@@ -13691,7 +13706,7 @@
         <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ61">
         <v>2.23</v>
@@ -13819,7 +13834,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14025,7 +14040,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14106,7 +14121,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14231,7 +14246,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14309,7 +14324,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
         <v>1.77</v>
@@ -14515,10 +14530,10 @@
         <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ65">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR65">
         <v>1.98</v>
@@ -14721,7 +14736,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
         <v>1.23</v>
@@ -14849,7 +14864,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14927,10 +14942,10 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -15136,7 +15151,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ68">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR68">
         <v>1.45</v>
@@ -15261,7 +15276,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15342,7 +15357,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ69">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15467,7 +15482,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15545,10 +15560,10 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ70">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR70">
         <v>1.11</v>
@@ -15751,10 +15766,10 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR71">
         <v>1.51</v>
@@ -15957,7 +15972,7 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -16085,7 +16100,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16497,7 +16512,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16703,7 +16718,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16784,7 +16799,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -17115,7 +17130,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17321,7 +17336,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17399,10 +17414,10 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17527,7 +17542,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17605,10 +17620,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR80">
         <v>1.08</v>
@@ -17811,10 +17826,10 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17939,7 +17954,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18017,10 +18032,10 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR82">
         <v>1.27</v>
@@ -18145,7 +18160,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18223,10 +18238,10 @@
         <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR83">
         <v>1.54</v>
@@ -18429,10 +18444,10 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ84">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR84">
         <v>2.03</v>
@@ -18557,7 +18572,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18638,7 +18653,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ85">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR85">
         <v>1.32</v>
@@ -18969,7 +18984,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19587,7 +19602,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19793,7 +19808,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19999,7 +20014,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20283,10 +20298,10 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -20411,7 +20426,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20489,7 +20504,7 @@
         <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ94">
         <v>1.77</v>
@@ -20617,7 +20632,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20698,7 +20713,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ95">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>1.27</v>
@@ -20823,7 +20838,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20904,7 +20919,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ96">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21107,10 +21122,10 @@
         <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ97">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21235,7 +21250,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21313,7 +21328,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ98">
         <v>1.23</v>
@@ -21441,7 +21456,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21519,10 +21534,10 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -21725,10 +21740,10 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ100">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -21934,7 +21949,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR101">
         <v>1.32</v>
@@ -22343,10 +22358,10 @@
         <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ103">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
         <v>1.47</v>
@@ -22552,7 +22567,7 @@
         <v>1</v>
       </c>
       <c r="AQ104">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR104">
         <v>1.19</v>
@@ -22755,10 +22770,10 @@
         <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ105">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR105">
         <v>1.29</v>
@@ -22961,7 +22976,7 @@
         <v>1.86</v>
       </c>
       <c r="AP106">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>2.23</v>
@@ -23167,7 +23182,7 @@
         <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ107">
         <v>0.46</v>
@@ -23913,7 +23928,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -23994,7 +24009,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ111">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR111">
         <v>1.89</v>
@@ -24119,7 +24134,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24197,7 +24212,7 @@
         <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ112">
         <v>1.15</v>
@@ -24406,7 +24421,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -24609,7 +24624,7 @@
         <v>0.75</v>
       </c>
       <c r="AP114">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>0.46</v>
@@ -24818,7 +24833,7 @@
         <v>1</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -24943,7 +24958,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25021,10 +25036,10 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25149,7 +25164,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25230,7 +25245,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ117">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25355,7 +25370,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25561,7 +25576,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25642,7 +25657,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ119">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR119">
         <v>1.85</v>
@@ -25767,7 +25782,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25845,7 +25860,7 @@
         <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ120">
         <v>2.23</v>
@@ -26051,7 +26066,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ121">
         <v>1.15</v>
@@ -26179,7 +26194,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26260,7 +26275,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ122">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR122">
         <v>1.28</v>
@@ -26385,7 +26400,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26463,7 +26478,7 @@
         <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ123">
         <v>1.77</v>
@@ -26591,7 +26606,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26672,7 +26687,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -27081,7 +27096,7 @@
         <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ126">
         <v>1.23</v>
@@ -27290,7 +27305,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ127">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27493,10 +27508,10 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR128">
         <v>1.37</v>
@@ -27621,7 +27636,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27827,7 +27842,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28111,10 +28126,10 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.17</v>
@@ -28317,10 +28332,10 @@
         <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ132">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR132">
         <v>1.43</v>
@@ -28526,7 +28541,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ133">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR133">
         <v>1.91</v>
@@ -28857,7 +28872,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29141,7 +29156,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP136">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ136">
         <v>0.62</v>
@@ -29269,7 +29284,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29350,7 +29365,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR137">
         <v>1.31</v>
@@ -29681,7 +29696,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29759,7 +29774,7 @@
         <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ139">
         <v>1.15</v>
@@ -29968,7 +29983,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ140">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR140">
         <v>1.7</v>
@@ -30171,10 +30186,10 @@
         <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ141">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR141">
         <v>1.93</v>
@@ -30299,7 +30314,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30380,7 +30395,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ142">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR142">
         <v>1.82</v>
@@ -30505,7 +30520,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30586,7 +30601,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ143">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR143">
         <v>1.33</v>
@@ -30995,7 +31010,7 @@
         <v>1.1</v>
       </c>
       <c r="AP145">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ145">
         <v>1.15</v>
@@ -31123,7 +31138,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31204,7 +31219,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ146">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR146">
         <v>1.73</v>
@@ -31407,7 +31422,7 @@
         <v>1.7</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ147">
         <v>1.77</v>
@@ -31613,7 +31628,7 @@
         <v>0.6</v>
       </c>
       <c r="AP148">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ148">
         <v>0.46</v>
@@ -31947,7 +31962,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32028,7 +32043,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ150">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32153,7 +32168,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32231,7 +32246,7 @@
         <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ151">
         <v>1.23</v>
@@ -32437,10 +32452,10 @@
         <v>1.9</v>
       </c>
       <c r="AP152">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ152">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR152">
         <v>1.42</v>
@@ -32646,7 +32661,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ153">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR153">
         <v>2.03</v>
@@ -32771,7 +32786,7 @@
         <v>147</v>
       </c>
       <c r="P154" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -32977,7 +32992,7 @@
         <v>84</v>
       </c>
       <c r="P155" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q155">
         <v>4</v>
@@ -33055,10 +33070,10 @@
         <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ155">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR155">
         <v>1.07</v>
@@ -33389,7 +33404,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33595,7 +33610,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33801,7 +33816,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33882,7 +33897,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR159">
         <v>1.89</v>
@@ -34007,7 +34022,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34497,7 +34512,7 @@
         <v>0.73</v>
       </c>
       <c r="AP162">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ162">
         <v>0.62</v>
@@ -34625,7 +34640,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -34703,10 +34718,10 @@
         <v>1.36</v>
       </c>
       <c r="AP163">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR163">
         <v>1.4</v>
@@ -34912,7 +34927,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ164">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR164">
         <v>1.26</v>
@@ -35037,7 +35052,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35118,7 +35133,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ165">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR165">
         <v>1.27</v>
@@ -35243,7 +35258,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35321,7 +35336,7 @@
         <v>1.45</v>
       </c>
       <c r="AP166">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ166">
         <v>1.23</v>
@@ -35449,7 +35464,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35527,10 +35542,10 @@
         <v>1.73</v>
       </c>
       <c r="AP167">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ167">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR167">
         <v>1.13</v>
@@ -35655,7 +35670,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35733,10 +35748,10 @@
         <v>1.73</v>
       </c>
       <c r="AP168">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ168">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR168">
         <v>1.45</v>
@@ -35861,7 +35876,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -35939,10 +35954,10 @@
         <v>2.36</v>
       </c>
       <c r="AP169">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ169">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR169">
         <v>1.94</v>
@@ -36067,7 +36082,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q170">
         <v>3.25</v>
@@ -36273,7 +36288,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q171">
         <v>4</v>
@@ -36685,7 +36700,7 @@
         <v>122</v>
       </c>
       <c r="P173" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q173">
         <v>3.6</v>
@@ -37303,7 +37318,7 @@
         <v>84</v>
       </c>
       <c r="P176" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q176">
         <v>3.25</v>
@@ -37460,6 +37475,1448 @@
       </c>
       <c r="BP176">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7537473</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F177">
+        <v>26</v>
+      </c>
+      <c r="G177" t="s">
+        <v>80</v>
+      </c>
+      <c r="H177" t="s">
+        <v>77</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
+        <v>193</v>
+      </c>
+      <c r="P177" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q177">
+        <v>1.62</v>
+      </c>
+      <c r="R177">
+        <v>2.88</v>
+      </c>
+      <c r="S177">
+        <v>10</v>
+      </c>
+      <c r="T177">
+        <v>1.25</v>
+      </c>
+      <c r="U177">
+        <v>3.75</v>
+      </c>
+      <c r="V177">
+        <v>2.2</v>
+      </c>
+      <c r="W177">
+        <v>1.62</v>
+      </c>
+      <c r="X177">
+        <v>5</v>
+      </c>
+      <c r="Y177">
+        <v>1.17</v>
+      </c>
+      <c r="Z177">
+        <v>1.15</v>
+      </c>
+      <c r="AA177">
+        <v>7</v>
+      </c>
+      <c r="AB177">
+        <v>12</v>
+      </c>
+      <c r="AC177">
+        <v>1.05</v>
+      </c>
+      <c r="AD177">
+        <v>11</v>
+      </c>
+      <c r="AE177">
+        <v>1.26</v>
+      </c>
+      <c r="AF177">
+        <v>3.8</v>
+      </c>
+      <c r="AG177">
+        <v>1.74</v>
+      </c>
+      <c r="AH177">
+        <v>1.97</v>
+      </c>
+      <c r="AI177">
+        <v>2.05</v>
+      </c>
+      <c r="AJ177">
+        <v>1.7</v>
+      </c>
+      <c r="AK177">
+        <v>1.06</v>
+      </c>
+      <c r="AL177">
+        <v>1.18</v>
+      </c>
+      <c r="AM177">
+        <v>3.5</v>
+      </c>
+      <c r="AN177">
+        <v>2.33</v>
+      </c>
+      <c r="AO177">
+        <v>1.5</v>
+      </c>
+      <c r="AP177">
+        <v>2.38</v>
+      </c>
+      <c r="AQ177">
+        <v>1.38</v>
+      </c>
+      <c r="AR177">
+        <v>1.95</v>
+      </c>
+      <c r="AS177">
+        <v>1.05</v>
+      </c>
+      <c r="AT177">
+        <v>3</v>
+      </c>
+      <c r="AU177">
+        <v>11</v>
+      </c>
+      <c r="AV177">
+        <v>3</v>
+      </c>
+      <c r="AW177">
+        <v>13</v>
+      </c>
+      <c r="AX177">
+        <v>3</v>
+      </c>
+      <c r="AY177">
+        <v>25</v>
+      </c>
+      <c r="AZ177">
+        <v>7</v>
+      </c>
+      <c r="BA177">
+        <v>9</v>
+      </c>
+      <c r="BB177">
+        <v>1</v>
+      </c>
+      <c r="BC177">
+        <v>10</v>
+      </c>
+      <c r="BD177">
+        <v>1.02</v>
+      </c>
+      <c r="BE177">
+        <v>19</v>
+      </c>
+      <c r="BF177">
+        <v>16.5</v>
+      </c>
+      <c r="BG177">
+        <v>1.38</v>
+      </c>
+      <c r="BH177">
+        <v>2.71</v>
+      </c>
+      <c r="BI177">
+        <v>1.7</v>
+      </c>
+      <c r="BJ177">
+        <v>2.03</v>
+      </c>
+      <c r="BK177">
+        <v>2.15</v>
+      </c>
+      <c r="BL177">
+        <v>1.59</v>
+      </c>
+      <c r="BM177">
+        <v>2.83</v>
+      </c>
+      <c r="BN177">
+        <v>1.33</v>
+      </c>
+      <c r="BO177">
+        <v>3.52</v>
+      </c>
+      <c r="BP177">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7537471</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F178">
+        <v>26</v>
+      </c>
+      <c r="G178" t="s">
+        <v>74</v>
+      </c>
+      <c r="H178" t="s">
+        <v>73</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>2</v>
+      </c>
+      <c r="O178" t="s">
+        <v>194</v>
+      </c>
+      <c r="P178" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q178">
+        <v>5.5</v>
+      </c>
+      <c r="R178">
+        <v>2</v>
+      </c>
+      <c r="S178">
+        <v>2.5</v>
+      </c>
+      <c r="T178">
+        <v>1.5</v>
+      </c>
+      <c r="U178">
+        <v>2.5</v>
+      </c>
+      <c r="V178">
+        <v>3.5</v>
+      </c>
+      <c r="W178">
+        <v>1.29</v>
+      </c>
+      <c r="X178">
+        <v>11</v>
+      </c>
+      <c r="Y178">
+        <v>1.05</v>
+      </c>
+      <c r="Z178">
+        <v>5.5</v>
+      </c>
+      <c r="AA178">
+        <v>3.65</v>
+      </c>
+      <c r="AB178">
+        <v>1.6</v>
+      </c>
+      <c r="AC178">
+        <v>1.09</v>
+      </c>
+      <c r="AD178">
+        <v>7.6</v>
+      </c>
+      <c r="AE178">
+        <v>1.45</v>
+      </c>
+      <c r="AF178">
+        <v>2.65</v>
+      </c>
+      <c r="AG178">
+        <v>2.2</v>
+      </c>
+      <c r="AH178">
+        <v>1.55</v>
+      </c>
+      <c r="AI178">
+        <v>2.1</v>
+      </c>
+      <c r="AJ178">
+        <v>1.67</v>
+      </c>
+      <c r="AK178">
+        <v>2.03</v>
+      </c>
+      <c r="AL178">
+        <v>1.34</v>
+      </c>
+      <c r="AM178">
+        <v>1.2</v>
+      </c>
+      <c r="AN178">
+        <v>0.92</v>
+      </c>
+      <c r="AO178">
+        <v>1.58</v>
+      </c>
+      <c r="AP178">
+        <v>0.92</v>
+      </c>
+      <c r="AQ178">
+        <v>1.54</v>
+      </c>
+      <c r="AR178">
+        <v>1.3</v>
+      </c>
+      <c r="AS178">
+        <v>1.59</v>
+      </c>
+      <c r="AT178">
+        <v>2.89</v>
+      </c>
+      <c r="AU178">
+        <v>6</v>
+      </c>
+      <c r="AV178">
+        <v>7</v>
+      </c>
+      <c r="AW178">
+        <v>7</v>
+      </c>
+      <c r="AX178">
+        <v>10</v>
+      </c>
+      <c r="AY178">
+        <v>13</v>
+      </c>
+      <c r="AZ178">
+        <v>20</v>
+      </c>
+      <c r="BA178">
+        <v>2</v>
+      </c>
+      <c r="BB178">
+        <v>3</v>
+      </c>
+      <c r="BC178">
+        <v>5</v>
+      </c>
+      <c r="BD178">
+        <v>2.9</v>
+      </c>
+      <c r="BE178">
+        <v>6.4</v>
+      </c>
+      <c r="BF178">
+        <v>1.52</v>
+      </c>
+      <c r="BG178">
+        <v>1.48</v>
+      </c>
+      <c r="BH178">
+        <v>2.28</v>
+      </c>
+      <c r="BI178">
+        <v>1.83</v>
+      </c>
+      <c r="BJ178">
+        <v>1.76</v>
+      </c>
+      <c r="BK178">
+        <v>2.35</v>
+      </c>
+      <c r="BL178">
+        <v>1.46</v>
+      </c>
+      <c r="BM178">
+        <v>3.1</v>
+      </c>
+      <c r="BN178">
+        <v>1.27</v>
+      </c>
+      <c r="BO178">
+        <v>4.1</v>
+      </c>
+      <c r="BP178">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7537474</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F179">
+        <v>26</v>
+      </c>
+      <c r="G179" t="s">
+        <v>76</v>
+      </c>
+      <c r="H179" t="s">
+        <v>72</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>84</v>
+      </c>
+      <c r="P179" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q179">
+        <v>3.1</v>
+      </c>
+      <c r="R179">
+        <v>1.83</v>
+      </c>
+      <c r="S179">
+        <v>4.75</v>
+      </c>
+      <c r="T179">
+        <v>1.62</v>
+      </c>
+      <c r="U179">
+        <v>2.2</v>
+      </c>
+      <c r="V179">
+        <v>4</v>
+      </c>
+      <c r="W179">
+        <v>1.22</v>
+      </c>
+      <c r="X179">
+        <v>15</v>
+      </c>
+      <c r="Y179">
+        <v>1.03</v>
+      </c>
+      <c r="Z179">
+        <v>2.1</v>
+      </c>
+      <c r="AA179">
+        <v>3</v>
+      </c>
+      <c r="AB179">
+        <v>3.75</v>
+      </c>
+      <c r="AC179">
+        <v>1.11</v>
+      </c>
+      <c r="AD179">
+        <v>6.8</v>
+      </c>
+      <c r="AE179">
+        <v>1.55</v>
+      </c>
+      <c r="AF179">
+        <v>2.2</v>
+      </c>
+      <c r="AG179">
+        <v>2.4</v>
+      </c>
+      <c r="AH179">
+        <v>1.46</v>
+      </c>
+      <c r="AI179">
+        <v>2.25</v>
+      </c>
+      <c r="AJ179">
+        <v>1.57</v>
+      </c>
+      <c r="AK179">
+        <v>1.29</v>
+      </c>
+      <c r="AL179">
+        <v>1.38</v>
+      </c>
+      <c r="AM179">
+        <v>1.73</v>
+      </c>
+      <c r="AN179">
+        <v>1.33</v>
+      </c>
+      <c r="AO179">
+        <v>1.17</v>
+      </c>
+      <c r="AP179">
+        <v>1.31</v>
+      </c>
+      <c r="AQ179">
+        <v>1.15</v>
+      </c>
+      <c r="AR179">
+        <v>1.15</v>
+      </c>
+      <c r="AS179">
+        <v>1.09</v>
+      </c>
+      <c r="AT179">
+        <v>2.24</v>
+      </c>
+      <c r="AU179">
+        <v>8</v>
+      </c>
+      <c r="AV179">
+        <v>5</v>
+      </c>
+      <c r="AW179">
+        <v>13</v>
+      </c>
+      <c r="AX179">
+        <v>11</v>
+      </c>
+      <c r="AY179">
+        <v>27</v>
+      </c>
+      <c r="AZ179">
+        <v>19</v>
+      </c>
+      <c r="BA179">
+        <v>4</v>
+      </c>
+      <c r="BB179">
+        <v>4</v>
+      </c>
+      <c r="BC179">
+        <v>8</v>
+      </c>
+      <c r="BD179">
+        <v>1.86</v>
+      </c>
+      <c r="BE179">
+        <v>6.25</v>
+      </c>
+      <c r="BF179">
+        <v>2.15</v>
+      </c>
+      <c r="BG179">
+        <v>1.48</v>
+      </c>
+      <c r="BH179">
+        <v>2.3</v>
+      </c>
+      <c r="BI179">
+        <v>1.83</v>
+      </c>
+      <c r="BJ179">
+        <v>1.77</v>
+      </c>
+      <c r="BK179">
+        <v>2.35</v>
+      </c>
+      <c r="BL179">
+        <v>1.46</v>
+      </c>
+      <c r="BM179">
+        <v>3.15</v>
+      </c>
+      <c r="BN179">
+        <v>1.26</v>
+      </c>
+      <c r="BO179">
+        <v>4.25</v>
+      </c>
+      <c r="BP179">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7537469</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F180">
+        <v>26</v>
+      </c>
+      <c r="G180" t="s">
+        <v>83</v>
+      </c>
+      <c r="H180" t="s">
+        <v>71</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>2</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>195</v>
+      </c>
+      <c r="P180" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q180">
+        <v>6.5</v>
+      </c>
+      <c r="R180">
+        <v>2.38</v>
+      </c>
+      <c r="S180">
+        <v>1.95</v>
+      </c>
+      <c r="T180">
+        <v>1.36</v>
+      </c>
+      <c r="U180">
+        <v>3</v>
+      </c>
+      <c r="V180">
+        <v>2.63</v>
+      </c>
+      <c r="W180">
+        <v>1.44</v>
+      </c>
+      <c r="X180">
+        <v>7</v>
+      </c>
+      <c r="Y180">
+        <v>1.1</v>
+      </c>
+      <c r="Z180">
+        <v>6.5</v>
+      </c>
+      <c r="AA180">
+        <v>4.7</v>
+      </c>
+      <c r="AB180">
+        <v>1.4</v>
+      </c>
+      <c r="AC180">
+        <v>1.01</v>
+      </c>
+      <c r="AD180">
+        <v>11</v>
+      </c>
+      <c r="AE180">
+        <v>1.24</v>
+      </c>
+      <c r="AF180">
+        <v>4</v>
+      </c>
+      <c r="AG180">
+        <v>1.65</v>
+      </c>
+      <c r="AH180">
+        <v>2.05</v>
+      </c>
+      <c r="AI180">
+        <v>1.95</v>
+      </c>
+      <c r="AJ180">
+        <v>1.8</v>
+      </c>
+      <c r="AK180">
+        <v>3.2</v>
+      </c>
+      <c r="AL180">
+        <v>1.2</v>
+      </c>
+      <c r="AM180">
+        <v>1.08</v>
+      </c>
+      <c r="AN180">
+        <v>0.83</v>
+      </c>
+      <c r="AO180">
+        <v>2.17</v>
+      </c>
+      <c r="AP180">
+        <v>1</v>
+      </c>
+      <c r="AQ180">
+        <v>2</v>
+      </c>
+      <c r="AR180">
+        <v>1.45</v>
+      </c>
+      <c r="AS180">
+        <v>1.64</v>
+      </c>
+      <c r="AT180">
+        <v>3.09</v>
+      </c>
+      <c r="AU180">
+        <v>10</v>
+      </c>
+      <c r="AV180">
+        <v>4</v>
+      </c>
+      <c r="AW180">
+        <v>9</v>
+      </c>
+      <c r="AX180">
+        <v>9</v>
+      </c>
+      <c r="AY180">
+        <v>22</v>
+      </c>
+      <c r="AZ180">
+        <v>17</v>
+      </c>
+      <c r="BA180">
+        <v>5</v>
+      </c>
+      <c r="BB180">
+        <v>7</v>
+      </c>
+      <c r="BC180">
+        <v>12</v>
+      </c>
+      <c r="BD180">
+        <v>3.4</v>
+      </c>
+      <c r="BE180">
+        <v>7</v>
+      </c>
+      <c r="BF180">
+        <v>1.38</v>
+      </c>
+      <c r="BG180">
+        <v>1.34</v>
+      </c>
+      <c r="BH180">
+        <v>2.75</v>
+      </c>
+      <c r="BI180">
+        <v>1.58</v>
+      </c>
+      <c r="BJ180">
+        <v>2.08</v>
+      </c>
+      <c r="BK180">
+        <v>1.96</v>
+      </c>
+      <c r="BL180">
+        <v>1.66</v>
+      </c>
+      <c r="BM180">
+        <v>2.48</v>
+      </c>
+      <c r="BN180">
+        <v>1.41</v>
+      </c>
+      <c r="BO180">
+        <v>3.25</v>
+      </c>
+      <c r="BP180">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7537468</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F181">
+        <v>26</v>
+      </c>
+      <c r="G181" t="s">
+        <v>79</v>
+      </c>
+      <c r="H181" t="s">
+        <v>78</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>3</v>
+      </c>
+      <c r="O181" t="s">
+        <v>196</v>
+      </c>
+      <c r="P181" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q181">
+        <v>2.5</v>
+      </c>
+      <c r="R181">
+        <v>2.1</v>
+      </c>
+      <c r="S181">
+        <v>5</v>
+      </c>
+      <c r="T181">
+        <v>1.44</v>
+      </c>
+      <c r="U181">
+        <v>2.63</v>
+      </c>
+      <c r="V181">
+        <v>3.25</v>
+      </c>
+      <c r="W181">
+        <v>1.33</v>
+      </c>
+      <c r="X181">
+        <v>10</v>
+      </c>
+      <c r="Y181">
+        <v>1.06</v>
+      </c>
+      <c r="Z181">
+        <v>1.64</v>
+      </c>
+      <c r="AA181">
+        <v>3.6</v>
+      </c>
+      <c r="AB181">
+        <v>5</v>
+      </c>
+      <c r="AC181">
+        <v>1.08</v>
+      </c>
+      <c r="AD181">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE181">
+        <v>1.4</v>
+      </c>
+      <c r="AF181">
+        <v>2.85</v>
+      </c>
+      <c r="AG181">
+        <v>2.1</v>
+      </c>
+      <c r="AH181">
+        <v>1.61</v>
+      </c>
+      <c r="AI181">
+        <v>2</v>
+      </c>
+      <c r="AJ181">
+        <v>1.75</v>
+      </c>
+      <c r="AK181">
+        <v>1.17</v>
+      </c>
+      <c r="AL181">
+        <v>1.32</v>
+      </c>
+      <c r="AM181">
+        <v>2.17</v>
+      </c>
+      <c r="AN181">
+        <v>1.58</v>
+      </c>
+      <c r="AO181">
+        <v>0.75</v>
+      </c>
+      <c r="AP181">
+        <v>1.46</v>
+      </c>
+      <c r="AQ181">
+        <v>0.92</v>
+      </c>
+      <c r="AR181">
+        <v>1.35</v>
+      </c>
+      <c r="AS181">
+        <v>1.28</v>
+      </c>
+      <c r="AT181">
+        <v>2.63</v>
+      </c>
+      <c r="AU181">
+        <v>2</v>
+      </c>
+      <c r="AV181">
+        <v>6</v>
+      </c>
+      <c r="AW181">
+        <v>11</v>
+      </c>
+      <c r="AX181">
+        <v>3</v>
+      </c>
+      <c r="AY181">
+        <v>16</v>
+      </c>
+      <c r="AZ181">
+        <v>9</v>
+      </c>
+      <c r="BA181">
+        <v>6</v>
+      </c>
+      <c r="BB181">
+        <v>1</v>
+      </c>
+      <c r="BC181">
+        <v>7</v>
+      </c>
+      <c r="BD181">
+        <v>1.35</v>
+      </c>
+      <c r="BE181">
+        <v>6.75</v>
+      </c>
+      <c r="BF181">
+        <v>3.55</v>
+      </c>
+      <c r="BG181">
+        <v>1.42</v>
+      </c>
+      <c r="BH181">
+        <v>2.48</v>
+      </c>
+      <c r="BI181">
+        <v>1.73</v>
+      </c>
+      <c r="BJ181">
+        <v>1.88</v>
+      </c>
+      <c r="BK181">
+        <v>2.17</v>
+      </c>
+      <c r="BL181">
+        <v>1.54</v>
+      </c>
+      <c r="BM181">
+        <v>2.85</v>
+      </c>
+      <c r="BN181">
+        <v>1.32</v>
+      </c>
+      <c r="BO181">
+        <v>3.8</v>
+      </c>
+      <c r="BP181">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7537470</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F182">
+        <v>26</v>
+      </c>
+      <c r="G182" t="s">
+        <v>82</v>
+      </c>
+      <c r="H182" t="s">
+        <v>75</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182" t="s">
+        <v>84</v>
+      </c>
+      <c r="P182" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q182">
+        <v>5.5</v>
+      </c>
+      <c r="R182">
+        <v>2.1</v>
+      </c>
+      <c r="S182">
+        <v>2.3</v>
+      </c>
+      <c r="T182">
+        <v>1.44</v>
+      </c>
+      <c r="U182">
+        <v>2.63</v>
+      </c>
+      <c r="V182">
+        <v>3.25</v>
+      </c>
+      <c r="W182">
+        <v>1.33</v>
+      </c>
+      <c r="X182">
+        <v>9</v>
+      </c>
+      <c r="Y182">
+        <v>1.07</v>
+      </c>
+      <c r="Z182">
+        <v>5.25</v>
+      </c>
+      <c r="AA182">
+        <v>3.6</v>
+      </c>
+      <c r="AB182">
+        <v>1.64</v>
+      </c>
+      <c r="AC182">
+        <v>1.08</v>
+      </c>
+      <c r="AD182">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE182">
+        <v>1.39</v>
+      </c>
+      <c r="AF182">
+        <v>2.9</v>
+      </c>
+      <c r="AG182">
+        <v>2</v>
+      </c>
+      <c r="AH182">
+        <v>1.67</v>
+      </c>
+      <c r="AI182">
+        <v>2</v>
+      </c>
+      <c r="AJ182">
+        <v>1.75</v>
+      </c>
+      <c r="AK182">
+        <v>2.19</v>
+      </c>
+      <c r="AL182">
+        <v>1.32</v>
+      </c>
+      <c r="AM182">
+        <v>1.16</v>
+      </c>
+      <c r="AN182">
+        <v>2.17</v>
+      </c>
+      <c r="AO182">
+        <v>1.83</v>
+      </c>
+      <c r="AP182">
+        <v>2.08</v>
+      </c>
+      <c r="AQ182">
+        <v>1.77</v>
+      </c>
+      <c r="AR182">
+        <v>1.55</v>
+      </c>
+      <c r="AS182">
+        <v>1.72</v>
+      </c>
+      <c r="AT182">
+        <v>3.27</v>
+      </c>
+      <c r="AU182">
+        <v>3</v>
+      </c>
+      <c r="AV182">
+        <v>5</v>
+      </c>
+      <c r="AW182">
+        <v>3</v>
+      </c>
+      <c r="AX182">
+        <v>9</v>
+      </c>
+      <c r="AY182">
+        <v>7</v>
+      </c>
+      <c r="AZ182">
+        <v>17</v>
+      </c>
+      <c r="BA182">
+        <v>4</v>
+      </c>
+      <c r="BB182">
+        <v>3</v>
+      </c>
+      <c r="BC182">
+        <v>7</v>
+      </c>
+      <c r="BD182">
+        <v>3.4</v>
+      </c>
+      <c r="BE182">
+        <v>6.75</v>
+      </c>
+      <c r="BF182">
+        <v>1.38</v>
+      </c>
+      <c r="BG182">
+        <v>1.47</v>
+      </c>
+      <c r="BH182">
+        <v>2.32</v>
+      </c>
+      <c r="BI182">
+        <v>1.82</v>
+      </c>
+      <c r="BJ182">
+        <v>1.78</v>
+      </c>
+      <c r="BK182">
+        <v>2.3</v>
+      </c>
+      <c r="BL182">
+        <v>1.47</v>
+      </c>
+      <c r="BM182">
+        <v>3.05</v>
+      </c>
+      <c r="BN182">
+        <v>1.27</v>
+      </c>
+      <c r="BO182">
+        <v>4.1</v>
+      </c>
+      <c r="BP182">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7537475</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F183">
+        <v>26</v>
+      </c>
+      <c r="G183" t="s">
+        <v>81</v>
+      </c>
+      <c r="H183" t="s">
+        <v>70</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
+        <v>197</v>
+      </c>
+      <c r="P183" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q183">
+        <v>6.5</v>
+      </c>
+      <c r="R183">
+        <v>2</v>
+      </c>
+      <c r="S183">
+        <v>2.38</v>
+      </c>
+      <c r="T183">
+        <v>1.53</v>
+      </c>
+      <c r="U183">
+        <v>2.38</v>
+      </c>
+      <c r="V183">
+        <v>3.75</v>
+      </c>
+      <c r="W183">
+        <v>1.25</v>
+      </c>
+      <c r="X183">
+        <v>11</v>
+      </c>
+      <c r="Y183">
+        <v>1.05</v>
+      </c>
+      <c r="Z183">
+        <v>3</v>
+      </c>
+      <c r="AA183">
+        <v>2.8</v>
+      </c>
+      <c r="AB183">
+        <v>2.5</v>
+      </c>
+      <c r="AC183">
+        <v>1.1</v>
+      </c>
+      <c r="AD183">
+        <v>7.2</v>
+      </c>
+      <c r="AE183">
+        <v>1.48</v>
+      </c>
+      <c r="AF183">
+        <v>2.4</v>
+      </c>
+      <c r="AG183">
+        <v>2.34</v>
+      </c>
+      <c r="AH183">
+        <v>1.49</v>
+      </c>
+      <c r="AI183">
+        <v>2.38</v>
+      </c>
+      <c r="AJ183">
+        <v>1.53</v>
+      </c>
+      <c r="AK183">
+        <v>1.56</v>
+      </c>
+      <c r="AL183">
+        <v>1.39</v>
+      </c>
+      <c r="AM183">
+        <v>1.4</v>
+      </c>
+      <c r="AN183">
+        <v>0.5</v>
+      </c>
+      <c r="AO183">
+        <v>1.33</v>
+      </c>
+      <c r="AP183">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ183">
+        <v>1.23</v>
+      </c>
+      <c r="AR183">
+        <v>1.11</v>
+      </c>
+      <c r="AS183">
+        <v>1.02</v>
+      </c>
+      <c r="AT183">
+        <v>2.13</v>
+      </c>
+      <c r="AU183">
+        <v>0</v>
+      </c>
+      <c r="AV183">
+        <v>5</v>
+      </c>
+      <c r="AW183">
+        <v>3</v>
+      </c>
+      <c r="AX183">
+        <v>12</v>
+      </c>
+      <c r="AY183">
+        <v>4</v>
+      </c>
+      <c r="AZ183">
+        <v>20</v>
+      </c>
+      <c r="BA183">
+        <v>0</v>
+      </c>
+      <c r="BB183">
+        <v>8</v>
+      </c>
+      <c r="BC183">
+        <v>8</v>
+      </c>
+      <c r="BD183">
+        <v>2.46</v>
+      </c>
+      <c r="BE183">
+        <v>6.3</v>
+      </c>
+      <c r="BF183">
+        <v>1.92</v>
+      </c>
+      <c r="BG183">
+        <v>1.41</v>
+      </c>
+      <c r="BH183">
+        <v>2.6</v>
+      </c>
+      <c r="BI183">
+        <v>1.77</v>
+      </c>
+      <c r="BJ183">
+        <v>1.94</v>
+      </c>
+      <c r="BK183">
+        <v>2.28</v>
+      </c>
+      <c r="BL183">
+        <v>1.53</v>
+      </c>
+      <c r="BM183">
+        <v>3.05</v>
+      </c>
+      <c r="BN183">
+        <v>1.28</v>
+      </c>
+      <c r="BO183">
+        <v>4.2</v>
+      </c>
+      <c r="BP183">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,10 +523,10 @@
     <t>['22', '61']</t>
   </si>
   <si>
-    <t>['22']</t>
+    <t>['6', '45', '62']</t>
   </si>
   <si>
-    <t>['6', '45', '62']</t>
+    <t>['22']</t>
   </si>
   <si>
     <t>['14']</t>
@@ -580,10 +580,10 @@
     <t>['6', '31']</t>
   </si>
   <si>
-    <t>['21', '90']</t>
+    <t>['71']</t>
   </si>
   <si>
-    <t>['71']</t>
+    <t>['21', '90']</t>
   </si>
   <si>
     <t>['34', '79']</t>
@@ -605,9 +605,6 @@
   </si>
   <si>
     <t>['58']</t>
-  </si>
-  <si>
-    <t>['5']</t>
   </si>
   <si>
     <t>['13', '73']</t>
@@ -748,6 +745,9 @@
     <t>['68', '85']</t>
   </si>
   <si>
+    <t>['5']</t>
+  </si>
+  <si>
     <t>['84']</t>
   </si>
   <si>
@@ -820,10 +820,10 @@
     <t>['2', '8', '30', '58', '67']</t>
   </si>
   <si>
-    <t>['9', '45']</t>
+    <t>['4', '16']</t>
   </si>
   <si>
-    <t>['4', '16']</t>
+    <t>['9', '45']</t>
   </si>
   <si>
     <t>['10']</t>
@@ -1218,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1474,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1680,7 +1680,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2298,7 +2298,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2710,7 +2710,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3122,7 +3122,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3328,7 +3328,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3534,7 +3534,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3615,7 +3615,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ12">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4436,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16">
         <v>2.23</v>
@@ -4564,7 +4564,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4976,7 +4976,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5182,7 +5182,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5388,7 +5388,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5594,7 +5594,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5878,7 +5878,7 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ23">
         <v>0.62</v>
@@ -6006,7 +6006,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6212,7 +6212,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6582,7 +6582,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7537312</v>
+        <v>7537310</v>
       </c>
       <c r="C27" t="s">
         <v>68</v>
@@ -6597,88 +6597,88 @@
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Q27">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="T27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z27">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA27">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB27">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE27">
         <v>1.33</v>
       </c>
       <c r="AF27">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AG27">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH27">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI27">
         <v>1.8</v>
@@ -6687,100 +6687,100 @@
         <v>1.95</v>
       </c>
       <c r="AK27">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AL27">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM27">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AR27">
-        <v>1.95</v>
+        <v>1</v>
       </c>
       <c r="AS27">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="AT27">
-        <v>3.84</v>
+        <v>2.32</v>
       </c>
       <c r="AU27">
+        <v>7</v>
+      </c>
+      <c r="AV27">
+        <v>6</v>
+      </c>
+      <c r="AW27">
         <v>4</v>
       </c>
-      <c r="AV27">
-        <v>5</v>
-      </c>
-      <c r="AW27">
-        <v>6</v>
-      </c>
       <c r="AX27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AY27">
         <v>16</v>
       </c>
       <c r="AZ27">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BA27">
         <v>6</v>
       </c>
       <c r="BB27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD27">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="BE27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BF27">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="BG27">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="BH27">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="BI27">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BJ27">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="BK27">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BL27">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BM27">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BN27">
         <v>1.25</v>
       </c>
       <c r="BO27">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="BP27">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="28" spans="1:68">
@@ -6788,7 +6788,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>7537310</v>
+        <v>7537312</v>
       </c>
       <c r="C28" t="s">
         <v>68</v>
@@ -6803,88 +6803,88 @@
         <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>84</v>
+      </c>
+      <c r="P28" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q28">
+        <v>2.5</v>
+      </c>
+      <c r="R28">
+        <v>2.2</v>
+      </c>
+      <c r="S28">
+        <v>4.5</v>
+      </c>
+      <c r="T28">
+        <v>1.4</v>
+      </c>
+      <c r="U28">
+        <v>2.75</v>
+      </c>
+      <c r="V28">
         <v>3</v>
       </c>
-      <c r="M28">
-        <v>2</v>
-      </c>
-      <c r="N28">
-        <v>5</v>
-      </c>
-      <c r="O28" t="s">
-        <v>100</v>
-      </c>
-      <c r="P28" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q28">
-        <v>3.75</v>
-      </c>
-      <c r="R28">
-        <v>2.1</v>
-      </c>
-      <c r="S28">
-        <v>3</v>
-      </c>
-      <c r="T28">
-        <v>1.44</v>
-      </c>
-      <c r="U28">
-        <v>2.63</v>
-      </c>
-      <c r="V28">
-        <v>3.25</v>
-      </c>
       <c r="W28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="AA28">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB28">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="AC28">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE28">
         <v>1.33</v>
       </c>
       <c r="AF28">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AH28">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AI28">
         <v>1.8</v>
@@ -6893,100 +6893,100 @@
         <v>1.95</v>
       </c>
       <c r="AK28">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AL28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM28">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="AN28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AR28">
-        <v>1</v>
+        <v>1.95</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.89</v>
       </c>
       <c r="AT28">
-        <v>2.32</v>
+        <v>3.84</v>
       </c>
       <c r="AU28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV28">
+        <v>5</v>
+      </c>
+      <c r="AW28">
         <v>6</v>
       </c>
-      <c r="AW28">
-        <v>4</v>
-      </c>
       <c r="AX28">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY28">
         <v>16</v>
       </c>
       <c r="AZ28">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BA28">
         <v>6</v>
       </c>
       <c r="BB28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BC28">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD28">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="BE28">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF28">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="BG28">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BH28">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="BI28">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BJ28">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="BK28">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="BL28">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BM28">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BN28">
         <v>1.25</v>
       </c>
       <c r="BO28">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="BP28">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="29" spans="1:68">
@@ -7117,7 +7117,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ29">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7242,7 +7242,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7654,7 +7654,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -8066,7 +8066,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8272,7 +8272,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8684,7 +8684,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8890,7 +8890,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9096,7 +9096,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9920,7 +9920,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43">
         <v>0.92</v>
@@ -10126,7 +10126,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10207,7 +10207,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10744,7 +10744,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10950,7 +10950,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11156,7 +11156,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11774,7 +11774,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12058,7 +12058,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ53">
         <v>1.23</v>
@@ -12186,7 +12186,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12392,7 +12392,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12804,7 +12804,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13010,7 +13010,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13091,7 +13091,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ58">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13216,7 +13216,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13834,7 +13834,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14040,7 +14040,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14246,7 +14246,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14864,7 +14864,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15276,7 +15276,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15482,7 +15482,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15560,7 +15560,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
         <v>2</v>
@@ -16100,7 +16100,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16512,7 +16512,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16718,7 +16718,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16799,7 +16799,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -17130,7 +17130,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17336,7 +17336,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17542,7 +17542,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17620,7 +17620,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ80">
         <v>1.38</v>
@@ -17829,7 +17829,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ81">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17954,7 +17954,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18160,7 +18160,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18572,7 +18572,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -20301,7 +20301,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ93">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -21250,7 +21250,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21328,7 +21328,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ98">
         <v>1.23</v>
@@ -21740,7 +21740,7 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ100">
         <v>1.77</v>
@@ -24134,7 +24134,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24421,7 +24421,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -26478,7 +26478,7 @@
         <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ123">
         <v>1.77</v>
@@ -26687,7 +26687,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ124">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -27511,7 +27511,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR128">
         <v>1.37</v>
@@ -28872,7 +28872,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29036,7 +29036,7 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>7537425</v>
+        <v>7537429</v>
       </c>
       <c r="C136" t="s">
         <v>68</v>
@@ -29051,190 +29051,190 @@
         <v>20</v>
       </c>
       <c r="G136" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H136" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N136">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O136" t="s">
         <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="Q136">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R136">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="T136">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="U136">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V136">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="W136">
+        <v>1.36</v>
+      </c>
+      <c r="X136">
+        <v>9</v>
+      </c>
+      <c r="Y136">
+        <v>1.07</v>
+      </c>
+      <c r="Z136">
+        <v>2</v>
+      </c>
+      <c r="AA136">
+        <v>3.3</v>
+      </c>
+      <c r="AB136">
+        <v>3.5</v>
+      </c>
+      <c r="AC136">
+        <v>1.07</v>
+      </c>
+      <c r="AD136">
+        <v>5.8</v>
+      </c>
+      <c r="AE136">
         <v>1.32</v>
       </c>
-      <c r="X136">
-        <v>7.73</v>
-      </c>
-      <c r="Y136">
-        <v>1.06</v>
-      </c>
-      <c r="Z136">
-        <v>1.85</v>
-      </c>
-      <c r="AA136">
+      <c r="AF136">
         <v>3.2</v>
       </c>
-      <c r="AB136">
-        <v>4</v>
-      </c>
-      <c r="AC136">
-        <v>1.09</v>
-      </c>
-      <c r="AD136">
-        <v>4.9</v>
-      </c>
-      <c r="AE136">
-        <v>1.42</v>
-      </c>
-      <c r="AF136">
-        <v>2.7</v>
-      </c>
       <c r="AG136">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AH136">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AI136">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AJ136">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AK136">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AL136">
         <v>1.36</v>
       </c>
       <c r="AM136">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AN136">
+        <v>1</v>
+      </c>
+      <c r="AO136">
+        <v>1</v>
+      </c>
+      <c r="AP136">
+        <v>1.38</v>
+      </c>
+      <c r="AQ136">
+        <v>0.92</v>
+      </c>
+      <c r="AR136">
+        <v>1.31</v>
+      </c>
+      <c r="AS136">
+        <v>1.25</v>
+      </c>
+      <c r="AT136">
+        <v>2.56</v>
+      </c>
+      <c r="AU136">
+        <v>9</v>
+      </c>
+      <c r="AV136">
+        <v>5</v>
+      </c>
+      <c r="AW136">
+        <v>14</v>
+      </c>
+      <c r="AX136">
+        <v>13</v>
+      </c>
+      <c r="AY136">
+        <v>25</v>
+      </c>
+      <c r="AZ136">
+        <v>24</v>
+      </c>
+      <c r="BA136">
+        <v>9</v>
+      </c>
+      <c r="BB136">
+        <v>8</v>
+      </c>
+      <c r="BC136">
+        <v>17</v>
+      </c>
+      <c r="BD136">
+        <v>1.47</v>
+      </c>
+      <c r="BE136">
+        <v>6.2</v>
+      </c>
+      <c r="BF136">
+        <v>3.5</v>
+      </c>
+      <c r="BG136">
         <v>1.44</v>
       </c>
-      <c r="AO136">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AP136">
-        <v>1.46</v>
-      </c>
-      <c r="AQ136">
-        <v>0.62</v>
-      </c>
-      <c r="AR136">
-        <v>1.4</v>
-      </c>
-      <c r="AS136">
-        <v>0.86</v>
-      </c>
-      <c r="AT136">
-        <v>2.26</v>
-      </c>
-      <c r="AU136">
-        <v>6</v>
-      </c>
-      <c r="AV136">
-        <v>4</v>
-      </c>
-      <c r="AW136">
-        <v>11</v>
-      </c>
-      <c r="AX136">
-        <v>6</v>
-      </c>
-      <c r="AY136">
-        <v>23</v>
-      </c>
-      <c r="AZ136">
-        <v>12</v>
-      </c>
-      <c r="BA136">
-        <v>7</v>
-      </c>
-      <c r="BB136">
-        <v>3</v>
-      </c>
-      <c r="BC136">
-        <v>10</v>
-      </c>
-      <c r="BD136">
-        <v>1.58</v>
-      </c>
-      <c r="BE136">
-        <v>6.25</v>
-      </c>
-      <c r="BF136">
-        <v>2.65</v>
-      </c>
-      <c r="BG136">
-        <v>1.46</v>
-      </c>
       <c r="BH136">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="BI136">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="BJ136">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="BK136">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="BL136">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BM136">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BN136">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO136">
         <v>4</v>
       </c>
       <c r="BP136">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="137" spans="1:68">
@@ -29242,7 +29242,7 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>7537429</v>
+        <v>7537425</v>
       </c>
       <c r="C137" t="s">
         <v>68</v>
@@ -29257,190 +29257,190 @@
         <v>20</v>
       </c>
       <c r="G137" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H137" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N137">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O137" t="s">
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="Q137">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S137">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="T137">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="U137">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V137">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="W137">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X137">
-        <v>9</v>
+        <v>7.73</v>
       </c>
       <c r="Y137">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z137">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA137">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB137">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC137">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AD137">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AE137">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AF137">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AG137">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH137">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AI137">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AJ137">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AK137">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AL137">
         <v>1.36</v>
       </c>
       <c r="AM137">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AN137">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP137">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AQ137">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR137">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AS137">
-        <v>1.25</v>
+        <v>0.86</v>
       </c>
       <c r="AT137">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AU137">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW137">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX137">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AY137">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ137">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BA137">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB137">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BC137">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BD137">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="BE137">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="BF137">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="BG137">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BH137">
-        <v>2.51</v>
+        <v>2.35</v>
       </c>
       <c r="BI137">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="BJ137">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="BK137">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BL137">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BM137">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="BN137">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BO137">
         <v>4</v>
       </c>
       <c r="BP137">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="138" spans="1:68">
@@ -29774,7 +29774,7 @@
         <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ139">
         <v>1.15</v>
@@ -30517,10 +30517,10 @@
         <v>2</v>
       </c>
       <c r="O143" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P143" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30601,7 +30601,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ143">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR143">
         <v>1.33</v>
@@ -30932,7 +30932,7 @@
         <v>84</v>
       </c>
       <c r="P145" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q145">
         <v>4.5</v>
@@ -32168,7 +32168,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32744,7 +32744,7 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>7537441</v>
+        <v>7537445</v>
       </c>
       <c r="C154" t="s">
         <v>68</v>
@@ -32759,10 +32759,10 @@
         <v>22</v>
       </c>
       <c r="G154" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -32774,40 +32774,40 @@
         <v>2</v>
       </c>
       <c r="L154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154">
         <v>2</v>
       </c>
       <c r="N154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O154" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="P154" t="s">
         <v>268</v>
       </c>
       <c r="Q154">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R154">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S154">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="T154">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U154">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V154">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W154">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X154">
         <v>13</v>
@@ -32816,133 +32816,133 @@
         <v>1.04</v>
       </c>
       <c r="Z154">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="AA154">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB154">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC154">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AD154">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AE154">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF154">
         <v>2.3</v>
       </c>
       <c r="AG154">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AH154">
         <v>1.5</v>
       </c>
       <c r="AI154">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ154">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK154">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AL154">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AM154">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="AN154">
+        <v>0.3</v>
+      </c>
+      <c r="AO154">
         <v>0.8</v>
       </c>
-      <c r="AO154">
+      <c r="AP154">
         <v>0.5</v>
       </c>
-      <c r="AP154">
-        <v>0.92</v>
-      </c>
       <c r="AQ154">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="AR154">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AS154">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="AT154">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AU154">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV154">
         <v>6</v>
       </c>
       <c r="AW154">
+        <v>15</v>
+      </c>
+      <c r="AX154">
+        <v>3</v>
+      </c>
+      <c r="AY154">
+        <v>24</v>
+      </c>
+      <c r="AZ154">
         <v>10</v>
       </c>
-      <c r="AX154">
-        <v>7</v>
-      </c>
-      <c r="AY154">
-        <v>20</v>
-      </c>
-      <c r="AZ154">
-        <v>15</v>
-      </c>
       <c r="BA154">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB154">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC154">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD154">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="BE154">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="BF154">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="BG154">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="BH154">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="BI154">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="BJ154">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="BK154">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="BL154">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="BM154">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BN154">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BO154">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="BP154">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="155" spans="1:68">
@@ -32950,7 +32950,7 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>7537445</v>
+        <v>7537441</v>
       </c>
       <c r="C155" t="s">
         <v>68</v>
@@ -32965,10 +32965,10 @@
         <v>22</v>
       </c>
       <c r="G155" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H155" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -32980,40 +32980,40 @@
         <v>2</v>
       </c>
       <c r="L155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155">
         <v>2</v>
       </c>
       <c r="N155">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O155" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="P155" t="s">
         <v>269</v>
       </c>
       <c r="Q155">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R155">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S155">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="T155">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U155">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V155">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W155">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X155">
         <v>13</v>
@@ -33022,133 +33022,133 @@
         <v>1.04</v>
       </c>
       <c r="Z155">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="AA155">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB155">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AC155">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AD155">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AE155">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF155">
         <v>2.3</v>
       </c>
       <c r="AG155">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH155">
         <v>1.5</v>
       </c>
       <c r="AI155">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ155">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK155">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AL155">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AM155">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="AN155">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="AO155">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AP155">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="AQ155">
-        <v>1.15</v>
+        <v>0.62</v>
       </c>
       <c r="AR155">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AS155">
-        <v>1.06</v>
+        <v>0.9</v>
       </c>
       <c r="AT155">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AU155">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV155">
         <v>6</v>
       </c>
       <c r="AW155">
+        <v>10</v>
+      </c>
+      <c r="AX155">
+        <v>7</v>
+      </c>
+      <c r="AY155">
+        <v>20</v>
+      </c>
+      <c r="AZ155">
         <v>15</v>
       </c>
-      <c r="AX155">
-        <v>3</v>
-      </c>
-      <c r="AY155">
-        <v>24</v>
-      </c>
-      <c r="AZ155">
+      <c r="BA155">
         <v>10</v>
       </c>
-      <c r="BA155">
-        <v>9</v>
-      </c>
       <c r="BB155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC155">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD155">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="BE155">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF155">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="BG155">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="BH155">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="BI155">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="BJ155">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="BK155">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="BL155">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="BM155">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="BN155">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BO155">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="BP155">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="156" spans="1:68">
@@ -33897,7 +33897,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ159">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR159">
         <v>1.89</v>
@@ -35464,7 +35464,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35542,7 +35542,7 @@
         <v>1.73</v>
       </c>
       <c r="AP167">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ167">
         <v>1.54</v>
@@ -36040,7 +36040,7 @@
         <v>169</v>
       </c>
       <c r="B170">
-        <v>7537466</v>
+        <v>7537462</v>
       </c>
       <c r="C170" t="s">
         <v>68</v>
@@ -36055,190 +36055,190 @@
         <v>25</v>
       </c>
       <c r="G170" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H170" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170">
         <v>0</v>
       </c>
       <c r="K170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M170">
         <v>1</v>
       </c>
       <c r="N170">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O170" t="s">
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="Q170">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R170">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S170">
+        <v>3</v>
+      </c>
+      <c r="T170">
+        <v>1.53</v>
+      </c>
+      <c r="U170">
+        <v>2.38</v>
+      </c>
+      <c r="V170">
         <v>3.5</v>
       </c>
-      <c r="T170">
-        <v>1.44</v>
-      </c>
-      <c r="U170">
-        <v>2.63</v>
-      </c>
-      <c r="V170">
-        <v>3.25</v>
-      </c>
       <c r="W170">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X170">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y170">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z170">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA170">
         <v>3</v>
       </c>
       <c r="AB170">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC170">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD170">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AE170">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AF170">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AG170">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH170">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI170">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ170">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AK170">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AL170">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AM170">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AN170">
-        <v>1.08</v>
+        <v>0.42</v>
       </c>
       <c r="AO170">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AP170">
-        <v>1.23</v>
+        <v>0.46</v>
       </c>
       <c r="AQ170">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="AR170">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AS170">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AT170">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="AU170">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV170">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW170">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AX170">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY170">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AZ170">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA170">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC170">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD170">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="BE170">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="BF170">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="BG170">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BH170">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BI170">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BJ170">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BK170">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="BL170">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BM170">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BN170">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BO170">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="BP170">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="171" spans="1:68">
@@ -36246,7 +36246,7 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>7537462</v>
+        <v>7537466</v>
       </c>
       <c r="C171" t="s">
         <v>68</v>
@@ -36261,190 +36261,190 @@
         <v>25</v>
       </c>
       <c r="G171" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H171" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171">
         <v>0</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M171">
         <v>1</v>
       </c>
       <c r="N171">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O171" t="s">
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="Q171">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R171">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S171">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T171">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="U171">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V171">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="W171">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X171">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y171">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z171">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AA171">
         <v>3</v>
       </c>
       <c r="AB171">
+        <v>2.8</v>
+      </c>
+      <c r="AC171">
+        <v>1.08</v>
+      </c>
+      <c r="AD171">
+        <v>8.6</v>
+      </c>
+      <c r="AE171">
+        <v>1.38</v>
+      </c>
+      <c r="AF171">
+        <v>2.95</v>
+      </c>
+      <c r="AG171">
+        <v>2.15</v>
+      </c>
+      <c r="AH171">
+        <v>1.57</v>
+      </c>
+      <c r="AI171">
+        <v>1.8</v>
+      </c>
+      <c r="AJ171">
+        <v>1.95</v>
+      </c>
+      <c r="AK171">
+        <v>1.44</v>
+      </c>
+      <c r="AL171">
+        <v>1.38</v>
+      </c>
+      <c r="AM171">
+        <v>1.52</v>
+      </c>
+      <c r="AN171">
+        <v>1.08</v>
+      </c>
+      <c r="AO171">
+        <v>0.67</v>
+      </c>
+      <c r="AP171">
+        <v>1.23</v>
+      </c>
+      <c r="AQ171">
+        <v>0.62</v>
+      </c>
+      <c r="AR171">
+        <v>1.27</v>
+      </c>
+      <c r="AS171">
+        <v>1</v>
+      </c>
+      <c r="AT171">
+        <v>2.27</v>
+      </c>
+      <c r="AU171">
+        <v>7</v>
+      </c>
+      <c r="AV171">
+        <v>5</v>
+      </c>
+      <c r="AW171">
+        <v>10</v>
+      </c>
+      <c r="AX171">
+        <v>6</v>
+      </c>
+      <c r="AY171">
+        <v>19</v>
+      </c>
+      <c r="AZ171">
+        <v>11</v>
+      </c>
+      <c r="BA171">
+        <v>7</v>
+      </c>
+      <c r="BB171">
+        <v>3</v>
+      </c>
+      <c r="BC171">
+        <v>10</v>
+      </c>
+      <c r="BD171">
+        <v>1.95</v>
+      </c>
+      <c r="BE171">
+        <v>6.1</v>
+      </c>
+      <c r="BF171">
+        <v>2.07</v>
+      </c>
+      <c r="BG171">
+        <v>1.53</v>
+      </c>
+      <c r="BH171">
         <v>2.2</v>
       </c>
-      <c r="AC171">
-        <v>1.1</v>
-      </c>
-      <c r="AD171">
-        <v>7.2</v>
-      </c>
-      <c r="AE171">
-        <v>1.46</v>
-      </c>
-      <c r="AF171">
-        <v>2.6</v>
-      </c>
-      <c r="AG171">
-        <v>2.2</v>
-      </c>
-      <c r="AH171">
-        <v>1.55</v>
-      </c>
-      <c r="AI171">
-        <v>2</v>
-      </c>
-      <c r="AJ171">
-        <v>1.75</v>
-      </c>
-      <c r="AK171">
-        <v>1.66</v>
-      </c>
-      <c r="AL171">
-        <v>1.39</v>
-      </c>
-      <c r="AM171">
-        <v>1.33</v>
-      </c>
-      <c r="AN171">
-        <v>0.42</v>
-      </c>
-      <c r="AO171">
-        <v>1.17</v>
-      </c>
-      <c r="AP171">
-        <v>0.46</v>
-      </c>
-      <c r="AQ171">
-        <v>1.15</v>
-      </c>
-      <c r="AR171">
+      <c r="BI171">
+        <v>1.89</v>
+      </c>
+      <c r="BJ171">
+        <v>1.72</v>
+      </c>
+      <c r="BK171">
+        <v>2.43</v>
+      </c>
+      <c r="BL171">
+        <v>1.43</v>
+      </c>
+      <c r="BM171">
+        <v>3.25</v>
+      </c>
+      <c r="BN171">
         <v>1.25</v>
       </c>
-      <c r="AS171">
-        <v>1.18</v>
-      </c>
-      <c r="AT171">
-        <v>2.43</v>
-      </c>
-      <c r="AU171">
-        <v>5</v>
-      </c>
-      <c r="AV171">
-        <v>8</v>
-      </c>
-      <c r="AW171">
-        <v>3</v>
-      </c>
-      <c r="AX171">
-        <v>3</v>
-      </c>
-      <c r="AY171">
-        <v>9</v>
-      </c>
-      <c r="AZ171">
-        <v>13</v>
-      </c>
-      <c r="BA171">
-        <v>8</v>
-      </c>
-      <c r="BB171">
-        <v>4</v>
-      </c>
-      <c r="BC171">
-        <v>12</v>
-      </c>
-      <c r="BD171">
-        <v>2.25</v>
-      </c>
-      <c r="BE171">
-        <v>6.25</v>
-      </c>
-      <c r="BF171">
-        <v>1.79</v>
-      </c>
-      <c r="BG171">
-        <v>1.49</v>
-      </c>
-      <c r="BH171">
-        <v>2.28</v>
-      </c>
-      <c r="BI171">
-        <v>1.84</v>
-      </c>
-      <c r="BJ171">
-        <v>1.77</v>
-      </c>
-      <c r="BK171">
-        <v>2.35</v>
-      </c>
-      <c r="BL171">
-        <v>1.46</v>
-      </c>
-      <c r="BM171">
-        <v>3.1</v>
-      </c>
-      <c r="BN171">
-        <v>1.26</v>
-      </c>
       <c r="BO171">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="BP171">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="172" spans="1:68">
@@ -37688,7 +37688,7 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>7537471</v>
+        <v>7537474</v>
       </c>
       <c r="C178" t="s">
         <v>68</v>
@@ -37703,10 +37703,10 @@
         <v>26</v>
       </c>
       <c r="G178" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H178" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -37718,157 +37718,157 @@
         <v>0</v>
       </c>
       <c r="L178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N178">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O178" t="s">
-        <v>194</v>
+        <v>84</v>
       </c>
       <c r="P178" t="s">
-        <v>247</v>
+        <v>84</v>
       </c>
       <c r="Q178">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="R178">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S178">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="T178">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U178">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V178">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="W178">
+        <v>1.22</v>
+      </c>
+      <c r="X178">
+        <v>15</v>
+      </c>
+      <c r="Y178">
+        <v>1.03</v>
+      </c>
+      <c r="Z178">
+        <v>2.1</v>
+      </c>
+      <c r="AA178">
+        <v>3</v>
+      </c>
+      <c r="AB178">
+        <v>3.75</v>
+      </c>
+      <c r="AC178">
+        <v>1.11</v>
+      </c>
+      <c r="AD178">
+        <v>6.8</v>
+      </c>
+      <c r="AE178">
+        <v>1.55</v>
+      </c>
+      <c r="AF178">
+        <v>2.2</v>
+      </c>
+      <c r="AG178">
+        <v>2.4</v>
+      </c>
+      <c r="AH178">
+        <v>1.46</v>
+      </c>
+      <c r="AI178">
+        <v>2.25</v>
+      </c>
+      <c r="AJ178">
+        <v>1.57</v>
+      </c>
+      <c r="AK178">
         <v>1.29</v>
       </c>
-      <c r="X178">
+      <c r="AL178">
+        <v>1.38</v>
+      </c>
+      <c r="AM178">
+        <v>1.73</v>
+      </c>
+      <c r="AN178">
+        <v>1.33</v>
+      </c>
+      <c r="AO178">
+        <v>1.17</v>
+      </c>
+      <c r="AP178">
+        <v>1.31</v>
+      </c>
+      <c r="AQ178">
+        <v>1.15</v>
+      </c>
+      <c r="AR178">
+        <v>1.15</v>
+      </c>
+      <c r="AS178">
+        <v>1.09</v>
+      </c>
+      <c r="AT178">
+        <v>2.24</v>
+      </c>
+      <c r="AU178">
+        <v>8</v>
+      </c>
+      <c r="AV178">
+        <v>5</v>
+      </c>
+      <c r="AW178">
+        <v>13</v>
+      </c>
+      <c r="AX178">
         <v>11</v>
       </c>
-      <c r="Y178">
-        <v>1.05</v>
-      </c>
-      <c r="Z178">
-        <v>5.5</v>
-      </c>
-      <c r="AA178">
-        <v>3.65</v>
-      </c>
-      <c r="AB178">
-        <v>1.6</v>
-      </c>
-      <c r="AC178">
-        <v>1.09</v>
-      </c>
-      <c r="AD178">
-        <v>7.6</v>
-      </c>
-      <c r="AE178">
-        <v>1.45</v>
-      </c>
-      <c r="AF178">
-        <v>2.65</v>
-      </c>
-      <c r="AG178">
-        <v>2.2</v>
-      </c>
-      <c r="AH178">
-        <v>1.55</v>
-      </c>
-      <c r="AI178">
-        <v>2.1</v>
-      </c>
-      <c r="AJ178">
-        <v>1.67</v>
-      </c>
-      <c r="AK178">
-        <v>2.03</v>
-      </c>
-      <c r="AL178">
-        <v>1.34</v>
-      </c>
-      <c r="AM178">
-        <v>1.2</v>
-      </c>
-      <c r="AN178">
-        <v>0.92</v>
-      </c>
-      <c r="AO178">
-        <v>1.58</v>
-      </c>
-      <c r="AP178">
-        <v>0.92</v>
-      </c>
-      <c r="AQ178">
-        <v>1.54</v>
-      </c>
-      <c r="AR178">
-        <v>1.3</v>
-      </c>
-      <c r="AS178">
-        <v>1.59</v>
-      </c>
-      <c r="AT178">
-        <v>2.89</v>
-      </c>
-      <c r="AU178">
-        <v>6</v>
-      </c>
-      <c r="AV178">
-        <v>7</v>
-      </c>
-      <c r="AW178">
-        <v>7</v>
-      </c>
-      <c r="AX178">
-        <v>10</v>
-      </c>
       <c r="AY178">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AZ178">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA178">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC178">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD178">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="BE178">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="BF178">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="BG178">
         <v>1.48</v>
       </c>
       <c r="BH178">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BI178">
         <v>1.83</v>
       </c>
       <c r="BJ178">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BK178">
         <v>2.35</v>
@@ -37877,16 +37877,16 @@
         <v>1.46</v>
       </c>
       <c r="BM178">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BN178">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO178">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="BP178">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="179" spans="1:68">
@@ -37894,7 +37894,7 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>7537474</v>
+        <v>7537471</v>
       </c>
       <c r="C179" t="s">
         <v>68</v>
@@ -37909,10 +37909,10 @@
         <v>26</v>
       </c>
       <c r="G179" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H179" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -37924,157 +37924,157 @@
         <v>0</v>
       </c>
       <c r="L179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O179" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="P179" t="s">
-        <v>84</v>
+        <v>247</v>
       </c>
       <c r="Q179">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="R179">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S179">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="T179">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="U179">
+        <v>2.5</v>
+      </c>
+      <c r="V179">
+        <v>3.5</v>
+      </c>
+      <c r="W179">
+        <v>1.29</v>
+      </c>
+      <c r="X179">
+        <v>11</v>
+      </c>
+      <c r="Y179">
+        <v>1.05</v>
+      </c>
+      <c r="Z179">
+        <v>5.5</v>
+      </c>
+      <c r="AA179">
+        <v>3.65</v>
+      </c>
+      <c r="AB179">
+        <v>1.6</v>
+      </c>
+      <c r="AC179">
+        <v>1.09</v>
+      </c>
+      <c r="AD179">
+        <v>7.6</v>
+      </c>
+      <c r="AE179">
+        <v>1.45</v>
+      </c>
+      <c r="AF179">
+        <v>2.65</v>
+      </c>
+      <c r="AG179">
         <v>2.2</v>
       </c>
-      <c r="V179">
-        <v>4</v>
-      </c>
-      <c r="W179">
-        <v>1.22</v>
-      </c>
-      <c r="X179">
-        <v>15</v>
-      </c>
-      <c r="Y179">
-        <v>1.03</v>
-      </c>
-      <c r="Z179">
+      <c r="AH179">
+        <v>1.55</v>
+      </c>
+      <c r="AI179">
         <v>2.1</v>
       </c>
-      <c r="AA179">
+      <c r="AJ179">
+        <v>1.67</v>
+      </c>
+      <c r="AK179">
+        <v>2.03</v>
+      </c>
+      <c r="AL179">
+        <v>1.34</v>
+      </c>
+      <c r="AM179">
+        <v>1.2</v>
+      </c>
+      <c r="AN179">
+        <v>0.92</v>
+      </c>
+      <c r="AO179">
+        <v>1.58</v>
+      </c>
+      <c r="AP179">
+        <v>0.92</v>
+      </c>
+      <c r="AQ179">
+        <v>1.54</v>
+      </c>
+      <c r="AR179">
+        <v>1.3</v>
+      </c>
+      <c r="AS179">
+        <v>1.59</v>
+      </c>
+      <c r="AT179">
+        <v>2.89</v>
+      </c>
+      <c r="AU179">
+        <v>6</v>
+      </c>
+      <c r="AV179">
+        <v>7</v>
+      </c>
+      <c r="AW179">
+        <v>7</v>
+      </c>
+      <c r="AX179">
+        <v>10</v>
+      </c>
+      <c r="AY179">
+        <v>13</v>
+      </c>
+      <c r="AZ179">
+        <v>20</v>
+      </c>
+      <c r="BA179">
+        <v>2</v>
+      </c>
+      <c r="BB179">
         <v>3</v>
       </c>
-      <c r="AB179">
-        <v>3.75</v>
-      </c>
-      <c r="AC179">
-        <v>1.11</v>
-      </c>
-      <c r="AD179">
-        <v>6.8</v>
-      </c>
-      <c r="AE179">
-        <v>1.55</v>
-      </c>
-      <c r="AF179">
-        <v>2.2</v>
-      </c>
-      <c r="AG179">
-        <v>2.4</v>
-      </c>
-      <c r="AH179">
-        <v>1.46</v>
-      </c>
-      <c r="AI179">
-        <v>2.25</v>
-      </c>
-      <c r="AJ179">
-        <v>1.57</v>
-      </c>
-      <c r="AK179">
-        <v>1.29</v>
-      </c>
-      <c r="AL179">
-        <v>1.38</v>
-      </c>
-      <c r="AM179">
-        <v>1.73</v>
-      </c>
-      <c r="AN179">
-        <v>1.33</v>
-      </c>
-      <c r="AO179">
-        <v>1.17</v>
-      </c>
-      <c r="AP179">
-        <v>1.31</v>
-      </c>
-      <c r="AQ179">
-        <v>1.15</v>
-      </c>
-      <c r="AR179">
-        <v>1.15</v>
-      </c>
-      <c r="AS179">
-        <v>1.09</v>
-      </c>
-      <c r="AT179">
-        <v>2.24</v>
-      </c>
-      <c r="AU179">
-        <v>8</v>
-      </c>
-      <c r="AV179">
+      <c r="BC179">
         <v>5</v>
       </c>
-      <c r="AW179">
-        <v>13</v>
-      </c>
-      <c r="AX179">
-        <v>11</v>
-      </c>
-      <c r="AY179">
-        <v>27</v>
-      </c>
-      <c r="AZ179">
-        <v>19</v>
-      </c>
-      <c r="BA179">
-        <v>4</v>
-      </c>
-      <c r="BB179">
-        <v>4</v>
-      </c>
-      <c r="BC179">
-        <v>8</v>
-      </c>
       <c r="BD179">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="BE179">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF179">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="BG179">
         <v>1.48</v>
       </c>
       <c r="BH179">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BI179">
         <v>1.83</v>
       </c>
       <c r="BJ179">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BK179">
         <v>2.35</v>
@@ -38083,16 +38083,16 @@
         <v>1.46</v>
       </c>
       <c r="BM179">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BN179">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BO179">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="BP179">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="180" spans="1:68">
@@ -38711,212 +38711,6 @@
       </c>
       <c r="BP182">
         <v>1.15</v>
-      </c>
-    </row>
-    <row r="183" spans="1:68">
-      <c r="A183" s="1">
-        <v>182</v>
-      </c>
-      <c r="B183">
-        <v>7537475</v>
-      </c>
-      <c r="C183" t="s">
-        <v>68</v>
-      </c>
-      <c r="D183" t="s">
-        <v>69</v>
-      </c>
-      <c r="E183" s="2">
-        <v>45725.58333333334</v>
-      </c>
-      <c r="F183">
-        <v>26</v>
-      </c>
-      <c r="G183" t="s">
-        <v>81</v>
-      </c>
-      <c r="H183" t="s">
-        <v>70</v>
-      </c>
-      <c r="I183">
-        <v>1</v>
-      </c>
-      <c r="J183">
-        <v>0</v>
-      </c>
-      <c r="K183">
-        <v>1</v>
-      </c>
-      <c r="L183">
-        <v>1</v>
-      </c>
-      <c r="M183">
-        <v>0</v>
-      </c>
-      <c r="N183">
-        <v>1</v>
-      </c>
-      <c r="O183" t="s">
-        <v>197</v>
-      </c>
-      <c r="P183" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q183">
-        <v>6.5</v>
-      </c>
-      <c r="R183">
-        <v>2</v>
-      </c>
-      <c r="S183">
-        <v>2.38</v>
-      </c>
-      <c r="T183">
-        <v>1.53</v>
-      </c>
-      <c r="U183">
-        <v>2.38</v>
-      </c>
-      <c r="V183">
-        <v>3.75</v>
-      </c>
-      <c r="W183">
-        <v>1.25</v>
-      </c>
-      <c r="X183">
-        <v>11</v>
-      </c>
-      <c r="Y183">
-        <v>1.05</v>
-      </c>
-      <c r="Z183">
-        <v>3</v>
-      </c>
-      <c r="AA183">
-        <v>2.8</v>
-      </c>
-      <c r="AB183">
-        <v>2.5</v>
-      </c>
-      <c r="AC183">
-        <v>1.1</v>
-      </c>
-      <c r="AD183">
-        <v>7.2</v>
-      </c>
-      <c r="AE183">
-        <v>1.48</v>
-      </c>
-      <c r="AF183">
-        <v>2.4</v>
-      </c>
-      <c r="AG183">
-        <v>2.34</v>
-      </c>
-      <c r="AH183">
-        <v>1.49</v>
-      </c>
-      <c r="AI183">
-        <v>2.38</v>
-      </c>
-      <c r="AJ183">
-        <v>1.53</v>
-      </c>
-      <c r="AK183">
-        <v>1.56</v>
-      </c>
-      <c r="AL183">
-        <v>1.39</v>
-      </c>
-      <c r="AM183">
-        <v>1.4</v>
-      </c>
-      <c r="AN183">
-        <v>0.5</v>
-      </c>
-      <c r="AO183">
-        <v>1.33</v>
-      </c>
-      <c r="AP183">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AQ183">
-        <v>1.23</v>
-      </c>
-      <c r="AR183">
-        <v>1.11</v>
-      </c>
-      <c r="AS183">
-        <v>1.02</v>
-      </c>
-      <c r="AT183">
-        <v>2.13</v>
-      </c>
-      <c r="AU183">
-        <v>0</v>
-      </c>
-      <c r="AV183">
-        <v>5</v>
-      </c>
-      <c r="AW183">
-        <v>3</v>
-      </c>
-      <c r="AX183">
-        <v>12</v>
-      </c>
-      <c r="AY183">
-        <v>4</v>
-      </c>
-      <c r="AZ183">
-        <v>20</v>
-      </c>
-      <c r="BA183">
-        <v>0</v>
-      </c>
-      <c r="BB183">
-        <v>8</v>
-      </c>
-      <c r="BC183">
-        <v>8</v>
-      </c>
-      <c r="BD183">
-        <v>2.46</v>
-      </c>
-      <c r="BE183">
-        <v>6.3</v>
-      </c>
-      <c r="BF183">
-        <v>1.92</v>
-      </c>
-      <c r="BG183">
-        <v>1.41</v>
-      </c>
-      <c r="BH183">
-        <v>2.6</v>
-      </c>
-      <c r="BI183">
-        <v>1.77</v>
-      </c>
-      <c r="BJ183">
-        <v>1.94</v>
-      </c>
-      <c r="BK183">
-        <v>2.28</v>
-      </c>
-      <c r="BL183">
-        <v>1.53</v>
-      </c>
-      <c r="BM183">
-        <v>3.05</v>
-      </c>
-      <c r="BN183">
-        <v>1.28</v>
-      </c>
-      <c r="BO183">
-        <v>4.2</v>
-      </c>
-      <c r="BP183">
-        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,13 +595,16 @@
     <t>['24', '51']</t>
   </si>
   <si>
+    <t>['5']</t>
+  </si>
+  <si>
     <t>['44']</t>
   </si>
   <si>
-    <t>['77']</t>
+    <t>['14', '90']</t>
   </si>
   <si>
-    <t>['14', '90']</t>
+    <t>['77']</t>
   </si>
   <si>
     <t>['58']</t>
@@ -743,9 +746,6 @@
   </si>
   <si>
     <t>['68', '85']</t>
-  </si>
-  <si>
-    <t>['5']</t>
   </si>
   <si>
     <t>['84']</t>
@@ -1218,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1474,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1680,7 +1680,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2298,7 +2298,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2710,7 +2710,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3122,7 +3122,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3328,7 +3328,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3534,7 +3534,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3615,7 +3615,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4436,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
         <v>2.23</v>
@@ -4564,7 +4564,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4976,7 +4976,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5182,7 +5182,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5388,7 +5388,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5594,7 +5594,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5878,7 +5878,7 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ23">
         <v>0.62</v>
@@ -6006,7 +6006,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6212,7 +6212,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6624,7 +6624,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q27">
         <v>3.75</v>
@@ -7117,7 +7117,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7242,7 +7242,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7654,7 +7654,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -8066,7 +8066,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8272,7 +8272,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8890,7 +8890,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9096,7 +9096,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9920,7 +9920,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ43">
         <v>0.92</v>
@@ -10126,7 +10126,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10207,7 +10207,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10744,7 +10744,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10950,7 +10950,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11156,7 +11156,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11774,7 +11774,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12058,7 +12058,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ53">
         <v>1.23</v>
@@ -12186,7 +12186,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12392,7 +12392,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12804,7 +12804,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13010,7 +13010,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13091,7 +13091,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13216,7 +13216,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13834,7 +13834,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14040,7 +14040,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14246,7 +14246,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14864,7 +14864,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15276,7 +15276,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15482,7 +15482,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15560,7 +15560,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ70">
         <v>2</v>
@@ -16100,7 +16100,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16512,7 +16512,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16718,7 +16718,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16799,7 +16799,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -17130,7 +17130,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17336,7 +17336,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17542,7 +17542,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17620,7 +17620,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ80">
         <v>1.38</v>
@@ -17829,7 +17829,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17954,7 +17954,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18160,7 +18160,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18572,7 +18572,7 @@
         <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -20301,7 +20301,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -21250,7 +21250,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21328,7 +21328,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ98">
         <v>1.23</v>
@@ -21740,7 +21740,7 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ100">
         <v>1.77</v>
@@ -24134,7 +24134,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24421,7 +24421,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -26478,7 +26478,7 @@
         <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ123">
         <v>1.77</v>
@@ -26687,7 +26687,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -27511,7 +27511,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR128">
         <v>1.37</v>
@@ -28872,7 +28872,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29774,7 +29774,7 @@
         <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ139">
         <v>1.15</v>
@@ -30520,7 +30520,7 @@
         <v>170</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30601,7 +30601,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ143">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR143">
         <v>1.33</v>
@@ -32168,7 +32168,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32864,7 +32864,7 @@
         <v>0.8</v>
       </c>
       <c r="AP154">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ154">
         <v>1.15</v>
@@ -33897,7 +33897,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR159">
         <v>1.89</v>
@@ -35464,7 +35464,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35542,7 +35542,7 @@
         <v>1.73</v>
       </c>
       <c r="AP167">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ167">
         <v>1.54</v>
@@ -36082,7 +36082,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q170">
         <v>4</v>
@@ -36288,7 +36288,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -37482,7 +37482,7 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>7537473</v>
+        <v>7537474</v>
       </c>
       <c r="C177" t="s">
         <v>68</v>
@@ -37497,190 +37497,190 @@
         <v>26</v>
       </c>
       <c r="G177" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H177" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177">
         <v>0</v>
       </c>
       <c r="K177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177">
         <v>0</v>
       </c>
       <c r="N177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O177" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="P177" t="s">
         <v>84</v>
       </c>
       <c r="Q177">
+        <v>3.1</v>
+      </c>
+      <c r="R177">
+        <v>1.83</v>
+      </c>
+      <c r="S177">
+        <v>4.75</v>
+      </c>
+      <c r="T177">
         <v>1.62</v>
       </c>
-      <c r="R177">
-        <v>2.88</v>
-      </c>
-      <c r="S177">
-        <v>10</v>
-      </c>
-      <c r="T177">
-        <v>1.25</v>
-      </c>
       <c r="U177">
+        <v>2.2</v>
+      </c>
+      <c r="V177">
+        <v>4</v>
+      </c>
+      <c r="W177">
+        <v>1.22</v>
+      </c>
+      <c r="X177">
+        <v>15</v>
+      </c>
+      <c r="Y177">
+        <v>1.03</v>
+      </c>
+      <c r="Z177">
+        <v>2.1</v>
+      </c>
+      <c r="AA177">
+        <v>3</v>
+      </c>
+      <c r="AB177">
         <v>3.75</v>
       </c>
-      <c r="V177">
+      <c r="AC177">
+        <v>1.11</v>
+      </c>
+      <c r="AD177">
+        <v>6.8</v>
+      </c>
+      <c r="AE177">
+        <v>1.55</v>
+      </c>
+      <c r="AF177">
         <v>2.2</v>
       </c>
-      <c r="W177">
-        <v>1.62</v>
-      </c>
-      <c r="X177">
+      <c r="AG177">
+        <v>2.4</v>
+      </c>
+      <c r="AH177">
+        <v>1.46</v>
+      </c>
+      <c r="AI177">
+        <v>2.25</v>
+      </c>
+      <c r="AJ177">
+        <v>1.57</v>
+      </c>
+      <c r="AK177">
+        <v>1.29</v>
+      </c>
+      <c r="AL177">
+        <v>1.38</v>
+      </c>
+      <c r="AM177">
+        <v>1.73</v>
+      </c>
+      <c r="AN177">
+        <v>1.33</v>
+      </c>
+      <c r="AO177">
+        <v>1.17</v>
+      </c>
+      <c r="AP177">
+        <v>1.31</v>
+      </c>
+      <c r="AQ177">
+        <v>1.15</v>
+      </c>
+      <c r="AR177">
+        <v>1.15</v>
+      </c>
+      <c r="AS177">
+        <v>1.09</v>
+      </c>
+      <c r="AT177">
+        <v>2.24</v>
+      </c>
+      <c r="AU177">
+        <v>8</v>
+      </c>
+      <c r="AV177">
         <v>5</v>
-      </c>
-      <c r="Y177">
-        <v>1.17</v>
-      </c>
-      <c r="Z177">
-        <v>1.15</v>
-      </c>
-      <c r="AA177">
-        <v>7</v>
-      </c>
-      <c r="AB177">
-        <v>12</v>
-      </c>
-      <c r="AC177">
-        <v>1.05</v>
-      </c>
-      <c r="AD177">
-        <v>11</v>
-      </c>
-      <c r="AE177">
-        <v>1.26</v>
-      </c>
-      <c r="AF177">
-        <v>3.8</v>
-      </c>
-      <c r="AG177">
-        <v>1.74</v>
-      </c>
-      <c r="AH177">
-        <v>1.97</v>
-      </c>
-      <c r="AI177">
-        <v>2.05</v>
-      </c>
-      <c r="AJ177">
-        <v>1.7</v>
-      </c>
-      <c r="AK177">
-        <v>1.06</v>
-      </c>
-      <c r="AL177">
-        <v>1.18</v>
-      </c>
-      <c r="AM177">
-        <v>3.5</v>
-      </c>
-      <c r="AN177">
-        <v>2.33</v>
-      </c>
-      <c r="AO177">
-        <v>1.5</v>
-      </c>
-      <c r="AP177">
-        <v>2.38</v>
-      </c>
-      <c r="AQ177">
-        <v>1.38</v>
-      </c>
-      <c r="AR177">
-        <v>1.95</v>
-      </c>
-      <c r="AS177">
-        <v>1.05</v>
-      </c>
-      <c r="AT177">
-        <v>3</v>
-      </c>
-      <c r="AU177">
-        <v>11</v>
-      </c>
-      <c r="AV177">
-        <v>3</v>
       </c>
       <c r="AW177">
         <v>13</v>
       </c>
       <c r="AX177">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AY177">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ177">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BA177">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BB177">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC177">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD177">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="BE177">
-        <v>19</v>
+        <v>6.25</v>
       </c>
       <c r="BF177">
-        <v>16.5</v>
+        <v>2.15</v>
       </c>
       <c r="BG177">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="BH177">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="BI177">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="BJ177">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="BK177">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="BL177">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="BM177">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="BN177">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BO177">
-        <v>3.52</v>
+        <v>4.25</v>
       </c>
       <c r="BP177">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="178" spans="1:68">
@@ -37688,7 +37688,7 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>7537474</v>
+        <v>7537475</v>
       </c>
       <c r="C178" t="s">
         <v>68</v>
@@ -37703,190 +37703,190 @@
         <v>26</v>
       </c>
       <c r="G178" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H178" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J178">
         <v>0</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M178">
         <v>0</v>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O178" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="P178" t="s">
         <v>84</v>
       </c>
       <c r="Q178">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="R178">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S178">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
       <c r="T178">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="U178">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V178">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W178">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X178">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y178">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z178">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AA178">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB178">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC178">
+        <v>1.1</v>
+      </c>
+      <c r="AD178">
+        <v>7.2</v>
+      </c>
+      <c r="AE178">
+        <v>1.48</v>
+      </c>
+      <c r="AF178">
+        <v>2.4</v>
+      </c>
+      <c r="AG178">
+        <v>2.34</v>
+      </c>
+      <c r="AH178">
+        <v>1.49</v>
+      </c>
+      <c r="AI178">
+        <v>2.38</v>
+      </c>
+      <c r="AJ178">
+        <v>1.53</v>
+      </c>
+      <c r="AK178">
+        <v>1.56</v>
+      </c>
+      <c r="AL178">
+        <v>1.39</v>
+      </c>
+      <c r="AM178">
+        <v>1.4</v>
+      </c>
+      <c r="AN178">
+        <v>0.5</v>
+      </c>
+      <c r="AO178">
+        <v>1.33</v>
+      </c>
+      <c r="AP178">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ178">
+        <v>1.23</v>
+      </c>
+      <c r="AR178">
         <v>1.11</v>
       </c>
-      <c r="AD178">
-        <v>6.8</v>
-      </c>
-      <c r="AE178">
-        <v>1.55</v>
-      </c>
-      <c r="AF178">
-        <v>2.2</v>
-      </c>
-      <c r="AG178">
-        <v>2.4</v>
-      </c>
-      <c r="AH178">
-        <v>1.46</v>
-      </c>
-      <c r="AI178">
-        <v>2.25</v>
-      </c>
-      <c r="AJ178">
-        <v>1.57</v>
-      </c>
-      <c r="AK178">
-        <v>1.29</v>
-      </c>
-      <c r="AL178">
-        <v>1.38</v>
-      </c>
-      <c r="AM178">
-        <v>1.73</v>
-      </c>
-      <c r="AN178">
-        <v>1.33</v>
-      </c>
-      <c r="AO178">
-        <v>1.17</v>
-      </c>
-      <c r="AP178">
-        <v>1.31</v>
-      </c>
-      <c r="AQ178">
-        <v>1.15</v>
-      </c>
-      <c r="AR178">
-        <v>1.15</v>
-      </c>
       <c r="AS178">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AT178">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AU178">
+        <v>-1</v>
+      </c>
+      <c r="AV178">
+        <v>-1</v>
+      </c>
+      <c r="AW178">
+        <v>-1</v>
+      </c>
+      <c r="AX178">
+        <v>-1</v>
+      </c>
+      <c r="AY178">
+        <v>-1</v>
+      </c>
+      <c r="AZ178">
+        <v>-1</v>
+      </c>
+      <c r="BA178">
+        <v>0</v>
+      </c>
+      <c r="BB178">
         <v>8</v>
-      </c>
-      <c r="AV178">
-        <v>5</v>
-      </c>
-      <c r="AW178">
-        <v>13</v>
-      </c>
-      <c r="AX178">
-        <v>11</v>
-      </c>
-      <c r="AY178">
-        <v>27</v>
-      </c>
-      <c r="AZ178">
-        <v>19</v>
-      </c>
-      <c r="BA178">
-        <v>4</v>
-      </c>
-      <c r="BB178">
-        <v>4</v>
       </c>
       <c r="BC178">
         <v>8</v>
       </c>
       <c r="BD178">
-        <v>1.86</v>
+        <v>2.46</v>
       </c>
       <c r="BE178">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="BF178">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="BG178">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="BH178">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="BI178">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BJ178">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="BK178">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BL178">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="BM178">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BN178">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BO178">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BP178">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="179" spans="1:68">
@@ -37894,7 +37894,7 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>7537471</v>
+        <v>7537473</v>
       </c>
       <c r="C179" t="s">
         <v>68</v>
@@ -37909,190 +37909,190 @@
         <v>26</v>
       </c>
       <c r="G179" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J179">
         <v>0</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179">
         <v>1</v>
       </c>
       <c r="M179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O179" t="s">
         <v>194</v>
       </c>
       <c r="P179" t="s">
-        <v>247</v>
+        <v>84</v>
       </c>
       <c r="Q179">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="R179">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="S179">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="T179">
+        <v>1.25</v>
+      </c>
+      <c r="U179">
+        <v>3.75</v>
+      </c>
+      <c r="V179">
+        <v>2.2</v>
+      </c>
+      <c r="W179">
+        <v>1.62</v>
+      </c>
+      <c r="X179">
+        <v>5</v>
+      </c>
+      <c r="Y179">
+        <v>1.17</v>
+      </c>
+      <c r="Z179">
+        <v>1.15</v>
+      </c>
+      <c r="AA179">
+        <v>7</v>
+      </c>
+      <c r="AB179">
+        <v>12</v>
+      </c>
+      <c r="AC179">
+        <v>1.05</v>
+      </c>
+      <c r="AD179">
+        <v>11</v>
+      </c>
+      <c r="AE179">
+        <v>1.26</v>
+      </c>
+      <c r="AF179">
+        <v>3.8</v>
+      </c>
+      <c r="AG179">
+        <v>1.74</v>
+      </c>
+      <c r="AH179">
+        <v>1.97</v>
+      </c>
+      <c r="AI179">
+        <v>2.05</v>
+      </c>
+      <c r="AJ179">
+        <v>1.7</v>
+      </c>
+      <c r="AK179">
+        <v>1.06</v>
+      </c>
+      <c r="AL179">
+        <v>1.18</v>
+      </c>
+      <c r="AM179">
+        <v>3.5</v>
+      </c>
+      <c r="AN179">
+        <v>2.33</v>
+      </c>
+      <c r="AO179">
         <v>1.5</v>
       </c>
-      <c r="U179">
-        <v>2.5</v>
-      </c>
-      <c r="V179">
-        <v>3.5</v>
-      </c>
-      <c r="W179">
-        <v>1.29</v>
-      </c>
-      <c r="X179">
+      <c r="AP179">
+        <v>2.38</v>
+      </c>
+      <c r="AQ179">
+        <v>1.38</v>
+      </c>
+      <c r="AR179">
+        <v>1.95</v>
+      </c>
+      <c r="AS179">
+        <v>1.05</v>
+      </c>
+      <c r="AT179">
+        <v>3</v>
+      </c>
+      <c r="AU179">
         <v>11</v>
       </c>
-      <c r="Y179">
-        <v>1.05</v>
-      </c>
-      <c r="Z179">
-        <v>5.5</v>
-      </c>
-      <c r="AA179">
-        <v>3.65</v>
-      </c>
-      <c r="AB179">
-        <v>1.6</v>
-      </c>
-      <c r="AC179">
-        <v>1.09</v>
-      </c>
-      <c r="AD179">
-        <v>7.6</v>
-      </c>
-      <c r="AE179">
-        <v>1.45</v>
-      </c>
-      <c r="AF179">
-        <v>2.65</v>
-      </c>
-      <c r="AG179">
-        <v>2.2</v>
-      </c>
-      <c r="AH179">
-        <v>1.55</v>
-      </c>
-      <c r="AI179">
-        <v>2.1</v>
-      </c>
-      <c r="AJ179">
-        <v>1.67</v>
-      </c>
-      <c r="AK179">
+      <c r="AV179">
+        <v>3</v>
+      </c>
+      <c r="AW179">
+        <v>13</v>
+      </c>
+      <c r="AX179">
+        <v>3</v>
+      </c>
+      <c r="AY179">
+        <v>25</v>
+      </c>
+      <c r="AZ179">
+        <v>7</v>
+      </c>
+      <c r="BA179">
+        <v>9</v>
+      </c>
+      <c r="BB179">
+        <v>1</v>
+      </c>
+      <c r="BC179">
+        <v>10</v>
+      </c>
+      <c r="BD179">
+        <v>1.02</v>
+      </c>
+      <c r="BE179">
+        <v>19</v>
+      </c>
+      <c r="BF179">
+        <v>16.5</v>
+      </c>
+      <c r="BG179">
+        <v>1.38</v>
+      </c>
+      <c r="BH179">
+        <v>2.71</v>
+      </c>
+      <c r="BI179">
+        <v>1.7</v>
+      </c>
+      <c r="BJ179">
         <v>2.03</v>
       </c>
-      <c r="AL179">
-        <v>1.34</v>
-      </c>
-      <c r="AM179">
-        <v>1.2</v>
-      </c>
-      <c r="AN179">
-        <v>0.92</v>
-      </c>
-      <c r="AO179">
-        <v>1.58</v>
-      </c>
-      <c r="AP179">
-        <v>0.92</v>
-      </c>
-      <c r="AQ179">
-        <v>1.54</v>
-      </c>
-      <c r="AR179">
-        <v>1.3</v>
-      </c>
-      <c r="AS179">
+      <c r="BK179">
+        <v>2.15</v>
+      </c>
+      <c r="BL179">
         <v>1.59</v>
       </c>
-      <c r="AT179">
-        <v>2.89</v>
-      </c>
-      <c r="AU179">
-        <v>6</v>
-      </c>
-      <c r="AV179">
-        <v>7</v>
-      </c>
-      <c r="AW179">
-        <v>7</v>
-      </c>
-      <c r="AX179">
-        <v>10</v>
-      </c>
-      <c r="AY179">
-        <v>13</v>
-      </c>
-      <c r="AZ179">
-        <v>20</v>
-      </c>
-      <c r="BA179">
-        <v>2</v>
-      </c>
-      <c r="BB179">
-        <v>3</v>
-      </c>
-      <c r="BC179">
-        <v>5</v>
-      </c>
-      <c r="BD179">
-        <v>2.9</v>
-      </c>
-      <c r="BE179">
-        <v>6.4</v>
-      </c>
-      <c r="BF179">
-        <v>1.52</v>
-      </c>
-      <c r="BG179">
-        <v>1.48</v>
-      </c>
-      <c r="BH179">
-        <v>2.28</v>
-      </c>
-      <c r="BI179">
-        <v>1.83</v>
-      </c>
-      <c r="BJ179">
-        <v>1.76</v>
-      </c>
-      <c r="BK179">
-        <v>2.35</v>
-      </c>
-      <c r="BL179">
-        <v>1.46</v>
-      </c>
       <c r="BM179">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="BN179">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO179">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="BP179">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="180" spans="1:68">
@@ -38306,7 +38306,7 @@
         <v>180</v>
       </c>
       <c r="B181">
-        <v>7537468</v>
+        <v>7537470</v>
       </c>
       <c r="C181" t="s">
         <v>68</v>
@@ -38321,10 +38321,10 @@
         <v>26</v>
       </c>
       <c r="G181" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H181" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -38336,28 +38336,28 @@
         <v>0</v>
       </c>
       <c r="L181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N181">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O181" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="P181" t="s">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="Q181">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="R181">
         <v>2.1</v>
       </c>
       <c r="S181">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="T181">
         <v>1.44</v>
@@ -38372,19 +38372,19 @@
         <v>1.33</v>
       </c>
       <c r="X181">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y181">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z181">
-        <v>1.64</v>
+        <v>5.25</v>
       </c>
       <c r="AA181">
         <v>3.6</v>
       </c>
       <c r="AB181">
-        <v>5</v>
+        <v>1.64</v>
       </c>
       <c r="AC181">
         <v>1.08</v>
@@ -38393,16 +38393,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AE181">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF181">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AG181">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH181">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AI181">
         <v>2</v>
@@ -38411,100 +38411,100 @@
         <v>1.75</v>
       </c>
       <c r="AK181">
-        <v>1.17</v>
+        <v>2.19</v>
       </c>
       <c r="AL181">
         <v>1.32</v>
       </c>
       <c r="AM181">
+        <v>1.16</v>
+      </c>
+      <c r="AN181">
         <v>2.17</v>
       </c>
-      <c r="AN181">
-        <v>1.58</v>
-      </c>
       <c r="AO181">
-        <v>0.75</v>
+        <v>1.83</v>
       </c>
       <c r="AP181">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="AQ181">
-        <v>0.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR181">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AS181">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="AT181">
-        <v>2.63</v>
+        <v>3.27</v>
       </c>
       <c r="AU181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV181">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW181">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX181">
+        <v>9</v>
+      </c>
+      <c r="AY181">
+        <v>7</v>
+      </c>
+      <c r="AZ181">
+        <v>17</v>
+      </c>
+      <c r="BA181">
+        <v>4</v>
+      </c>
+      <c r="BB181">
         <v>3</v>
-      </c>
-      <c r="AY181">
-        <v>16</v>
-      </c>
-      <c r="AZ181">
-        <v>9</v>
-      </c>
-      <c r="BA181">
-        <v>6</v>
-      </c>
-      <c r="BB181">
-        <v>1</v>
       </c>
       <c r="BC181">
         <v>7</v>
       </c>
       <c r="BD181">
-        <v>1.35</v>
+        <v>3.4</v>
       </c>
       <c r="BE181">
         <v>6.75</v>
       </c>
       <c r="BF181">
-        <v>3.55</v>
+        <v>1.38</v>
       </c>
       <c r="BG181">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BH181">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="BI181">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BJ181">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BK181">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="BL181">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="BM181">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="BN181">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BO181">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP181">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="182" spans="1:68">
@@ -38512,7 +38512,7 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>7537470</v>
+        <v>7537471</v>
       </c>
       <c r="C182" t="s">
         <v>68</v>
@@ -38527,10 +38527,10 @@
         <v>26</v>
       </c>
       <c r="G182" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H182" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -38542,166 +38542,166 @@
         <v>0</v>
       </c>
       <c r="L182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O182" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="P182" t="s">
-        <v>84</v>
+        <v>247</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
       </c>
       <c r="R182">
+        <v>2</v>
+      </c>
+      <c r="S182">
+        <v>2.5</v>
+      </c>
+      <c r="T182">
+        <v>1.5</v>
+      </c>
+      <c r="U182">
+        <v>2.5</v>
+      </c>
+      <c r="V182">
+        <v>3.5</v>
+      </c>
+      <c r="W182">
+        <v>1.29</v>
+      </c>
+      <c r="X182">
+        <v>11</v>
+      </c>
+      <c r="Y182">
+        <v>1.05</v>
+      </c>
+      <c r="Z182">
+        <v>5.5</v>
+      </c>
+      <c r="AA182">
+        <v>3.65</v>
+      </c>
+      <c r="AB182">
+        <v>1.6</v>
+      </c>
+      <c r="AC182">
+        <v>1.09</v>
+      </c>
+      <c r="AD182">
+        <v>7.6</v>
+      </c>
+      <c r="AE182">
+        <v>1.45</v>
+      </c>
+      <c r="AF182">
+        <v>2.65</v>
+      </c>
+      <c r="AG182">
+        <v>2.2</v>
+      </c>
+      <c r="AH182">
+        <v>1.55</v>
+      </c>
+      <c r="AI182">
         <v>2.1</v>
       </c>
-      <c r="S182">
-        <v>2.3</v>
-      </c>
-      <c r="T182">
-        <v>1.44</v>
-      </c>
-      <c r="U182">
-        <v>2.63</v>
-      </c>
-      <c r="V182">
-        <v>3.25</v>
-      </c>
-      <c r="W182">
-        <v>1.33</v>
-      </c>
-      <c r="X182">
-        <v>9</v>
-      </c>
-      <c r="Y182">
-        <v>1.07</v>
-      </c>
-      <c r="Z182">
-        <v>5.25</v>
-      </c>
-      <c r="AA182">
-        <v>3.6</v>
-      </c>
-      <c r="AB182">
-        <v>1.64</v>
-      </c>
-      <c r="AC182">
-        <v>1.08</v>
-      </c>
-      <c r="AD182">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AE182">
-        <v>1.39</v>
-      </c>
-      <c r="AF182">
-        <v>2.9</v>
-      </c>
-      <c r="AG182">
-        <v>2</v>
-      </c>
-      <c r="AH182">
+      <c r="AJ182">
         <v>1.67</v>
       </c>
-      <c r="AI182">
-        <v>2</v>
-      </c>
-      <c r="AJ182">
-        <v>1.75</v>
-      </c>
       <c r="AK182">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="AL182">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AM182">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AN182">
-        <v>2.17</v>
+        <v>0.92</v>
       </c>
       <c r="AO182">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AP182">
-        <v>2.08</v>
+        <v>0.92</v>
       </c>
       <c r="AQ182">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AR182">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AS182">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AT182">
-        <v>3.27</v>
+        <v>2.89</v>
       </c>
       <c r="AU182">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV182">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW182">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX182">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY182">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AZ182">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA182">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB182">
         <v>3</v>
       </c>
       <c r="BC182">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD182">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="BE182">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF182">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="BG182">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BH182">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BI182">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BJ182">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BK182">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="BL182">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BM182">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BN182">
         <v>1.27</v>
@@ -38711,6 +38711,212 @@
       </c>
       <c r="BP182">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7537468</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F183">
+        <v>26</v>
+      </c>
+      <c r="G183" t="s">
+        <v>79</v>
+      </c>
+      <c r="H183" t="s">
+        <v>78</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>2</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183" t="s">
+        <v>197</v>
+      </c>
+      <c r="P183" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q183">
+        <v>2.5</v>
+      </c>
+      <c r="R183">
+        <v>2.1</v>
+      </c>
+      <c r="S183">
+        <v>5</v>
+      </c>
+      <c r="T183">
+        <v>1.44</v>
+      </c>
+      <c r="U183">
+        <v>2.63</v>
+      </c>
+      <c r="V183">
+        <v>3.25</v>
+      </c>
+      <c r="W183">
+        <v>1.33</v>
+      </c>
+      <c r="X183">
+        <v>10</v>
+      </c>
+      <c r="Y183">
+        <v>1.06</v>
+      </c>
+      <c r="Z183">
+        <v>1.64</v>
+      </c>
+      <c r="AA183">
+        <v>3.6</v>
+      </c>
+      <c r="AB183">
+        <v>5</v>
+      </c>
+      <c r="AC183">
+        <v>1.08</v>
+      </c>
+      <c r="AD183">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE183">
+        <v>1.4</v>
+      </c>
+      <c r="AF183">
+        <v>2.85</v>
+      </c>
+      <c r="AG183">
+        <v>2.1</v>
+      </c>
+      <c r="AH183">
+        <v>1.61</v>
+      </c>
+      <c r="AI183">
+        <v>2</v>
+      </c>
+      <c r="AJ183">
+        <v>1.75</v>
+      </c>
+      <c r="AK183">
+        <v>1.17</v>
+      </c>
+      <c r="AL183">
+        <v>1.32</v>
+      </c>
+      <c r="AM183">
+        <v>2.17</v>
+      </c>
+      <c r="AN183">
+        <v>1.58</v>
+      </c>
+      <c r="AO183">
+        <v>0.75</v>
+      </c>
+      <c r="AP183">
+        <v>1.46</v>
+      </c>
+      <c r="AQ183">
+        <v>0.92</v>
+      </c>
+      <c r="AR183">
+        <v>1.35</v>
+      </c>
+      <c r="AS183">
+        <v>1.28</v>
+      </c>
+      <c r="AT183">
+        <v>2.63</v>
+      </c>
+      <c r="AU183">
+        <v>2</v>
+      </c>
+      <c r="AV183">
+        <v>6</v>
+      </c>
+      <c r="AW183">
+        <v>11</v>
+      </c>
+      <c r="AX183">
+        <v>3</v>
+      </c>
+      <c r="AY183">
+        <v>16</v>
+      </c>
+      <c r="AZ183">
+        <v>9</v>
+      </c>
+      <c r="BA183">
+        <v>6</v>
+      </c>
+      <c r="BB183">
+        <v>1</v>
+      </c>
+      <c r="BC183">
+        <v>7</v>
+      </c>
+      <c r="BD183">
+        <v>1.35</v>
+      </c>
+      <c r="BE183">
+        <v>6.75</v>
+      </c>
+      <c r="BF183">
+        <v>3.55</v>
+      </c>
+      <c r="BG183">
+        <v>1.42</v>
+      </c>
+      <c r="BH183">
+        <v>2.48</v>
+      </c>
+      <c r="BI183">
+        <v>1.73</v>
+      </c>
+      <c r="BJ183">
+        <v>1.88</v>
+      </c>
+      <c r="BK183">
+        <v>2.17</v>
+      </c>
+      <c r="BL183">
+        <v>1.54</v>
+      </c>
+      <c r="BM183">
+        <v>2.85</v>
+      </c>
+      <c r="BN183">
+        <v>1.32</v>
+      </c>
+      <c r="BO183">
+        <v>3.8</v>
+      </c>
+      <c r="BP183">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="286">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,15 @@
     <t>['58']</t>
   </si>
   <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -626,9 +635,6 @@
   </si>
   <si>
     <t>['39']</t>
-  </si>
-  <si>
-    <t>['12']</t>
   </si>
   <si>
     <t>['41', '79', '81']</t>
@@ -857,6 +863,15 @@
   </si>
   <si>
     <t>['60', '84']</t>
+  </si>
+  <si>
+    <t>['6', '87']</t>
+  </si>
+  <si>
+    <t>['37', '58']</t>
+  </si>
+  <si>
+    <t>['72', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1489,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1680,7 +1695,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2298,7 +2313,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2379,7 +2394,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ6">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2710,7 +2725,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2788,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ8">
         <v>0.46</v>
@@ -2994,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ9">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3122,7 +3137,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3203,7 +3218,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ10">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3328,7 +3343,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3534,7 +3549,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3612,10 +3627,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4027,7 +4042,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ14">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4358,7 +4373,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4564,7 +4579,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4848,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18">
         <v>0.92</v>
@@ -4976,7 +4991,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5182,7 +5197,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5388,7 +5403,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5594,7 +5609,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -6006,7 +6021,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6084,10 +6099,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR24">
         <v>2.26</v>
@@ -6212,7 +6227,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6293,7 +6308,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ25">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>0.98</v>
@@ -6624,7 +6639,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q27">
         <v>3.75</v>
@@ -6702,10 +6717,10 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -7117,7 +7132,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ29">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR29">
         <v>2.28</v>
@@ -7242,7 +7257,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7654,7 +7669,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7732,7 +7747,7 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32">
         <v>1.23</v>
@@ -8066,7 +8081,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8272,7 +8287,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8890,7 +8905,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -8968,10 +8983,10 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ38">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9096,7 +9111,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9174,7 +9189,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ39">
         <v>1.23</v>
@@ -9383,7 +9398,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ40">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR40">
         <v>2.09</v>
@@ -9589,7 +9604,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR41">
         <v>1.71</v>
@@ -9920,7 +9935,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10126,7 +10141,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10207,7 +10222,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -10410,7 +10425,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ45">
         <v>1.77</v>
@@ -10744,7 +10759,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10950,7 +10965,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11156,7 +11171,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11774,7 +11789,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12186,7 +12201,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12267,7 +12282,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ54">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR54">
         <v>2.03</v>
@@ -12392,7 +12407,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12470,7 +12485,7 @@
         <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ55">
         <v>1.54</v>
@@ -12804,7 +12819,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13010,7 +13025,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13088,10 +13103,10 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ58">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR58">
         <v>1.3</v>
@@ -13216,7 +13231,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13706,7 +13721,7 @@
         <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61">
         <v>2.23</v>
@@ -13834,7 +13849,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13915,7 +13930,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ62">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR62">
         <v>1.7</v>
@@ -14040,7 +14055,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14246,7 +14261,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14327,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR64">
         <v>1.31</v>
@@ -14864,7 +14879,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14945,7 +14960,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR67">
         <v>1.46</v>
@@ -15276,7 +15291,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15482,7 +15497,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15766,7 +15781,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
         <v>1.38</v>
@@ -15972,10 +15987,10 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ72">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR72">
         <v>1.28</v>
@@ -16100,7 +16115,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16181,7 +16196,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ73">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR73">
         <v>1.13</v>
@@ -16512,7 +16527,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16590,7 +16605,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ75">
         <v>0.62</v>
@@ -16718,7 +16733,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16799,7 +16814,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR76">
         <v>1.06</v>
@@ -17130,7 +17145,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17336,7 +17351,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17542,7 +17557,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17829,7 +17844,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ81">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17954,7 +17969,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18032,7 +18047,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ82">
         <v>1.54</v>
@@ -18160,7 +18175,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18238,7 +18253,7 @@
         <v>2.6</v>
       </c>
       <c r="AP83">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ83">
         <v>2</v>
@@ -18653,7 +18668,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ85">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR85">
         <v>1.32</v>
@@ -18984,7 +18999,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19271,7 +19286,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ88">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR88">
         <v>1.86</v>
@@ -19602,7 +19617,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19680,7 +19695,7 @@
         <v>1.67</v>
       </c>
       <c r="AP90">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90">
         <v>2.23</v>
@@ -19808,7 +19823,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -20014,7 +20029,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20095,7 +20110,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ92">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR92">
         <v>1.7</v>
@@ -20301,7 +20316,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ93">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR93">
         <v>1.95</v>
@@ -20426,7 +20441,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20507,7 +20522,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ94">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20632,7 +20647,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20838,7 +20853,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20916,7 +20931,7 @@
         <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ96">
         <v>1.77</v>
@@ -21122,7 +21137,7 @@
         <v>1.83</v>
       </c>
       <c r="AP97">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ97">
         <v>1.54</v>
@@ -21250,7 +21265,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21456,7 +21471,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21537,7 +21552,7 @@
         <v>1</v>
       </c>
       <c r="AQ99">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -22770,7 +22785,7 @@
         <v>2.71</v>
       </c>
       <c r="AP105">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ105">
         <v>2</v>
@@ -23803,7 +23818,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ110">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR110">
         <v>1.66</v>
@@ -23928,7 +23943,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24009,7 +24024,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ111">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR111">
         <v>1.89</v>
@@ -24134,7 +24149,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24212,10 +24227,10 @@
         <v>1.14</v>
       </c>
       <c r="AP112">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ112">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR112">
         <v>1.43</v>
@@ -24418,10 +24433,10 @@
         <v>1.71</v>
       </c>
       <c r="AP113">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ113">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR113">
         <v>1.13</v>
@@ -24958,7 +24973,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25164,7 +25179,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25370,7 +25385,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25576,7 +25591,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25782,7 +25797,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25860,7 +25875,7 @@
         <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ120">
         <v>2.23</v>
@@ -26069,7 +26084,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ121">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR121">
         <v>1.96</v>
@@ -26194,7 +26209,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26400,7 +26415,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26481,7 +26496,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ123">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR123">
         <v>1.09</v>
@@ -26606,7 +26621,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26687,7 +26702,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ124">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR124">
         <v>1.66</v>
@@ -27096,7 +27111,7 @@
         <v>1.63</v>
       </c>
       <c r="AP126">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126">
         <v>1.23</v>
@@ -27302,10 +27317,10 @@
         <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ127">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27511,7 +27526,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR128">
         <v>1.37</v>
@@ -27636,7 +27651,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27842,7 +27857,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28126,7 +28141,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28872,7 +28887,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -28953,7 +28968,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ135">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR135">
         <v>1.26</v>
@@ -29078,7 +29093,7 @@
         <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29156,7 +29171,7 @@
         <v>1</v>
       </c>
       <c r="AP136">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ136">
         <v>0.92</v>
@@ -29362,7 +29377,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP137">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ137">
         <v>0.62</v>
@@ -29696,7 +29711,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29777,7 +29792,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ139">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR139">
         <v>1.11</v>
@@ -29983,7 +29998,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ140">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR140">
         <v>1.7</v>
@@ -30314,7 +30329,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30520,7 +30535,7 @@
         <v>170</v>
       </c>
       <c r="P143" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30601,7 +30616,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ143">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR143">
         <v>1.33</v>
@@ -31013,7 +31028,7 @@
         <v>1</v>
       </c>
       <c r="AQ145">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31138,7 +31153,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31422,10 +31437,10 @@
         <v>1.7</v>
       </c>
       <c r="AP147">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ147">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31628,7 +31643,7 @@
         <v>0.6</v>
       </c>
       <c r="AP148">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ148">
         <v>0.46</v>
@@ -31962,7 +31977,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32040,7 +32055,7 @@
         <v>2.3</v>
       </c>
       <c r="AP150">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ150">
         <v>2</v>
@@ -32168,7 +32183,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32786,7 +32801,7 @@
         <v>84</v>
       </c>
       <c r="P154" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -32867,7 +32882,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ154">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR154">
         <v>1.07</v>
@@ -32992,7 +33007,7 @@
         <v>147</v>
       </c>
       <c r="P155" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q155">
         <v>2.63</v>
@@ -33276,7 +33291,7 @@
         <v>1.45</v>
       </c>
       <c r="AP156">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ156">
         <v>1.23</v>
@@ -33404,7 +33419,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33485,7 +33500,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ157">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR157">
         <v>2.15</v>
@@ -33610,7 +33625,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33691,7 +33706,7 @@
         <v>1</v>
       </c>
       <c r="AQ158">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR158">
         <v>1.13</v>
@@ -33816,7 +33831,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33897,7 +33912,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ159">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR159">
         <v>1.89</v>
@@ -34022,7 +34037,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34512,7 +34527,7 @@
         <v>0.73</v>
       </c>
       <c r="AP162">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ162">
         <v>0.62</v>
@@ -34640,7 +34655,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35052,7 +35067,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35133,7 +35148,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ165">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR165">
         <v>1.27</v>
@@ -35258,7 +35273,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35464,7 +35479,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35670,7 +35685,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35748,7 +35763,7 @@
         <v>1.73</v>
       </c>
       <c r="AP168">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ168">
         <v>1.77</v>
@@ -35876,7 +35891,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36082,7 +36097,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q170">
         <v>4</v>
@@ -36163,7 +36178,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ170">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR170">
         <v>1.25</v>
@@ -36288,7 +36303,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36700,7 +36715,7 @@
         <v>122</v>
       </c>
       <c r="P173" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q173">
         <v>3.6</v>
@@ -36781,7 +36796,7 @@
         <v>1</v>
       </c>
       <c r="AQ173">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR173">
         <v>1.15</v>
@@ -36984,7 +36999,7 @@
         <v>0.5</v>
       </c>
       <c r="AP174">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ174">
         <v>0.46</v>
@@ -37318,7 +37333,7 @@
         <v>84</v>
       </c>
       <c r="P176" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q176">
         <v>3.25</v>
@@ -37602,10 +37617,10 @@
         <v>1.17</v>
       </c>
       <c r="AP177">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ177">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR177">
         <v>1.15</v>
@@ -37811,7 +37826,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ178">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR178">
         <v>1.11</v>
@@ -38142,7 +38157,7 @@
         <v>195</v>
       </c>
       <c r="P180" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q180">
         <v>6.5</v>
@@ -38554,7 +38569,7 @@
         <v>196</v>
       </c>
       <c r="P182" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38760,7 +38775,7 @@
         <v>197</v>
       </c>
       <c r="P183" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -38838,7 +38853,7 @@
         <v>0.75</v>
       </c>
       <c r="AP183">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ183">
         <v>0.92</v>
@@ -38917,6 +38932,830 @@
       </c>
       <c r="BP183">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7856948</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184" t="s">
+        <v>77</v>
+      </c>
+      <c r="H184" t="s">
+        <v>74</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>2</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>3</v>
+      </c>
+      <c r="O184" t="s">
+        <v>198</v>
+      </c>
+      <c r="P184" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q184">
+        <v>3</v>
+      </c>
+      <c r="R184">
+        <v>2</v>
+      </c>
+      <c r="S184">
+        <v>4</v>
+      </c>
+      <c r="T184">
+        <v>1.5</v>
+      </c>
+      <c r="U184">
+        <v>2.5</v>
+      </c>
+      <c r="V184">
+        <v>3.4</v>
+      </c>
+      <c r="W184">
+        <v>1.3</v>
+      </c>
+      <c r="X184">
+        <v>10</v>
+      </c>
+      <c r="Y184">
+        <v>1.06</v>
+      </c>
+      <c r="Z184">
+        <v>2.25</v>
+      </c>
+      <c r="AA184">
+        <v>3.1</v>
+      </c>
+      <c r="AB184">
+        <v>3.1</v>
+      </c>
+      <c r="AC184">
+        <v>0</v>
+      </c>
+      <c r="AD184">
+        <v>0</v>
+      </c>
+      <c r="AE184">
+        <v>0</v>
+      </c>
+      <c r="AF184">
+        <v>0</v>
+      </c>
+      <c r="AG184">
+        <v>2.1</v>
+      </c>
+      <c r="AH184">
+        <v>1.6</v>
+      </c>
+      <c r="AI184">
+        <v>1.95</v>
+      </c>
+      <c r="AJ184">
+        <v>1.8</v>
+      </c>
+      <c r="AK184">
+        <v>0</v>
+      </c>
+      <c r="AL184">
+        <v>0</v>
+      </c>
+      <c r="AM184">
+        <v>0</v>
+      </c>
+      <c r="AN184">
+        <v>1.38</v>
+      </c>
+      <c r="AO184">
+        <v>1.77</v>
+      </c>
+      <c r="AP184">
+        <v>1.29</v>
+      </c>
+      <c r="AQ184">
+        <v>1.86</v>
+      </c>
+      <c r="AR184">
+        <v>1.46</v>
+      </c>
+      <c r="AS184">
+        <v>1.18</v>
+      </c>
+      <c r="AT184">
+        <v>2.64</v>
+      </c>
+      <c r="AU184">
+        <v>-1</v>
+      </c>
+      <c r="AV184">
+        <v>-1</v>
+      </c>
+      <c r="AW184">
+        <v>-1</v>
+      </c>
+      <c r="AX184">
+        <v>-1</v>
+      </c>
+      <c r="AY184">
+        <v>-1</v>
+      </c>
+      <c r="AZ184">
+        <v>-1</v>
+      </c>
+      <c r="BA184">
+        <v>-1</v>
+      </c>
+      <c r="BB184">
+        <v>-1</v>
+      </c>
+      <c r="BC184">
+        <v>-1</v>
+      </c>
+      <c r="BD184">
+        <v>0</v>
+      </c>
+      <c r="BE184">
+        <v>0</v>
+      </c>
+      <c r="BF184">
+        <v>0</v>
+      </c>
+      <c r="BG184">
+        <v>0</v>
+      </c>
+      <c r="BH184">
+        <v>0</v>
+      </c>
+      <c r="BI184">
+        <v>0</v>
+      </c>
+      <c r="BJ184">
+        <v>0</v>
+      </c>
+      <c r="BK184">
+        <v>0</v>
+      </c>
+      <c r="BL184">
+        <v>0</v>
+      </c>
+      <c r="BM184">
+        <v>0</v>
+      </c>
+      <c r="BN184">
+        <v>0</v>
+      </c>
+      <c r="BO184">
+        <v>0</v>
+      </c>
+      <c r="BP184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7856949</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45745.5625</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" t="s">
+        <v>83</v>
+      </c>
+      <c r="H185" t="s">
+        <v>70</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>2</v>
+      </c>
+      <c r="O185" t="s">
+        <v>199</v>
+      </c>
+      <c r="P185" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q185">
+        <v>3</v>
+      </c>
+      <c r="R185">
+        <v>2</v>
+      </c>
+      <c r="S185">
+        <v>4</v>
+      </c>
+      <c r="T185">
+        <v>1.5</v>
+      </c>
+      <c r="U185">
+        <v>2.5</v>
+      </c>
+      <c r="V185">
+        <v>3.4</v>
+      </c>
+      <c r="W185">
+        <v>1.3</v>
+      </c>
+      <c r="X185">
+        <v>10</v>
+      </c>
+      <c r="Y185">
+        <v>1.06</v>
+      </c>
+      <c r="Z185">
+        <v>2.1</v>
+      </c>
+      <c r="AA185">
+        <v>3.1</v>
+      </c>
+      <c r="AB185">
+        <v>3.4</v>
+      </c>
+      <c r="AC185">
+        <v>1.03</v>
+      </c>
+      <c r="AD185">
+        <v>7.5</v>
+      </c>
+      <c r="AE185">
+        <v>1.38</v>
+      </c>
+      <c r="AF185">
+        <v>2.7</v>
+      </c>
+      <c r="AG185">
+        <v>2.15</v>
+      </c>
+      <c r="AH185">
+        <v>1.57</v>
+      </c>
+      <c r="AI185">
+        <v>1.95</v>
+      </c>
+      <c r="AJ185">
+        <v>1.8</v>
+      </c>
+      <c r="AK185">
+        <v>1.3</v>
+      </c>
+      <c r="AL185">
+        <v>1.34</v>
+      </c>
+      <c r="AM185">
+        <v>1.63</v>
+      </c>
+      <c r="AN185">
+        <v>1</v>
+      </c>
+      <c r="AO185">
+        <v>1.23</v>
+      </c>
+      <c r="AP185">
+        <v>1</v>
+      </c>
+      <c r="AQ185">
+        <v>1.21</v>
+      </c>
+      <c r="AR185">
+        <v>1.5</v>
+      </c>
+      <c r="AS185">
+        <v>1.02</v>
+      </c>
+      <c r="AT185">
+        <v>2.52</v>
+      </c>
+      <c r="AU185">
+        <v>-1</v>
+      </c>
+      <c r="AV185">
+        <v>-1</v>
+      </c>
+      <c r="AW185">
+        <v>-1</v>
+      </c>
+      <c r="AX185">
+        <v>-1</v>
+      </c>
+      <c r="AY185">
+        <v>-1</v>
+      </c>
+      <c r="AZ185">
+        <v>-1</v>
+      </c>
+      <c r="BA185">
+        <v>-1</v>
+      </c>
+      <c r="BB185">
+        <v>-1</v>
+      </c>
+      <c r="BC185">
+        <v>-1</v>
+      </c>
+      <c r="BD185">
+        <v>1.71</v>
+      </c>
+      <c r="BE185">
+        <v>6.45</v>
+      </c>
+      <c r="BF185">
+        <v>2.83</v>
+      </c>
+      <c r="BG185">
+        <v>1.39</v>
+      </c>
+      <c r="BH185">
+        <v>2.67</v>
+      </c>
+      <c r="BI185">
+        <v>1.72</v>
+      </c>
+      <c r="BJ185">
+        <v>2</v>
+      </c>
+      <c r="BK185">
+        <v>2.19</v>
+      </c>
+      <c r="BL185">
+        <v>1.57</v>
+      </c>
+      <c r="BM185">
+        <v>2.92</v>
+      </c>
+      <c r="BN185">
+        <v>1.31</v>
+      </c>
+      <c r="BO185">
+        <v>3.75</v>
+      </c>
+      <c r="BP185">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7856950</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186" t="s">
+        <v>79</v>
+      </c>
+      <c r="H186" t="s">
+        <v>82</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>2</v>
+      </c>
+      <c r="N186">
+        <v>2</v>
+      </c>
+      <c r="O186" t="s">
+        <v>84</v>
+      </c>
+      <c r="P186" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q186">
+        <v>3.6</v>
+      </c>
+      <c r="R186">
+        <v>1.91</v>
+      </c>
+      <c r="S186">
+        <v>3.6</v>
+      </c>
+      <c r="T186">
+        <v>1.57</v>
+      </c>
+      <c r="U186">
+        <v>2.25</v>
+      </c>
+      <c r="V186">
+        <v>3.75</v>
+      </c>
+      <c r="W186">
+        <v>1.25</v>
+      </c>
+      <c r="X186">
+        <v>13</v>
+      </c>
+      <c r="Y186">
+        <v>1.04</v>
+      </c>
+      <c r="Z186">
+        <v>3.1</v>
+      </c>
+      <c r="AA186">
+        <v>2.9</v>
+      </c>
+      <c r="AB186">
+        <v>2.35</v>
+      </c>
+      <c r="AC186">
+        <v>0</v>
+      </c>
+      <c r="AD186">
+        <v>0</v>
+      </c>
+      <c r="AE186">
+        <v>1.5</v>
+      </c>
+      <c r="AF186">
+        <v>2.4</v>
+      </c>
+      <c r="AG186">
+        <v>2.2</v>
+      </c>
+      <c r="AH186">
+        <v>1.57</v>
+      </c>
+      <c r="AI186">
+        <v>2.05</v>
+      </c>
+      <c r="AJ186">
+        <v>1.7</v>
+      </c>
+      <c r="AK186">
+        <v>0</v>
+      </c>
+      <c r="AL186">
+        <v>0</v>
+      </c>
+      <c r="AM186">
+        <v>0</v>
+      </c>
+      <c r="AN186">
+        <v>1.46</v>
+      </c>
+      <c r="AO186">
+        <v>1.15</v>
+      </c>
+      <c r="AP186">
+        <v>1.36</v>
+      </c>
+      <c r="AQ186">
+        <v>1.29</v>
+      </c>
+      <c r="AR186">
+        <v>1.35</v>
+      </c>
+      <c r="AS186">
+        <v>1.21</v>
+      </c>
+      <c r="AT186">
+        <v>2.56</v>
+      </c>
+      <c r="AU186">
+        <v>-1</v>
+      </c>
+      <c r="AV186">
+        <v>-1</v>
+      </c>
+      <c r="AW186">
+        <v>-1</v>
+      </c>
+      <c r="AX186">
+        <v>-1</v>
+      </c>
+      <c r="AY186">
+        <v>-1</v>
+      </c>
+      <c r="AZ186">
+        <v>-1</v>
+      </c>
+      <c r="BA186">
+        <v>-1</v>
+      </c>
+      <c r="BB186">
+        <v>-1</v>
+      </c>
+      <c r="BC186">
+        <v>-1</v>
+      </c>
+      <c r="BD186">
+        <v>0</v>
+      </c>
+      <c r="BE186">
+        <v>0</v>
+      </c>
+      <c r="BF186">
+        <v>0</v>
+      </c>
+      <c r="BG186">
+        <v>0</v>
+      </c>
+      <c r="BH186">
+        <v>0</v>
+      </c>
+      <c r="BI186">
+        <v>0</v>
+      </c>
+      <c r="BJ186">
+        <v>0</v>
+      </c>
+      <c r="BK186">
+        <v>0</v>
+      </c>
+      <c r="BL186">
+        <v>0</v>
+      </c>
+      <c r="BM186">
+        <v>0</v>
+      </c>
+      <c r="BN186">
+        <v>0</v>
+      </c>
+      <c r="BO186">
+        <v>0</v>
+      </c>
+      <c r="BP186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7856951</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45745.64583333334</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187" t="s">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s">
+        <v>72</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187">
+        <v>2</v>
+      </c>
+      <c r="N187">
+        <v>3</v>
+      </c>
+      <c r="O187" t="s">
+        <v>200</v>
+      </c>
+      <c r="P187" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q187">
+        <v>3.5</v>
+      </c>
+      <c r="R187">
+        <v>1.8</v>
+      </c>
+      <c r="S187">
+        <v>4</v>
+      </c>
+      <c r="T187">
+        <v>1.67</v>
+      </c>
+      <c r="U187">
+        <v>2.1</v>
+      </c>
+      <c r="V187">
+        <v>4.33</v>
+      </c>
+      <c r="W187">
+        <v>1.2</v>
+      </c>
+      <c r="X187">
+        <v>15</v>
+      </c>
+      <c r="Y187">
+        <v>1.03</v>
+      </c>
+      <c r="Z187">
+        <v>2.5</v>
+      </c>
+      <c r="AA187">
+        <v>2.75</v>
+      </c>
+      <c r="AB187">
+        <v>3.1</v>
+      </c>
+      <c r="AC187">
+        <v>1.08</v>
+      </c>
+      <c r="AD187">
+        <v>5.6</v>
+      </c>
+      <c r="AE187">
+        <v>1.6</v>
+      </c>
+      <c r="AF187">
+        <v>2.2</v>
+      </c>
+      <c r="AG187">
+        <v>2.37</v>
+      </c>
+      <c r="AH187">
+        <v>1.48</v>
+      </c>
+      <c r="AI187">
+        <v>2.25</v>
+      </c>
+      <c r="AJ187">
+        <v>1.57</v>
+      </c>
+      <c r="AK187">
+        <v>1.35</v>
+      </c>
+      <c r="AL187">
+        <v>1.41</v>
+      </c>
+      <c r="AM187">
+        <v>1.47</v>
+      </c>
+      <c r="AN187">
+        <v>1.31</v>
+      </c>
+      <c r="AO187">
+        <v>1.15</v>
+      </c>
+      <c r="AP187">
+        <v>1.21</v>
+      </c>
+      <c r="AQ187">
+        <v>1.29</v>
+      </c>
+      <c r="AR187">
+        <v>1.23</v>
+      </c>
+      <c r="AS187">
+        <v>1.14</v>
+      </c>
+      <c r="AT187">
+        <v>2.37</v>
+      </c>
+      <c r="AU187">
+        <v>-1</v>
+      </c>
+      <c r="AV187">
+        <v>-1</v>
+      </c>
+      <c r="AW187">
+        <v>-1</v>
+      </c>
+      <c r="AX187">
+        <v>-1</v>
+      </c>
+      <c r="AY187">
+        <v>-1</v>
+      </c>
+      <c r="AZ187">
+        <v>-1</v>
+      </c>
+      <c r="BA187">
+        <v>-1</v>
+      </c>
+      <c r="BB187">
+        <v>-1</v>
+      </c>
+      <c r="BC187">
+        <v>-1</v>
+      </c>
+      <c r="BD187">
+        <v>2.52</v>
+      </c>
+      <c r="BE187">
+        <v>5.95</v>
+      </c>
+      <c r="BF187">
+        <v>1.89</v>
+      </c>
+      <c r="BG187">
+        <v>1.73</v>
+      </c>
+      <c r="BH187">
+        <v>1.99</v>
+      </c>
+      <c r="BI187">
+        <v>2.23</v>
+      </c>
+      <c r="BJ187">
+        <v>1.55</v>
+      </c>
+      <c r="BK187">
+        <v>3.08</v>
+      </c>
+      <c r="BL187">
+        <v>1.28</v>
+      </c>
+      <c r="BM187">
+        <v>4.2</v>
+      </c>
+      <c r="BN187">
+        <v>1.17</v>
+      </c>
+      <c r="BO187">
+        <v>5.93</v>
+      </c>
+      <c r="BP187">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="287">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -873,6 +873,9 @@
   <si>
     <t>['72', '90+3']</t>
   </si>
+  <si>
+    <t>['78']</t>
+  </si>
 </sst>
 </file>
 
@@ -1233,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2806,7 +2809,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ8">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3215,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ10">
         <v>1.29</v>
@@ -3424,7 +3427,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ11">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>2.01</v>
@@ -6305,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ25">
         <v>1.29</v>
@@ -8368,7 +8371,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ35">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -10634,7 +10637,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ46">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR46">
         <v>1.16</v>
@@ -10837,7 +10840,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ47">
         <v>1.38</v>
@@ -13312,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13515,7 +13518,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ60">
         <v>1.77</v>
@@ -16193,7 +16196,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ73">
         <v>1.86</v>
@@ -17020,7 +17023,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ77">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR77">
         <v>1.69</v>
@@ -18874,7 +18877,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ86">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR86">
         <v>1.38</v>
@@ -19489,7 +19492,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ89">
         <v>1.23</v>
@@ -20725,7 +20728,7 @@
         <v>2.67</v>
       </c>
       <c r="AP95">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ95">
         <v>2</v>
@@ -23200,7 +23203,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ107">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.96</v>
@@ -23403,7 +23406,7 @@
         <v>1.71</v>
       </c>
       <c r="AP108">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108">
         <v>1.23</v>
@@ -24642,7 +24645,7 @@
         <v>1</v>
       </c>
       <c r="AQ114">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR114">
         <v>1.39</v>
@@ -26287,7 +26290,7 @@
         <v>2.13</v>
       </c>
       <c r="AP122">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ122">
         <v>1.54</v>
@@ -28759,10 +28762,10 @@
         <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ134">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR134">
         <v>1.25</v>
@@ -30613,7 +30616,7 @@
         <v>1.5</v>
       </c>
       <c r="AP143">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ143">
         <v>1.21</v>
@@ -31646,7 +31649,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ148">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR148">
         <v>1.44</v>
@@ -34115,7 +34118,7 @@
         <v>2.09</v>
       </c>
       <c r="AP160">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ160">
         <v>2.23</v>
@@ -34324,7 +34327,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ161">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -36381,7 +36384,7 @@
         <v>0.67</v>
       </c>
       <c r="AP171">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ171">
         <v>0.62</v>
@@ -37002,7 +37005,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ174">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR174">
         <v>1.42</v>
@@ -39074,31 +39077,31 @@
         <v>2.64</v>
       </c>
       <c r="AU184">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV184">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW184">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AX184">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY184">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AZ184">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BA184">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB184">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC184">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD184">
         <v>0</v>
@@ -39280,31 +39283,31 @@
         <v>2.52</v>
       </c>
       <c r="AU185">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV185">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW185">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX185">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY185">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ185">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA185">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB185">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC185">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD185">
         <v>1.71</v>
@@ -39486,31 +39489,31 @@
         <v>2.56</v>
       </c>
       <c r="AU186">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV186">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW186">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX186">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AY186">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AZ186">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="BA186">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB186">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC186">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD186">
         <v>0</v>
@@ -39692,31 +39695,31 @@
         <v>2.37</v>
       </c>
       <c r="AU187">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV187">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW187">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX187">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AY187">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ187">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="BA187">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB187">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC187">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD187">
         <v>2.52</v>
@@ -39756,6 +39759,212 @@
       </c>
       <c r="BP187">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7856952</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45746.45833333334</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188" t="s">
+        <v>78</v>
+      </c>
+      <c r="H188" t="s">
+        <v>81</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>113</v>
+      </c>
+      <c r="P188" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q188">
+        <v>2.63</v>
+      </c>
+      <c r="R188">
+        <v>2</v>
+      </c>
+      <c r="S188">
+        <v>5</v>
+      </c>
+      <c r="T188">
+        <v>1.5</v>
+      </c>
+      <c r="U188">
+        <v>2.5</v>
+      </c>
+      <c r="V188">
+        <v>3.5</v>
+      </c>
+      <c r="W188">
+        <v>1.29</v>
+      </c>
+      <c r="X188">
+        <v>11</v>
+      </c>
+      <c r="Y188">
+        <v>1.05</v>
+      </c>
+      <c r="Z188">
+        <v>1.71</v>
+      </c>
+      <c r="AA188">
+        <v>3.3</v>
+      </c>
+      <c r="AB188">
+        <v>4.7</v>
+      </c>
+      <c r="AC188">
+        <v>1.05</v>
+      </c>
+      <c r="AD188">
+        <v>6.65</v>
+      </c>
+      <c r="AE188">
+        <v>1.42</v>
+      </c>
+      <c r="AF188">
+        <v>2.56</v>
+      </c>
+      <c r="AG188">
+        <v>2.1</v>
+      </c>
+      <c r="AH188">
+        <v>1.61</v>
+      </c>
+      <c r="AI188">
+        <v>2.05</v>
+      </c>
+      <c r="AJ188">
+        <v>1.7</v>
+      </c>
+      <c r="AK188">
+        <v>1.23</v>
+      </c>
+      <c r="AL188">
+        <v>1.31</v>
+      </c>
+      <c r="AM188">
+        <v>1.85</v>
+      </c>
+      <c r="AN188">
+        <v>1.23</v>
+      </c>
+      <c r="AO188">
+        <v>0.46</v>
+      </c>
+      <c r="AP188">
+        <v>1.21</v>
+      </c>
+      <c r="AQ188">
+        <v>0.5</v>
+      </c>
+      <c r="AR188">
+        <v>1.32</v>
+      </c>
+      <c r="AS188">
+        <v>1</v>
+      </c>
+      <c r="AT188">
+        <v>2.32</v>
+      </c>
+      <c r="AU188">
+        <v>6</v>
+      </c>
+      <c r="AV188">
+        <v>3</v>
+      </c>
+      <c r="AW188">
+        <v>8</v>
+      </c>
+      <c r="AX188">
+        <v>3</v>
+      </c>
+      <c r="AY188">
+        <v>15</v>
+      </c>
+      <c r="AZ188">
+        <v>6</v>
+      </c>
+      <c r="BA188">
+        <v>8</v>
+      </c>
+      <c r="BB188">
+        <v>3</v>
+      </c>
+      <c r="BC188">
+        <v>11</v>
+      </c>
+      <c r="BD188">
+        <v>1.51</v>
+      </c>
+      <c r="BE188">
+        <v>8.4</v>
+      </c>
+      <c r="BF188">
+        <v>3.2</v>
+      </c>
+      <c r="BG188">
+        <v>1.44</v>
+      </c>
+      <c r="BH188">
+        <v>2.51</v>
+      </c>
+      <c r="BI188">
+        <v>1.81</v>
+      </c>
+      <c r="BJ188">
+        <v>1.89</v>
+      </c>
+      <c r="BK188">
+        <v>2.32</v>
+      </c>
+      <c r="BL188">
+        <v>1.51</v>
+      </c>
+      <c r="BM188">
+        <v>3.14</v>
+      </c>
+      <c r="BN188">
+        <v>1.27</v>
+      </c>
+      <c r="BO188">
+        <v>4</v>
+      </c>
+      <c r="BP188">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,12 @@
     <t>['31']</t>
   </si>
   <si>
+    <t>['22', '47']</t>
+  </si>
+  <si>
+    <t>['1', '16', '51', '82']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -875,6 +881,12 @@
   </si>
   <si>
     <t>['78']</t>
+  </si>
+  <si>
+    <t>['58', '66', '85']</t>
+  </si>
+  <si>
+    <t>['25', '75']</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1492,7 +1504,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1698,7 +1710,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -2316,7 +2328,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2600,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ7">
         <v>1.38</v>
@@ -2728,7 +2740,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3140,7 +3152,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3346,7 +3358,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3424,7 +3436,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -4248,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ15">
         <v>0.62</v>
@@ -4376,7 +4388,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4582,7 +4594,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4994,7 +5006,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5200,7 +5212,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5406,7 +5418,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5487,7 +5499,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR21">
         <v>1.23</v>
@@ -5612,7 +5624,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5693,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6024,7 +6036,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6230,7 +6242,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6514,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ26">
         <v>1.23</v>
@@ -6642,7 +6654,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q27">
         <v>3.75</v>
@@ -6929,7 +6941,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR28">
         <v>1.95</v>
@@ -7132,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ29">
         <v>1.21</v>
@@ -7260,7 +7272,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7341,7 +7353,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ30">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR30">
         <v>0.96</v>
@@ -7672,7 +7684,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -8084,7 +8096,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8290,7 +8302,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8908,7 +8920,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9114,7 +9126,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9398,7 +9410,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ40">
         <v>1.86</v>
@@ -9810,10 +9822,10 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ42">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR42">
         <v>1.99</v>
@@ -9938,7 +9950,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10144,7 +10156,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10762,7 +10774,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10968,7 +10980,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11174,7 +11186,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11255,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11792,7 +11804,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12204,7 +12216,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12282,7 +12294,7 @@
         <v>0.67</v>
       </c>
       <c r="AP54">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ54">
         <v>1.29</v>
@@ -12410,7 +12422,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12491,7 +12503,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ55">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR55">
         <v>1.16</v>
@@ -12822,7 +12834,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -12900,10 +12912,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR57">
         <v>1.84</v>
@@ -13028,7 +13040,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13234,7 +13246,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13852,7 +13864,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14058,7 +14070,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14264,7 +14276,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14548,7 +14560,7 @@
         <v>1.2</v>
       </c>
       <c r="AP65">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ65">
         <v>0.92</v>
@@ -14882,7 +14894,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15169,7 +15181,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ68">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
         <v>1.45</v>
@@ -15294,7 +15306,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15500,7 +15512,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15581,7 +15593,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ70">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR70">
         <v>1.11</v>
@@ -16118,7 +16130,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16402,7 +16414,7 @@
         <v>1.8</v>
       </c>
       <c r="AP74">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ74">
         <v>1.23</v>
@@ -16530,7 +16542,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16736,7 +16748,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17148,7 +17160,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17354,7 +17366,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17560,7 +17572,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17972,7 +17984,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18053,7 +18065,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ82">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR82">
         <v>1.27</v>
@@ -18178,7 +18190,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18259,7 +18271,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR83">
         <v>1.54</v>
@@ -18462,7 +18474,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ84">
         <v>1.77</v>
@@ -19002,7 +19014,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19286,7 +19298,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ88">
         <v>1.29</v>
@@ -19620,7 +19632,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19826,7 +19838,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -20032,7 +20044,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20316,7 +20328,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ93">
         <v>1.21</v>
@@ -20444,7 +20456,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20650,7 +20662,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20731,7 +20743,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR95">
         <v>1.27</v>
@@ -20856,7 +20868,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21143,7 +21155,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ97">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21268,7 +21280,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21474,7 +21486,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22585,7 +22597,7 @@
         <v>1</v>
       </c>
       <c r="AQ104">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR104">
         <v>1.19</v>
@@ -22791,7 +22803,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ105">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR105">
         <v>1.29</v>
@@ -23200,7 +23212,7 @@
         <v>0.86</v>
       </c>
       <c r="AP107">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -23946,7 +23958,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24024,7 +24036,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ111">
         <v>1.29</v>
@@ -24152,7 +24164,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24976,7 +24988,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25182,7 +25194,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25388,7 +25400,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25594,7 +25606,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25675,7 +25687,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR119">
         <v>1.85</v>
@@ -25800,7 +25812,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26084,7 +26096,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ121">
         <v>1.29</v>
@@ -26212,7 +26224,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26293,7 +26305,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ122">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR122">
         <v>1.28</v>
@@ -26418,7 +26430,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26624,7 +26636,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26908,7 +26920,7 @@
         <v>0.63</v>
       </c>
       <c r="AP125">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ125">
         <v>0.62</v>
@@ -27654,7 +27666,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27860,7 +27872,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28353,7 +28365,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR132">
         <v>1.43</v>
@@ -28890,7 +28902,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29096,7 +29108,7 @@
         <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29586,7 +29598,7 @@
         <v>1.44</v>
       </c>
       <c r="AP138">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ138">
         <v>1.23</v>
@@ -29714,7 +29726,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -30204,10 +30216,10 @@
         <v>2</v>
       </c>
       <c r="AP141">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ141">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR141">
         <v>1.93</v>
@@ -30332,7 +30344,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30538,7 +30550,7 @@
         <v>170</v>
       </c>
       <c r="P143" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -31156,7 +31168,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31980,7 +31992,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32061,7 +32073,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ150">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32186,7 +32198,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32264,7 +32276,7 @@
         <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ151">
         <v>1.23</v>
@@ -32473,7 +32485,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ152">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR152">
         <v>1.42</v>
@@ -32676,7 +32688,7 @@
         <v>0.9</v>
       </c>
       <c r="AP153">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ153">
         <v>0.92</v>
@@ -32804,7 +32816,7 @@
         <v>84</v>
       </c>
       <c r="P154" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33010,7 +33022,7 @@
         <v>147</v>
       </c>
       <c r="P155" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q155">
         <v>2.63</v>
@@ -33422,7 +33434,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33500,7 +33512,7 @@
         <v>1.82</v>
       </c>
       <c r="AP157">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ157">
         <v>1.86</v>
@@ -33628,7 +33640,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33834,7 +33846,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -34040,7 +34052,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34658,7 +34670,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35070,7 +35082,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35276,7 +35288,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35482,7 +35494,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35563,7 +35575,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ167">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR167">
         <v>1.13</v>
@@ -35688,7 +35700,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35894,7 +35906,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -35972,10 +35984,10 @@
         <v>2.36</v>
       </c>
       <c r="AP169">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ169">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR169">
         <v>1.94</v>
@@ -36100,7 +36112,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q170">
         <v>4</v>
@@ -36306,7 +36318,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36718,7 +36730,7 @@
         <v>122</v>
       </c>
       <c r="P173" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q173">
         <v>3.6</v>
@@ -37336,7 +37348,7 @@
         <v>84</v>
       </c>
       <c r="P176" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q176">
         <v>3.25</v>
@@ -37414,7 +37426,7 @@
         <v>2.17</v>
       </c>
       <c r="AP176">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ176">
         <v>2.23</v>
@@ -38032,7 +38044,7 @@
         <v>1.5</v>
       </c>
       <c r="AP179">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ179">
         <v>1.38</v>
@@ -38160,7 +38172,7 @@
         <v>195</v>
       </c>
       <c r="P180" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q180">
         <v>6.5</v>
@@ -38241,7 +38253,7 @@
         <v>1</v>
       </c>
       <c r="AQ180">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR180">
         <v>1.45</v>
@@ -38572,7 +38584,7 @@
         <v>196</v>
       </c>
       <c r="P182" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38653,7 +38665,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ182">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR182">
         <v>1.3</v>
@@ -38778,7 +38790,7 @@
         <v>197</v>
       </c>
       <c r="P183" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -38984,7 +38996,7 @@
         <v>198</v>
       </c>
       <c r="P184" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39301,13 +39313,13 @@
         <v>10</v>
       </c>
       <c r="BA185">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB185">
         <v>4</v>
       </c>
       <c r="BC185">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD185">
         <v>1.71</v>
@@ -39396,7 +39408,7 @@
         <v>84</v>
       </c>
       <c r="P186" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
@@ -39602,7 +39614,7 @@
         <v>200</v>
       </c>
       <c r="P187" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q187">
         <v>3.5</v>
@@ -39808,7 +39820,7 @@
         <v>113</v>
       </c>
       <c r="P188" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q188">
         <v>2.63</v>
@@ -39965,6 +39977,418 @@
       </c>
       <c r="BP188">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7856953</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45746.54166666666</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>75</v>
+      </c>
+      <c r="H189" t="s">
+        <v>71</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>2</v>
+      </c>
+      <c r="M189">
+        <v>3</v>
+      </c>
+      <c r="N189">
+        <v>5</v>
+      </c>
+      <c r="O189" t="s">
+        <v>201</v>
+      </c>
+      <c r="P189" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q189">
+        <v>2.75</v>
+      </c>
+      <c r="R189">
+        <v>2.1</v>
+      </c>
+      <c r="S189">
+        <v>4</v>
+      </c>
+      <c r="T189">
+        <v>1.44</v>
+      </c>
+      <c r="U189">
+        <v>2.63</v>
+      </c>
+      <c r="V189">
+        <v>3</v>
+      </c>
+      <c r="W189">
+        <v>1.36</v>
+      </c>
+      <c r="X189">
+        <v>9</v>
+      </c>
+      <c r="Y189">
+        <v>1.07</v>
+      </c>
+      <c r="Z189">
+        <v>1.95</v>
+      </c>
+      <c r="AA189">
+        <v>3.3</v>
+      </c>
+      <c r="AB189">
+        <v>3.7</v>
+      </c>
+      <c r="AC189">
+        <v>1.02</v>
+      </c>
+      <c r="AD189">
+        <v>7.8</v>
+      </c>
+      <c r="AE189">
+        <v>1.31</v>
+      </c>
+      <c r="AF189">
+        <v>3.02</v>
+      </c>
+      <c r="AG189">
+        <v>2</v>
+      </c>
+      <c r="AH189">
+        <v>1.67</v>
+      </c>
+      <c r="AI189">
+        <v>1.8</v>
+      </c>
+      <c r="AJ189">
+        <v>1.95</v>
+      </c>
+      <c r="AK189">
+        <v>1.33</v>
+      </c>
+      <c r="AL189">
+        <v>1.31</v>
+      </c>
+      <c r="AM189">
+        <v>1.63</v>
+      </c>
+      <c r="AN189">
+        <v>2.31</v>
+      </c>
+      <c r="AO189">
+        <v>2</v>
+      </c>
+      <c r="AP189">
+        <v>2.14</v>
+      </c>
+      <c r="AQ189">
+        <v>2.07</v>
+      </c>
+      <c r="AR189">
+        <v>2.06</v>
+      </c>
+      <c r="AS189">
+        <v>1.63</v>
+      </c>
+      <c r="AT189">
+        <v>3.69</v>
+      </c>
+      <c r="AU189">
+        <v>4</v>
+      </c>
+      <c r="AV189">
+        <v>5</v>
+      </c>
+      <c r="AW189">
+        <v>11</v>
+      </c>
+      <c r="AX189">
+        <v>5</v>
+      </c>
+      <c r="AY189">
+        <v>21</v>
+      </c>
+      <c r="AZ189">
+        <v>12</v>
+      </c>
+      <c r="BA189">
+        <v>3</v>
+      </c>
+      <c r="BB189">
+        <v>1</v>
+      </c>
+      <c r="BC189">
+        <v>4</v>
+      </c>
+      <c r="BD189">
+        <v>1.5</v>
+      </c>
+      <c r="BE189">
+        <v>8.5</v>
+      </c>
+      <c r="BF189">
+        <v>3.24</v>
+      </c>
+      <c r="BG189">
+        <v>1.41</v>
+      </c>
+      <c r="BH189">
+        <v>2.6</v>
+      </c>
+      <c r="BI189">
+        <v>1.76</v>
+      </c>
+      <c r="BJ189">
+        <v>1.95</v>
+      </c>
+      <c r="BK189">
+        <v>2.25</v>
+      </c>
+      <c r="BL189">
+        <v>1.54</v>
+      </c>
+      <c r="BM189">
+        <v>3.04</v>
+      </c>
+      <c r="BN189">
+        <v>1.29</v>
+      </c>
+      <c r="BO189">
+        <v>4.3</v>
+      </c>
+      <c r="BP189">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7856954</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45746.625</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190" t="s">
+        <v>80</v>
+      </c>
+      <c r="H190" t="s">
+        <v>73</v>
+      </c>
+      <c r="I190">
+        <v>2</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>3</v>
+      </c>
+      <c r="L190">
+        <v>4</v>
+      </c>
+      <c r="M190">
+        <v>2</v>
+      </c>
+      <c r="N190">
+        <v>6</v>
+      </c>
+      <c r="O190" t="s">
+        <v>202</v>
+      </c>
+      <c r="P190" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q190">
+        <v>2.38</v>
+      </c>
+      <c r="R190">
+        <v>2.1</v>
+      </c>
+      <c r="S190">
+        <v>5.5</v>
+      </c>
+      <c r="T190">
+        <v>1.5</v>
+      </c>
+      <c r="U190">
+        <v>2.5</v>
+      </c>
+      <c r="V190">
+        <v>3.4</v>
+      </c>
+      <c r="W190">
+        <v>1.3</v>
+      </c>
+      <c r="X190">
+        <v>10</v>
+      </c>
+      <c r="Y190">
+        <v>1.06</v>
+      </c>
+      <c r="Z190">
+        <v>1.63</v>
+      </c>
+      <c r="AA190">
+        <v>3.4</v>
+      </c>
+      <c r="AB190">
+        <v>5.3</v>
+      </c>
+      <c r="AC190">
+        <v>1.07</v>
+      </c>
+      <c r="AD190">
+        <v>7.5</v>
+      </c>
+      <c r="AE190">
+        <v>1.4</v>
+      </c>
+      <c r="AF190">
+        <v>2.91</v>
+      </c>
+      <c r="AG190">
+        <v>2.1</v>
+      </c>
+      <c r="AH190">
+        <v>1.6</v>
+      </c>
+      <c r="AI190">
+        <v>2.1</v>
+      </c>
+      <c r="AJ190">
+        <v>1.67</v>
+      </c>
+      <c r="AK190">
+        <v>1.16</v>
+      </c>
+      <c r="AL190">
+        <v>1.28</v>
+      </c>
+      <c r="AM190">
+        <v>2.1</v>
+      </c>
+      <c r="AN190">
+        <v>2.38</v>
+      </c>
+      <c r="AO190">
+        <v>1.54</v>
+      </c>
+      <c r="AP190">
+        <v>2.43</v>
+      </c>
+      <c r="AQ190">
+        <v>1.43</v>
+      </c>
+      <c r="AR190">
+        <v>2</v>
+      </c>
+      <c r="AS190">
+        <v>1.63</v>
+      </c>
+      <c r="AT190">
+        <v>3.63</v>
+      </c>
+      <c r="AU190">
+        <v>9</v>
+      </c>
+      <c r="AV190">
+        <v>3</v>
+      </c>
+      <c r="AW190">
+        <v>6</v>
+      </c>
+      <c r="AX190">
+        <v>5</v>
+      </c>
+      <c r="AY190">
+        <v>18</v>
+      </c>
+      <c r="AZ190">
+        <v>12</v>
+      </c>
+      <c r="BA190">
+        <v>3</v>
+      </c>
+      <c r="BB190">
+        <v>0</v>
+      </c>
+      <c r="BC190">
+        <v>3</v>
+      </c>
+      <c r="BD190">
+        <v>1.41</v>
+      </c>
+      <c r="BE190">
+        <v>8.5</v>
+      </c>
+      <c r="BF190">
+        <v>3.59</v>
+      </c>
+      <c r="BG190">
+        <v>1.56</v>
+      </c>
+      <c r="BH190">
+        <v>2.12</v>
+      </c>
+      <c r="BI190">
+        <v>1.92</v>
+      </c>
+      <c r="BJ190">
+        <v>1.88</v>
+      </c>
+      <c r="BK190">
+        <v>2.5</v>
+      </c>
+      <c r="BL190">
+        <v>1.4</v>
+      </c>
+      <c r="BM190">
+        <v>3.4</v>
+      </c>
+      <c r="BN190">
+        <v>1.23</v>
+      </c>
+      <c r="BO190">
+        <v>4.6</v>
+      </c>
+      <c r="BP190">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -625,6 +625,12 @@
     <t>['1', '16', '51', '82']</t>
   </si>
   <si>
+    <t>['28', '44', '80']</t>
+  </si>
+  <si>
+    <t>['61', '90+3']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -887,6 +893,9 @@
   </si>
   <si>
     <t>['25', '75']</t>
+  </si>
+  <si>
+    <t>['45', '78']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1513,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1710,7 +1719,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1791,7 +1800,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ3">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1994,10 +2003,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2328,7 +2337,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2615,7 +2624,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2740,7 +2749,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3152,7 +3161,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3358,7 +3367,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -4263,7 +4272,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ15">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4388,7 +4397,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4466,7 +4475,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ16">
         <v>2.23</v>
@@ -4594,7 +4603,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4672,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ17">
         <v>1.23</v>
@@ -4881,7 +4890,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -5006,7 +5015,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5084,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19">
         <v>1.77</v>
@@ -5212,7 +5221,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5293,7 +5302,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ20">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5418,7 +5427,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5624,7 +5633,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -5908,10 +5917,10 @@
         <v>0.5</v>
       </c>
       <c r="AP23">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ23">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR23">
         <v>0.92</v>
@@ -6036,7 +6045,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6242,7 +6251,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6654,7 +6663,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>3.75</v>
@@ -7272,7 +7281,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7556,7 +7565,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ31">
         <v>2.23</v>
@@ -7684,7 +7693,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7968,10 +7977,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ33">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR33">
         <v>0.97</v>
@@ -8096,7 +8105,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8177,7 +8186,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ34">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR34">
         <v>1.44</v>
@@ -8302,7 +8311,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8795,7 +8804,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ37">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR37">
         <v>1.17</v>
@@ -8920,7 +8929,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9126,7 +9135,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9950,7 +9959,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10028,10 +10037,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR43">
         <v>1.06</v>
@@ -10156,7 +10165,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10646,7 +10655,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
@@ -10774,7 +10783,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10855,7 +10864,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ47">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR47">
         <v>1.06</v>
@@ -10980,7 +10989,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11186,7 +11195,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11264,7 +11273,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49">
         <v>2.07</v>
@@ -11679,7 +11688,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ51">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR51">
         <v>1.35</v>
@@ -11804,7 +11813,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -12088,7 +12097,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ53">
         <v>1.23</v>
@@ -12216,7 +12225,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12422,7 +12431,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12706,10 +12715,10 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ56">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR56">
         <v>1.14</v>
@@ -12834,7 +12843,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13040,7 +13049,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13246,7 +13255,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13324,7 +13333,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59">
         <v>0.5</v>
@@ -13864,7 +13873,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -14070,7 +14079,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14151,7 +14160,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ63">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14276,7 +14285,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14563,7 +14572,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ65">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR65">
         <v>1.98</v>
@@ -14894,7 +14903,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -14972,7 +14981,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ67">
         <v>1.29</v>
@@ -15306,7 +15315,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15512,7 +15521,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -15590,7 +15599,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ70">
         <v>2.07</v>
@@ -15799,7 +15808,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ71">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR71">
         <v>1.51</v>
@@ -16130,7 +16139,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16542,7 +16551,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16623,7 +16632,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ75">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR75">
         <v>1.19</v>
@@ -16748,7 +16757,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16826,7 +16835,7 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ76">
         <v>1.21</v>
@@ -17160,7 +17169,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17366,7 +17375,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17447,7 +17456,7 @@
         <v>1</v>
       </c>
       <c r="AQ79">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17572,7 +17581,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17650,10 +17659,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ80">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR80">
         <v>1.08</v>
@@ -17856,7 +17865,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ81">
         <v>1.21</v>
@@ -17984,7 +17993,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18190,7 +18199,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -19014,7 +19023,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19092,7 +19101,7 @@
         <v>1.6</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ87">
         <v>1.23</v>
@@ -19632,7 +19641,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19838,7 +19847,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19919,7 +19928,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ91">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -20044,7 +20053,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20456,7 +20465,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20534,7 +20543,7 @@
         <v>1.83</v>
       </c>
       <c r="AP94">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94">
         <v>1.86</v>
@@ -20662,7 +20671,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20868,7 +20877,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -21280,7 +21289,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21358,7 +21367,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ98">
         <v>1.23</v>
@@ -21486,7 +21495,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21770,7 +21779,7 @@
         <v>1.43</v>
       </c>
       <c r="AP100">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ100">
         <v>1.77</v>
@@ -21979,7 +21988,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR101">
         <v>1.32</v>
@@ -22388,10 +22397,10 @@
         <v>1.29</v>
       </c>
       <c r="AP103">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ103">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR103">
         <v>1.47</v>
@@ -22594,7 +22603,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ104">
         <v>1.43</v>
@@ -23627,7 +23636,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ109">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR109">
         <v>1.74</v>
@@ -23958,7 +23967,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24164,7 +24173,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24860,10 +24869,10 @@
         <v>1.13</v>
       </c>
       <c r="AP115">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ115">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -24988,7 +24997,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25066,10 +25075,10 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ116">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25194,7 +25203,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25400,7 +25409,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25606,7 +25615,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25812,7 +25821,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -26224,7 +26233,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26430,7 +26439,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26508,7 +26517,7 @@
         <v>1.38</v>
       </c>
       <c r="AP123">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ123">
         <v>1.86</v>
@@ -26636,7 +26645,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26923,7 +26932,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ125">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR125">
         <v>1.95</v>
@@ -27666,7 +27675,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27872,7 +27881,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -27950,7 +27959,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ130">
         <v>1.23</v>
@@ -28159,7 +28168,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR131">
         <v>1.17</v>
@@ -28362,7 +28371,7 @@
         <v>2.44</v>
       </c>
       <c r="AP132">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ132">
         <v>2.07</v>
@@ -28902,7 +28911,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -29108,7 +29117,7 @@
         <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29189,7 +29198,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ136">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR136">
         <v>1.31</v>
@@ -29395,7 +29404,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ137">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR137">
         <v>1.4</v>
@@ -29726,7 +29735,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -29804,7 +29813,7 @@
         <v>0.89</v>
       </c>
       <c r="AP139">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ139">
         <v>1.29</v>
@@ -30344,7 +30353,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30425,7 +30434,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ142">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR142">
         <v>1.82</v>
@@ -30550,7 +30559,7 @@
         <v>170</v>
       </c>
       <c r="P143" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30834,7 +30843,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ144">
         <v>2.23</v>
@@ -31168,7 +31177,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31992,7 +32001,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32198,7 +32207,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32482,7 +32491,7 @@
         <v>1.9</v>
       </c>
       <c r="AP152">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ152">
         <v>1.43</v>
@@ -32691,7 +32700,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ153">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR153">
         <v>2.03</v>
@@ -32816,7 +32825,7 @@
         <v>84</v>
       </c>
       <c r="P154" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -32894,7 +32903,7 @@
         <v>0.8</v>
       </c>
       <c r="AP154">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ154">
         <v>1.29</v>
@@ -33022,7 +33031,7 @@
         <v>147</v>
       </c>
       <c r="P155" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q155">
         <v>2.63</v>
@@ -33103,7 +33112,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ155">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR155">
         <v>1.19</v>
@@ -33434,7 +33443,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33640,7 +33649,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33718,7 +33727,7 @@
         <v>1.27</v>
       </c>
       <c r="AP158">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ158">
         <v>1.29</v>
@@ -33846,7 +33855,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -34052,7 +34061,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34545,7 +34554,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ162">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -34670,7 +34679,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -34751,7 +34760,7 @@
         <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR163">
         <v>1.4</v>
@@ -34957,7 +34966,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ164">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR164">
         <v>1.26</v>
@@ -35082,7 +35091,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35288,7 +35297,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35366,7 +35375,7 @@
         <v>1.45</v>
       </c>
       <c r="AP166">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ166">
         <v>1.23</v>
@@ -35494,7 +35503,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35572,7 +35581,7 @@
         <v>1.73</v>
       </c>
       <c r="AP167">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ167">
         <v>1.43</v>
@@ -35700,7 +35709,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35906,7 +35915,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36112,7 +36121,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q170">
         <v>4</v>
@@ -36318,7 +36327,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36399,7 +36408,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ171">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR171">
         <v>1.27</v>
@@ -36730,7 +36739,7 @@
         <v>122</v>
       </c>
       <c r="P173" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q173">
         <v>3.6</v>
@@ -36808,7 +36817,7 @@
         <v>1.67</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ173">
         <v>1.86</v>
@@ -37348,7 +37357,7 @@
         <v>84</v>
       </c>
       <c r="P176" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q176">
         <v>3.25</v>
@@ -37838,7 +37847,7 @@
         <v>1.33</v>
       </c>
       <c r="AP178">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ178">
         <v>1.21</v>
@@ -38047,7 +38056,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ179">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR179">
         <v>1.95</v>
@@ -38172,7 +38181,7 @@
         <v>195</v>
       </c>
       <c r="P180" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q180">
         <v>6.5</v>
@@ -38456,7 +38465,7 @@
         <v>1.83</v>
       </c>
       <c r="AP181">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ181">
         <v>1.77</v>
@@ -38584,7 +38593,7 @@
         <v>196</v>
       </c>
       <c r="P182" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38790,7 +38799,7 @@
         <v>197</v>
       </c>
       <c r="P183" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -38871,7 +38880,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ183">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR183">
         <v>1.35</v>
@@ -38996,7 +39005,7 @@
         <v>198</v>
       </c>
       <c r="P184" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39408,7 +39417,7 @@
         <v>84</v>
       </c>
       <c r="P186" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
@@ -39614,7 +39623,7 @@
         <v>200</v>
       </c>
       <c r="P187" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q187">
         <v>3.5</v>
@@ -39820,7 +39829,7 @@
         <v>113</v>
       </c>
       <c r="P188" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q188">
         <v>2.63</v>
@@ -40026,7 +40035,7 @@
         <v>201</v>
       </c>
       <c r="P189" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40232,7 +40241,7 @@
         <v>202</v>
       </c>
       <c r="P190" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q190">
         <v>2.38</v>
@@ -40389,6 +40398,624 @@
       </c>
       <c r="BP190">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7856955</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F191">
+        <v>2</v>
+      </c>
+      <c r="G191" t="s">
+        <v>72</v>
+      </c>
+      <c r="H191" t="s">
+        <v>78</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>2</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>3</v>
+      </c>
+      <c r="O191" t="s">
+        <v>203</v>
+      </c>
+      <c r="P191" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q191">
+        <v>2.6</v>
+      </c>
+      <c r="R191">
+        <v>2.1</v>
+      </c>
+      <c r="S191">
+        <v>4.75</v>
+      </c>
+      <c r="T191">
+        <v>1.44</v>
+      </c>
+      <c r="U191">
+        <v>2.63</v>
+      </c>
+      <c r="V191">
+        <v>3.25</v>
+      </c>
+      <c r="W191">
+        <v>1.33</v>
+      </c>
+      <c r="X191">
+        <v>9</v>
+      </c>
+      <c r="Y191">
+        <v>1.07</v>
+      </c>
+      <c r="Z191">
+        <v>2</v>
+      </c>
+      <c r="AA191">
+        <v>3</v>
+      </c>
+      <c r="AB191">
+        <v>3.9</v>
+      </c>
+      <c r="AC191">
+        <v>1.06</v>
+      </c>
+      <c r="AD191">
+        <v>8</v>
+      </c>
+      <c r="AE191">
+        <v>1.36</v>
+      </c>
+      <c r="AF191">
+        <v>2.95</v>
+      </c>
+      <c r="AG191">
+        <v>2.1</v>
+      </c>
+      <c r="AH191">
+        <v>1.61</v>
+      </c>
+      <c r="AI191">
+        <v>1.95</v>
+      </c>
+      <c r="AJ191">
+        <v>1.8</v>
+      </c>
+      <c r="AK191">
+        <v>1.23</v>
+      </c>
+      <c r="AL191">
+        <v>1.3</v>
+      </c>
+      <c r="AM191">
+        <v>1.85</v>
+      </c>
+      <c r="AN191">
+        <v>1</v>
+      </c>
+      <c r="AO191">
+        <v>0.92</v>
+      </c>
+      <c r="AP191">
+        <v>1.14</v>
+      </c>
+      <c r="AQ191">
+        <v>0.86</v>
+      </c>
+      <c r="AR191">
+        <v>1.2</v>
+      </c>
+      <c r="AS191">
+        <v>1.27</v>
+      </c>
+      <c r="AT191">
+        <v>2.47</v>
+      </c>
+      <c r="AU191">
+        <v>9</v>
+      </c>
+      <c r="AV191">
+        <v>0</v>
+      </c>
+      <c r="AW191">
+        <v>11</v>
+      </c>
+      <c r="AX191">
+        <v>8</v>
+      </c>
+      <c r="AY191">
+        <v>24</v>
+      </c>
+      <c r="AZ191">
+        <v>10</v>
+      </c>
+      <c r="BA191">
+        <v>3</v>
+      </c>
+      <c r="BB191">
+        <v>5</v>
+      </c>
+      <c r="BC191">
+        <v>8</v>
+      </c>
+      <c r="BD191">
+        <v>1.37</v>
+      </c>
+      <c r="BE191">
+        <v>9.1</v>
+      </c>
+      <c r="BF191">
+        <v>3.94</v>
+      </c>
+      <c r="BG191">
+        <v>1.44</v>
+      </c>
+      <c r="BH191">
+        <v>2.5</v>
+      </c>
+      <c r="BI191">
+        <v>1.8</v>
+      </c>
+      <c r="BJ191">
+        <v>1.85</v>
+      </c>
+      <c r="BK191">
+        <v>2.4</v>
+      </c>
+      <c r="BL191">
+        <v>1.47</v>
+      </c>
+      <c r="BM191">
+        <v>3.4</v>
+      </c>
+      <c r="BN191">
+        <v>1.26</v>
+      </c>
+      <c r="BO191">
+        <v>3.9</v>
+      </c>
+      <c r="BP191">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7856956</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F192">
+        <v>2</v>
+      </c>
+      <c r="G192" t="s">
+        <v>82</v>
+      </c>
+      <c r="H192" t="s">
+        <v>77</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>2</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>2</v>
+      </c>
+      <c r="O192" t="s">
+        <v>204</v>
+      </c>
+      <c r="P192" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q192">
+        <v>2.4</v>
+      </c>
+      <c r="R192">
+        <v>2.1</v>
+      </c>
+      <c r="S192">
+        <v>5</v>
+      </c>
+      <c r="T192">
+        <v>1.44</v>
+      </c>
+      <c r="U192">
+        <v>2.63</v>
+      </c>
+      <c r="V192">
+        <v>3</v>
+      </c>
+      <c r="W192">
+        <v>1.36</v>
+      </c>
+      <c r="X192">
+        <v>9</v>
+      </c>
+      <c r="Y192">
+        <v>1.07</v>
+      </c>
+      <c r="Z192">
+        <v>1.8</v>
+      </c>
+      <c r="AA192">
+        <v>3.25</v>
+      </c>
+      <c r="AB192">
+        <v>5.25</v>
+      </c>
+      <c r="AC192">
+        <v>1.06</v>
+      </c>
+      <c r="AD192">
+        <v>8</v>
+      </c>
+      <c r="AE192">
+        <v>1.33</v>
+      </c>
+      <c r="AF192">
+        <v>3.1</v>
+      </c>
+      <c r="AG192">
+        <v>2.05</v>
+      </c>
+      <c r="AH192">
+        <v>1.75</v>
+      </c>
+      <c r="AI192">
+        <v>1.91</v>
+      </c>
+      <c r="AJ192">
+        <v>1.91</v>
+      </c>
+      <c r="AK192">
+        <v>1.19</v>
+      </c>
+      <c r="AL192">
+        <v>1.26</v>
+      </c>
+      <c r="AM192">
+        <v>2.05</v>
+      </c>
+      <c r="AN192">
+        <v>2.08</v>
+      </c>
+      <c r="AO192">
+        <v>1.38</v>
+      </c>
+      <c r="AP192">
+        <v>2.14</v>
+      </c>
+      <c r="AQ192">
+        <v>1.29</v>
+      </c>
+      <c r="AR192">
+        <v>1.49</v>
+      </c>
+      <c r="AS192">
+        <v>1.03</v>
+      </c>
+      <c r="AT192">
+        <v>2.52</v>
+      </c>
+      <c r="AU192">
+        <v>12</v>
+      </c>
+      <c r="AV192">
+        <v>2</v>
+      </c>
+      <c r="AW192">
+        <v>12</v>
+      </c>
+      <c r="AX192">
+        <v>5</v>
+      </c>
+      <c r="AY192">
+        <v>24</v>
+      </c>
+      <c r="AZ192">
+        <v>7</v>
+      </c>
+      <c r="BA192">
+        <v>9</v>
+      </c>
+      <c r="BB192">
+        <v>2</v>
+      </c>
+      <c r="BC192">
+        <v>11</v>
+      </c>
+      <c r="BD192">
+        <v>1.39</v>
+      </c>
+      <c r="BE192">
+        <v>9</v>
+      </c>
+      <c r="BF192">
+        <v>3.8</v>
+      </c>
+      <c r="BG192">
+        <v>1.39</v>
+      </c>
+      <c r="BH192">
+        <v>2.65</v>
+      </c>
+      <c r="BI192">
+        <v>1.72</v>
+      </c>
+      <c r="BJ192">
+        <v>1.93</v>
+      </c>
+      <c r="BK192">
+        <v>2.25</v>
+      </c>
+      <c r="BL192">
+        <v>1.53</v>
+      </c>
+      <c r="BM192">
+        <v>3.2</v>
+      </c>
+      <c r="BN192">
+        <v>1.29</v>
+      </c>
+      <c r="BO192">
+        <v>4.05</v>
+      </c>
+      <c r="BP192">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7856957</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45752.58333333334</v>
+      </c>
+      <c r="F193">
+        <v>2</v>
+      </c>
+      <c r="G193" t="s">
+        <v>81</v>
+      </c>
+      <c r="H193" t="s">
+        <v>83</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>2</v>
+      </c>
+      <c r="N193">
+        <v>2</v>
+      </c>
+      <c r="O193" t="s">
+        <v>84</v>
+      </c>
+      <c r="P193" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q193">
+        <v>4.75</v>
+      </c>
+      <c r="R193">
+        <v>2</v>
+      </c>
+      <c r="S193">
+        <v>2.75</v>
+      </c>
+      <c r="T193">
+        <v>1.5</v>
+      </c>
+      <c r="U193">
+        <v>2.5</v>
+      </c>
+      <c r="V193">
+        <v>3.5</v>
+      </c>
+      <c r="W193">
+        <v>1.29</v>
+      </c>
+      <c r="X193">
+        <v>11</v>
+      </c>
+      <c r="Y193">
+        <v>1.05</v>
+      </c>
+      <c r="Z193">
+        <v>3</v>
+      </c>
+      <c r="AA193">
+        <v>3</v>
+      </c>
+      <c r="AB193">
+        <v>2.35</v>
+      </c>
+      <c r="AC193">
+        <v>1.07</v>
+      </c>
+      <c r="AD193">
+        <v>7.5</v>
+      </c>
+      <c r="AE193">
+        <v>1.42</v>
+      </c>
+      <c r="AF193">
+        <v>2.75</v>
+      </c>
+      <c r="AG193">
+        <v>2.2</v>
+      </c>
+      <c r="AH193">
+        <v>1.55</v>
+      </c>
+      <c r="AI193">
+        <v>2</v>
+      </c>
+      <c r="AJ193">
+        <v>1.75</v>
+      </c>
+      <c r="AK193">
+        <v>1.75</v>
+      </c>
+      <c r="AL193">
+        <v>1.31</v>
+      </c>
+      <c r="AM193">
+        <v>1.26</v>
+      </c>
+      <c r="AN193">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO193">
+        <v>0.62</v>
+      </c>
+      <c r="AP193">
+        <v>0.64</v>
+      </c>
+      <c r="AQ193">
+        <v>0.79</v>
+      </c>
+      <c r="AR193">
+        <v>1.11</v>
+      </c>
+      <c r="AS193">
+        <v>1.02</v>
+      </c>
+      <c r="AT193">
+        <v>2.13</v>
+      </c>
+      <c r="AU193">
+        <v>2</v>
+      </c>
+      <c r="AV193">
+        <v>6</v>
+      </c>
+      <c r="AW193">
+        <v>3</v>
+      </c>
+      <c r="AX193">
+        <v>9</v>
+      </c>
+      <c r="AY193">
+        <v>5</v>
+      </c>
+      <c r="AZ193">
+        <v>17</v>
+      </c>
+      <c r="BA193">
+        <v>1</v>
+      </c>
+      <c r="BB193">
+        <v>4</v>
+      </c>
+      <c r="BC193">
+        <v>5</v>
+      </c>
+      <c r="BD193">
+        <v>2.48</v>
+      </c>
+      <c r="BE193">
+        <v>7.3</v>
+      </c>
+      <c r="BF193">
+        <v>1.81</v>
+      </c>
+      <c r="BG193">
+        <v>1.39</v>
+      </c>
+      <c r="BH193">
+        <v>2.7</v>
+      </c>
+      <c r="BI193">
+        <v>1.72</v>
+      </c>
+      <c r="BJ193">
+        <v>1.93</v>
+      </c>
+      <c r="BK193">
+        <v>2.25</v>
+      </c>
+      <c r="BL193">
+        <v>1.53</v>
+      </c>
+      <c r="BM193">
+        <v>3.1</v>
+      </c>
+      <c r="BN193">
+        <v>1.3</v>
+      </c>
+      <c r="BO193">
+        <v>3.8</v>
+      </c>
+      <c r="BP193">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,12 @@
     <t>['61', '90+3']</t>
   </si>
   <si>
+    <t>['5', '11']</t>
+  </si>
+  <si>
+    <t>['17', '80', '88']</t>
+  </si>
+  <si>
     <t>['13', '73']</t>
   </si>
   <si>
@@ -896,6 +902,9 @@
   </si>
   <si>
     <t>['45', '78']</t>
+  </si>
+  <si>
+    <t>['47']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1522,7 @@
         <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q2">
         <v>8.5</v>
@@ -1591,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1719,7 +1728,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q3">
         <v>1.57</v>
@@ -1797,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3">
         <v>0.86</v>
@@ -2209,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ5">
         <v>1.23</v>
@@ -2337,7 +2346,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2749,7 +2758,7 @@
         <v>84</v>
       </c>
       <c r="P8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -3161,7 +3170,7 @@
         <v>84</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3367,7 +3376,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>1.45</v>
@@ -3857,10 +3866,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ13">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR13">
         <v>1.83</v>
@@ -4063,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ14">
         <v>1.29</v>
@@ -4397,7 +4406,7 @@
         <v>84</v>
       </c>
       <c r="P16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q16">
         <v>8.5</v>
@@ -4478,7 +4487,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ16">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4603,7 +4612,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5015,7 +5024,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -5096,7 +5105,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ19">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR19">
         <v>1.38</v>
@@ -5221,7 +5230,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -5299,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ20">
         <v>1.29</v>
@@ -5427,7 +5436,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -5633,7 +5642,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -6045,7 +6054,7 @@
         <v>98</v>
       </c>
       <c r="P24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6251,7 +6260,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6538,7 +6547,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ26">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR26">
         <v>1.48</v>
@@ -6663,7 +6672,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q27">
         <v>3.75</v>
@@ -6947,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
         <v>1.43</v>
@@ -7281,7 +7290,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q30">
         <v>7.5</v>
@@ -7359,7 +7368,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>2.07</v>
@@ -7568,7 +7577,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ31">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR31">
         <v>1.29</v>
@@ -7693,7 +7702,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -8105,7 +8114,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>1.57</v>
@@ -8183,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ34">
         <v>0.86</v>
@@ -8311,7 +8320,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8598,7 +8607,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR36">
         <v>2.14</v>
@@ -8801,7 +8810,7 @@
         <v>0.67</v>
       </c>
       <c r="AP37">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ37">
         <v>0.79</v>
@@ -8929,7 +8938,7 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -9135,7 +9144,7 @@
         <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9216,7 +9225,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ39">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -9625,7 +9634,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ41">
         <v>1.29</v>
@@ -9959,7 +9968,7 @@
         <v>113</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10165,7 +10174,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10452,7 +10461,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ45">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10783,7 +10792,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10989,7 +10998,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11195,7 +11204,7 @@
         <v>84</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q49">
         <v>7</v>
@@ -11479,10 +11488,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ50">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR50">
         <v>1.74</v>
@@ -11685,7 +11694,7 @@
         <v>0.75</v>
       </c>
       <c r="AP51">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ51">
         <v>0.86</v>
@@ -11813,7 +11822,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
@@ -11894,7 +11903,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ52">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR52">
         <v>1.4</v>
@@ -12225,7 +12234,7 @@
         <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>1.73</v>
@@ -12431,7 +12440,7 @@
         <v>84</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12843,7 +12852,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13049,7 +13058,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>3</v>
@@ -13255,7 +13264,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>2.75</v>
@@ -13542,7 +13551,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ60">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR60">
         <v>1.32</v>
@@ -13748,7 +13757,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ61">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR61">
         <v>1.69</v>
@@ -13873,7 +13882,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13951,7 +13960,7 @@
         <v>1.75</v>
       </c>
       <c r="AP62">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ62">
         <v>1.29</v>
@@ -14079,7 +14088,7 @@
         <v>104</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>1.73</v>
@@ -14157,7 +14166,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ63">
         <v>1.29</v>
@@ -14285,7 +14294,7 @@
         <v>84</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -14778,7 +14787,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR66">
         <v>1.31</v>
@@ -14903,7 +14912,7 @@
         <v>126</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -15187,7 +15196,7 @@
         <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ68">
         <v>1.43</v>
@@ -15315,7 +15324,7 @@
         <v>84</v>
       </c>
       <c r="P69" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -15396,7 +15405,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ69">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15521,7 +15530,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>7.5</v>
@@ -16139,7 +16148,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>3.5</v>
@@ -16551,7 +16560,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16757,7 +16766,7 @@
         <v>132</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17041,7 +17050,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ77">
         <v>0.5</v>
@@ -17169,7 +17178,7 @@
         <v>133</v>
       </c>
       <c r="P78" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17247,10 +17256,10 @@
         <v>1.4</v>
       </c>
       <c r="AP78">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ78">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR78">
         <v>1.72</v>
@@ -17375,7 +17384,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17581,7 +17590,7 @@
         <v>135</v>
       </c>
       <c r="P80" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17993,7 +18002,7 @@
         <v>136</v>
       </c>
       <c r="P82" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q82">
         <v>6</v>
@@ -18199,7 +18208,7 @@
         <v>137</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18486,7 +18495,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ84">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR84">
         <v>2.03</v>
@@ -18895,7 +18904,7 @@
         <v>0.83</v>
       </c>
       <c r="AP86">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ86">
         <v>0.5</v>
@@ -19023,7 +19032,7 @@
         <v>140</v>
       </c>
       <c r="P87" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19104,7 +19113,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ87">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR87">
         <v>1.2</v>
@@ -19641,7 +19650,7 @@
         <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q90">
         <v>7</v>
@@ -19722,7 +19731,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ90">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19847,7 +19856,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q91">
         <v>1.67</v>
@@ -19925,7 +19934,7 @@
         <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ91">
         <v>0.79</v>
@@ -20053,7 +20062,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>2.05</v>
@@ -20131,7 +20140,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ92">
         <v>1.86</v>
@@ -20465,7 +20474,7 @@
         <v>146</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20671,7 +20680,7 @@
         <v>147</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q95">
         <v>8</v>
@@ -20877,7 +20886,7 @@
         <v>148</v>
       </c>
       <c r="P96" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q96">
         <v>7</v>
@@ -20958,7 +20967,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ96">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21289,7 +21298,7 @@
         <v>84</v>
       </c>
       <c r="P98" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21370,7 +21379,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ98">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR98">
         <v>1.1</v>
@@ -21495,7 +21504,7 @@
         <v>149</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21782,7 +21791,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ100">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR100">
         <v>1.18</v>
@@ -22191,7 +22200,7 @@
         <v>1.29</v>
       </c>
       <c r="AP102">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ102">
         <v>1.23</v>
@@ -23018,7 +23027,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -23430,7 +23439,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ108">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR108">
         <v>1.22</v>
@@ -23633,7 +23642,7 @@
         <v>0.71</v>
       </c>
       <c r="AP109">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ109">
         <v>0.79</v>
@@ -23839,7 +23848,7 @@
         <v>1.57</v>
       </c>
       <c r="AP110">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ110">
         <v>1.86</v>
@@ -23967,7 +23976,7 @@
         <v>154</v>
       </c>
       <c r="P111" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q111">
         <v>1.57</v>
@@ -24173,7 +24182,7 @@
         <v>155</v>
       </c>
       <c r="P112" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24997,7 +25006,7 @@
         <v>84</v>
       </c>
       <c r="P116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25203,7 +25212,7 @@
         <v>159</v>
       </c>
       <c r="P117" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q117">
         <v>8.5</v>
@@ -25281,10 +25290,10 @@
         <v>1.63</v>
       </c>
       <c r="AP117">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ117">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25409,7 +25418,7 @@
         <v>84</v>
       </c>
       <c r="P118" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25615,7 +25624,7 @@
         <v>160</v>
       </c>
       <c r="P119" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q119">
         <v>3.1</v>
@@ -25693,7 +25702,7 @@
         <v>2.75</v>
       </c>
       <c r="AP119">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ119">
         <v>2.07</v>
@@ -25821,7 +25830,7 @@
         <v>84</v>
       </c>
       <c r="P120" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q120">
         <v>8</v>
@@ -25902,7 +25911,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ120">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR120">
         <v>1.23</v>
@@ -26233,7 +26242,7 @@
         <v>162</v>
       </c>
       <c r="P122" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>7</v>
@@ -26439,7 +26448,7 @@
         <v>84</v>
       </c>
       <c r="P123" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q123">
         <v>4.33</v>
@@ -26645,7 +26654,7 @@
         <v>163</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>1.62</v>
@@ -26723,7 +26732,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ124">
         <v>1.21</v>
@@ -27138,7 +27147,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ126">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27675,7 +27684,7 @@
         <v>108</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>7</v>
@@ -27756,7 +27765,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ129">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR129">
         <v>1.26</v>
@@ -27881,7 +27890,7 @@
         <v>104</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28577,10 +28586,10 @@
         <v>1.78</v>
       </c>
       <c r="AP133">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ133">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR133">
         <v>1.91</v>
@@ -28911,7 +28920,7 @@
         <v>84</v>
       </c>
       <c r="P135" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
@@ -28989,7 +28998,7 @@
         <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ135">
         <v>1.86</v>
@@ -29117,7 +29126,7 @@
         <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29610,7 +29619,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ138">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR138">
         <v>2.02</v>
@@ -29735,7 +29744,7 @@
         <v>84</v>
       </c>
       <c r="P139" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q139">
         <v>5</v>
@@ -30019,7 +30028,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ140">
         <v>1.29</v>
@@ -30353,7 +30362,7 @@
         <v>172</v>
       </c>
       <c r="P142" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30431,7 +30440,7 @@
         <v>1.5</v>
       </c>
       <c r="AP142">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ142">
         <v>1.29</v>
@@ -30559,7 +30568,7 @@
         <v>170</v>
       </c>
       <c r="P143" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q143">
         <v>3.25</v>
@@ -30846,7 +30855,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ144">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR144">
         <v>1.16</v>
@@ -31177,7 +31186,7 @@
         <v>136</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31255,10 +31264,10 @@
         <v>1.6</v>
       </c>
       <c r="AP146">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR146">
         <v>1.73</v>
@@ -31873,10 +31882,10 @@
         <v>1.3</v>
       </c>
       <c r="AP149">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ149">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR149">
         <v>1.24</v>
@@ -32001,7 +32010,7 @@
         <v>84</v>
       </c>
       <c r="P150" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q150">
         <v>5.5</v>
@@ -32207,7 +32216,7 @@
         <v>173</v>
       </c>
       <c r="P151" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q151">
         <v>1.8</v>
@@ -32825,7 +32834,7 @@
         <v>84</v>
       </c>
       <c r="P154" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33031,7 +33040,7 @@
         <v>147</v>
       </c>
       <c r="P155" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q155">
         <v>2.63</v>
@@ -33443,7 +33452,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q157">
         <v>1.73</v>
@@ -33649,7 +33658,7 @@
         <v>178</v>
       </c>
       <c r="P158" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q158">
         <v>4.33</v>
@@ -33855,7 +33864,7 @@
         <v>179</v>
       </c>
       <c r="P159" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q159">
         <v>1.73</v>
@@ -33933,7 +33942,7 @@
         <v>1.45</v>
       </c>
       <c r="AP159">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ159">
         <v>1.21</v>
@@ -34061,7 +34070,7 @@
         <v>84</v>
       </c>
       <c r="P160" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q160">
         <v>13</v>
@@ -34142,7 +34151,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ160">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR160">
         <v>1.33</v>
@@ -34345,7 +34354,7 @@
         <v>0.55</v>
       </c>
       <c r="AP161">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
@@ -34679,7 +34688,7 @@
         <v>182</v>
       </c>
       <c r="P163" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>3.1</v>
@@ -35091,7 +35100,7 @@
         <v>184</v>
       </c>
       <c r="P165" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35169,7 +35178,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ165">
         <v>1.29</v>
@@ -35297,7 +35306,7 @@
         <v>185</v>
       </c>
       <c r="P166" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q166">
         <v>2.2</v>
@@ -35378,7 +35387,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ166">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR166">
         <v>1.46</v>
@@ -35503,7 +35512,7 @@
         <v>186</v>
       </c>
       <c r="P167" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q167">
         <v>9</v>
@@ -35709,7 +35718,7 @@
         <v>84</v>
       </c>
       <c r="P168" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q168">
         <v>7</v>
@@ -35790,7 +35799,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ168">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR168">
         <v>1.45</v>
@@ -35915,7 +35924,7 @@
         <v>187</v>
       </c>
       <c r="P169" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36121,7 +36130,7 @@
         <v>188</v>
       </c>
       <c r="P170" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q170">
         <v>4</v>
@@ -36199,7 +36208,7 @@
         <v>1.17</v>
       </c>
       <c r="AP170">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AQ170">
         <v>1.29</v>
@@ -36327,7 +36336,7 @@
         <v>189</v>
       </c>
       <c r="P171" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36611,10 +36620,10 @@
         <v>1.33</v>
       </c>
       <c r="AP172">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ172">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR172">
         <v>1.91</v>
@@ -36739,7 +36748,7 @@
         <v>122</v>
       </c>
       <c r="P173" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q173">
         <v>3.6</v>
@@ -37229,7 +37238,7 @@
         <v>1.33</v>
       </c>
       <c r="AP175">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ175">
         <v>1.23</v>
@@ -37357,7 +37366,7 @@
         <v>84</v>
       </c>
       <c r="P176" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q176">
         <v>3.25</v>
@@ -37438,7 +37447,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ176">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AR176">
         <v>2.18</v>
@@ -38181,7 +38190,7 @@
         <v>195</v>
       </c>
       <c r="P180" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q180">
         <v>6.5</v>
@@ -38468,7 +38477,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ181">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR181">
         <v>1.55</v>
@@ -38593,7 +38602,7 @@
         <v>196</v>
       </c>
       <c r="P182" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38799,7 +38808,7 @@
         <v>197</v>
       </c>
       <c r="P183" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39005,7 +39014,7 @@
         <v>198</v>
       </c>
       <c r="P184" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39417,7 +39426,7 @@
         <v>84</v>
       </c>
       <c r="P186" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
@@ -39623,7 +39632,7 @@
         <v>200</v>
       </c>
       <c r="P187" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q187">
         <v>3.5</v>
@@ -39829,7 +39838,7 @@
         <v>113</v>
       </c>
       <c r="P188" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q188">
         <v>2.63</v>
@@ -40035,7 +40044,7 @@
         <v>201</v>
       </c>
       <c r="P189" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40241,7 +40250,7 @@
         <v>202</v>
       </c>
       <c r="P190" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q190">
         <v>2.38</v>
@@ -40859,7 +40868,7 @@
         <v>84</v>
       </c>
       <c r="P193" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q193">
         <v>4.75</v>
@@ -41016,6 +41025,624 @@
       </c>
       <c r="BP193">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7856958</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45753.45833333334</v>
+      </c>
+      <c r="F194">
+        <v>2</v>
+      </c>
+      <c r="G194" t="s">
+        <v>70</v>
+      </c>
+      <c r="H194" t="s">
+        <v>76</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194" t="s">
+        <v>84</v>
+      </c>
+      <c r="P194" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q194">
+        <v>3.2</v>
+      </c>
+      <c r="R194">
+        <v>1.91</v>
+      </c>
+      <c r="S194">
+        <v>4.33</v>
+      </c>
+      <c r="T194">
+        <v>1.62</v>
+      </c>
+      <c r="U194">
+        <v>2.2</v>
+      </c>
+      <c r="V194">
+        <v>4</v>
+      </c>
+      <c r="W194">
+        <v>1.22</v>
+      </c>
+      <c r="X194">
+        <v>13</v>
+      </c>
+      <c r="Y194">
+        <v>1.04</v>
+      </c>
+      <c r="Z194">
+        <v>2.35</v>
+      </c>
+      <c r="AA194">
+        <v>2.9</v>
+      </c>
+      <c r="AB194">
+        <v>3.1</v>
+      </c>
+      <c r="AC194">
+        <v>1.05</v>
+      </c>
+      <c r="AD194">
+        <v>6.5</v>
+      </c>
+      <c r="AE194">
+        <v>1.5</v>
+      </c>
+      <c r="AF194">
+        <v>2.3</v>
+      </c>
+      <c r="AG194">
+        <v>2.4</v>
+      </c>
+      <c r="AH194">
+        <v>1.46</v>
+      </c>
+      <c r="AI194">
+        <v>2.1</v>
+      </c>
+      <c r="AJ194">
+        <v>1.67</v>
+      </c>
+      <c r="AK194">
+        <v>1.3</v>
+      </c>
+      <c r="AL194">
+        <v>1.4</v>
+      </c>
+      <c r="AM194">
+        <v>1.57</v>
+      </c>
+      <c r="AN194">
+        <v>0.46</v>
+      </c>
+      <c r="AO194">
+        <v>1.23</v>
+      </c>
+      <c r="AP194">
+        <v>0.5</v>
+      </c>
+      <c r="AQ194">
+        <v>1.21</v>
+      </c>
+      <c r="AR194">
+        <v>1.24</v>
+      </c>
+      <c r="AS194">
+        <v>0.96</v>
+      </c>
+      <c r="AT194">
+        <v>2.2</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>3</v>
+      </c>
+      <c r="AW194">
+        <v>9</v>
+      </c>
+      <c r="AX194">
+        <v>4</v>
+      </c>
+      <c r="AY194">
+        <v>15</v>
+      </c>
+      <c r="AZ194">
+        <v>9</v>
+      </c>
+      <c r="BA194">
+        <v>3</v>
+      </c>
+      <c r="BB194">
+        <v>2</v>
+      </c>
+      <c r="BC194">
+        <v>5</v>
+      </c>
+      <c r="BD194">
+        <v>1.76</v>
+      </c>
+      <c r="BE194">
+        <v>6.1</v>
+      </c>
+      <c r="BF194">
+        <v>2.33</v>
+      </c>
+      <c r="BG194">
+        <v>1.6</v>
+      </c>
+      <c r="BH194">
+        <v>2.06</v>
+      </c>
+      <c r="BI194">
+        <v>2.02</v>
+      </c>
+      <c r="BJ194">
+        <v>1.63</v>
+      </c>
+      <c r="BK194">
+        <v>2.63</v>
+      </c>
+      <c r="BL194">
+        <v>1.37</v>
+      </c>
+      <c r="BM194">
+        <v>3.55</v>
+      </c>
+      <c r="BN194">
+        <v>1.21</v>
+      </c>
+      <c r="BO194">
+        <v>4.8</v>
+      </c>
+      <c r="BP194">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7856959</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45753.5625</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" t="s">
+        <v>71</v>
+      </c>
+      <c r="H195" t="s">
+        <v>80</v>
+      </c>
+      <c r="I195">
+        <v>2</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>1</v>
+      </c>
+      <c r="N195">
+        <v>3</v>
+      </c>
+      <c r="O195" t="s">
+        <v>205</v>
+      </c>
+      <c r="P195" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q195">
+        <v>3.4</v>
+      </c>
+      <c r="R195">
+        <v>2.05</v>
+      </c>
+      <c r="S195">
+        <v>3.4</v>
+      </c>
+      <c r="T195">
+        <v>1.44</v>
+      </c>
+      <c r="U195">
+        <v>2.63</v>
+      </c>
+      <c r="V195">
+        <v>3.25</v>
+      </c>
+      <c r="W195">
+        <v>1.33</v>
+      </c>
+      <c r="X195">
+        <v>10</v>
+      </c>
+      <c r="Y195">
+        <v>1.06</v>
+      </c>
+      <c r="Z195">
+        <v>2.65</v>
+      </c>
+      <c r="AA195">
+        <v>2.95</v>
+      </c>
+      <c r="AB195">
+        <v>2.65</v>
+      </c>
+      <c r="AC195">
+        <v>1.01</v>
+      </c>
+      <c r="AD195">
+        <v>8.4</v>
+      </c>
+      <c r="AE195">
+        <v>1.32</v>
+      </c>
+      <c r="AF195">
+        <v>2.97</v>
+      </c>
+      <c r="AG195">
+        <v>2.05</v>
+      </c>
+      <c r="AH195">
+        <v>1.65</v>
+      </c>
+      <c r="AI195">
+        <v>1.8</v>
+      </c>
+      <c r="AJ195">
+        <v>1.95</v>
+      </c>
+      <c r="AK195">
+        <v>1.5</v>
+      </c>
+      <c r="AL195">
+        <v>1.35</v>
+      </c>
+      <c r="AM195">
+        <v>1.44</v>
+      </c>
+      <c r="AN195">
+        <v>1.54</v>
+      </c>
+      <c r="AO195">
+        <v>2.23</v>
+      </c>
+      <c r="AP195">
+        <v>1.64</v>
+      </c>
+      <c r="AQ195">
+        <v>2.07</v>
+      </c>
+      <c r="AR195">
+        <v>1.78</v>
+      </c>
+      <c r="AS195">
+        <v>1.82</v>
+      </c>
+      <c r="AT195">
+        <v>3.6</v>
+      </c>
+      <c r="AU195">
+        <v>3</v>
+      </c>
+      <c r="AV195">
+        <v>2</v>
+      </c>
+      <c r="AW195">
+        <v>5</v>
+      </c>
+      <c r="AX195">
+        <v>9</v>
+      </c>
+      <c r="AY195">
+        <v>9</v>
+      </c>
+      <c r="AZ195">
+        <v>15</v>
+      </c>
+      <c r="BA195">
+        <v>2</v>
+      </c>
+      <c r="BB195">
+        <v>5</v>
+      </c>
+      <c r="BC195">
+        <v>7</v>
+      </c>
+      <c r="BD195">
+        <v>1.98</v>
+      </c>
+      <c r="BE195">
+        <v>6.1</v>
+      </c>
+      <c r="BF195">
+        <v>2.05</v>
+      </c>
+      <c r="BG195">
+        <v>1.56</v>
+      </c>
+      <c r="BH195">
+        <v>2.14</v>
+      </c>
+      <c r="BI195">
+        <v>1.95</v>
+      </c>
+      <c r="BJ195">
+        <v>1.67</v>
+      </c>
+      <c r="BK195">
+        <v>2.55</v>
+      </c>
+      <c r="BL195">
+        <v>1.4</v>
+      </c>
+      <c r="BM195">
+        <v>3.4</v>
+      </c>
+      <c r="BN195">
+        <v>1.23</v>
+      </c>
+      <c r="BO195">
+        <v>4.6</v>
+      </c>
+      <c r="BP195">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7856960</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45753.64583333334</v>
+      </c>
+      <c r="F196">
+        <v>2</v>
+      </c>
+      <c r="G196" t="s">
+        <v>73</v>
+      </c>
+      <c r="H196" t="s">
+        <v>75</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>3</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>4</v>
+      </c>
+      <c r="O196" t="s">
+        <v>206</v>
+      </c>
+      <c r="P196" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q196">
+        <v>3.5</v>
+      </c>
+      <c r="R196">
+        <v>2</v>
+      </c>
+      <c r="S196">
+        <v>3.4</v>
+      </c>
+      <c r="T196">
+        <v>1.5</v>
+      </c>
+      <c r="U196">
+        <v>2.5</v>
+      </c>
+      <c r="V196">
+        <v>3.5</v>
+      </c>
+      <c r="W196">
+        <v>1.29</v>
+      </c>
+      <c r="X196">
+        <v>10</v>
+      </c>
+      <c r="Y196">
+        <v>1.06</v>
+      </c>
+      <c r="Z196">
+        <v>2.5</v>
+      </c>
+      <c r="AA196">
+        <v>2.95</v>
+      </c>
+      <c r="AB196">
+        <v>2.85</v>
+      </c>
+      <c r="AC196">
+        <v>1.09</v>
+      </c>
+      <c r="AD196">
+        <v>7</v>
+      </c>
+      <c r="AE196">
+        <v>1.44</v>
+      </c>
+      <c r="AF196">
+        <v>2.7</v>
+      </c>
+      <c r="AG196">
+        <v>2.15</v>
+      </c>
+      <c r="AH196">
+        <v>1.57</v>
+      </c>
+      <c r="AI196">
+        <v>1.95</v>
+      </c>
+      <c r="AJ196">
+        <v>1.8</v>
+      </c>
+      <c r="AK196">
+        <v>1.45</v>
+      </c>
+      <c r="AL196">
+        <v>1.3</v>
+      </c>
+      <c r="AM196">
+        <v>1.42</v>
+      </c>
+      <c r="AN196">
+        <v>2.31</v>
+      </c>
+      <c r="AO196">
+        <v>1.77</v>
+      </c>
+      <c r="AP196">
+        <v>2.36</v>
+      </c>
+      <c r="AQ196">
+        <v>1.64</v>
+      </c>
+      <c r="AR196">
+        <v>1.96</v>
+      </c>
+      <c r="AS196">
+        <v>1.71</v>
+      </c>
+      <c r="AT196">
+        <v>3.67</v>
+      </c>
+      <c r="AU196">
+        <v>6</v>
+      </c>
+      <c r="AV196">
+        <v>7</v>
+      </c>
+      <c r="AW196">
+        <v>4</v>
+      </c>
+      <c r="AX196">
+        <v>17</v>
+      </c>
+      <c r="AY196">
+        <v>11</v>
+      </c>
+      <c r="AZ196">
+        <v>29</v>
+      </c>
+      <c r="BA196">
+        <v>2</v>
+      </c>
+      <c r="BB196">
+        <v>14</v>
+      </c>
+      <c r="BC196">
+        <v>16</v>
+      </c>
+      <c r="BD196">
+        <v>2.12</v>
+      </c>
+      <c r="BE196">
+        <v>6.4</v>
+      </c>
+      <c r="BF196">
+        <v>1.91</v>
+      </c>
+      <c r="BG196">
+        <v>1.35</v>
+      </c>
+      <c r="BH196">
+        <v>2.7</v>
+      </c>
+      <c r="BI196">
+        <v>1.61</v>
+      </c>
+      <c r="BJ196">
+        <v>2.04</v>
+      </c>
+      <c r="BK196">
+        <v>2</v>
+      </c>
+      <c r="BL196">
+        <v>1.64</v>
+      </c>
+      <c r="BM196">
+        <v>2.55</v>
+      </c>
+      <c r="BN196">
+        <v>1.38</v>
+      </c>
+      <c r="BO196">
+        <v>3.4</v>
+      </c>
+      <c r="BP196">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2221,7 +2221,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ5">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ6">
         <v>1.29</v>
@@ -4693,7 +4693,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ17">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5514,7 +5514,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ21">
         <v>2.07</v>
@@ -7783,7 +7783,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ32">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR32">
         <v>1.34</v>
@@ -8398,7 +8398,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
@@ -10252,7 +10252,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ44">
         <v>1.21</v>
@@ -11079,7 +11079,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11900,7 +11900,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ52">
         <v>1.21</v>
@@ -12109,7 +12109,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ53">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -15402,7 +15402,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ69">
         <v>1.64</v>
@@ -16435,7 +16435,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ74">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR74">
         <v>1.64</v>
@@ -18698,7 +18698,7 @@
         <v>0.6</v>
       </c>
       <c r="AP85">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ85">
         <v>1.29</v>
@@ -19525,7 +19525,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ89">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR89">
         <v>1.12</v>
@@ -21994,7 +21994,7 @@
         <v>1.57</v>
       </c>
       <c r="AP101">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ101">
         <v>1.29</v>
@@ -22203,7 +22203,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ102">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -25496,10 +25496,10 @@
         <v>1.13</v>
       </c>
       <c r="AP118">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ118">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR118">
         <v>1.32</v>
@@ -27762,7 +27762,7 @@
         <v>1.89</v>
       </c>
       <c r="AP129">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ129">
         <v>2.07</v>
@@ -27971,7 +27971,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ130">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR130">
         <v>1.17</v>
@@ -32297,7 +32297,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ151">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR151">
         <v>1.88</v>
@@ -33118,7 +33118,7 @@
         <v>0.5</v>
       </c>
       <c r="AP155">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ155">
         <v>0.79</v>
@@ -33327,7 +33327,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ156">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR156">
         <v>1.37</v>
@@ -34972,7 +34972,7 @@
         <v>0.82</v>
       </c>
       <c r="AP164">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ164">
         <v>0.86</v>
@@ -37241,7 +37241,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ175">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR175">
         <v>1.77</v>
@@ -38680,7 +38680,7 @@
         <v>1.58</v>
       </c>
       <c r="AP182">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ182">
         <v>1.43</v>
@@ -41643,6 +41643,212 @@
       </c>
       <c r="BP196">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7856961</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45754.5</v>
+      </c>
+      <c r="F197">
+        <v>2</v>
+      </c>
+      <c r="G197" t="s">
+        <v>74</v>
+      </c>
+      <c r="H197" t="s">
+        <v>79</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>84</v>
+      </c>
+      <c r="P197" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q197">
+        <v>2.75</v>
+      </c>
+      <c r="R197">
+        <v>1.95</v>
+      </c>
+      <c r="S197">
+        <v>4.75</v>
+      </c>
+      <c r="T197">
+        <v>1.57</v>
+      </c>
+      <c r="U197">
+        <v>2.25</v>
+      </c>
+      <c r="V197">
+        <v>3.75</v>
+      </c>
+      <c r="W197">
+        <v>1.25</v>
+      </c>
+      <c r="X197">
+        <v>11</v>
+      </c>
+      <c r="Y197">
+        <v>1.05</v>
+      </c>
+      <c r="Z197">
+        <v>2.25</v>
+      </c>
+      <c r="AA197">
+        <v>2.9</v>
+      </c>
+      <c r="AB197">
+        <v>3.3</v>
+      </c>
+      <c r="AC197">
+        <v>1.05</v>
+      </c>
+      <c r="AD197">
+        <v>6.65</v>
+      </c>
+      <c r="AE197">
+        <v>1.48</v>
+      </c>
+      <c r="AF197">
+        <v>2.37</v>
+      </c>
+      <c r="AG197">
+        <v>2.4</v>
+      </c>
+      <c r="AH197">
+        <v>1.53</v>
+      </c>
+      <c r="AI197">
+        <v>2.1</v>
+      </c>
+      <c r="AJ197">
+        <v>1.67</v>
+      </c>
+      <c r="AK197">
+        <v>1.25</v>
+      </c>
+      <c r="AL197">
+        <v>1.36</v>
+      </c>
+      <c r="AM197">
+        <v>1.75</v>
+      </c>
+      <c r="AN197">
+        <v>0.92</v>
+      </c>
+      <c r="AO197">
+        <v>1.23</v>
+      </c>
+      <c r="AP197">
+        <v>0.86</v>
+      </c>
+      <c r="AQ197">
+        <v>1.36</v>
+      </c>
+      <c r="AR197">
+        <v>1.31</v>
+      </c>
+      <c r="AS197">
+        <v>1.02</v>
+      </c>
+      <c r="AT197">
+        <v>2.33</v>
+      </c>
+      <c r="AU197">
+        <v>6</v>
+      </c>
+      <c r="AV197">
+        <v>4</v>
+      </c>
+      <c r="AW197">
+        <v>10</v>
+      </c>
+      <c r="AX197">
+        <v>6</v>
+      </c>
+      <c r="AY197">
+        <v>16</v>
+      </c>
+      <c r="AZ197">
+        <v>10</v>
+      </c>
+      <c r="BA197">
+        <v>5</v>
+      </c>
+      <c r="BB197">
+        <v>1</v>
+      </c>
+      <c r="BC197">
+        <v>6</v>
+      </c>
+      <c r="BD197">
+        <v>1.91</v>
+      </c>
+      <c r="BE197">
+        <v>7.5</v>
+      </c>
+      <c r="BF197">
+        <v>2.2</v>
+      </c>
+      <c r="BG197">
+        <v>1.53</v>
+      </c>
+      <c r="BH197">
+        <v>2.25</v>
+      </c>
+      <c r="BI197">
+        <v>1.82</v>
+      </c>
+      <c r="BJ197">
+        <v>1.98</v>
+      </c>
+      <c r="BK197">
+        <v>2.7</v>
+      </c>
+      <c r="BL197">
+        <v>1.38</v>
+      </c>
+      <c r="BM197">
+        <v>3.9</v>
+      </c>
+      <c r="BN197">
+        <v>1.2</v>
+      </c>
+      <c r="BO197">
+        <v>4.5</v>
+      </c>
+      <c r="BP197">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -625,7 +625,7 @@
     <t>['1', '16', '51', '82']</t>
   </si>
   <si>
-    <t>['28', '44', '80']</t>
+    <t>['28', '44', '81']</t>
   </si>
   <si>
     <t>['61', '90+3']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Greece Super League_20242025.xlsx
@@ -1726,10 +1726,10 @@
         <v>7</v>
       </c>
       <c r="AY2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA2">
         <v>3</v>
@@ -1932,10 +1932,10 @@
         <v>5</v>
       </c>
       <c r="AY3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA3">
         <v>9</v>
@@ -2138,10 +2138,10 @@
         <v>2</v>
       </c>
       <c r="AY4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA4">
         <v>2</v>
@@ -2344,10 +2344,10 @@
         <v>6</v>
       </c>
       <c r="AY5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA5">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8</v>
       </c>
       <c r="AZ6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA6">
         <v>3</v>
@@ -2756,10 +2756,10 @@
         <v>2</v>
       </c>
       <c r="AY7">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA7">
         <v>6</v>
@@ -2962,7 +2962,7 @@
         <v>8</v>
       </c>
       <c r="AY8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
         <v>13</v>
@@ -3168,10 +3168,10 @@
         <v>8</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ9">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA9">
         <v>4</v>
@@ -3374,10 +3374,10 @@
         <v>3</v>
       </c>
       <c r="AY10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA10">
         <v>4</v>
@@ -3580,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="AY11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="AZ11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA11">
         <v>13</v>
@@ -3786,10 +3786,10 @@
         <v>2</v>
       </c>
       <c r="AY12">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA12">
         <v>13</v>
@@ -3992,10 +3992,10 @@
         <v>2</v>
       </c>
       <c r="AY13">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA13">
         <v>4</v>
@@ -4198,10 +4198,10 @@
         <v>3</v>
       </c>
       <c r="AY14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA14">
         <v>7</v>
@@ -4404,10 +4404,10 @@
         <v>2</v>
       </c>
       <c r="AY15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA15">
         <v>7</v>
@@ -4610,10 +4610,10 @@
         <v>5</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ16">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA16">
         <v>4</v>
@@ -4816,10 +4816,10 @@
         <v>3</v>
       </c>
       <c r="AY17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA17">
         <v>4</v>
@@ -5022,10 +5022,10 @@
         <v>6</v>
       </c>
       <c r="AY18">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA18">
         <v>3</v>
@@ -5228,19 +5228,19 @@
         <v>6</v>
       </c>
       <c r="AY19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB19">
         <v>6</v>
       </c>
       <c r="BC19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD19">
         <v>8.199999999999999</v>
@@ -5434,10 +5434,10 @@
         <v>2</v>
       </c>
       <c r="AY20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA20">
         <v>7</v>
@@ -5640,10 +5640,10 @@
         <v>2</v>
       </c>
       <c r="AY21">
+        <v>6</v>
+      </c>
+      <c r="AZ21">
         <v>8</v>
-      </c>
-      <c r="AZ21">
-        <v>10</v>
       </c>
       <c r="BA21">
         <v>4</v>
@@ -5846,10 +5846,10 @@
         <v>5</v>
       </c>
       <c r="AY22">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AZ22">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA22">
         <v>9</v>
@@ -6052,10 +6052,10 @@
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA23">
         <v>1</v>
@@ -6258,7 +6258,7 @@
         <v>6</v>
       </c>
       <c r="AY24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ24">
         <v>9</v>
@@ -6464,10 +6464,10 @@
         <v>3</v>
       </c>
       <c r="AY25">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA25">
         <v>2</v>
@@ -6670,7 +6670,7 @@
         <v>8</v>
       </c>
       <c r="AY26">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AZ26">
         <v>8</v>
@@ -6876,10 +6876,10 @@
         <v>8</v>
       </c>
       <c r="AY27">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ27">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA27">
         <v>6</v>
@@ -7082,10 +7082,10 @@
         <v>1</v>
       </c>
       <c r="AY28">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA28">
         <v>6</v>
@@ -7288,10 +7288,10 @@
         <v>6</v>
       </c>
       <c r="AY29">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ29">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA29">
         <v>3</v>
@@ -7494,10 +7494,10 @@
         <v>3</v>
       </c>
       <c r="AY30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ30">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA30">
         <v>4</v>
@@ -7700,10 +7700,10 @@
         <v>6</v>
       </c>
       <c r="AY31">
+        <v>8</v>
+      </c>
+      <c r="AZ31">
         <v>9</v>
-      </c>
-      <c r="AZ31">
-        <v>14</v>
       </c>
       <c r="BA31">
         <v>3</v>
@@ -7906,10 +7906,10 @@
         <v>5</v>
       </c>
       <c r="AY32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA32">
         <v>1</v>
@@ -8112,10 +8112,10 @@
         <v>1</v>
       </c>
       <c r="AY33">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA33">
         <v>4</v>
@@ -8318,10 +8318,10 @@
         <v>5</v>
       </c>
       <c r="AY34">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA34">
         <v>7</v>
@@ -8524,10 +8524,10 @@
         <v>2</v>
       </c>
       <c r="AY35">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA35">
         <v>6</v>
@@ -8730,10 +8730,10 @@
         <v>8</v>
       </c>
       <c r="AY36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ36">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA36">
         <v>2</v>
@@ -8936,10 +8936,10 @@
         <v>1</v>
       </c>
       <c r="AY37">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA37">
         <v>6</v>
@@ -9142,10 +9142,10 @@
         <v>6</v>
       </c>
       <c r="AY38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ38">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA38">
         <v>4</v>
@@ -9348,10 +9348,10 @@
         <v>5</v>
       </c>
       <c r="AY39">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ39">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA39">
         <v>4</v>
@@ -9554,10 +9554,10 @@
         <v>2</v>
       </c>
       <c r="AY40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ40">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA40">
         <v>5</v>
@@ -9760,10 +9760,10 @@
         <v>2</v>
       </c>
       <c r="AY41">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA41">
         <v>5</v>
@@ -9966,10 +9966,10 @@
         <v>3</v>
       </c>
       <c r="AY42">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA42">
         <v>6</v>
@@ -10172,10 +10172,10 @@
         <v>4</v>
       </c>
       <c r="AY43">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ43">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA43">
         <v>6</v>
@@ -10378,10 +10378,10 @@
         <v>1</v>
       </c>
       <c r="AY44">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA44">
         <v>5</v>
@@ -11820,10 +11820,10 @@
         <v>6</v>
       </c>
       <c r="AY51">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AZ51">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA51">
         <v>8</v>
@@ -13262,10 +13262,10 @@
         <v>10</v>
       </c>
       <c r="AY58">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ58">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA58">
         <v>2</v>
@@ -13468,10 +13468,10 @@
         <v>7</v>
       </c>
       <c r="AY59">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ59">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA59">
         <v>3</v>
@@ -13674,10 +13674,10 @@
         <v>14</v>
       </c>
       <c r="AY60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ60">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BA60">
         <v>2</v>
@@ -13880,10 +13880,10 @@
         <v>12</v>
       </c>
       <c r="AY61">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ61">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA61">
         <v>3</v>
@@ -14086,10 +14086,10 @@
         <v>5</v>
       </c>
       <c r="AY62">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ62">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA62">
         <v>5</v>
@@ -14292,10 +14292,10 @@
         <v>5</v>
       </c>
       <c r="AY63">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ63">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA63">
         <v>5</v>
@@ -14498,10 +14498,10 @@
         <v>7</v>
       </c>
       <c r="AY64">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ64">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA64">
         <v>4</v>
@@ -14704,10 +14704,10 @@
         <v>2</v>
       </c>
       <c r="AY65">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA65">
         <v>8</v>
@@ -14910,10 +14910,10 @@
         <v>6</v>
       </c>
       <c r="AY66">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ66">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA66">
         <v>6</v>
@@ -15116,10 +15116,10 @@
         <v>4</v>
       </c>
       <c r="AY67">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ67">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA67">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>10</v>
       </c>
       <c r="AZ68">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BA68">
         <v>2</v>
@@ -15531,7 +15531,7 @@
         <v>6</v>
       </c>
       <c r="AZ69">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA69">
         <v>5</v>
@@ -15734,10 +15734,10 @@
         <v>7</v>
       </c>
       <c r="AY70">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ70">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA70">
         <v>1</v>
@@ -15940,10 +15940,10 @@
         <v>7</v>
       </c>
       <c r="AY71">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ71">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA71">
         <v>6</v>
@@ -16146,10 +16146,10 @@
         <v>4</v>
       </c>
       <c r="AY72">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ72">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA72">
         <v>7</v>
@@ -16352,10 +16352,10 @@
         <v>1</v>
       </c>
       <c r="AY73">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ73">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA73">
         <v>3</v>
@@ -16558,10 +16558,10 @@
         <v>3</v>
       </c>
       <c r="AY74">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AZ74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA74">
         <v>6</v>
@@ -16764,10 +16764,10 @@
         <v>10</v>
       </c>
       <c r="AY75">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ75">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA75">
         <v>2</v>
@@ -16970,10 +16970,10 @@
         <v>1</v>
       </c>
       <c r="AY76">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA76">
         <v>6</v>
@@ -17176,10 +17176,10 @@
         <v>0</v>
       </c>
       <c r="AY77">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA77">
         <v>7</v>
@@ -17382,10 +17382,10 @@
         <v>4</v>
       </c>
       <c r="AY78">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ78">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA78">
         <v>4</v>
@@ -17588,10 +17588,10 @@
         <v>10</v>
       </c>
       <c r="AY79">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ79">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA79">
         <v>8</v>
@@ -18824,10 +18824,10 @@
         <v>4</v>
       </c>
       <c r="AY85">
+        <v>7</v>
+      </c>
+      <c r="AZ85">
         <v>9</v>
-      </c>
-      <c r="AZ85">
-        <v>12</v>
       </c>
       <c r="BA85">
         <v>4</v>
@@ -19030,10 +19030,10 @@
         <v>6</v>
       </c>
       <c r="AY86">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ86">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA86">
         <v>6</v>
@@ -19239,7 +19239,7 @@
         <v>9</v>
       </c>
       <c r="AZ87">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA87">
         <v>5</v>
@@ -19442,10 +19442,10 @@
         <v>2</v>
       </c>
       <c r="AY88">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ88">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA88">
         <v>7</v>
@@ -19648,10 +19648,10 @@
         <v>6</v>
       </c>
       <c r="AY89">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ89">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA89">
         <v>7</v>
@@ -20060,10 +20060,10 @@
         <v>5</v>
       </c>
       <c r="AY91">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ91">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA91">
         <v>7</v>
@@ -20472,10 +20472,10 @@
         <v>2</v>
       </c>
       <c r="AY93">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA93">
         <v>5</v>
@@ -20678,10 +20678,10 @@
         <v>3</v>
       </c>
       <c r="AY94">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ94">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA94">
         <v>1</v>
@@ -21093,7 +21093,7 @@
         <v>4</v>
       </c>
       <c r="AZ96">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA96">
         <v>0</v>
@@ -21296,10 +21296,10 @@
         <v>8</v>
       </c>
       <c r="AY97">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ97">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BA97">
         <v>6</v>
@@ -21708,10 +21708,10 @@
         <v>5</v>
       </c>
       <c r="AY99">
+        <v>10</v>
+      </c>
+      <c r="AZ99">
         <v>12</v>
-      </c>
-      <c r="AZ99">
-        <v>13</v>
       </c>
       <c r="BA99">
         <v>6</v>
@@ -21914,10 +21914,10 @@
         <v>9</v>
       </c>
       <c r="AY100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ100">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA100">
         <v>2</v>
@@ -22120,10 +22120,10 @@
         <v>3</v>
       </c>
       <c r="AY101">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA101">
         <v>4</v>
@@ -22329,7 +22329,7 @@
         <v>5</v>
       </c>
       <c r="AZ102">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA102">
         <v>1</v>
@@ -22532,10 +22532,10 @@
         <v>6</v>
       </c>
       <c r="AY103">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ103">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA103">
         <v>6</v>
@@ -22738,10 +22738,10 @@
         <v>7</v>
       </c>
       <c r="AY104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ104">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA104">
         <v>1</v>
@@ -22944,10 +22944,10 @@
         <v>5</v>
       </c>
       <c r="AY105">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ105">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA105">
         <v>3</v>
@@ -23150,10 +23150,10 @@
         <v>6</v>
       </c>
       <c r="AY106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ106">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA106">
         <v>5</v>
@@ -23356,10 +23356,10 @@
         <v>2</v>
       </c>
       <c r="AY107">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ107">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA107">
         <v>8</v>
@@ -23562,10 +23562,10 @@
         <v>4</v>
       </c>
       <c r="AY108">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ108">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA108">
         <v>4</v>
@@ -23768,7 +23768,7 @@
         <v>1</v>
       </c>
       <c r="AY109">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AZ109">
         <v>3</v>
@@ -23974,10 +23974,10 @@
         <v>3</v>
       </c>
       <c r="AY110">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ110">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA110">
         <v>7</v>
@@ -24180,10 +24180,10 @@
         <v>1</v>
       </c>
       <c r="AY111">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AZ111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA111">
         <v>9</v>
@@ -24386,10 +24386,10 @@
         <v>5</v>
       </c>
       <c r="AY112">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ112">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA112">
         <v>1</v>
@@ -24592,10 +24592,10 @@
         <v>6</v>
       </c>
       <c r="AY113">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA113">
         <v>3</v>
@@ -24798,10 +24798,10 @@
         <v>4</v>
       </c>
       <c r="AY114">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA114">
         <v>3</v>
@@ -25004,10 +25004,10 @@
         <v>6</v>
       </c>
       <c r="AY115">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA115">
         <v>5</v>
@@ -25210,10 +25210,10 @@
         <v>3</v>
       </c>
       <c r="AY116">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ116">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA116">
         <v>12</v>
@@ -25416,10 +25416,10 @@
         <v>6</v>
       </c>
       <c r="AY117">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ117">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA117">
         <v>3</v>
@@ -25622,10 +25622,10 @@
         <v>7</v>
       </c>
       <c r="AY118">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ118">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA118">
         <v>4</v>
@@ -25828,10 +25828,10 @@
         <v>1</v>
       </c>
       <c r="AY119">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA119">
         <v>9</v>
@@ -26034,10 +26034,10 @@
         <v>9</v>
       </c>
       <c r="AY120">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ120">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA120">
         <v>0</v>
@@ -26240,7 +26240,7 @@
         <v>2</v>
       </c>
       <c r="AY121">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ121">
         <v>6</v>
@@ -26446,10 +26446,10 @@
         <v>5</v>
       </c>
       <c r="AY122">
+        <v>8</v>
+      </c>
+      <c r="AZ122">
         <v>11</v>
-      </c>
-      <c r="AZ122">
-        <v>13</v>
       </c>
       <c r="BA122">
         <v>1</v>
@@ -26858,7 +26858,7 @@
         <v>2</v>
       </c>
       <c r="AY124">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ124">
         <v>10</v>
@@ -27064,10 +27064,10 @@
         <v>4</v>
       </c>
       <c r="AY125">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AZ125">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA125">
         <v>9</v>
@@ -27270,10 +27270,10 @@
         <v>6</v>
       </c>
       <c r="AY126">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ126">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA126">
         <v>4</v>
@@ -27476,10 +27476,10 @@
         <v>6</v>
       </c>
       <c r="AY127">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AZ127">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA127">
         <v>3</v>
@@ -27682,10 +27682,10 @@
         <v>8</v>
       </c>
       <c r="AY128">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ128">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA128">
         <v>3</v>
@@ -28094,10 +28094,10 @@
         <v>7</v>
       </c>
       <c r="AY130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ130">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA130">
         <v>2</v>
@@ -28300,10 +28300,10 @@
         <v>6</v>
       </c>
       <c r="AY131">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ131">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA131">
         <v>4</v>
@@ -28506,10 +28506,10 @@
         <v>11</v>
       </c>
       <c r="AY132">
+        <v>13</v>
+      </c>
+      <c r="AZ132">
         <v>17</v>
-      </c>
-      <c r="AZ132">
-        <v>21</v>
       </c>
       <c r="BA132">
         <v>5</v>
@@ -28715,7 +28715,7 @@
         <v>8</v>
       </c>
       <c r="AZ133">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA133">
         <v>0</v>
@@ -28921,7 +28921,7 @@
         <v>20</v>
       </c>
       <c r="AZ134">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA134">
         <v>4</v>
@@ -29124,7 +29124,7 @@
         <v>4</v>
       </c>
       <c r="AY135">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ135">
         <v>7</v>
@@ -29330,10 +29330,10 @@
         <v>13</v>
       </c>
       <c r="AY136">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ136">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA136">
         <v>9</v>
@@ -29536,10 +29536,10 @@
         <v>6</v>
       </c>
       <c r="AY137">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ137">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA137">
         <v>7</v>
@@ -29742,10 +29742,10 @@
         <v>4</v>
       </c>
       <c r="AY138">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ138">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA138">
         <v>7</v>
@@ -29948,10 +29948,10 @@
         <v>11</v>
       </c>
       <c r="AY139">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ139">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA139">
         <v>3</v>
@@ -30154,10 +30154,10 @@
         <v>6</v>
       </c>
       <c r="AY140">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ140">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA140">
         <v>10</v>
@@ -30360,10 +30360,10 @@
         <v>4</v>
       </c>
       <c r="AY141">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ141">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA141">
         <v>2</v>
@@ -30566,7 +30566,7 @@
         <v>3</v>
       </c>
       <c r="AY142">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ142">
         <v>8</v>
@@ -30772,10 +30772,10 @@
         <v>10</v>
       </c>
       <c r="AY143">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ143">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA143">
         <v>4</v>
@@ -30978,10 +30978,10 @@
         <v>11</v>
       </c>
       <c r="AY144">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ144">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA144">
         <v>3</v>
@@ -31184,10 +31184,10 @@
         <v>11</v>
       </c>
       <c r="AY145">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AZ145">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA145">
         <v>10</v>
@@ -31390,10 +31390,10 @@
         <v>10</v>
       </c>
       <c r="AY146">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ146">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31599,7 +31599,7 @@
         <v>6</v>
       </c>
       <c r="AZ147">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BA147">
         <v>0</v>
@@ -31802,10 +31802,10 @@
         <v>13</v>
       </c>
       <c r="AY148">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ148">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA148">
         <v>3</v>
@@ -32008,7 +32008,7 @@
         <v>4</v>
       </c>
       <c r="AY149">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ149">
         <v>8</v>
@@ -32214,10 +32214,10 @@
         <v>8</v>
       </c>
       <c r="AY150">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ150">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA150">
         <v>4</v>
@@ -32420,7 +32420,7 @@
         <v>2</v>
       </c>
       <c r="AY151">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AZ151">
         <v>5</v>
@@ -32626,7 +32626,7 @@
         <v>5</v>
       </c>
       <c r="AY152">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ152">
         <v>8</v>
@@ -32832,10 +32832,10 @@
         <v>6</v>
       </c>
       <c r="AY153">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AZ153">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA153">
         <v>10</v>
@@ -33038,10 +33038,10 @@
         <v>3</v>
       </c>
       <c r="AY154">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ154">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA154">
         <v>9</v>
@@ -33244,10 +33244,10 @@
         <v>7</v>
       </c>
       <c r="AY155">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ155">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA155">
         <v>10</v>
@@ -33450,7 +33450,7 @@
         <v>2</v>
       </c>
       <c r="AY156">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ156">
         <v>5</v>
@@ -33656,10 +33656,10 @@
         <v>4</v>
       </c>
       <c r="AY157">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ157">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA157">
         <v>6</v>
@@ -33862,10 +33862,10 @@
         <v>7</v>
       </c>
       <c r="AY158">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ158">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA158">
         <v>6</v>
@@ -34068,10 +34068,10 @@
         <v>4</v>
       </c>
       <c r="AY159">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ159">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA159">
         <v>6</v>
@@ -34274,10 +34274,10 @@
         <v>8</v>
       </c>
       <c r="AY160">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ160">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA160">
         <v>0</v>
@@ -34480,10 +34480,10 @@
         <v>4</v>
       </c>
       <c r="AY161">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ161">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA161">
         <v>8</v>
@@ -34686,10 +34686,10 @@
         <v>5</v>
       </c>
       <c r="AY162">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ162">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA162">
         <v>6</v>
@@ -34892,10 +34892,10 @@
         <v>2</v>
       </c>
       <c r="AY163">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ163">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA163">
         <v>10</v>
@@ -35098,10 +35098,10 @@
         <v>6</v>
       </c>
       <c r="AY164">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ164">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA164">
         <v>6</v>
@@ -35304,10 +35304,10 @@
         <v>6</v>
       </c>
       <c r="AY165">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ165">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA165">
         <v>4</v>
@@ -35510,10 +35510,10 @@
         <v>6</v>
       </c>
       <c r="AY166">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AZ166">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA166">
         <v>4</v>
@@ -35716,10 +35716,10 @@
         <v>11</v>
       </c>
       <c r="AY167">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ167">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BA167">
         <v>5</v>
@@ -35925,7 +35925,7 @@
         <v>3</v>
       </c>
       <c r="AZ168">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA168">
         <v>0</v>
@@ -36128,7 +36128,7 @@
         <v>2</v>
       </c>
       <c r="AY169">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ169">
         <v>10</v>
@@ -36334,10 +36334,10 @@
         <v>3</v>
       </c>
       <c r="AY170">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ170">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA170">
         <v>8</v>
@@ -36540,7 +36540,7 @@
         <v>6</v>
       </c>
       <c r="AY171">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ171">
         <v>11</v>
@@ -36746,10 +36746,10 @@
         <v>8</v>
       </c>
       <c r="AY172">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AZ172">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA172">
         <v>5</v>
@@ -36952,10 +36952,10 @@
         <v>6</v>
       </c>
       <c r="AY173">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ173">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA173">
         <v>7</v>
@@ -37158,19 +37158,19 @@
         <v>7</v>
       </c>
       <c r="AY174">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ174">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA174">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB174">
         <v>3</v>
       </c>
       <c r="BC174">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD174">
         <v>1.44</v>
@@ -37367,7 +37367,7 @@
         <v>16</v>
       </c>
       <c r="AZ175">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA175">
         <v>5</v>
@@ -37570,7 +37570,7 @@
         <v>3</v>
       </c>
       <c r="AY176">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ176">
         <v>7</v>
@@ -37776,10 +37776,10 @@
         <v>11</v>
       </c>
       <c r="AY177">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AZ177">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA177">
         <v>4</v>
@@ -37988,13 +37988,13 @@
         <v>-1</v>
       </c>
       <c r="BA178">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BB178">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BC178">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BD178">
         <v>2.46</v>
@@ -38188,10 +38188,10 @@
         <v>3</v>
       </c>
       <c r="AY179">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ179">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA179">
         <v>9</v>
@@ -38394,10 +38394,10 @@
         <v>9</v>
       </c>
       <c r="AY180">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ180">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA180">
         <v>5</v>
@@ -38600,10 +38600,10 @@
         <v>9</v>
       </c>
       <c r="AY181">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ181">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA181">
         <v>4</v>
@@ -38809,7 +38809,7 @@
         <v>13</v>
       </c>
       <c r="AZ182">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA182">
         <v>2</v>
@@ -39012,7 +39012,7 @@
         <v>3</v>
       </c>
       <c r="AY183">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ183">
         <v>9</v>
@@ -39218,7 +39218,7 @@
         <v>8</v>
       </c>
       <c r="AY184">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ184">
         <v>14</v>
@@ -39424,19 +39424,19 @@
         <v>3</v>
       </c>
       <c r="AY185">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ185">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA185">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB185">
         <v>4</v>
       </c>
       <c r="BC185">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD185">
         <v>1.71</v>
@@ -39633,7 +39633,7 @@
         <v>10</v>
       </c>
       <c r="AZ186">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA186">
         <v>3</v>
@@ -39836,10 +39836,10 @@
         <v>14</v>
       </c>
       <c r="AY187">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ187">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA187">
         <v>2</v>
@@ -40042,7 +40042,7 @@
         <v>3</v>
       </c>
       <c r="AY188">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ188">
         <v>6</v>
@@ -40248,10 +40248,10 @@
         <v>5</v>
       </c>
       <c r="AY189">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ189">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA189">
         <v>3</v>
@@ -40454,10 +40454,10 @@
         <v>5</v>
       </c>
       <c r="AY190">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ190">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA190">
         <v>3</v>
@@ -40660,10 +40660,10 @@
         <v>8</v>
       </c>
       <c r="AY191">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ191">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41075,7 +41075,7 @@
         <v>5</v>
       </c>
       <c r="AZ193">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA193">
         <v>1</v>
@@ -41278,10 +41278,10 @@
         <v>4</v>
       </c>
       <c r="AY194">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ194">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA194">
         <v>3</v>
@@ -41484,10 +41484,10 @@
         <v>9</v>
       </c>
       <c r="AY195">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ195">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA195">
         <v>2</v>
@@ -41690,10 +41690,10 @@
         <v>17</v>
       </c>
       <c r="AY196">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ196">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BA196">
         <v>2</v>
@@ -42102,10 +42102,10 @@
         <v>7</v>
       </c>
       <c r="AY198">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ198">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA198">
         <v>3</v>
@@ -42308,10 +42308,10 @@
         <v>2</v>
       </c>
       <c r="AY199">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ199">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA199">
         <v>5</v>
@@ -42514,7 +42514,7 @@
         <v>2</v>
       </c>
       <c r="AY200">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ200">
         <v>4</v>
@@ -42926,10 +42926,10 @@
         <v>7</v>
       </c>
       <c r="AY202">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ202">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA202">
         <v>4</v>
@@ -43338,7 +43338,7 @@
         <v>0</v>
       </c>
       <c r="AY204">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ204">
         <v>2</v>
@@ -43544,10 +43544,10 @@
         <v>8</v>
       </c>
       <c r="AY205">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ205">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA205">
         <v>7</v>
@@ -43753,7 +43753,7 @@
         <v>4</v>
       </c>
       <c r="AZ206">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA206">
         <v>0</v>
@@ -43956,10 +43956,10 @@
         <v>6</v>
       </c>
       <c r="AY207">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ207">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA207">
         <v>4</v>
@@ -44162,7 +44162,7 @@
         <v>9</v>
       </c>
       <c r="AY208">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ208">
         <v>18</v>
@@ -44574,10 +44574,10 @@
         <v>4</v>
       </c>
       <c r="AY210">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ210">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA210">
         <v>8</v>
@@ -44780,10 +44780,10 @@
         <v>1</v>
       </c>
       <c r="AY211">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA211">
         <v>8</v>
@@ -44986,10 +44986,10 @@
         <v>4</v>
       </c>
       <c r="AY212">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA212">
         <v>3</v>
@@ -45192,7 +45192,7 @@
         <v>2</v>
       </c>
       <c r="AY213">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ213">
         <v>8</v>
@@ -45398,10 +45398,10 @@
         <v>5</v>
       </c>
       <c r="AY214">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ214">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA214">
         <v>8</v>
@@ -46016,10 +46016,10 @@
         <v>6</v>
       </c>
       <c r="AY217">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ217">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA217">
         <v>5</v>
@@ -46222,10 +46222,10 @@
         <v>7</v>
       </c>
       <c r="AY218">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ218">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA218">
         <v>4</v>
@@ -46428,10 +46428,10 @@
         <v>5</v>
       </c>
       <c r="AY219">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ219">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA219">
         <v>3</v>
@@ -46634,10 +46634,10 @@
         <v>8</v>
       </c>
       <c r="AY220">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ220">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA220">
         <v>10</v>
@@ -46840,10 +46840,10 @@
         <v>9</v>
       </c>
       <c r="AY221">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ221">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA221">
         <v>4</v>
@@ -47046,10 +47046,10 @@
         <v>5</v>
       </c>
       <c r="AY222">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ222">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA222">
         <v>7</v>
@@ -47252,10 +47252,10 @@
         <v>7</v>
       </c>
       <c r="AY223">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ223">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA223">
         <v>2</v>
@@ -47870,10 +47870,10 @@
         <v>6</v>
       </c>
       <c r="AY226">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ226">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA226">
         <v>3</v>
@@ -48282,10 +48282,10 @@
         <v>3</v>
       </c>
       <c r="AY228">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ228">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA228">
         <v>8</v>
@@ -48488,10 +48488,10 @@
         <v>10</v>
       </c>
       <c r="AY229">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ229">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA229">
         <v>8</v>
@@ -48694,10 +48694,10 @@
         <v>9</v>
       </c>
       <c r="AY230">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ230">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA230">
         <v>3</v>
@@ -48900,10 +48900,10 @@
         <v>3</v>
       </c>
       <c r="AY231">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ231">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA231">
         <v>4</v>
@@ -49106,10 +49106,10 @@
         <v>13</v>
       </c>
       <c r="AY232">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ232">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA232">
         <v>3</v>
@@ -49312,10 +49312,10 @@
         <v>5</v>
       </c>
       <c r="AY233">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ233">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA233">
         <v>2</v>
@@ -49518,10 +49518,10 @@
         <v>4</v>
       </c>
       <c r="AY234">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ234">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA234">
         <v>6</v>
@@ -49724,10 +49724,10 @@
         <v>8</v>
       </c>
       <c r="AY235">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ235">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA235">
         <v>2</v>
@@ -49930,7 +49930,7 @@
         <v>4</v>
       </c>
       <c r="AY236">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ236">
         <v>8</v>
@@ -50136,10 +50136,10 @@
         <v>8</v>
       </c>
       <c r="AY237">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ237">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA237">
         <v>1</v>
